--- a/classification/results/evaluation_results.xlsx
+++ b/classification/results/evaluation_results.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,68 +457,68 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8645833333333334</v>
+        <v>0.8584571832979476</v>
       </c>
       <c r="D2" t="n">
-        <v>0.868375</v>
+        <v>0.8627176220806794</v>
       </c>
       <c r="E2" t="n">
-        <v>4.941198099997564</v>
+        <v>4.919160899999042</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hybrid_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.855</v>
+        <v>0.83</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8523083191158871</v>
+        <v>0.8255336617405583</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8550996918845968</v>
+        <v>0.8294417077175698</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001515000003564637</v>
+        <v>0.05313310000019555</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>hybrid_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>Logistic Regression</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8217514196226223</v>
+        <v>0.8243075651095495</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8251203177917548</v>
+        <v>0.8287350144687887</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05073660000198288</v>
+        <v>0.0001986999996006489</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hybrid_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
     </row>
@@ -538,59 +538,59 @@
         <v>0.4769317413831945</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001634000000194646</v>
+        <v>0.0001670000001467997</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hybrid_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.845</v>
+        <v>0.85</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8425396825396825</v>
+        <v>0.841621792841305</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8452952380952381</v>
+        <v>0.846721571111815</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001172999982372858</v>
+        <v>4.849505600001066</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>preprocessed_text</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Transformer (DistilBERT)</t>
+          <t>Logistic Regression</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0.845</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8388731515891785</v>
+        <v>0.8421226859514654</v>
       </c>
       <c r="D7" t="n">
-        <v>0.843271914550794</v>
+        <v>0.8451065671869828</v>
       </c>
       <c r="E7" t="n">
-        <v>4.910199299996748</v>
+        <v>0.0001354000014543999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>preprocessed_text</t>
         </is>
       </c>
     </row>
@@ -601,20 +601,20 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.825</v>
+        <v>0.835</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8217514196226223</v>
+        <v>0.8319370527870439</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8251203177917548</v>
+        <v>0.8351134424893687</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04062010000052396</v>
+        <v>0.04932879999978468</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>preprocessed_text</t>
         </is>
       </c>
     </row>
@@ -634,105 +634,9 @@
         <v>0.4769317413831945</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0001656000022194348</v>
+        <v>0.0001670999990892597</v>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>ner_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.8584571832979476</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.8627176220806794</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4.77889569999752</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>preprocessed_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.8421226859514654</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.8451065671869828</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0001181000006909017</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>preprocessed_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.8319370527870439</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8351134424893687</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.04859190000206581</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>preprocessed_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DummyClassifier</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.4743560862056019</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.4769317413831945</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0001636000015423633</v>
-      </c>
-      <c r="F13" t="inlineStr">
         <is>
           <t>preprocessed_text</t>
         </is>
@@ -749,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1241,13 +1145,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="E17" t="n">
         <v>0.9473684210526315</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="G17" t="n">
         <v>114</v>
@@ -1270,13 +1174,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.9154929577464789</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7558139534883721</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8280254777070064</v>
+        <v>0.8051948051948052</v>
       </c>
       <c r="G18" t="n">
         <v>86</v>
@@ -1299,16 +1203,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.865</v>
+        <v>0.85</v>
       </c>
       <c r="E19" t="n">
-        <v>0.865</v>
+        <v>0.85</v>
       </c>
       <c r="F19" t="n">
-        <v>0.865</v>
+        <v>0.85</v>
       </c>
       <c r="G19" t="n">
-        <v>0.865</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20">
@@ -1328,13 +1232,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8763511300360302</v>
+        <v>0.8649732620320856</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8515911872705018</v>
+        <v>0.8341493268053854</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8584571832979476</v>
+        <v>0.841621792841305</v>
       </c>
       <c r="G20" t="n">
         <v>200</v>
@@ -1357,13 +1261,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8708712741565674</v>
+        <v>0.8584224598930481</v>
       </c>
       <c r="E21" t="n">
-        <v>0.865</v>
+        <v>0.85</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8627176220806794</v>
+        <v>0.846721571111815</v>
       </c>
       <c r="G21" t="n">
         <v>200</v>
@@ -1372,7 +1276,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1386,13 +1290,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8738738738738738</v>
+        <v>0.8278688524590164</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8508771929824561</v>
+        <v>0.8859649122807017</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8622222222222222</v>
+        <v>0.8559322033898306</v>
       </c>
       <c r="G22" t="n">
         <v>114</v>
@@ -1401,7 +1305,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1415,13 +1319,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8089887640449438</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.7558139534883721</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8228571428571428</v>
+        <v>0.7926829268292683</v>
       </c>
       <c r="G23" t="n">
         <v>86</v>
@@ -1430,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1444,22 +1348,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.845</v>
+        <v>0.83</v>
       </c>
       <c r="E24" t="n">
-        <v>0.845</v>
+        <v>0.83</v>
       </c>
       <c r="F24" t="n">
-        <v>0.845</v>
+        <v>0.83</v>
       </c>
       <c r="G24" t="n">
-        <v>0.845</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1473,13 +1377,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8414313189594088</v>
+        <v>0.8306010928961749</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8440432476540187</v>
+        <v>0.8208894328845369</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8425396825396825</v>
+        <v>0.8243075651095495</v>
       </c>
       <c r="G25" t="n">
         <v>200</v>
@@ -1488,7 +1392,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1502,13 +1406,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8459732766474339</v>
+        <v>0.8302185792349727</v>
       </c>
       <c r="E26" t="n">
-        <v>0.845</v>
+        <v>0.83</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8452952380952381</v>
+        <v>0.8287350144687887</v>
       </c>
       <c r="G26" t="n">
         <v>200</v>
@@ -1517,7 +1421,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1531,13 +1435,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.8495575221238938</v>
+        <v>0.8389830508474576</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8458149779735683</v>
+        <v>0.853448275862069</v>
       </c>
       <c r="G27" t="n">
         <v>114</v>
@@ -1546,7 +1450,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1560,13 +1464,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.8170731707317073</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.7790697674418605</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7976190476190477</v>
       </c>
       <c r="G28" t="n">
         <v>86</v>
@@ -1575,7 +1479,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1589,22 +1493,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="E29" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="F29" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="G29" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1618,13 +1522,13 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8213304851998779</v>
+        <v>0.8280281107895824</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8222154222766218</v>
+        <v>0.8237454100367197</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8217514196226223</v>
+        <v>0.8255336617405583</v>
       </c>
       <c r="G30" t="n">
         <v>200</v>
@@ -1633,7 +1537,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1647,13 +1551,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.8252822703692402</v>
+        <v>0.829561802397685</v>
       </c>
       <c r="E31" t="n">
-        <v>0.825</v>
+        <v>0.83</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8251203177917548</v>
+        <v>0.8294417077175698</v>
       </c>
       <c r="G31" t="n">
         <v>200</v>
@@ -1662,7 +1566,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1691,7 +1595,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1720,7 +1624,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1749,7 +1653,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1778,7 +1682,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1807,7 +1711,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1821,13 +1725,13 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.832</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9122807017543859</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8702928870292888</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G37" t="n">
         <v>114</v>
@@ -1836,7 +1740,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1850,13 +1754,13 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9154929577464789</v>
       </c>
       <c r="E38" t="n">
         <v>0.7558139534883721</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8074534161490683</v>
+        <v>0.8280254777070064</v>
       </c>
       <c r="G38" t="n">
         <v>86</v>
@@ -1865,7 +1769,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1879,22 +1783,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.845</v>
+        <v>0.865</v>
       </c>
       <c r="E39" t="n">
-        <v>0.845</v>
+        <v>0.865</v>
       </c>
       <c r="F39" t="n">
-        <v>0.845</v>
+        <v>0.865</v>
       </c>
       <c r="G39" t="n">
-        <v>0.845</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1908,13 +1812,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.8493333333333333</v>
+        <v>0.8763511300360302</v>
       </c>
       <c r="E40" t="n">
-        <v>0.834047327621379</v>
+        <v>0.8515911872705018</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8388731515891785</v>
+        <v>0.8584571832979476</v>
       </c>
       <c r="G40" t="n">
         <v>200</v>
@@ -1923,7 +1827,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ner_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1937,595 +1841,15 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.8469066666666666</v>
+        <v>0.8708712741565674</v>
       </c>
       <c r="E41" t="n">
-        <v>0.845</v>
+        <v>0.865</v>
       </c>
       <c r="F41" t="n">
-        <v>0.843271914550794</v>
+        <v>0.8627176220806794</v>
       </c>
       <c r="G41" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>0.8761061946902655</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.868421052631579</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.8722466960352423</v>
-      </c>
-      <c r="G42" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.8275862068965517</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0.8372093023255814</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.8323699421965318</v>
-      </c>
-      <c r="G43" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.855</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>macro avg</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0.8518462007934087</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0.8528151774785802</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.8523083191158871</v>
-      </c>
-      <c r="G45" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>weighted avg</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0.8552425999389687</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.8550996918845968</v>
-      </c>
-      <c r="G46" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0.8495575221238938</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.8421052631578947</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.8458149779735683</v>
-      </c>
-      <c r="G47" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>0.7931034482758621</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.8023255813953488</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.7976878612716763</v>
-      </c>
-      <c r="G48" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.825</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>macro avg</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>0.8213304851998779</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.8222154222766218</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.8217514196226223</v>
-      </c>
-      <c r="G50" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>weighted avg</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0.8252822703692402</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.8251203177917548</v>
-      </c>
-      <c r="G51" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>DummyClassifier</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>0.5483870967741935</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.4473684210526316</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.4927536231884058</v>
-      </c>
-      <c r="G52" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>DummyClassifier</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>0.411214953271028</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.5116279069767442</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.4559585492227979</v>
-      </c>
-      <c r="G53" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>DummyClassifier</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.475</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>DummyClassifier</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>macro avg</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0.4798010250226108</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.4794981640146879</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.4743560862056019</v>
-      </c>
-      <c r="G55" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>DummyClassifier</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>weighted avg</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>0.4894030750678324</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.4769317413831945</v>
-      </c>
-      <c r="G56" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>0.8492063492063492</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0.9385964912280702</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0.8916666666666667</v>
-      </c>
-      <c r="G57" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>0.9054054054054054</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0.7790697674418605</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.8375</v>
-      </c>
-      <c r="G58" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>macro avg</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0.8773058773058773</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.8588331293349654</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.8645833333333334</v>
-      </c>
-      <c r="G60" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>hybrid_text</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>weighted avg</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>0.8733719433719433</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.868375</v>
-      </c>
-      <c r="G61" t="n">
         <v>200</v>
       </c>
     </row>
@@ -2540,7 +1864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K201"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2566,7 +1890,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>hybrid_text</t>
+          <t>augmented_text</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -2581,22 +1905,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ner_text_prediction_model</t>
+          <t>augmented_text_prediction_model</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ner_text_prediction_result</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>hybrid_text_prediction_model</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>hybrid_text_prediction_result</t>
+          <t>augmented_text_prediction_result</t>
         </is>
       </c>
     </row>
@@ -2619,7 +1933,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>extremely bad far thor 2 iron 3 well not stop roll eye child age scott lang daughter extremely bad far thor 2 iron 3 stop roll eye child age scott lang daughter</t>
+          <t>extremely bad far thor 2 iron 3 well not stop roll eye child age scott lang daughter extremely bad far thor 2 iron 3 stop roll eye child age scott lang daughter [SEP]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2634,20 +1948,10 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -2669,14 +1973,10 @@
           <t>sure wandavision whatif watch love totally worth hype not watch series wandavision probably go disappoint like sequel series understand deeply emotionally series people watch include x man watch mom   not hall know backstory whine complain wanda orient not agree show powerful wandavision prepare able sure wandavision whatif love totally worth hype series wandavision probably disappoint like sequel series understand deeply emotionally series people include x mom   hall know backstory whine complain wanda orient agree powerful wandavision prepare able</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>series wandavision probably disappoint like sequel series understand deeply emotionally series people include x mom   hall know backstory whine complain wanda orient agree powerful wandavision prepare able</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sure wandavision whatif watch love totally worth hype not watch series wandavision probably go disappoint like sequel series understand deeply emotionally series people watch include x man watch mom   not hall know backstory whine complain wanda orient not agree show powerful wandavision prepare able sure wandavision whatif love totally worth hype series wandavision probably disappoint like sequel series understand deeply emotionally series people include x mom   hall know backstory whine complain wanda orient agree powerful wandavision prepare able series wandavision probably disappoint like sequel series understand deeply emotionally series people include x mom   hall know backstory whine complain wanda orient agree powerful wandavision prepare able</t>
+          <t>sure wandavision whatif watch love totally worth hype not watch series wandavision probably go disappoint like sequel series understand deeply emotionally series people watch include x man watch mom   not hall know backstory whine complain wanda orient not agree show powerful wandavision prepare able sure wandavision whatif love totally worth hype series wandavision probably disappoint like sequel series understand deeply emotionally series people include x mom   hall know backstory whine complain wanda orient agree powerful wandavision prepare able [SEP]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2691,20 +1991,10 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -2726,14 +2016,10 @@
           <t>stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   not waste money superman instead stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   waste money superman instead</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   waste money superman instead</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   not waste money superman instead stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   waste money superman instead stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   waste money superman instead</t>
+          <t>stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   not waste money superman instead stupid plot ridiculous understand check realism door superhero cmon interesting plot hole inconsistency mention plus spoiler list   waste money superman instead [SEP]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2748,20 +2034,10 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -2783,14 +2059,10 @@
           <t>disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke not action guy drax destroyer give action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation see disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke action guy drax destroyer action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke action guy drax destroyer action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke not action guy drax destroyer give action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation see disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke action guy drax destroyer action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke action guy drax destroyer action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation</t>
+          <t>disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke not action guy drax destroyer give action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation see disappoint care joke good plot potential spoiler visual okay great point kinda look animate acting perfect plot horrible comedy sequence feel force villian underwhelme overact pace issue overuse formula   feel choppy   bloated joke joke mean fan force ripoff joke action guy drax destroyer action sequence comeon spoiler nebula try kill kill gamora later forgive   feel messy thing learn gotg 2 high expectation [SEP]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2805,20 +2077,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -2842,12 +2104,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>expect pleasantly surprised tend enjoy big blockbuster superhero venom exception boyfriend love time come recent spider andrew garfield second tobey maguire assume lose time ask million question enjoy fun actually pretty easy follow general knowledge mcu genuinely hilarious moment like huge fan type try ll surprise</t>
+          <t>ENTLBL_PERSON ENTTXT_andrew_garfield</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>not expect pleasantly surprised tend enjoy big blockbuster superhero movie venom exception boyfriend love time come having see recent spider movie andrew garfield one second tobey maguire one assume lose time ask million question enjoy fun actually pretty easy follow general knowledge mcu genuinely hilarious moment like not huge fan type movie try ll surprise expect pleasantly surprised tend enjoy big blockbuster superhero venom exception boyfriend love time come having recent spider andrew garfield second tobey maguire assume lose time ask million question enjoy fun actually pretty easy follow general knowledge mcu genuinely hilarious moment like huge fan type try ll surprise expect pleasantly surprised tend enjoy big blockbuster superhero venom exception boyfriend love time come recent spider andrew garfield second tobey maguire assume lose time ask million question enjoy fun actually pretty easy follow general knowledge mcu genuinely hilarious moment like huge fan type try ll surprise</t>
+          <t>not expect pleasantly surprised tend enjoy big blockbuster superhero movie venom exception boyfriend love time come having see recent spider movie andrew garfield one second tobey maguire one assume lose time ask million question enjoy fun actually pretty easy follow general knowledge mcu genuinely hilarious moment like not huge fan type movie try ll surprise expect pleasantly surprised tend enjoy big blockbuster superhero venom exception boyfriend love time come having recent spider andrew garfield second tobey maguire assume lose time ask million question enjoy fun actually pretty easy follow general knowledge mcu genuinely hilarious moment like huge fan type try ll surprise [SEP] ENTLBL_PERSON ENTTXT_andrew_garfield</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2857,27 +2119,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
     </row>
@@ -2897,14 +2149,10 @@
           <t>traumatic not need tell shred feeling body go able enjoy guardian galaxy 3 brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye watch positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc traumatic need tell shred feeling body able enjoy guardian galaxy 3 brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>traumatic need tell brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>traumatic not need tell shred feeling body go able enjoy guardian galaxy 3 brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye watch positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc traumatic need tell shred feeling body able enjoy guardian galaxy 3 brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc traumatic need tell brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc</t>
+          <t>traumatic not need tell shred feeling body go able enjoy guardian galaxy 3 brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye watch positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc traumatic need tell shred feeling body able enjoy guardian galaxy 3 brutal dark need trauma content warning people tolerate depiction animal abuse cgi able write narrative let depict way indicate lack empathy spend portion hand eye positive moment insufficient redeem save grace close come soundtrack resolution couple cross arc [SEP]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2919,20 +2167,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -2954,14 +2192,10 @@
           <t>lame   well kid give bad review go see imax high hope base vol 2 lame lose plot hole plot time drag   mind last comic book an stretch far lame old joke joke lame like lase face   keep stop watch like stop watch star war lame   kid bad review imax high hope base vol 2 lame lose plot hole plot time drag   mind comic book stretch far lame old joke joke lame like lase face   stop like stop star war</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>lame   kid bad review imax high hope base vol 2 lame lose plot hole plot time drag   mind comic book stretch far lame old joke joke lame like lase face   stop like stop star war</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>lame   well kid give bad review go see imax high hope base vol 2 lame lose plot hole plot time drag   mind last comic book an stretch far lame old joke joke lame like lase face   keep stop watch like stop watch star war lame   kid bad review imax high hope base vol 2 lame lose plot hole plot time drag   mind comic book stretch far lame old joke joke lame like lase face   stop like stop star war lame   kid bad review imax high hope base vol 2 lame lose plot hole plot time drag   mind comic book stretch far lame old joke joke lame like lase face   stop like stop star war</t>
+          <t>lame   well kid give bad review go see imax high hope base vol 2 lame lose plot hole plot time drag   mind last comic book an stretch far lame old joke joke lame like lase face   keep stop watch like stop watch star war lame   kid bad review imax high hope base vol 2 lame lose plot hole plot time drag   mind comic book stretch far lame old joke joke lame like lase face   stop like stop star war [SEP]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2976,20 +2210,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3011,14 +2235,10 @@
           <t>fine wayy fun action good feel overpacke time 3 movie early death ajak feel dry think not not budget expect feel like massive speedrun feel fun dry fine wayy fun action good feel overpacke time 3 early death ajak feel dry think budget expect feel like massive speedrun feel fun dry</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>fine wayy fun action good feel overpacke time 3 early death ajak feel dry think budget expect feel like massive speedrun feel fun dry</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>fine wayy fun action good feel overpacke time 3 movie early death ajak feel dry think not not budget expect feel like massive speedrun feel fun dry fine wayy fun action good feel overpacke time 3 early death ajak feel dry think budget expect feel like massive speedrun feel fun dry fine wayy fun action good feel overpacke time 3 early death ajak feel dry think budget expect feel like massive speedrun feel fun dry</t>
+          <t>fine wayy fun action good feel overpacke time 3 movie early death ajak feel dry think not not budget expect feel like massive speedrun feel fun dry fine wayy fun action good feel overpacke time 3 early death ajak feel dry think budget expect feel like massive speedrun feel fun dry [SEP]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3033,20 +2253,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3070,12 +2280,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>comic_strip kid particularly like tobey maguire spider dislike andrew garfield spider bother second studio disney right maybe build everybody rave appeal couple good moment find james gunns script irritatingly weak like draft gag placeholder write ham fiste talk teamwork overcome adversity topic tackle clumsily aim little obviously child friendly 12a   child friendly dumbe maybe m old nonsense plus fact huge hit nice finger sony capture world imagination famous superhero time spider right wick verdict think crap know yetanotherfilmreviewblogtumblrcom</t>
+          <t>ENTLBL_PERSON ENTTXT_andrew_garfield ENTLBL_PERSON ENTTXT_america_meander ENTLBL_ORG ENTTXT_sony</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>not comic_strip kid not particularly like tobey maguire spider film dislike andrew garfield spider not bother see second studio own disney right iron ve enjoy cinematic release pretty grant iron sequel flawed captain america meander bit ve enjoy maybe build everybody rave not appeal couple good moment find james gunns script irritatingly weak like draft gag placeholder well one write ham fiste talk teamwork overcome adversity topic tackle clumsily film aim little obviously child friendly 12a   child friendly not dumbe maybe m get old nonsense plus fact huge hit nice finger sony not capture world imagination famous superhero time spider get right wick verdict think crap know yetanotherfilmreviewblogtumblrcom comic_strip kid particularly like tobey maguire spider dislike andrew garfield spider bother second studio disney right iron ve enjoy cinematic release pretty grant iron sequel flawed captain america meander bit ve enjoy maybe build everybody rave appeal couple good moment find james gunns script irritatingly weak like draft gag placeholder write ham fiste talk teamwork overcome adversity topic tackle clumsily aim little obviously child friendly 12a   child friendly dumbe maybe m old nonsense plus fact huge hit nice finger sony capture world imagination famous superhero time spider right wick verdict think crap know yetanotherfilmreviewblogtumblrcom comic_strip kid particularly like tobey maguire spider dislike andrew garfield spider bother second studio disney right maybe build everybody rave appeal couple good moment find james gunns script irritatingly weak like draft gag placeholder write ham fiste talk teamwork overcome adversity topic tackle clumsily aim little obviously child friendly 12a   child friendly dumbe maybe m old nonsense plus fact huge hit nice finger sony capture world imagination famous superhero time spider right wick verdict think crap know yetanotherfilmreviewblogtumblrcom</t>
+          <t>not comic_strip kid not particularly like tobey maguire spider film dislike andrew garfield spider not bother see second studio own disney right iron ve enjoy cinematic release pretty grant iron sequel flawed captain america meander bit ve enjoy maybe build everybody rave not appeal couple good moment find james gunns script irritatingly weak like draft gag placeholder well one write ham fiste talk teamwork overcome adversity topic tackle clumsily film aim little obviously child friendly 12a   child friendly not dumbe maybe m get old nonsense plus fact huge hit nice finger sony not capture world imagination famous superhero time spider get right wick verdict think crap know yetanotherfilmreviewblogtumblrcom comic_strip kid particularly like tobey maguire spider dislike andrew garfield spider bother second studio disney right iron ve enjoy cinematic release pretty grant iron sequel flawed captain america meander bit ve enjoy maybe build everybody rave appeal couple good moment find james gunns script irritatingly weak like draft gag placeholder write ham fiste talk teamwork overcome adversity topic tackle clumsily aim little obviously child friendly 12a   child friendly dumbe maybe m old nonsense plus fact huge hit nice finger sony capture world imagination famous superhero time spider right wick verdict think crap know yetanotherfilmreviewblogtumblrcom [SEP] ENTLBL_PERSON ENTTXT_andrew_garfield ENTLBL_PERSON ENTTXT_america_meander ENTLBL_ORG ENTTXT_sony</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3090,20 +2300,10 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3127,12 +2327,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yawn     wake m sure end cameo enjoyable thank nostalgia recipe captain america   civil war 1 cup american patriotism 2 cup moral quandary forget end half cup explosion pinch action sprinkle superhero cameo action ve save enjoyable moment flick penultimate fight appear trailer lose common sense duration civil war deify personality belief support thing d catch dead past 1 cup patriotism liberally stir tell choke idea government world control superhumans alien magician genius inventor arsenal explode gadget literal deity leader country dimension trillion dollar company follow precede involve small segment favourite hero destroy supposedly powerful organisation world tell swallow cup moral quandary awful innocent people die hero save day ignore fact planet destroy thrice hard claim government care year city destroy truthful rarely hero   honestly plot bad want snore fact action sorely lack lustre help hurt tony stark attitude annoying point captain america fulfill stereotype jock rush second thought nearly destroy thing process think suppose peg plot friendship important sacrifice freedom friendship possibly planet year yeah right</t>
+          <t>ENTLBL_PERSON ENTTXT_tony_stark</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yawn     wake m sure get end think black panther thing save fall asleep childhood favourite superhero cameo enjoyable thank nostalgia recipe captain america   civil war 1 cup american patriotism 2 cup moral quandary forget end half cup explosion pinch action sprinkle superhero cameo action ve save enjoyable moment flick penultimate fight appear trailer lose common sense duration civil war deify personality belief support thing d catch dead past 1 cup patriotism liberally stir tell choke idea government world control superhumans alien magician genius inventor arsenal explode gadget literal deity leader country dimension trillion dollar company follow precede involve small segment favourite hero destroy supposedly powerful organisation world tell swallow cup moral quandary awful innocent people die hero save day ignore fact planet destroy thrice hard claim government care year city destroy truthful rarely hero   honestly plot bad want snore fact action sorely lack lustre help hurt tony stark attitude annoying point captain america fulfill stereotype jock rush second thought nearly destroy thing process think suppose peg plot friendship important sacrifice freedom friendship possibly planet not see year yeah right yawn     wake m sure end think black panther thing save fall asleep childhood favourite superhero cameo enjoyable thank nostalgia recipe captain america   civil war 1 cup american patriotism 2 cup moral quandary forget end half cup explosion pinch action sprinkle superhero cameo action ve save enjoyable moment flick penultimate fight appear trailer lose common sense duration civil war deify personality belief support thing d catch dead past 1 cup patriotism liberally stir tell choke idea government world control superhumans alien magician genius inventor arsenal explode gadget literal deity leader country dimension trillion dollar company follow precede involve small segment favourite hero destroy supposedly powerful organisation world tell swallow cup moral quandary awful innocent people die hero save day ignore fact planet destroy thrice hard claim government care year city destroy truthful rarely hero   honestly plot bad want snore fact action sorely lack lustre help hurt tony stark attitude annoying point captain america fulfill stereotype jock rush second thought nearly destroy thing process think suppose peg plot friendship important sacrifice freedom friendship possibly planet year yeah right yawn     wake m sure end cameo enjoyable thank nostalgia recipe captain america   civil war 1 cup american patriotism 2 cup moral quandary forget end half cup explosion pinch action sprinkle superhero cameo action ve save enjoyable moment flick penultimate fight appear trailer lose common sense duration civil war deify personality belief support thing d catch dead past 1 cup patriotism liberally stir tell choke idea government world control superhumans alien magician genius inventor arsenal explode gadget literal deity leader country dimension trillion dollar company follow precede involve small segment favourite hero destroy supposedly powerful organisation world tell swallow cup moral quandary awful innocent people die hero save day ignore fact planet destroy thrice hard claim government care year city destroy truthful rarely hero   honestly plot bad want snore fact action sorely lack lustre help hurt tony stark attitude annoying point captain america fulfill stereotype jock rush second thought nearly destroy thing process think suppose peg plot friendship important sacrifice freedom friendship possibly planet year yeah right</t>
+          <t>yawn     wake m sure get end think black panther thing save fall asleep childhood favourite superhero cameo enjoyable thank nostalgia recipe captain america   civil war 1 cup american patriotism 2 cup moral quandary forget end half cup explosion pinch action sprinkle superhero cameo action ve save enjoyable moment flick penultimate fight appear trailer lose common sense duration civil war deify personality belief support thing d catch dead past 1 cup patriotism liberally stir tell choke idea government world control superhumans alien magician genius inventor arsenal explode gadget literal deity leader country dimension trillion dollar company follow precede involve small segment favourite hero destroy supposedly powerful organisation world tell swallow cup moral quandary awful innocent people die hero save day ignore fact planet destroy thrice hard claim government care year city destroy truthful rarely hero   honestly plot bad want snore fact action sorely lack lustre help hurt tony stark attitude annoying point captain america fulfill stereotype jock rush second thought nearly destroy thing process think suppose peg plot friendship important sacrifice freedom friendship possibly planet not see year yeah right yawn     wake m sure end think black panther thing save fall asleep childhood favourite superhero cameo enjoyable thank nostalgia recipe captain america   civil war 1 cup american patriotism 2 cup moral quandary forget end half cup explosion pinch action sprinkle superhero cameo action ve save enjoyable moment flick penultimate fight appear trailer lose common sense duration civil war deify personality belief support thing d catch dead past 1 cup patriotism liberally stir tell choke idea government world control superhumans alien magician genius inventor arsenal explode gadget literal deity leader country dimension trillion dollar company follow precede involve small segment favourite hero destroy supposedly powerful organisation world tell swallow cup moral quandary awful innocent people die hero save day ignore fact planet destroy thrice hard claim government care year city destroy truthful rarely hero   honestly plot bad want snore fact action sorely lack lustre help hurt tony stark attitude annoying point captain america fulfill stereotype jock rush second thought nearly destroy thing process think suppose peg plot friendship important sacrifice freedom friendship possibly planet year yeah right [SEP] ENTLBL_PERSON ENTTXT_tony_stark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3147,20 +2347,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -3184,12 +2374,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>disney series scrap pretend exist clearly short series disney mackie cap work support plot armor way version captain america beats ross red hulk nelson leader annoying raft forget second time ve hulk succumb form mind control cinematic run idea huge library comic_strip book pull good action sequence glad address huge celestial indian ocean believable way real world country definitely fight ownership resource introduce adamantium genuinely exciting</t>
+          <t>ENTLBL_ORG ENTTXT_disney_series_scrap ENTLBL_PERSON ENTTXT_disney_mackie ENTLBL_PERSON ENTTXT_nelson_leader</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>disney series scrap pretend not exist clearly short series disney mackie cap work well support plot armor way version captain america beats ross red hulk nelson leader annoying keep raft forget second time ve hulk succumb form mind control cinematic run idea huge library comic_strip book pull good action sequence glad address huge celestial indian ocean believable way real world country definitely fight ownership resource introduce adamantium genuinely exciting disney series scrap pretend exist clearly short series disney mackie cap work support plot armor way version captain america beats ross red hulk nelson leader annoying raft forget second time ve hulk succumb form mind control cinematic run idea huge library comic_strip book pull good action sequence glad address huge celestial indian ocean believable way real world country definitely fight ownership resource introduce adamantium genuinely exciting disney series scrap pretend exist clearly short series disney mackie cap work support plot armor way version captain america beats ross red hulk nelson leader annoying raft forget second time ve hulk succumb form mind control cinematic run idea huge library comic_strip book pull good action sequence glad address huge celestial indian ocean believable way real world country definitely fight ownership resource introduce adamantium genuinely exciting</t>
+          <t>disney series scrap pretend not exist clearly short series disney mackie cap work well support plot armor way version captain america beats ross red hulk nelson leader annoying keep raft forget second time ve hulk succumb form mind control cinematic run idea huge library comic_strip book pull good action sequence glad address huge celestial indian ocean believable way real world country definitely fight ownership resource introduce adamantium genuinely exciting disney series scrap pretend exist clearly short series disney mackie cap work support plot armor way version captain america beats ross red hulk nelson leader annoying raft forget second time ve hulk succumb form mind control cinematic run idea huge library comic_strip book pull good action sequence glad address huge celestial indian ocean believable way real world country definitely fight ownership resource introduce adamantium genuinely exciting [SEP] ENTLBL_ORG ENTTXT_disney_series_scrap ENTLBL_PERSON ENTTXT_disney_mackie ENTLBL_PERSON ENTTXT_nelson_leader</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3204,20 +2394,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3239,14 +2419,10 @@
           <t>epic not multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe well iron 3 not instead opportunity profound gripping face off villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director iron regular guy invention hero power machine give regular human task take toll physically emotionally narcissist tony stark deny personal decay revel attention iron bring denial not change fact machine take tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron powerful realistic clever tactic battle intellect machine prove equally powerful battle stalemate instead iteration iron suit destroy discretion like brilliantly design symbolic source power intend disposable prop villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead get im3 false villain pretend evil real villain unbelievable power seemingly go invincible end convenient disappear ignore false villain concept brilliant not joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit not work happen villain power consistent im3 consistency line iron world intact ignore im3 think epic multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe iron 3 instead opportunity profound gripping face villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director iron regular guy invention hero power machine regular human task toll physically emotionally narcissist tony stark deny personal decay revel attention iron bring denial change fact machine tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron powerful realistic use clever tactic battle intellect machine prove equally powerful battle stalemate instead iteration iron suit destroy discretion like brilliantly design symbolic source power intend disposable prop villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead im3 false villain pretend evil real villain unbelievable power seemingly invincible end convenient disappear ignore false villain concept brilliant joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit work happen villain power consistent im3 consistency line iron world intact ignore im3 think</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>epic multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe iron 3 instead opportunity profound gripping face villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director denial change fact machine tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead im3 false villain pretend evil real villain unbelievable power seemingly invincible end convenient disappear ignore false villain concept brilliant joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit work happen villain power consistent im3 consistency</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>epic not multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe well iron 3 not instead opportunity profound gripping face off villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director iron regular guy invention hero power machine give regular human task take toll physically emotionally narcissist tony stark deny personal decay revel attention iron bring denial not change fact machine take tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron powerful realistic clever tactic battle intellect machine prove equally powerful battle stalemate instead iteration iron suit destroy discretion like brilliantly design symbolic source power intend disposable prop villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead get im3 false villain pretend evil real villain unbelievable power seemingly go invincible end convenient disappear ignore false villain concept brilliant not joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit not work happen villain power consistent im3 consistency line iron world intact ignore im3 think epic multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe iron 3 instead opportunity profound gripping face villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director iron regular guy invention hero power machine regular human task toll physically emotionally narcissist tony stark deny personal decay revel attention iron bring denial change fact machine tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron powerful realistic use clever tactic battle intellect machine prove equally powerful battle stalemate instead iteration iron suit destroy discretion like brilliantly design symbolic source power intend disposable prop villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead im3 false villain pretend evil real villain unbelievable power seemingly invincible end convenient disappear ignore false villain concept brilliant joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit work happen villain power consistent im3 consistency line iron world intact ignore im3 think epic multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe iron 3 instead opportunity profound gripping face villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director denial change fact machine tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead im3 false villain pretend evil real villain unbelievable power seemingly invincible end convenient disappear ignore false villain concept brilliant joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit work happen villain power consistent im3 consistency</t>
+          <t>epic not multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe well iron 3 not instead opportunity profound gripping face off villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director iron regular guy invention hero power machine give regular human task take toll physically emotionally narcissist tony stark deny personal decay revel attention iron bring denial not change fact machine take tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron powerful realistic clever tactic battle intellect machine prove equally powerful battle stalemate instead iteration iron suit destroy discretion like brilliantly design symbolic source power intend disposable prop villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead get im3 false villain pretend evil real villain unbelievable power seemingly go invincible end convenient disappear ignore false villain concept brilliant not joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit not work happen villain power consistent im3 consistency line iron world intact ignore im3 think epic multi build invent machine machine machine begin consume sequence iconic villain play rate actor prepare experience equal dark knight maybe iron 3 instead opportunity profound gripping face villain hero trade sitcom oversimplification play gimmick basic premise good idea final product look like edit studio executive committee understanding comic superhero world instead visionary director iron regular guy invention hero power machine regular human task toll physically emotionally narcissist tony stark deny personal decay revel attention iron bring denial change fact machine tony fall apart role superhero overwhelm begin destroy instead iron 3 script forget trade stunt uncharacteristic nonsensical decision supra genius villain iron powerful realistic use clever tactic battle intellect machine prove equally powerful battle stalemate instead iteration iron suit destroy discretion like brilliantly design symbolic source power intend disposable prop villain iron 3 epic unsettlingly realistic psychopath mandarin equal great heath ledger joker instead im3 false villain pretend evil real villain unbelievable power seemingly invincible end convenient disappear ignore false villain concept brilliant joke accept villain ampe type power outrageous inconsistent relation tony come brilliant solution overcome villain power brute force suit work happen villain power consistent im3 consistency line iron world intact ignore im3 think [SEP]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3261,20 +2437,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3296,14 +2462,10 @@
           <t>restore faith absolute fan   upcoming movie letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray olden music way amazing   bring memory   restore faith restore faith absolute fan   upcoming letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray use olden music way amazing   bring memory   restore faith</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>restore faith absolute fan   upcoming letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray use olden music way amazing   bring memory   restore faith</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>restore faith absolute fan   upcoming movie letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray olden music way amazing   bring memory   restore faith restore faith absolute fan   upcoming letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray use olden music way amazing   bring memory   restore faith restore faith absolute fan   upcoming letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray use olden music way amazing   bring memory   restore faith</t>
+          <t>restore faith absolute fan   upcoming movie letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray olden music way amazing   bring memory   restore faith restore faith absolute fan   upcoming letdown   fantastic 4     nostalgia costume amazing manage capture essence time portray use olden music way amazing   bring memory   restore faith [SEP]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3318,20 +2480,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -3353,14 +2505,10 @@
           <t>want play phone not start pink floyd hope quickly dash high hope guess get expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android not understand create mute head eternal ability heal   give mute eternal ability speak suppose mute heal repair message not project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old make sense 7000 year old spending minute 40year old want play phone start pink floyd hope quickly dash high hope guess expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android understand create mute head eternal ability heal   mute eternal ability speak suppose mute heal repair message project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old sense 7000 year old spending minute 40year old</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>want play phone start pink floyd hope quickly dash high hope guess expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android understand create mute head eternal ability heal   mute eternal ability speak suppose mute heal repair message project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old sense 7000 year old spending minute 40year old</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>want play phone not start pink floyd hope quickly dash high hope guess get expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android not understand create mute head eternal ability heal   give mute eternal ability speak suppose mute heal repair message not project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old make sense 7000 year old spending minute 40year old want play phone start pink floyd hope quickly dash high hope guess expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android understand create mute head eternal ability heal   mute eternal ability speak suppose mute heal repair message project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old sense 7000 year old spending minute 40year old want play phone start pink floyd hope quickly dash high hope guess expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android understand create mute head eternal ability heal   mute eternal ability speak suppose mute heal repair message project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old sense 7000 year old spending minute 40year old</t>
+          <t>want play phone not start pink floyd hope quickly dash high hope guess get expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android not understand create mute head eternal ability heal   give mute eternal ability speak suppose mute heal repair message not project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old make sense 7000 year old spending minute 40year old want play phone start pink floyd hope quickly dash high hope guess expect greatly decline tell stop try check box subplot enjoy bollywood portion harish patel terrific near salma hayek angelina jolie terrible generally blame director editor bad acting   learn eternal basically android understand create mute head eternal ability heal   mute eternal ability speak suppose mute heal repair message project box check know earth 7000 year d super smart smart hard time talk simple human 40 year life experience amaze smart screen writer type explore look like twilight 100 year old hang 16 year old sense 7000 year old spending minute 40year old [SEP]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3375,20 +2523,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3412,12 +2550,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>guy stay calm wrong good computer generate imagery seriously think 8 year old   guy respect hollywood history fair rating emotional   5 cause spider laugh great comedy genre   love spiderman series wanna deep breath away mood   way like thai guy laugh alot   thing think kiss parker girlfriend bad seriously professional</t>
+          <t>ENTLBL_PERSON ENTTXT_kiss_parker</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>guy stay calm wrong good computer generate imagery movie seriously think 8 year old   guy respect hollywood history fair rating emotional one   5 cause spider movie make laugh great comedy genre   love spiderman series wanna deep breath away movie mood   way like thai guy laugh alot   thing think kiss parker girlfriend bad seriously professional guy stay calm wrong good computer generate imagery seriously think 8 year old   guy respect hollywood history fair rating emotional   5 cause spider laugh great comedy genre   love spiderman series wanna deep breath away mood   way like thai guy laugh alot   thing think kiss parker girlfriend bad seriously professional guy stay calm wrong good computer generate imagery seriously think 8 year old   guy respect hollywood history fair rating emotional   5 cause spider laugh great comedy genre   love spiderman series wanna deep breath away mood   way like thai guy laugh alot   thing think kiss parker girlfriend bad seriously professional</t>
+          <t>guy stay calm wrong good computer generate imagery movie seriously think 8 year old   guy respect hollywood history fair rating emotional one   5 cause spider movie make laugh great comedy genre   love spiderman series wanna deep breath away movie mood   way like thai guy laugh alot   thing think kiss parker girlfriend bad seriously professional guy stay calm wrong good computer generate imagery seriously think 8 year old   guy respect hollywood history fair rating emotional   5 cause spider laugh great comedy genre   love spiderman series wanna deep breath away mood   way like thai guy laugh alot   thing think kiss parker girlfriend bad seriously professional [SEP] ENTLBL_PERSON ENTTXT_kiss_parker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3432,20 +2570,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -3467,14 +2595,10 @@
           <t>nostalgia fill lousy script tribute tony stark use second line lousy kiddish script nostalgia fill lousy script tribute tony stark use second line lousy kiddish script</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>nostalgia fill lousy script tribute tony stark use second line lousy kiddish script</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>nostalgia fill lousy script tribute tony stark use second line lousy kiddish script nostalgia fill lousy script tribute tony stark use second line lousy kiddish script nostalgia fill lousy script tribute tony stark use second line lousy kiddish script</t>
+          <t>nostalgia fill lousy script tribute tony stark use second line lousy kiddish script nostalgia fill lousy script tribute tony stark use second line lousy kiddish script [SEP]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3489,20 +2613,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3524,14 +2638,10 @@
           <t>crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight say anymore crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight anymore</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight anymore</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight say anymore crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight anymore crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight anymore</t>
+          <t>crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight say anymore crossover captain america civil war follow feudrivalry iron captain america lead amazing telling phenomenal fight great cross cinema history infinity endgame civil war simply brilliant cross good amazing fight action attention start end want hard time find major flaw love surprise entrant tony roger team fight anymore [SEP]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3546,20 +2656,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -3583,12 +2683,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>expect big pile meh hardcore cinematic fan grow read comic_strip 90 black widow little interest recent experience think d benefit doubt hope cinematic magic alas little like foremost fake russian accent come reason irk help think subpar acting performance actor know deliver ton johansson harbour weisz etc   directing place action hot mess special effect disgrace cinematic stamp writing plot hole thing sense m try count disappointing overall far weak cinematic date skip</t>
+          <t>ENTLBL_PERSON ENTTXT_deliver_ton_johansson</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>expect big pile meh hardcore cinematic fan grow read comic_strip 90 fresh cinematic marathon end endgame skeptical show like wandavision falcon   winter soldier premise not sound interesting end like black widow little interest recent experience think d benefit doubt hope cinematic magic alas little like foremost fake russian accent come go reason irk not help think subpar acting performance actor know deliver ton johansson harbour weisz etc   directing place action hot mess special effect disgrace cinematic stamp writing plot hole thing not sense m go try count disappointing overall far weak cinematic date skip expect big pile meh hardcore cinematic fan grow read comic_strip 90 fresh cinematic marathon end endgame skeptical like wandavision falcon   winter soldier premise sound interesting end like black widow little interest recent experience think d benefit doubt hope cinematic magic alas little like foremost fake russian accent come reason irk help think subpar acting performance actor know deliver ton johansson harbour weisz etc   directing place action hot mess special effect disgrace cinematic stamp writing plot hole thing sense m try count disappointing overall far weak cinematic date skip expect big pile meh hardcore cinematic fan grow read comic_strip 90 black widow little interest recent experience think d benefit doubt hope cinematic magic alas little like foremost fake russian accent come reason irk help think subpar acting performance actor know deliver ton johansson harbour weisz etc   directing place action hot mess special effect disgrace cinematic stamp writing plot hole thing sense m try count disappointing overall far weak cinematic date skip</t>
+          <t>expect big pile meh hardcore cinematic fan grow read comic_strip 90 fresh cinematic marathon end endgame skeptical show like wandavision falcon   winter soldier premise not sound interesting end like black widow little interest recent experience think d benefit doubt hope cinematic magic alas little like foremost fake russian accent come go reason irk not help think subpar acting performance actor know deliver ton johansson harbour weisz etc   directing place action hot mess special effect disgrace cinematic stamp writing plot hole thing not sense m go try count disappointing overall far weak cinematic date skip expect big pile meh hardcore cinematic fan grow read comic_strip 90 fresh cinematic marathon end endgame skeptical like wandavision falcon   winter soldier premise sound interesting end like black widow little interest recent experience think d benefit doubt hope cinematic magic alas little like foremost fake russian accent come reason irk help think subpar acting performance actor know deliver ton johansson harbour weisz etc   directing place action hot mess special effect disgrace cinematic stamp writing plot hole thing sense m try count disappointing overall far weak cinematic date skip [SEP] ENTLBL_PERSON ENTTXT_deliver_ton_johansson</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3603,20 +2703,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3640,12 +2730,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>woah amazing start epic epitome great cinema probably good opening amazing action pack fight expect fourth wall breakinggritty storytelling prepared stomach ache deadpool intense joke humor pacing execute moment time eye screen miss fill ton easter egg reference good year</t>
+          <t>ENTLBL_PERSON ENTTXT_fill_ton</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>good endgame woah amazing start epic epitome great cinema probably good opening see amazing action pack fight expect fourth wall breakinggritty storytelling prepared stomach ache watch deadpool intense joke humor pacing execute moment time eye screen miss fill ton easter egg reference good year good endgame woah amazing start epic epitome great cinema probably good opening amazing action pack fight expect fourth wall breakinggritty storytelling prepared stomach ache deadpool intense joke humor pacing execute moment time eye screen miss fill ton easter egg reference good year woah amazing start epic epitome great cinema probably good opening amazing action pack fight expect fourth wall breakinggritty storytelling prepared stomach ache deadpool intense joke humor pacing execute moment time eye screen miss fill ton easter egg reference good year</t>
+          <t>good endgame woah amazing start epic epitome great cinema probably good opening see amazing action pack fight expect fourth wall breakinggritty storytelling prepared stomach ache watch deadpool intense joke humor pacing execute moment time eye screen miss fill ton easter egg reference good year good endgame woah amazing start epic epitome great cinema probably good opening amazing action pack fight expect fourth wall breakinggritty storytelling prepared stomach ache deadpool intense joke humor pacing execute moment time eye screen miss fill ton easter egg reference good year [SEP] ENTLBL_PERSON ENTTXT_fill_ton</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3660,20 +2750,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -3697,12 +2777,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>captain america brave new world 2025 worthy successor despite hate trailer zero expectation honestly pleasantly surprised understand hate solid superhero great action political intrigue strong performance anthony mackie hold captain america prove need super soldier serum true hero journey feel ground leadership earn new falcon joaquin torre great addition bring fresh energy team big surprise red hulk harrison ford thunderbolt ross absolute powerhouse political tension add weight new villain menacing maybe iconic past cinematic villain overall craft entertaining respect legacy captain america carve path fence shot surprised</t>
+          <t>ENTLBL_PERSON ENTTXT_anthony_mackie ENTLBL_ORG ENTTXT_ford ENTLBL_PERSON ENTTXT_thunderbolt_ross</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>captain america brave new world 2025 worthy successor despite hate not trailer go zero expectation honestly pleasantly surprised not understand hate solid superhero great action political intrigue strong performance anthony mackie hold captain america prove not need super soldier serum true hero journey feel ground leadership earn new falcon joaquin torre great addition bring fresh energy team movie big surprise red hulk harrison ford thunderbolt ross absolute powerhouse political tension add weight new villain menacing maybe iconic past cinematic villain overall craft entertaining respect legacy captain america carve path fence shot surprised captain america brave new world 2025 worthy successor despite hate trailer zero expectation honestly pleasantly surprised understand hate solid superhero great action political intrigue strong performance anthony mackie hold captain america prove need super soldier serum true hero journey feel ground leadership earn new falcon joaquin torre great addition bring fresh energy team big surprise red hulk harrison ford thunderbolt ross absolute powerhouse political tension add weight new villain menacing maybe iconic past cinematic villain overall craft entertaining respect legacy captain america carve path fence shot surprised captain america brave new world 2025 worthy successor despite hate trailer zero expectation honestly pleasantly surprised understand hate solid superhero great action political intrigue strong performance anthony mackie hold captain america prove need super soldier serum true hero journey feel ground leadership earn new falcon joaquin torre great addition bring fresh energy team big surprise red hulk harrison ford thunderbolt ross absolute powerhouse political tension add weight new villain menacing maybe iconic past cinematic villain overall craft entertaining respect legacy captain america carve path fence shot surprised</t>
+          <t>captain america brave new world 2025 worthy successor despite hate not trailer go zero expectation honestly pleasantly surprised not understand hate solid superhero great action political intrigue strong performance anthony mackie hold captain america prove not need super soldier serum true hero journey feel ground leadership earn new falcon joaquin torre great addition bring fresh energy team movie big surprise red hulk harrison ford thunderbolt ross absolute powerhouse political tension add weight new villain menacing maybe iconic past cinematic villain overall craft entertaining respect legacy captain america carve path fence shot surprised captain america brave new world 2025 worthy successor despite hate trailer zero expectation honestly pleasantly surprised understand hate solid superhero great action political intrigue strong performance anthony mackie hold captain america prove need super soldier serum true hero journey feel ground leadership earn new falcon joaquin torre great addition bring fresh energy team big surprise red hulk harrison ford thunderbolt ross absolute powerhouse political tension add weight new villain menacing maybe iconic past cinematic villain overall craft entertaining respect legacy captain america carve path fence shot surprised [SEP] ENTLBL_PERSON ENTTXT_anthony_mackie ENTLBL_ORG ENTTXT_ford ENTLBL_PERSON ENTTXT_thunderbolt_ross</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3717,20 +2797,10 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -3752,14 +2822,10 @@
           <t>decline continue not know people leave high review see not guardian installment take work previous guardian movie throw away terrible line poorly time bad good bad joke not start adam warlock lame costume choice bad bad not want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end take break sadly let pay ticket price film wait hit streaming disney fix decline continue know people leave high review guardian installment work previous guardian throw away terrible line poorly time bad good bad joke start adam warlock lame costume choice bad bad want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end break sadly let pay ticket price wait hit streaming disney fix</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>decline continue know people leave high review guardian installment work previous guardian throw away terrible line poorly time bad good bad joke start adam warlock lame costume choice bad bad want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end break sadly let pay ticket price wait hit streaming disney fix</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>decline continue not know people leave high review see not guardian installment take work previous guardian movie throw away terrible line poorly time bad good bad joke not start adam warlock lame costume choice bad bad not want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end take break sadly let pay ticket price film wait hit streaming disney fix decline continue know people leave high review guardian installment work previous guardian throw away terrible line poorly time bad good bad joke start adam warlock lame costume choice bad bad want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end break sadly let pay ticket price wait hit streaming disney fix decline continue know people leave high review guardian installment work previous guardian throw away terrible line poorly time bad good bad joke start adam warlock lame costume choice bad bad want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end break sadly let pay ticket price wait hit streaming disney fix</t>
+          <t>decline continue not know people leave high review see not guardian installment take work previous guardian movie throw away terrible line poorly time bad good bad joke not start adam warlock lame costume choice bad bad not want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end take break sadly let pay ticket price film wait hit streaming disney fix decline continue know people leave high review guardian installment work previous guardian throw away terrible line poorly time bad good bad joke start adam warlock lame costume choice bad bad want away short bad favor wait come online way turn high hope want awesome hop decline cinematic end break sadly let pay ticket price wait hit streaming disney fix [SEP]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3774,20 +2840,10 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3811,12 +2867,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lazy liner seven shadow   waist 2 hour tell end thank painful foreshadowing possibly mid level hop good remotely likable care planet destroy try hard cheekiness jason ben old tired quiet soulless quality reed cold boring let face annoy selfishness sue insult good job mother world war share view little speech come country government hand baby invadenuke know country exist briefly mention london tv poor baby act soul mainly poor little bugger cry possible gareth big baddie cliche interesting thing fact lot lot lot small panel normal sized people build m sure try desperately massive scale    time enjoy spend silly money aaaaaalllllllllll super hero guff ve fart far</t>
+          <t>ENTLBL_PERSON ENTTXT_jason_ben_old</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>lazy liner seven shadow   waist 2 hour not tell end thank painful foreshadowing possibly not watch movie go watch mid level hop good remotely likable not care planet destroy try hard cheekiness jason ben old tired quiet soulless quality reed cold boring let face annoy selfishness sue insult good job mother world war not share view little speech come country government say hand baby invadenuke know country exist briefly mention london tv poor baby act soul mainly poor little bugger cry possible gareth big baddie call cliche interesting thing fact lot lot lot small panel normal sized people build m sure try desperately massive scale    time enjoy spend silly amount money aaaaaalllllllllll super hero guff ve fart far lazy liner seven shadow   waist 2 hour tell end thank painful foreshadowing possibly mid level hop good remotely likable care planet destroy try hard cheekiness jason ben old tired quiet soulless quality reed cold boring let face annoy selfishness sue insult good job mother world war share view little speech come country government hand baby invadenuke know country exist briefly mention london tv poor baby act soul mainly poor little bugger cry possible gareth big baddie cliche interesting thing fact lot lot lot small panel normal sized people build m sure try desperately massive scale    time enjoy spend silly money aaaaaalllllllllll super hero guff ve fart far lazy liner seven shadow   waist 2 hour tell end thank painful foreshadowing possibly mid level hop good remotely likable care planet destroy try hard cheekiness jason ben old tired quiet soulless quality reed cold boring let face annoy selfishness sue insult good job mother world war share view little speech come country government hand baby invadenuke know country exist briefly mention london tv poor baby act soul mainly poor little bugger cry possible gareth big baddie cliche interesting thing fact lot lot lot small panel normal sized people build m sure try desperately massive scale    time enjoy spend silly money aaaaaalllllllllll super hero guff ve fart far</t>
+          <t>lazy liner seven shadow   waist 2 hour not tell end thank painful foreshadowing possibly not watch movie go watch mid level hop good remotely likable not care planet destroy try hard cheekiness jason ben old tired quiet soulless quality reed cold boring let face annoy selfishness sue insult good job mother world war not share view little speech come country government say hand baby invadenuke know country exist briefly mention london tv poor baby act soul mainly poor little bugger cry possible gareth big baddie call cliche interesting thing fact lot lot lot small panel normal sized people build m sure try desperately massive scale    time enjoy spend silly amount money aaaaaalllllllllll super hero guff ve fart far lazy liner seven shadow   waist 2 hour tell end thank painful foreshadowing possibly mid level hop good remotely likable care planet destroy try hard cheekiness jason ben old tired quiet soulless quality reed cold boring let face annoy selfishness sue insult good job mother world war share view little speech come country government hand baby invadenuke know country exist briefly mention london tv poor baby act soul mainly poor little bugger cry possible gareth big baddie cliche interesting thing fact lot lot lot small panel normal sized people build m sure try desperately massive scale    time enjoy spend silly money aaaaaalllllllllll super hero guff ve fart far [SEP] ENTLBL_PERSON ENTTXT_jason_ben_old</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3831,20 +2887,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3866,14 +2912,10 @@
           <t>identity fraud captain america brave new world struggle find identity waver element past film like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline make forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft film heart quality early success identity fraud captain america brave new world struggle find identity waver element past like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft heart quality early success</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>identity fraud captain america brave new world struggle find identity waver element past like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft heart quality early success</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>identity fraud captain america brave new world struggle find identity waver element past film like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline make forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft film heart quality early success identity fraud captain america brave new world struggle find identity waver element past like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft heart quality early success identity fraud captain america brave new world struggle find identity waver element past like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft heart quality early success</t>
+          <t>identity fraud captain america brave new world struggle find identity waver element past film like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline make forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft film heart quality early success identity fraud captain america brave new world struggle find identity waver element past like captain america hulk fully commit unfortunately result fall short expectation feel underdeveloped storyline forgettable performance unremarkable lack depth need lasting impact disappointing stray root sincerely hope return craft heart quality early success [SEP]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3888,20 +2930,10 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3923,14 +2955,10 @@
           <t>well bp decent lot flaw pretty good pretty okay superhero come think black panther boring point fall asleep think produce single good couple year television show miss abysmal failure par marvel middle work far outshine black panther issue computer generate imagery lack good business watch iron computer graphic hold today know well highly annoy effort late movie female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending go spoil bit contrived couple moment lot minor complaint ruin say namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump bp decent lot flaw pretty good pretty okay superhero come think black panther boring point fall asleep think produce single good couple year television miss abysmal failure par middle work far outshine black panther issue computer generate imagery lack use good business iron computer graphic hold today know highly annoy effort late female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending spoil bit contrived couple moment lot minor complaint ruin namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>bp decent lot flaw pretty good pretty okay superhero think produce single good couple year television miss abysmal failure issue computer generate imagery lack female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending spoil bit contrived couple moment lot minor complaint ruin namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>well bp decent lot flaw pretty good pretty okay superhero come think black panther boring point fall asleep think produce single good couple year television show miss abysmal failure par marvel middle work far outshine black panther issue computer generate imagery lack good business watch iron computer graphic hold today know well highly annoy effort late movie female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending go spoil bit contrived couple moment lot minor complaint ruin say namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump bp decent lot flaw pretty good pretty okay superhero come think black panther boring point fall asleep think produce single good couple year television miss abysmal failure par middle work far outshine black panther issue computer generate imagery lack use good business iron computer graphic hold today know highly annoy effort late female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending spoil bit contrived couple moment lot minor complaint ruin namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump bp decent lot flaw pretty good pretty okay superhero think produce single good couple year television miss abysmal failure issue computer generate imagery lack female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending spoil bit contrived couple moment lot minor complaint ruin namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump</t>
+          <t>well bp decent lot flaw pretty good pretty okay superhero come think black panther boring point fall asleep think produce single good couple year television show miss abysmal failure par marvel middle work far outshine black panther issue computer generate imagery lack good business watch iron computer graphic hold today know well highly annoy effort late movie female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending go spoil bit contrived couple moment lot minor complaint ruin say namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump bp decent lot flaw pretty good pretty okay superhero come think black panther boring point fall asleep think produce single good couple year television miss abysmal failure par middle work far outshine black panther issue computer generate imagery lack use good business iron computer graphic hold today know highly annoy effort late female scientific team sudden scientific solution create couple super woman contrived speak focus woman border laughable woman namor happen good figure final main complaint ending spoil bit contrived couple moment lot minor complaint ruin namor excellent new antagonistic royal painfully obnoxious comic_strip background bit change complain acting great involved definitely bore mid tier tentatively recommend normal find thing complain decent job entertaininglet hope slump [SEP]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3945,20 +2973,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -3980,14 +2998,10 @@
           <t>spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow make grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate make statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow not lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow make grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate make statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow not lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical</t>
+          <t>spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow make grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate make statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow not lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical spiderman 57 year old idea good cinematic form beautiful picture large ground insanely fantastical deeply intimate close dancing smoothly edge humorous sad charming personal existential jump central small simple gesture 17 year old dangerous threat constitute reality land trilogy franchise   tender coming age kid grow grow need expertly externalize adorable contrast similar embed origin meeting young youthful awkwardness old momentary school crush beginning romance flamboyant rage pinkish craving sense embroid sense justice world blessedcurse true power true palpable physically touchable difference experience heaviness world impossibility rule crave escape eventually find growth eventuality young kid young kid truly hero construct hero clumsy journey honest confrontation self past future picture celebrate growth hopeful despite dread loss necessitate statement world continue embrace loss death confrontation devil past end journey beauty hope core adulthood speak picture beautiful fun heavy dark sad heartbreake pay homage moment grow lean heavily nostalgic embrace smoothly essence feel natural true doubt good installment series heavy emotional culmination huge franchise cleverly passion love abundant despite mishap magical [SEP]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4002,20 +3016,10 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4039,12 +3043,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>perfect balance great super hero perfect balance journey lead steve rogers captain america steve rogers play chris evans want difference despite small room roger stand odd stack stop fight fair right lack physicality health deny army dr abraham erskine play stanley tucci recognize pureness roger erskine create formula super soldier use rogers captain america create roger strong fast big challenge steve roger face odd stack army recognize ability deem worthy fight war nazi heroic action save countless war captain america line hydra red skull play hugo weaving head hydra obtain similar power captain america red skull hitler sane red skull want destroy entire world good finally super hero actual hero captain america find way save person danger</t>
+          <t>ENTLBL_PERSON ENTTXT_steve ENTLBL_PERSON ENTTXT_america_steve ENTLBL_PERSON ENTTXT_chris_evans ENTLBL_PERSON ENTTXT_abraham_erskine ENTLBL_ORG ENTTXT_stanley_tucci ENTLBL_PERSON ENTTXT_roger_erskine ENTLBL_PERSON ENTTXT_roger_strong_fast_big_challenge_steve_roger ENTLBL_ORG ENTTXT_hydra_red_skull_play ENTLBL_EVENT ENTTXT_hugo ENTLBL_PERSON ENTTXT_hydra</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>perfect balance great super hero perfect balance show journey lead steve rogers captain america steve rogers play chris evans want difference despite small room roger stand odd stack stop fight fair right lack physicality health keep get deny army dr abraham erskine play stanley tucci recognize pureness roger erskine create formula super soldier go rogers captain america create roger strong fast big challenge steve roger face odd stack army recognize ability deem worthy fight war nazi heroic action save countless man war captain america line hydra red skull play hugo weaving head hydra obtain similar power captain america red skull make hitler sane red skull want destroy entire world good finally super hero actual hero captain america find way save person danger perfect balance great super hero perfect balance journey lead steve rogers captain america steve rogers play chris evans want difference despite small room roger stand odd stack stop fight fair right lack physicality health deny army dr abraham erskine play stanley tucci recognize pureness roger erskine create formula super soldier use rogers captain america create roger strong fast big challenge steve roger face odd stack army recognize ability deem worthy fight war nazi heroic action save countless war captain america line hydra red skull play hugo weaving head hydra obtain similar power captain america red skull hitler sane red skull want destroy entire world good finally super hero actual hero captain america find way save person danger perfect balance great super hero perfect balance journey lead steve rogers captain america steve rogers play chris evans want difference despite small room roger stand odd stack stop fight fair right lack physicality health deny army dr abraham erskine play stanley tucci recognize pureness roger erskine create formula super soldier use rogers captain america create roger strong fast big challenge steve roger face odd stack army recognize ability deem worthy fight war nazi heroic action save countless war captain america line hydra red skull play hugo weaving head hydra obtain similar power captain america red skull hitler sane red skull want destroy entire world good finally super hero actual hero captain america find way save person danger</t>
+          <t>perfect balance great super hero perfect balance show journey lead steve rogers captain america steve rogers play chris evans want difference despite small room roger stand odd stack stop fight fair right lack physicality health keep get deny army dr abraham erskine play stanley tucci recognize pureness roger erskine create formula super soldier go rogers captain america create roger strong fast big challenge steve roger face odd stack army recognize ability deem worthy fight war nazi heroic action save countless man war captain america line hydra red skull play hugo weaving head hydra obtain similar power captain america red skull make hitler sane red skull want destroy entire world good finally super hero actual hero captain america find way save person danger perfect balance great super hero perfect balance journey lead steve rogers captain america steve rogers play chris evans want difference despite small room roger stand odd stack stop fight fair right lack physicality health deny army dr abraham erskine play stanley tucci recognize pureness roger erskine create formula super soldier use rogers captain america create roger strong fast big challenge steve roger face odd stack army recognize ability deem worthy fight war nazi heroic action save countless war captain america line hydra red skull play hugo weaving head hydra obtain similar power captain america red skull hitler sane red skull want destroy entire world good finally super hero actual hero captain america find way save person danger [SEP] ENTLBL_PERSON ENTTXT_steve ENTLBL_PERSON ENTTXT_america_steve ENTLBL_PERSON ENTTXT_chris_evans ENTLBL_PERSON ENTTXT_abraham_erskine ENTLBL_ORG ENTTXT_stanley_tucci ENTLBL_PERSON ENTTXT_roger_erskine ENTLBL_PERSON ENTTXT_roger_strong_fast_big_challenge_steve_roger ENTLBL_ORG ENTTXT_hydra_red_skull_play ENTLBL_EVENT ENTTXT_hugo ENTLBL_PERSON ENTTXT_hydra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4059,20 +3063,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4094,14 +3088,10 @@
           <t>talk action exactly like title talk action spiderman way home end multi verse plotline not know connect thunderbolt group bunch mediocre get like dcs suicide squad entire drag forever real storyline well hour nonsense talk cutout keep 15 hour long not justify high rating imdb real disappointment finish write review middle talk action exactly like title talk action spiderman way home end multi verse plotline know connect thunderbolt group bunch mediocre like dcs suicide squad entire drag forever real storyline hour nonsense talk cutout 15 hour long justify high rating imdb real disappointment finish write review middle</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>talk action exactly like title talk action thunderbolt group bunch mediocre like dcs suicide squad entire drag forever real storyline hour nonsense talk cutout 15 hour long justify high rating imdb real disappointment finish write review middle</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>talk action exactly like title talk action spiderman way home end multi verse plotline not know connect thunderbolt group bunch mediocre get like dcs suicide squad entire drag forever real storyline well hour nonsense talk cutout keep 15 hour long not justify high rating imdb real disappointment finish write review middle talk action exactly like title talk action spiderman way home end multi verse plotline know connect thunderbolt group bunch mediocre like dcs suicide squad entire drag forever real storyline hour nonsense talk cutout 15 hour long justify high rating imdb real disappointment finish write review middle talk action exactly like title talk action thunderbolt group bunch mediocre like dcs suicide squad entire drag forever real storyline hour nonsense talk cutout 15 hour long justify high rating imdb real disappointment finish write review middle</t>
+          <t>talk action exactly like title talk action spiderman way home end multi verse plotline not know connect thunderbolt group bunch mediocre get like dcs suicide squad entire drag forever real storyline well hour nonsense talk cutout keep 15 hour long not justify high rating imdb real disappointment finish write review middle talk action exactly like title talk action spiderman way home end multi verse plotline know connect thunderbolt group bunch mediocre like dcs suicide squad entire drag forever real storyline hour nonsense talk cutout 15 hour long justify high rating imdb real disappointment finish write review middle [SEP]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4116,20 +3106,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4153,12 +3133,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>james gunn cinematic need cpr 76 james gunn deliver emotionally charge visually spectacular sendoff piece original guardian greatly help nostalgia induce soundtrack change aspect ratio rocket hard hit origin centrepiece definitive storyline gunn remarkable storyteller know ground superlative ability banter band misfit continue laugh loud humourous plot transition rocket past guardians present think gunn able teary eyed sudden demise adorable computer generate imagery animal mean explain mastery emotion storytelle guardian hisher moment impact add high possibly breezy 25 hour ll experience cinematic phase   edit section come jar set counter earth stand visually icky gunn quickly bounce epic final act heartwarming climax music continue integral component gunn taste welcome open arm beastie boy needle drop couple wonderfully craft indoor set piece whoaaaaa moment consider conclusion piece mid end credit serve purpose prosthetic use single like wow</t>
+          <t>ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_james_gunn_cinematic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>james gunn give cinematic need cpr 76 james gunn deliver emotionally charge visually spectacular sendoff piece original guardian greatly help nostalgia induce soundtrack change aspect ratio rocket get hard hit origin story make centrepiece definitive storyline gunn remarkable storyteller know ground superlative ability banter band misfit continue laugh loud humourous plot keep transition rocket past guardians present think gunn able teary eyed sudden demise adorable computer generate imagery animal mean explain mastery emotion storytelle guardian get hisher moment impact add high possibly breezy 25 hour ll experience cinematic phase   edit section come jar set counter earth stand visually icky gunn quickly bounce epic final act heartwarming climax music continue integral component film gunn taste welcome open arm beastie boy needle drop couple wonderfully craft indoor set piece whoaaaaa moment consider conclusion piece mid end credit serve purpose prosthetic single like wow james gunn cinematic need cpr 76 james gunn deliver emotionally charge visually spectacular sendoff piece original guardian greatly help nostalgia induce soundtrack change aspect ratio rocket hard hit origin centrepiece definitive storyline gunn remarkable storyteller know ground superlative ability banter band misfit continue laugh loud humourous plot transition rocket past guardians present think gunn able teary eyed sudden demise adorable computer generate imagery animal mean explain mastery emotion storytelle guardian hisher moment impact add high possibly breezy 25 hour ll experience cinematic phase   edit section come jar set counter earth stand visually icky gunn quickly bounce epic final act heartwarming climax music continue integral component gunn taste welcome open arm beastie boy needle drop couple wonderfully craft indoor set piece whoaaaaa moment consider conclusion piece mid end credit serve purpose prosthetic use single like wow james gunn cinematic need cpr 76 james gunn deliver emotionally charge visually spectacular sendoff piece original guardian greatly help nostalgia induce soundtrack change aspect ratio rocket hard hit origin centrepiece definitive storyline gunn remarkable storyteller know ground superlative ability banter band misfit continue laugh loud humourous plot transition rocket past guardians present think gunn able teary eyed sudden demise adorable computer generate imagery animal mean explain mastery emotion storytelle guardian hisher moment impact add high possibly breezy 25 hour ll experience cinematic phase   edit section come jar set counter earth stand visually icky gunn quickly bounce epic final act heartwarming climax music continue integral component gunn taste welcome open arm beastie boy needle drop couple wonderfully craft indoor set piece whoaaaaa moment consider conclusion piece mid end credit serve purpose prosthetic use single like wow</t>
+          <t>james gunn give cinematic need cpr 76 james gunn deliver emotionally charge visually spectacular sendoff piece original guardian greatly help nostalgia induce soundtrack change aspect ratio rocket get hard hit origin story make centrepiece definitive storyline gunn remarkable storyteller know ground superlative ability banter band misfit continue laugh loud humourous plot keep transition rocket past guardians present think gunn able teary eyed sudden demise adorable computer generate imagery animal mean explain mastery emotion storytelle guardian get hisher moment impact add high possibly breezy 25 hour ll experience cinematic phase   edit section come jar set counter earth stand visually icky gunn quickly bounce epic final act heartwarming climax music continue integral component film gunn taste welcome open arm beastie boy needle drop couple wonderfully craft indoor set piece whoaaaaa moment consider conclusion piece mid end credit serve purpose prosthetic single like wow james gunn cinematic need cpr 76 james gunn deliver emotionally charge visually spectacular sendoff piece original guardian greatly help nostalgia induce soundtrack change aspect ratio rocket hard hit origin centrepiece definitive storyline gunn remarkable storyteller know ground superlative ability banter band misfit continue laugh loud humourous plot transition rocket past guardians present think gunn able teary eyed sudden demise adorable computer generate imagery animal mean explain mastery emotion storytelle guardian hisher moment impact add high possibly breezy 25 hour ll experience cinematic phase   edit section come jar set counter earth stand visually icky gunn quickly bounce epic final act heartwarming climax music continue integral component gunn taste welcome open arm beastie boy needle drop couple wonderfully craft indoor set piece whoaaaaa moment consider conclusion piece mid end credit serve purpose prosthetic use single like wow [SEP] ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_james_gunn_cinematic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4173,20 +3153,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4208,14 +3178,10 @@
           <t>fun way well hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool movie theater know enjoy yes 4th wall break ton reference film coherent not main focus time feel like requirement fox cinematic property understand go movie understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny not wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor get chance reprise roll play year wish focus deadpool group friend like movie severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic film end ok definitely terrible wish feel like deadpool cinematic fun way hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool theater know enjoy yes 4th wall break ton reference coherent main focus time feel like requirement fox cinematic property understand understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor chance reprise roll play year wish focus deadpool group friend like severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic end ok definitely terrible wish feel like deadpool cinematic</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>fun way hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool theater know enjoy yes 4th wall break ton reference coherent main focus time feel like requirement fox cinematic property understand understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor chance reprise roll play year wish focus deadpool group friend like severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic end ok definitely terrible wish feel like deadpool cinematic</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>fun way well hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool movie theater know enjoy yes 4th wall break ton reference film coherent not main focus time feel like requirement fox cinematic property understand go movie understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny not wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor get chance reprise roll play year wish focus deadpool group friend like movie severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic film end ok definitely terrible wish feel like deadpool cinematic fun way hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool theater know enjoy yes 4th wall break ton reference coherent main focus time feel like requirement fox cinematic property understand understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor chance reprise roll play year wish focus deadpool group friend like severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic end ok definitely terrible wish feel like deadpool cinematic fun way hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool theater know enjoy yes 4th wall break ton reference coherent main focus time feel like requirement fox cinematic property understand understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor chance reprise roll play year wish focus deadpool group friend like severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic end ok definitely terrible wish feel like deadpool cinematic</t>
+          <t>fun way well hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool movie theater know enjoy yes 4th wall break ton reference film coherent not main focus time feel like requirement fox cinematic property understand go movie understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny not wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor get chance reprise roll play year wish focus deadpool group friend like movie severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic film end ok definitely terrible wish feel like deadpool cinematic fun way hype finally die think finally time talk honestly ok compare nearly good especially second thing like deadpool theater know enjoy yes 4th wall break ton reference coherent main focus time feel like requirement fox cinematic property understand understand definitely enjoy lot feel like spoof time dark actioncomedy like villain actress play main hope stuff amazing yes extremely funny wrong fun time laugh nonstop action incredible wish good action comedy enjoy reference love fact actor chance reprise roll play year wish focus deadpool group friend like severe lack colossus teenage warhead definitely feel mean reference deep cut industry able understand understanding reference pretty mean spirited enjoyable like wrap love non cinematic end ok definitely terrible wish feel like deadpool cinematic [SEP]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4230,20 +3196,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4265,14 +3221,10 @@
           <t>tie iron 3 bad far entirely hype feel emotion good bad serve purpose great scheme thing dull origin merely set location final fight infinity war not figure role fill phase take politically charge nonsensical plot appease racebater bad disappointed result tie iron 3 bad far entirely hype feel emotion good bad serve purpose great scheme thing dull origin merely set location final fight infinity war figure role fill phase politically charge nonsensical plot appease racebater bad disappointed result</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>feel emotion good bad serve purpose great scheme thing figure role fill phase politically charge nonsensical plot appease racebater bad disappointed result</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>tie iron 3 bad far entirely hype feel emotion good bad serve purpose great scheme thing dull origin merely set location final fight infinity war not figure role fill phase take politically charge nonsensical plot appease racebater bad disappointed result tie iron 3 bad far entirely hype feel emotion good bad serve purpose great scheme thing dull origin merely set location final fight infinity war figure role fill phase politically charge nonsensical plot appease racebater bad disappointed result feel emotion good bad serve purpose great scheme thing figure role fill phase politically charge nonsensical plot appease racebater bad disappointed result</t>
+          <t>tie iron 3 bad far entirely hype feel emotion good bad serve purpose great scheme thing dull origin merely set location final fight infinity war not figure role fill phase take politically charge nonsensical plot appease racebater bad disappointed result tie iron 3 bad far entirely hype feel emotion good bad serve purpose great scheme thing dull origin merely set location final fight infinity war figure role fill phase politically charge nonsensical plot appease racebater bad disappointed result [SEP]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4287,20 +3239,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4322,14 +3264,10 @@
           <t>uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy not land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy not land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance</t>
+          <t>uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy not land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance uneven awesome visual great fight sequence funny joke unbelievably heart wrench truly breathtake cinematography narrative mess lot comedy land feel like like bad theme park ride questionable decision genuinely stupid writing decision particularly bad assassination great post credit waste fun fun drown substance [SEP]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4344,20 +3282,10 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4379,14 +3307,10 @@
           <t>great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement set right civil war end right infinity war decide tell kill endgame confuse ve fit perfectly civil war ve give black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward see yelena fit wide cinematic great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement set right civil war end right infinity war decide tell kill endgame confuse ve fit perfectly civil war ve black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward yelena fit wide cinematic</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement decide tell kill endgame confuse ve fit perfectly civil war ve black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward yelena fit wide cinematic</t>
-        </is>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement set right civil war end right infinity war decide tell kill endgame confuse ve fit perfectly civil war ve give black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward see yelena fit wide cinematic great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement set right civil war end right infinity war decide tell kill endgame confuse ve fit perfectly civil war ve black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward yelena fit wide cinematic great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement decide tell kill endgame confuse ve fit perfectly civil war ve black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward yelena fit wide cinematic</t>
+          <t>great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement set right civil war end right infinity war decide tell kill endgame confuse ve fit perfectly civil war ve give black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward see yelena fit wide cinematic great action wish come soon opening sequence soundtrack grainy gritty camera shot hint actionviolence set tone hit home atrocious nature natashas past big gripe lack consequence wide mcu mainly chronological placement set right civil war end right infinity war decide tell kill endgame confuse ve fit perfectly civil war ve black widow solo deserve whilst alive member team overall enjoyable actionspy flick funny dialogue hard hit look forward yelena fit wide cinematic [SEP]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4401,20 +3325,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4438,12 +3352,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>remember amazing teaser trailer expect opposite word use eh bit vague think bit thing like good amazing crazy use welcome review age ultron open fine start fact amazing start fresh intense action pack sequence end favourite yes m spell right m american yknow unfortunately toss bit consider new consider upcoming die development adore scarlet witch power actually opening downhill slightly ultron introduction terrible explain invisible force suddenly speak inside load technological material know feel pretty dumb comic_strip suppose complain guess translate screen kind dull twitch seat different time thing action sequence fantastic thing hold ultron like teaser trailer hype want dark gritty intense heart break half horror advertising false point sue remember scarlet gut wrench scream maybe ultron string teaser trailer guess find thing feel bit satisfied act ultron plan finally reveal turn amazing computer generate imagery effect absolutely incredible shot trailer reveal plan extend second eye end review finally figure word sum   overrate mark review unhelpful care opinion definitely guess fan comic_strip prepare completely different market trailer thank reading know somebody agree edit sippy sip mug tea spit screen rat 79 change normal rating bad simply try lower rating deserve nerd attack average crazy rate higher 6 goodbye</t>
+          <t>ENTLBL_PERSON ENTTXT_sip_mug</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>remember amazing teaser trailer expect opposite word will not use eh bit vague think bit well thing like good amazing crazy use welcome review age ultron open fine start fact amazing start fresh intense action pack sequence introduce sequel new scarlet witch quicksilver end favourite yes m spell right m american yknow unfortunately toss bit consider new consider upcoming die get development adore scarlet witch power part actually opening go downhill slightly ultron introduction terrible explain invisible force suddenly speak inside load technological material not know feel pretty dumb comic_strip suppose not complain guess not translate screen kind dull keep twitch seat different time thing action sequence fantastic thing hold ultron like teaser trailer get hype want dark gritty intense heart break half horror advertising false point sue remember scarlet gut wrench scream maybe ultron say string teaser trailer guess find thing make feel bit satisfied act ultron plan finally reveal turn amazing computer generate imagery effect absolutely incredible shot trailer reveal plan extend second eye end review finally figure word sum overrate mark review unhelpful not care opinion definitely guess fan comic_strip prepare completely different market trailer thank reading know somebody agree edit sippy sip mug tea spit screen rat 79 change normal rating bad simply try lower rating deserve nerd attack average crazy rate higher 6 goodbye remember amazing teaser trailer expect opposite word use eh bit vague think bit thing like good amazing crazy use welcome review age ultron open fine start fact amazing start fresh intense action pack sequence introduce sequel new scarlet witch quicksilver end favourite yes m spell right m american yknow unfortunately toss bit consider new consider upcoming die development adore scarlet witch power actually opening downhill slightly ultron introduction terrible explain invisible force suddenly speak inside load technological material know feel pretty dumb comic_strip suppose complain guess translate screen kind dull twitch seat different time thing action sequence fantastic thing hold ultron like teaser trailer hype want dark gritty intense heart break half horror advertising false point sue remember scarlet gut wrench scream maybe ultron string teaser trailer guess find thing feel bit satisfied act ultron plan finally reveal turn amazing computer generate imagery effect absolutely incredible shot trailer reveal plan extend second eye end review finally figure word sum overrate mark review unhelpful care opinion definitely guess fan comic_strip prepare completely different market trailer thank reading know somebody agree edit sippy sip mug tea spit screen rat 79 change normal rating bad simply try lower rating deserve nerd attack average crazy rate higher 6 goodbye remember amazing teaser trailer expect opposite word use eh bit vague think bit thing like good amazing crazy use welcome review age ultron open fine start fact amazing start fresh intense action pack sequence end favourite yes m spell right m american yknow unfortunately toss bit consider new consider upcoming die development adore scarlet witch power actually opening downhill slightly ultron introduction terrible explain invisible force suddenly speak inside load technological material know feel pretty dumb comic_strip suppose complain guess translate screen kind dull twitch seat different time thing action sequence fantastic thing hold ultron like teaser trailer hype want dark gritty intense heart break half horror advertising false point sue remember scarlet gut wrench scream maybe ultron string teaser trailer guess find thing feel bit satisfied act ultron plan finally reveal turn amazing computer generate imagery effect absolutely incredible shot trailer reveal plan extend second eye end review finally figure word sum   overrate mark review unhelpful care opinion definitely guess fan comic_strip prepare completely different market trailer thank reading know somebody agree edit sippy sip mug tea spit screen rat 79 change normal rating bad simply try lower rating deserve nerd attack average crazy rate higher 6 goodbye</t>
+          <t>remember amazing teaser trailer expect opposite word will not use eh bit vague think bit well thing like good amazing crazy use welcome review age ultron open fine start fact amazing start fresh intense action pack sequence introduce sequel new scarlet witch quicksilver end favourite yes m spell right m american yknow unfortunately toss bit consider new consider upcoming die get development adore scarlet witch power part actually opening go downhill slightly ultron introduction terrible explain invisible force suddenly speak inside load technological material not know feel pretty dumb comic_strip suppose not complain guess not translate screen kind dull keep twitch seat different time thing action sequence fantastic thing hold ultron like teaser trailer get hype want dark gritty intense heart break half horror advertising false point sue remember scarlet gut wrench scream maybe ultron say string teaser trailer guess find thing make feel bit satisfied act ultron plan finally reveal turn amazing computer generate imagery effect absolutely incredible shot trailer reveal plan extend second eye end review finally figure word sum overrate mark review unhelpful not care opinion definitely guess fan comic_strip prepare completely different market trailer thank reading know somebody agree edit sippy sip mug tea spit screen rat 79 change normal rating bad simply try lower rating deserve nerd attack average crazy rate higher 6 goodbye remember amazing teaser trailer expect opposite word use eh bit vague think bit thing like good amazing crazy use welcome review age ultron open fine start fact amazing start fresh intense action pack sequence introduce sequel new scarlet witch quicksilver end favourite yes m spell right m american yknow unfortunately toss bit consider new consider upcoming die development adore scarlet witch power actually opening downhill slightly ultron introduction terrible explain invisible force suddenly speak inside load technological material know feel pretty dumb comic_strip suppose complain guess translate screen kind dull twitch seat different time thing action sequence fantastic thing hold ultron like teaser trailer hype want dark gritty intense heart break half horror advertising false point sue remember scarlet gut wrench scream maybe ultron string teaser trailer guess find thing feel bit satisfied act ultron plan finally reveal turn amazing computer generate imagery effect absolutely incredible shot trailer reveal plan extend second eye end review finally figure word sum overrate mark review unhelpful care opinion definitely guess fan comic_strip prepare completely different market trailer thank reading know somebody agree edit sippy sip mug tea spit screen rat 79 change normal rating bad simply try lower rating deserve nerd attack average crazy rate higher 6 goodbye [SEP] ENTLBL_PERSON ENTTXT_sip_mug</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4458,20 +3372,10 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4493,14 +3397,10 @@
           <t>awesome iron good hero storyline great location set outstanding awesome iron good hero storyline great location set outstanding</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>awesome iron good hero storyline great location set outstanding</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>awesome iron good hero storyline great location set outstanding awesome iron good hero storyline great location set outstanding awesome iron good hero storyline great location set outstanding</t>
+          <t>awesome iron good hero storyline great location set outstanding awesome iron good hero storyline great location set outstanding [SEP]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4515,20 +3415,10 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4552,12 +3442,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>fall short actually like ant expect good action sequence humor entertain disappoint level acting plot underwhelming tv action act chemistry tell maybe blue screen actual good action ridiculous look shake head special effect good time extremely bad time forget edit main villain developed poorly act actress actor act fit know actor guest star michael douglas laurence fishburne michelle pfeiffer   underwhelming performance definitely oscar humor lack originality fall flat find humor ridiculous look edit poor terrible act liner lack originality plot humor forgettable villain 2 1 2 low decent performance paul rudd relationship daughter strong point 3 star cinematic blame director mcu</t>
+          <t>ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_paul_rudd</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>fall short actually like ant go expect good action sequence humor entertain disappoint level acting plot underwhelming tv action show well act chemistry tell maybe blue screen actual good action ridiculous look shake head special effect good time extremely bad time forget edit main villain developed poorly act actress actor not act not fit part know actor guest star michael douglas laurence fishburne michelle pfeiffer   underwhelming performance definitely oscar humor lack originality fall flat find humor ridiculous look edit poor terrible act liner lack originality plot humor forgettable villain 2 1 2 low decent performance paul rudd relationship daughter strong point give 3 star cinematic blame director mcu well fall short actually like ant expect good action sequence humor entertain disappoint level acting plot underwhelming tv action act chemistry tell maybe blue screen actual good action ridiculous look shake head special effect good time extremely bad time forget edit main villain developed poorly act actress actor act fit know actor guest star michael douglas laurence fishburne michelle pfeiffer   underwhelming performance definitely oscar humor lack originality fall flat find humor ridiculous look edit poor terrible act liner lack originality plot humor forgettable villain 2 1 2 low decent performance paul rudd relationship daughter strong point 3 star cinematic blame director mcu fall short actually like ant expect good action sequence humor entertain disappoint level acting plot underwhelming tv action act chemistry tell maybe blue screen actual good action ridiculous look shake head special effect good time extremely bad time forget edit main villain developed poorly act actress actor act fit know actor guest star michael douglas laurence fishburne michelle pfeiffer   underwhelming performance definitely oscar humor lack originality fall flat find humor ridiculous look edit poor terrible act liner lack originality plot humor forgettable villain 2 1 2 low decent performance paul rudd relationship daughter strong point 3 star cinematic blame director mcu</t>
+          <t>fall short actually like ant go expect good action sequence humor entertain disappoint level acting plot underwhelming tv action show well act chemistry tell maybe blue screen actual good action ridiculous look shake head special effect good time extremely bad time forget edit main villain developed poorly act actress actor not act not fit part know actor guest star michael douglas laurence fishburne michelle pfeiffer   underwhelming performance definitely oscar humor lack originality fall flat find humor ridiculous look edit poor terrible act liner lack originality plot humor forgettable villain 2 1 2 low decent performance paul rudd relationship daughter strong point give 3 star cinematic blame director mcu well fall short actually like ant expect good action sequence humor entertain disappoint level acting plot underwhelming tv action act chemistry tell maybe blue screen actual good action ridiculous look shake head special effect good time extremely bad time forget edit main villain developed poorly act actress actor act fit know actor guest star michael douglas laurence fishburne michelle pfeiffer   underwhelming performance definitely oscar humor lack originality fall flat find humor ridiculous look edit poor terrible act liner lack originality plot humor forgettable villain 2 1 2 low decent performance paul rudd relationship daughter strong point 3 star cinematic blame director mcu [SEP] ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_paul_rudd</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4572,20 +3462,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4607,14 +3487,10 @@
           <t>marvel review let start say not rate usually good bad time rating far mark get gall current rating cinematic outing time embark super hero adventure watch miss help well understand marvel main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell marvel lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh not listen hater cinematic instalment not miss review let start rate usually good bad time rating far mark gall current rating cinematic outing time embark super hero adventure miss help understand main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh listen hater cinematic instalment miss</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>review let start rate usually good bad time rating far mark gall current rating cinematic outing time embark super hero adventure miss help understand main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh listen hater cinematic instalment miss</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>marvel review let start say not rate usually good bad time rating far mark get gall current rating cinematic outing time embark super hero adventure watch miss help well understand marvel main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell marvel lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh not listen hater cinematic instalment not miss review let start rate usually good bad time rating far mark gall current rating cinematic outing time embark super hero adventure miss help understand main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh listen hater cinematic instalment miss review let start rate usually good bad time rating far mark gall current rating cinematic outing time embark super hero adventure miss help understand main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh listen hater cinematic instalment miss</t>
+          <t>marvel review let start say not rate usually good bad time rating far mark get gall current rating cinematic outing time embark super hero adventure watch miss help well understand marvel main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell marvel lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh not listen hater cinematic instalment not miss review let start rate usually good bad time rating far mark gall current rating cinematic outing time embark super hero adventure miss help understand main glad clarify 6 mini series good entertainment ve enjoy late ironically drive rate reason m rat bear deep dive cinematic mcus inability correctly capture spirit original comic_strip read   try analysis racial stereotyping hollywood failure address break   tell lot fun good acting good special effect fantastic notch entertainment family spoil careful formulation discuss quarter way let stem familiar cat space station manage provoke genuine belly laugh listen hater cinematic instalment miss [SEP]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4629,20 +3505,10 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4666,12 +3532,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>miss mark comic_strip avid comicbook reader cast completely miss mark mash theme flashbacksflash forwards cast sense melting audience stead try comicbook terrible great</t>
+          <t>ENTLBL_PERSON ENTTXT_mark_comic_strip_avid ENTLBL_PERSON ENTTXT_reader_cast ENTLBL_PERSON ENTTXT_mark</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>miss mark comic_strip avid comicbook reader cast completely miss mark mash theme flashbacksflash forwards cast sense melting audience stead try comicbook terrible great miss mark comic_strip avid comicbook reader cast completely miss mark mash theme flashbacksflash forwards cast sense melting audience stead try comicbook terrible great miss mark comic_strip avid comicbook reader cast completely miss mark mash theme flashbacksflash forwards cast sense melting audience stead try comicbook terrible great</t>
+          <t>miss mark comic_strip avid comicbook reader cast completely miss mark mash theme flashbacksflash forwards cast sense melting audience stead try comicbook terrible great miss mark comic_strip avid comicbook reader cast completely miss mark mash theme flashbacksflash forwards cast sense melting audience stead try comicbook terrible great [SEP] ENTLBL_PERSON ENTTXT_mark_comic_strip_avid ENTLBL_PERSON ENTTXT_reader_cast ENTLBL_PERSON ENTTXT_mark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4686,20 +3552,10 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4721,14 +3577,10 @@
           <t>endgame people wonder not know cinematic magic plug say iron transitionnostalgia worth great computer generate imagery act zendaya endgame people wonder know cinematic magic plug iron transitionnostalgia worth great computer generate imagery act zendaya</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>know cinematic magic plug</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>endgame people wonder not know cinematic magic plug say iron transitionnostalgia worth great computer generate imagery act zendaya endgame people wonder know cinematic magic plug iron transitionnostalgia worth great computer generate imagery act zendaya know cinematic magic plug</t>
+          <t>endgame people wonder not know cinematic magic plug say iron transitionnostalgia worth great computer generate imagery act zendaya endgame people wonder know cinematic magic plug iron transitionnostalgia worth great computer generate imagery act zendaya [SEP]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4743,20 +3595,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4778,14 +3620,10 @@
           <t>midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept give especially illuminati midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept especially illuminati</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept especially illuminati</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept give especially illuminati midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept especially illuminati midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept especially illuminati</t>
+          <t>midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept give especially illuminati midtiverse miss bad plot bad pacing bad cinematography bad arc overall bad multiverse concept especially illuminati [SEP]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4800,20 +3638,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4837,12 +3665,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>antastic consequently come sigh relief late newcomer ant      shrink apocalyptic pretension   bring director peyton reed replace british writer   director edgar wright helm possibly imaginative atypical superhero saga summer miniaturization cornerstone clever little yarn mind completely appreciate ant director jack arnolds seminal science fiction feature incredible shrink 1957 unfortunate fellow fault find reduce size toothpick tangle predatory house cat refuge child doll house loom time large peculiar planet earth 51 exciting episode course honorable mention include dennis quaid comedy innerspace 1987 rick moranis farce honey shrink kid 1989   ant open 1989 naturally stark regret pym departure pym exit shield endeavor duplicate pym particle ant shrink suit technology pym lose wife experiment technology deem far dangerous anybody trifle   long alive proclaim pym formula early fascinate filmmaker actor michael douglas incredible computerized makeover appear year young record hollywood alter comic_strip canon year kind pym exit shield form company pym technology ironically hank estrange daughter hope van dyne evangeline lilly lose   appear work league treacherous cross meantime idealistic thief scott lang paul rudd leave san quentin serve year stretch burglary actually scott qualify sympathetic ex con cinematic history maggie stonewall scott smarmy fiance paxton bobby cannavale spy   happen cop scott struggle straight land job baskin robbin boss learn prison record fire desperate child support money scott resort burglary skill break hank pyms house steal exotic helmet suit later discover outfit enable shrink ant size enhance fighting prowess   chance earn look daughter eye hero think scott join hank outlandish plan prevent megalomaniacal cross sell pym particle shield nemesis hydra silly superficial preposterous ant deliver score hilarious suspenseful shenanigan marveldisney release ant hollywood ignore thing petite pursuit big big big blockbuster meantime creative intellect plan ant shaun dead director edgar wright embark project decade ago creative difference force wright reed helm ant emerge revelation summer like goofy guardians galaxy summer concept cast mighty mite short brilliant consistently entertaining level ant plumb new depth superhero genre provide superstar michael douglas good role director david fincher 1997 thriller game self deprecatory rudd succeed combination panache charisma funny guy try funny come funny like eponymous creepy crawlie tote time body weight ant deliver time entertainment superhero saga despite downsized spectacle clearly pest habitually ruin picnic undergo massive publicity campaign place formulaic superhero entirely different perspective altogether ant antastic</t>
+          <t>ENTLBL_PERSON ENTTXT_peyton_reed ENTLBL_PERSON ENTTXT_edgar_wright ENTLBL_PERSON ENTTXT_jack_arnolds ENTLBL_PERSON ENTTXT_richard_fleischers ENTLBL_PERSON ENTTXT_irwin_allen ENTLBL_PERSON ENTTXT_rick_moranis_farce_honey ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_howard_stark_john_slattery ENTLBL_ORG ENTTXT_pym_tony ENTLBL_PERSON ENTTXT_stark_bruce_banner ENTLBL_ORG ENTTXT_pym_exit ENTLBL_ORG ENTTXT_darren_cross ENTLBL_PERSON ENTTXT_corey_stoll_bourne ENTLBL_PERSON ENTTXT_van_dyne ENTLBL_ORG ENTTXT_lilly ENTLBL_PERSON ENTTXT_scott_lang_paul_rudd ENTLBL_ORG ENTTXT_scott ENTLBL_PERSON ENTTXT_judy_greer ENTLBL_PERSON ENTTXT_abby ENTLBL_PERSON ENTTXT_maggie_stonewall ENTLBL_PERSON ENTTXT_paxton_bobby_cannavale ENTLBL_ORG ENTTXT_scott_board ENTLBL_PERSON ENTTXT_luis_steal ENTLBL_PERSON ENTTXT_michael_pena_fury ENTLBL_ORG ENTTXT_scott_resort_burglary_skill_break ENTLBL_ORG ENTTXT_hank_pyms_house ENTLBL_PERSON ENTTXT_scott_chance ENTLBL_PERSON ENTTXT_scott_join ENTLBL_ORG ENTTXT_megalomaniacal_cross ENTLBL_ORG ENTTXT_pym_particle_shield ENTLBL_PERSON ENTTXT_hydra ENTLBL_ORG ENTTXT_goofy ENTLBL_PERSON ENTTXT_david_fincher ENTLBL_PERSON ENTTXT_paul_rudd_role_model ENTLBL_ORG ENTTXT_chance_come_pym_warn</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>antastic comic_strip keep get big spectacular appearance iron captain america thor fantastic x man wolverine guardian galaxy consequently come sigh relief late newcomer ant      shrink apocalyptic pretension bring director peyton reed replace british writer   director edgar wright helm possibly imaginative atypical superhero saga summer miniaturization cornerstone clever little yarn mind completely appreciate ant not see director jack arnolds seminal science fiction feature incredible shrink 1957 unfortunate fellow fault find reduce size toothpick tangle predatory house cat take refuge child doll house similarly major magnify shrinkage director richard fleischers fantastic voyage 1966   scale scientist microscopic dimension inject comatose scientist bloodstream save lethal blood clot appropriately television capitalize thing minuscule irwin allen land giant 1968 1970 crew passenger spindrift commercial sub orbital transport spaceship travel treacherous outer space turbulence crash unknown planet loom time large peculiar planet earth make 51 exciting episode course honorable mention include dennis quaid comedy innerspace 1987 rick moranis farce honey shrink kid 1989   ant open 1989 dr hank pym michael douglas hand howard stark john slattery iron 2 resignation leave espionage law enforcement counterterrorism agency shield naturally stark regret pym departure pym exit shield go endeavor duplicate pym particle ant shrink suit technology pym lose wife experiment technology deem far dangerous anybody trifle long alive proclaim pym go formula early fascinate filmmaker give actor michael douglas incredible computerized makeover appear year young record hollywood alter comic_strip canon comic_strip pym tony stark bruce banner originally create villainous ultron menace heroic quintet age ultron year kind pym exit shield form company pym technology sadly pyms evil protege darren cross corey stoll bourne legacy   seize control feverishly scheme replicate prize pym particle ironically hank estrange daughter hope van dyne evangeline lilly lose   appear work league treacherous cross meantime idealistic thief scott lang paul rudd leave san quentin serve year stretch burglary actually scott qualify sympathetic ex con cinematic history divorce wife maggie judy greer jurassic world not pay penny child support scott visit adorable daughter cassie newcomer abby ryder fortson   miss miss maggie stonewall scott smarmy fiance paxton bobby cannavale spy   happen cop reluctantly scott board cellmate luis steal michael pena fury   lure life crime scott struggle straight land job baskin robbin boss learn prison record fire desperate child support money scott resort burglary skill break hank pyms house steal exotic helmet suit later discover outfit enable shrink ant size enhance fighting prowess second chance not come pym warn scott chance earn look daughter eye hero think scott join hank outlandish plan prevent megalomaniacal cross sell pym particle shield nemesis hydra silly superficial preposterous ant deliver score hilarious suspenseful shenanigan marveldisney release ant hollywood ignore thing petite pursuit big big big blockbuster meantime creative intellect plan ant shaun dead director edgar wright embark project decade ago creative difference force wright reed take helm ant emerge revelation summer like goofy guardians galaxy summer concept cast mighty mite short brilliant consistently entertaining level ant plumb new depth superhero genre provide superstar michael douglas good role director david fincher 1997 thriller game romantic comedy lead paul rudd role model guy d imagine diminutive hero self deprecatory rudd succeed combination panache charisma funny guy not try funny come funny like eponymous creepy crawlie tote time body weight ant deliver time entertainment superhero saga despite downsized spectacle surprisingly origin opus cover roughly ground iron great creativity considerably small scale clearly pest habitually ruin picnic undergo massive publicity campaign place formulaic superhero entirely different perspective altogether ant antastic antastic comic_strip big spectacular appearance iron captain america thor fantastic x wolverine guardian galaxy consequently come sigh relief late newcomer ant      shrink apocalyptic pretension bring director peyton reed replace british writer   director edgar wright helm possibly imaginative atypical superhero saga summer miniaturization cornerstone clever little yarn mind completely appreciate ant director jack arnolds seminal science fiction feature incredible shrink 1957 unfortunate fellow fault find reduce size toothpick tangle predatory house cat refuge child doll house similarly major magnify shrinkage director richard fleischers fantastic voyage 1966   scale scientist microscopic dimension inject comatose scientist bloodstream save lethal blood clot appropriately television capitalize thing minuscule irwin allen land giant 1968 1970 crew passenger spindrift commercial sub orbital transport spaceship travel treacherous outer space turbulence crash unknown planet loom time large peculiar planet earth 51 exciting episode course honorable mention include dennis quaid comedy innerspace 1987 rick moranis farce honey shrink kid 1989   ant open 1989 dr hank pym michael douglas hand howard stark john slattery iron 2 resignation leave espionage law enforcement counterterrorism agency shield naturally stark regret pym departure pym exit shield endeavor duplicate pym particle ant shrink suit technology pym lose wife experiment technology deem far dangerous anybody trifle long alive proclaim pym formula early fascinate filmmaker actor michael douglas incredible computerized makeover appear year young record hollywood alter comic_strip canon comic_strip pym tony stark bruce banner originally create villainous ultron menace heroic quintet age ultron year kind pym exit shield form company pym technology sadly pyms evil protege darren cross corey stoll bourne legacy   seize control feverishly scheme replicate prize pym particle ironically hank estrange daughter hope van dyne evangeline lilly lose   appear work league treacherous cross meantime idealistic thief scott lang paul rudd leave san quentin serve year stretch burglary actually scott qualify sympathetic ex con cinematic history divorce wife maggie judy greer jurassic world pay penny child support scott visit adorable daughter cassie newcomer abby ryder fortson   miss miss maggie stonewall scott smarmy fiance paxton bobby cannavale spy   happen cop reluctantly scott board cellmate luis steal michael pena fury   lure life crime scott struggle straight land job baskin robbin boss learn prison record fire desperate child support money scott resort burglary skill break hank pyms house steal exotic helmet suit later discover outfit enable shrink ant size enhance fighting prowess second chance come pym warn scott chance earn look daughter eye hero think scott join hank outlandish plan prevent megalomaniacal cross sell pym particle shield nemesis hydra silly superficial preposterous ant deliver score hilarious suspenseful shenanigan marveldisney release ant hollywood ignore thing petite pursuit big big big blockbuster meantime creative intellect plan ant shaun dead director edgar wright embark project decade ago creative difference force wright reed helm ant emerge revelation summer like goofy guardians galaxy summer concept cast mighty mite short brilliant consistently entertaining level ant plumb new depth superhero genre provide superstar michael douglas good role director david fincher 1997 thriller game romantic comedy lead paul rudd role model guy d imagine diminutive hero self deprecatory rudd succeed combination panache charisma funny guy try funny come funny like eponymous creepy crawlie tote time body weight ant deliver time entertainment superhero saga despite downsized spectacle surprisingly origin opus cover roughly ground iron great creativity considerably small scale clearly pest habitually ruin picnic undergo massive publicity campaign place formulaic superhero entirely different perspective altogether ant antastic antastic consequently come sigh relief late newcomer ant      shrink apocalyptic pretension   bring director peyton reed replace british writer   director edgar wright helm possibly imaginative atypical superhero saga summer miniaturization cornerstone clever little yarn mind completely appreciate ant director jack arnolds seminal science fiction feature incredible shrink 1957 unfortunate fellow fault find reduce size toothpick tangle predatory house cat refuge child doll house loom time large peculiar planet earth 51 exciting episode course honorable mention include dennis quaid comedy innerspace 1987 rick moranis farce honey shrink kid 1989   ant open 1989 naturally stark regret pym departure pym exit shield endeavor duplicate pym particle ant shrink suit technology pym lose wife experiment technology deem far dangerous anybody trifle   long alive proclaim pym formula early fascinate filmmaker actor michael douglas incredible computerized makeover appear year young record hollywood alter comic_strip canon year kind pym exit shield form company pym technology ironically hank estrange daughter hope van dyne evangeline lilly lose   appear work league treacherous cross meantime idealistic thief scott lang paul rudd leave san quentin serve year stretch burglary actually scott qualify sympathetic ex con cinematic history maggie stonewall scott smarmy fiance paxton bobby cannavale spy   happen cop scott struggle straight land job baskin robbin boss learn prison record fire desperate child support money scott resort burglary skill break hank pyms house steal exotic helmet suit later discover outfit enable shrink ant size enhance fighting prowess   chance earn look daughter eye hero think scott join hank outlandish plan prevent megalomaniacal cross sell pym particle shield nemesis hydra silly superficial preposterous ant deliver score hilarious suspenseful shenanigan marveldisney release ant hollywood ignore thing petite pursuit big big big blockbuster meantime creative intellect plan ant shaun dead director edgar wright embark project decade ago creative difference force wright reed helm ant emerge revelation summer like goofy guardians galaxy summer concept cast mighty mite short brilliant consistently entertaining level ant plumb new depth superhero genre provide superstar michael douglas good role director david fincher 1997 thriller game self deprecatory rudd succeed combination panache charisma funny guy try funny come funny like eponymous creepy crawlie tote time body weight ant deliver time entertainment superhero saga despite downsized spectacle clearly pest habitually ruin picnic undergo massive publicity campaign place formulaic superhero entirely different perspective altogether ant antastic</t>
+          <t>antastic comic_strip keep get big spectacular appearance iron captain america thor fantastic x man wolverine guardian galaxy consequently come sigh relief late newcomer ant      shrink apocalyptic pretension bring director peyton reed replace british writer   director edgar wright helm possibly imaginative atypical superhero saga summer miniaturization cornerstone clever little yarn mind completely appreciate ant not see director jack arnolds seminal science fiction feature incredible shrink 1957 unfortunate fellow fault find reduce size toothpick tangle predatory house cat take refuge child doll house similarly major magnify shrinkage director richard fleischers fantastic voyage 1966   scale scientist microscopic dimension inject comatose scientist bloodstream save lethal blood clot appropriately television capitalize thing minuscule irwin allen land giant 1968 1970 crew passenger spindrift commercial sub orbital transport spaceship travel treacherous outer space turbulence crash unknown planet loom time large peculiar planet earth make 51 exciting episode course honorable mention include dennis quaid comedy innerspace 1987 rick moranis farce honey shrink kid 1989   ant open 1989 dr hank pym michael douglas hand howard stark john slattery iron 2 resignation leave espionage law enforcement counterterrorism agency shield naturally stark regret pym departure pym exit shield go endeavor duplicate pym particle ant shrink suit technology pym lose wife experiment technology deem far dangerous anybody trifle long alive proclaim pym go formula early fascinate filmmaker give actor michael douglas incredible computerized makeover appear year young record hollywood alter comic_strip canon comic_strip pym tony stark bruce banner originally create villainous ultron menace heroic quintet age ultron year kind pym exit shield form company pym technology sadly pyms evil protege darren cross corey stoll bourne legacy   seize control feverishly scheme replicate prize pym particle ironically hank estrange daughter hope van dyne evangeline lilly lose   appear work league treacherous cross meantime idealistic thief scott lang paul rudd leave san quentin serve year stretch burglary actually scott qualify sympathetic ex con cinematic history divorce wife maggie judy greer jurassic world not pay penny child support scott visit adorable daughter cassie newcomer abby ryder fortson   miss miss maggie stonewall scott smarmy fiance paxton bobby cannavale spy   happen cop reluctantly scott board cellmate luis steal michael pena fury   lure life crime scott struggle straight land job baskin robbin boss learn prison record fire desperate child support money scott resort burglary skill break hank pyms house steal exotic helmet suit later discover outfit enable shrink ant size enhance fighting prowess second chance not come pym warn scott chance earn look daughter eye hero think scott join hank outlandish plan prevent megalomaniacal cross sell pym particle shield nemesis hydra silly superficial preposterous ant deliver score hilarious suspenseful shenanigan marveldisney release ant hollywood ignore thing petite pursuit big big big blockbuster meantime creative intellect plan ant shaun dead director edgar wright embark project decade ago creative difference force wright reed take helm ant emerge revelation summer like goofy guardians galaxy summer concept cast mighty mite short brilliant consistently entertaining level ant plumb new depth superhero genre provide superstar michael douglas good role director david fincher 1997 thriller game romantic comedy lead paul rudd role model guy d imagine diminutive hero self deprecatory rudd succeed combination panache charisma funny guy not try funny come funny like eponymous creepy crawlie tote time body weight ant deliver time entertainment superhero saga despite downsized spectacle surprisingly origin opus cover roughly ground iron great creativity considerably small scale clearly pest habitually ruin picnic undergo massive publicity campaign place formulaic superhero entirely different perspective altogether ant antastic antastic comic_strip big spectacular appearance iron captain america thor fantastic x wolverine guardian galaxy consequently come sigh relief late newcomer ant      shrink apocalyptic pretension bring director peyton reed replace british writer   director edgar wright helm possibly imaginative atypical superhero saga summer miniaturization cornerstone clever little yarn mind completely appreciate ant director jack arnolds seminal science fiction feature incredible shrink 1957 unfortunate fellow fault find reduce size toothpick tangle predatory house cat refuge child doll house similarly major magnify shrinkage director richard fleischers fantastic voyage 1966   scale scientist microscopic dimension inject comatose scientist bloodstream save lethal blood clot appropriately television capitalize thing minuscule irwin allen land giant 1968 1970 crew passenger spindrift commercial sub orbital transport spaceship travel treacherous outer space turbulence crash unknown planet loom time large peculiar planet earth 51 exciting episode course honorable mention include dennis quaid comedy innerspace 1987 rick moranis farce honey shrink kid 1989   ant open 1989 dr hank pym michael douglas hand howard stark john slattery iron 2 resignation leave espionage law enforcement counterterrorism agency shield naturally stark regret pym departure pym exit shield endeavor duplicate pym particle ant shrink suit technology pym lose wife experiment technology deem far dangerous anybody trifle long alive proclaim pym formula early fascinate filmmaker actor michael douglas incredible computerized makeover appear year young record hollywood alter comic_strip canon comic_strip pym tony stark bruce banner originally create villainous ultron menace heroic quintet age ultron year kind pym exit shield form company pym technology sadly pyms evil protege darren cross corey stoll bourne legacy   seize control feverishly scheme replicate prize pym particle ironically hank estrange daughter hope van dyne evangeline lilly lose   appear work league treacherous cross meantime idealistic thief scott lang paul rudd leave san quentin serve year stretch burglary actually scott qualify sympathetic ex con cinematic history divorce wife maggie judy greer jurassic world pay penny child support scott visit adorable daughter cassie newcomer abby ryder fortson   miss miss maggie stonewall scott smarmy fiance paxton bobby cannavale spy   happen cop reluctantly scott board cellmate luis steal michael pena fury   lure life crime scott struggle straight land job baskin robbin boss learn prison record fire desperate child support money scott resort burglary skill break hank pyms house steal exotic helmet suit later discover outfit enable shrink ant size enhance fighting prowess second chance come pym warn scott chance earn look daughter eye hero think scott join hank outlandish plan prevent megalomaniacal cross sell pym particle shield nemesis hydra silly superficial preposterous ant deliver score hilarious suspenseful shenanigan marveldisney release ant hollywood ignore thing petite pursuit big big big blockbuster meantime creative intellect plan ant shaun dead director edgar wright embark project decade ago creative difference force wright reed helm ant emerge revelation summer like goofy guardians galaxy summer concept cast mighty mite short brilliant consistently entertaining level ant plumb new depth superhero genre provide superstar michael douglas good role director david fincher 1997 thriller game romantic comedy lead paul rudd role model guy d imagine diminutive hero self deprecatory rudd succeed combination panache charisma funny guy try funny come funny like eponymous creepy crawlie tote time body weight ant deliver time entertainment superhero saga despite downsized spectacle surprisingly origin opus cover roughly ground iron great creativity considerably small scale clearly pest habitually ruin picnic undergo massive publicity campaign place formulaic superhero entirely different perspective altogether ant antastic [SEP] ENTLBL_PERSON ENTTXT_peyton_reed ENTLBL_PERSON ENTTXT_edgar_wright ENTLBL_PERSON ENTTXT_jack_arnolds ENTLBL_PERSON ENTTXT_richard_fleischers ENTLBL_PERSON ENTTXT_irwin_allen ENTLBL_PERSON ENTTXT_rick_moranis_farce_honey ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_howard_stark_john_slattery ENTLBL_ORG ENTTXT_pym_tony ENTLBL_PERSON ENTTXT_stark_bruce_banner ENTLBL_ORG ENTTXT_pym_exit ENTLBL_ORG ENTTXT_darren_cross ENTLBL_PERSON ENTTXT_corey_stoll_bourne ENTLBL_PERSON ENTTXT_van_dyne ENTLBL_ORG ENTTXT_lilly ENTLBL_PERSON ENTTXT_scott_lang_paul_rudd ENTLBL_ORG ENTTXT_scott ENTLBL_PERSON ENTTXT_judy_greer ENTLBL_PERSON ENTTXT_abby ENTLBL_PERSON ENTTXT_maggie_stonewall ENTLBL_PERSON ENTTXT_paxton_bobby_cannavale ENTLBL_ORG ENTTXT_scott_board ENTLBL_PERSON ENTTXT_luis_steal ENTLBL_PERSON ENTTXT_michael_pena_fury ENTLBL_ORG ENTTXT_scott_resort_burglary_skill_break ENTLBL_ORG ENTTXT_hank_pyms_house ENTLBL_PERSON ENTTXT_scott_chance ENTLBL_PERSON ENTTXT_scott_join ENTLBL_ORG ENTTXT_megalomaniacal_cross ENTLBL_ORG ENTTXT_pym_particle_shield ENTLBL_PERSON ENTTXT_hydra ENTLBL_ORG ENTTXT_goofy ENTLBL_PERSON ENTTXT_david_fincher ENTLBL_PERSON ENTTXT_paul_rudd_role_model ENTLBL_ORG ENTTXT_chance_come_pym_warn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4857,20 +3685,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -4894,12 +3712,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>enjoy joke ridiculousness world god child think catchy good intro oldy rock music plotline waste unfortunately god butcher christian bale badass villain return jane natalie portman feel waste review harp silly dialogue sharp comedy goofiness cheap laugh remain asgardian like bunch refugee idiot fun wait development</t>
+          <t>ENTLBL_PERSON ENTTXT_intro</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>fun installation thor fun enjoy joke ridiculousness world god thor long honorable vike god funny cuz casual situation intentionally goofy sure like good use gunsn rose song grow child think catchy good intro oldy rock music plotline waste unfortunately god butcher christian bale badass villain return jane natalie portman feel waste review harp silly dialogue sharp comedy goofiness cheap laugh remain asgardian like bunch refugee idiot fun wait development fun installation thor fun enjoy joke ridiculousness world god thor long honorable vike god use funny cuz casual situation intentionally goofy sure like good use gunsn rose song grow child think catchy good intro oldy rock music plotline waste unfortunately god butcher christian bale badass villain return jane natalie portman feel waste review harp silly dialogue sharp comedy goofiness cheap laugh remain asgardian like bunch refugee idiot fun wait development enjoy joke ridiculousness world god child think catchy good intro oldy rock music plotline waste unfortunately god butcher christian bale badass villain return jane natalie portman feel waste review harp silly dialogue sharp comedy goofiness cheap laugh remain asgardian like bunch refugee idiot fun wait development</t>
+          <t>fun installation thor fun enjoy joke ridiculousness world god thor long honorable vike god funny cuz casual situation intentionally goofy sure like good use gunsn rose song grow child think catchy good intro oldy rock music plotline waste unfortunately god butcher christian bale badass villain return jane natalie portman feel waste review harp silly dialogue sharp comedy goofiness cheap laugh remain asgardian like bunch refugee idiot fun wait development fun installation thor fun enjoy joke ridiculousness world god thor long honorable vike god use funny cuz casual situation intentionally goofy sure like good use gunsn rose song grow child think catchy good intro oldy rock music plotline waste unfortunately god butcher christian bale badass villain return jane natalie portman feel waste review harp silly dialogue sharp comedy goofiness cheap laugh remain asgardian like bunch refugee idiot fun wait development [SEP] ENTLBL_PERSON ENTTXT_intro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4914,20 +3732,10 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -4951,12 +3759,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>amazing amazing believe people hate dialogue great plot simple stay true comic book acting superb especially robert downy jr come lot recently finally action small compare superhero good people judge iron lack action people agree far action comic book great excited prepare second instalment 2010 hear lot personal friend hear want know definitely worth ps620 pay know iron comic_strip use cartoon version believe great idea finally close eye probably true comic book far look comic book   believe instant classic recommend comic book fan general public</t>
+          <t>ENTLBL_PERSON ENTTXT_robert_downy_jr_come_lot</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>amazing amazing not believe people hate dialogue great plot simple stay true comic book acting superb especially robert downy jr come lot recently finally action small compare superhero movie good people judge iron lack action people agree far action comic book film great keep excited prepare second instalment 2010 hear lot personal friend hear want know definitely worth ps620 pay not know iron comic_strip cartoon version believe great idea finally close eye make probably true comic book see far look comic book   believe instant classic recommend comic book fan general public amazing amazing believe people hate dialogue great plot simple stay true comic book acting superb especially robert downy jr come lot recently finally action small compare superhero good people judge iron lack action people agree far action comic book great excited prepare second instalment 2010 hear lot personal friend hear want know definitely worth ps620 pay know iron comic_strip use cartoon version believe great idea finally close eye probably true comic book far look comic book   believe instant classic recommend comic book fan general public amazing amazing believe people hate dialogue great plot simple stay true comic book acting superb especially robert downy jr come lot recently finally action small compare superhero good people judge iron lack action people agree far action comic book great excited prepare second instalment 2010 hear lot personal friend hear want know definitely worth ps620 pay know iron comic_strip use cartoon version believe great idea finally close eye probably true comic book far look comic book   believe instant classic recommend comic book fan general public</t>
+          <t>amazing amazing not believe people hate dialogue great plot simple stay true comic book acting superb especially robert downy jr come lot recently finally action small compare superhero movie good people judge iron lack action people agree far action comic book film great keep excited prepare second instalment 2010 hear lot personal friend hear want know definitely worth ps620 pay not know iron comic_strip cartoon version believe great idea finally close eye make probably true comic book see far look comic book   believe instant classic recommend comic book fan general public amazing amazing believe people hate dialogue great plot simple stay true comic book acting superb especially robert downy jr come lot recently finally action small compare superhero good people judge iron lack action people agree far action comic book great excited prepare second instalment 2010 hear lot personal friend hear want know definitely worth ps620 pay know iron comic_strip use cartoon version believe great idea finally close eye probably true comic book far look comic book   believe instant classic recommend comic book fan general public [SEP] ENTLBL_PERSON ENTTXT_robert_downy_jr_come_lot</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4971,20 +3779,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -5008,12 +3806,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10 star tom hiddleston loki reason portrayal save</t>
+          <t>ENTLBL_ORG ENTTXT_hiddleston_loki_reason</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>10 star tom hiddleston loki reason portrayal save movie 10 star tom hiddleston loki reason portrayal save 10 star tom hiddleston loki reason portrayal save</t>
+          <t>10 star tom hiddleston loki reason portrayal save movie 10 star tom hiddleston loki reason portrayal save [SEP] ENTLBL_ORG ENTTXT_hiddleston_loki_reason</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5028,22 +3826,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
     </row>
@@ -5065,12 +3853,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>bad thing ve spider far home exactly like homecoming bad completely ruin good spider belong spider 2 far home disgrace spider franchise   understand create bunch cash grab disney mediocre bad point disappointing shame   sony ps end credit good</t>
+          <t>ENTLBL_PERSON ENTTXT_andrew_garfield ENTLBL_PERSON ENTTXT_tom_holland ENTLBL_ORG ENTTXT_ps</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>bad thing ve see spider far home exactly like homecoming bad completely ruin far bad spider create andrew garfield well spider tom holland far spider 2 great spider time good spider belong spider 2 far home disgrace spider franchise   not understand create bunch cash grab disney mediocre well bad point disappointing shame   sony ps end credit good bad thing ve spider far home exactly like homecoming bad completely ruin far bad spider create andrew garfield spider tom holland far spider 2 great spider time good spider belong spider 2 far home disgrace spider franchise   understand create bunch cash grab disney mediocre bad point disappointing shame   sony ps end credit good bad thing ve spider far home exactly like homecoming bad completely ruin good spider belong spider 2 far home disgrace spider franchise   understand create bunch cash grab disney mediocre bad point disappointing shame   sony ps end credit good</t>
+          <t>bad thing ve see spider far home exactly like homecoming bad completely ruin far bad spider create andrew garfield well spider tom holland far spider 2 great spider time good spider belong spider 2 far home disgrace spider franchise   not understand create bunch cash grab disney mediocre well bad point disappointing shame   sony ps end credit good bad thing ve spider far home exactly like homecoming bad completely ruin far bad spider create andrew garfield spider tom holland far spider 2 great spider time good spider belong spider 2 far home disgrace spider franchise   understand create bunch cash grab disney mediocre bad point disappointing shame   sony ps end credit good [SEP] ENTLBL_PERSON ENTTXT_andrew_garfield ENTLBL_PERSON ENTTXT_tom_holland ENTLBL_ORG ENTTXT_ps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5085,20 +3873,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5122,12 +3900,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>people expect iron revolutionary comic book people claim fact disappointing think corny backwards state comic book acting good come robert downey jr reason respect lift garbage mediocrity terrence howard fan annoying jeff bridges utilize ability directing average action un satisfying fail engross whatsoever try hard involve feel like drag bad conclusion bad suppose great writing non existent mind effect good awe obviously enjoy die hard comic book fan probably enjoy fan look different comic book dark knight iron</t>
+          <t>ENTLBL_PERSON ENTTXT_robert_downey_jr_reason ENTLBL_PERSON ENTTXT_jeff_bridges ENTLBL_ORG ENTTXT_un</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>people say get expect iron revolutionary comic book people claim fact disappointing think corny backwards state comic book movie acting good come robert downey jr reason respect lift garbage mediocrity terrence howard fan annoying jeff bridges utilize ability directing average action un satisfying fail engross whatsoever try hard involve feel like drag get bad conclusion bad suppose great writing non existent mind effect good awe obviously enjoy die hard comic book fan probably enjoy fan look different comic book dark knight iron people expect iron revolutionary comic book people claim fact disappointing think corny backwards state comic book acting good come robert downey jr reason respect lift garbage mediocrity terrence howard fan annoying jeff bridges utilize ability directing average action un satisfying fail engross whatsoever try hard involve feel like drag bad conclusion bad suppose great writing non existent mind effect good awe obviously enjoy die hard comic book fan probably enjoy fan look different comic book dark knight iron people expect iron revolutionary comic book people claim fact disappointing think corny backwards state comic book acting good come robert downey jr reason respect lift garbage mediocrity terrence howard fan annoying jeff bridges utilize ability directing average action un satisfying fail engross whatsoever try hard involve feel like drag bad conclusion bad suppose great writing non existent mind effect good awe obviously enjoy die hard comic book fan probably enjoy fan look different comic book dark knight iron</t>
+          <t>people say get expect iron revolutionary comic book people claim fact disappointing think corny backwards state comic book movie acting good come robert downey jr reason respect lift garbage mediocrity terrence howard fan annoying jeff bridges utilize ability directing average action un satisfying fail engross whatsoever try hard involve feel like drag get bad conclusion bad suppose great writing non existent mind effect good awe obviously enjoy die hard comic book fan probably enjoy fan look different comic book dark knight iron people expect iron revolutionary comic book people claim fact disappointing think corny backwards state comic book acting good come robert downey jr reason respect lift garbage mediocrity terrence howard fan annoying jeff bridges utilize ability directing average action un satisfying fail engross whatsoever try hard involve feel like drag bad conclusion bad suppose great writing non existent mind effect good awe obviously enjoy die hard comic book fan probably enjoy fan look different comic book dark knight iron [SEP] ENTLBL_PERSON ENTTXT_robert_downey_jr_reason ENTLBL_PERSON ENTTXT_jeff_bridges ENTLBL_ORG ENTTXT_un</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5142,20 +3920,10 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5179,12 +3947,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ang lee come forgive edward norton tim roth good worth drama suspense tension mystery thrilling moment humor surprising   bland cause bit empathy stupid boring action crap lousy cgi 4510</t>
+          <t>ENTLBL_PERSON ENTTXT_ang_lee_come_everything_forgive ENTLBL_PERSON ENTTXT_tim_roth ENTLBL_PERSON ENTTXT_ang_lee_come_forgive_edward_norton</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ang lee come everything forgive edward norton tim roth good worth drama suspense tension mystery thrilling moment humor surprising   bland cause bit empathy stupid boring action crap lousy cgi think 2003 hulk bad probably skip 4510 ang lee come forgive edward norton tim roth good worth drama suspense tension mystery thrilling moment humor surprising   bland cause bit empathy stupid boring action crap lousy cgi think 2003 hulk bad probably skip 4510 ang lee come forgive edward norton tim roth good worth drama suspense tension mystery thrilling moment humor surprising   bland cause bit empathy stupid boring action crap lousy cgi 4510</t>
+          <t>ang lee come everything forgive edward norton tim roth good worth drama suspense tension mystery thrilling moment humor surprising   bland cause bit empathy stupid boring action crap lousy cgi think 2003 hulk bad probably skip 4510 ang lee come forgive edward norton tim roth good worth drama suspense tension mystery thrilling moment humor surprising   bland cause bit empathy stupid boring action crap lousy cgi think 2003 hulk bad probably skip 4510 [SEP] ENTLBL_PERSON ENTTXT_ang_lee_come_everything_forgive ENTLBL_PERSON ENTTXT_tim_roth ENTLBL_PERSON ENTTXT_ang_lee_come_forgive_edward_norton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5199,20 +3967,10 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5236,12 +3994,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>good expect good emotional 3 spiderman expect trailer expect spider literaly cry</t>
+          <t>ENTLBL_PERSON ENTTXT_literaly ENTLBL_ORG ENTTXT_literaly_cry</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>good expect good movie watch emotional 3 spiderman expect watch trailer expect spider see literaly cry good expect good emotional 3 spiderman expect trailer expect spider literaly cry good expect good emotional 3 spiderman expect trailer expect spider literaly cry</t>
+          <t>good expect good movie watch emotional 3 spiderman expect watch trailer expect spider see literaly cry good expect good emotional 3 spiderman expect trailer expect spider literaly cry [SEP] ENTLBL_PERSON ENTTXT_literaly ENTLBL_ORG ENTTXT_literaly_cry</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5256,22 +4014,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
     </row>
@@ -5291,14 +4039,10 @@
           <t>obviously fail box office good reason simply generic joke not land recommend maybe wait streaming obviously fail box office good reason simply generic joke land recommend maybe wait streaming</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>obviously fail box office good reason simply generic joke land recommend maybe wait streaming</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>obviously fail box office good reason simply generic joke not land recommend maybe wait streaming obviously fail box office good reason simply generic joke land recommend maybe wait streaming obviously fail box office good reason simply generic joke land recommend maybe wait streaming</t>
+          <t>obviously fail box office good reason simply generic joke not land recommend maybe wait streaming obviously fail box office good reason simply generic joke land recommend maybe wait streaming [SEP]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5313,20 +4057,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5350,12 +4084,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>action sequence incredibly dull interesting think way onward thrust dialog obscure understand stark problem expect understand little hint robert downey junior need speak slowly articulate word mickey rourke bizarre look gwyneth old look face draw stunning figure scarlett alluring dark hair action sequence near end good role bit puzzling forget waste time fighting silly look iron lame</t>
+          <t>ENTLBL_PERSON ENTTXT_robert_downey_junior</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>boring not understand dialog prefer iron part action sequence incredibly dull interesting think way onward thrust dialog obscure understand say stark problem expect understand little hint robert downey junior need speak slowly articulate word mickey rourke bizarre look gwyneth old look face draw stunning figure scarlett alluring dark hair action sequence near end good role bit puzzling forget waste time fighting silly look iron man lame boring understand dialog prefer iron action sequence incredibly dull interesting think way onward thrust dialog obscure understand stark problem expect understand little hint robert downey junior need speak slowly articulate word mickey rourke bizarre look gwyneth old look face draw stunning figure scarlett alluring dark hair action sequence near end good role bit puzzling forget waste time fighting silly look iron lame action sequence incredibly dull interesting think way onward thrust dialog obscure understand stark problem expect understand little hint robert downey junior need speak slowly articulate word mickey rourke bizarre look gwyneth old look face draw stunning figure scarlett alluring dark hair action sequence near end good role bit puzzling forget waste time fighting silly look iron lame</t>
+          <t>boring not understand dialog prefer iron part action sequence incredibly dull interesting think way onward thrust dialog obscure understand say stark problem expect understand little hint robert downey junior need speak slowly articulate word mickey rourke bizarre look gwyneth old look face draw stunning figure scarlett alluring dark hair action sequence near end good role bit puzzling forget waste time fighting silly look iron man lame boring understand dialog prefer iron action sequence incredibly dull interesting think way onward thrust dialog obscure understand stark problem expect understand little hint robert downey junior need speak slowly articulate word mickey rourke bizarre look gwyneth old look face draw stunning figure scarlett alluring dark hair action sequence near end good role bit puzzling forget waste time fighting silly look iron lame [SEP] ENTLBL_PERSON ENTTXT_robert_downey_junior</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5370,20 +4104,10 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5405,14 +4129,10 @@
           <t>purely kid bad spiderman try fictional movie blend reality clearly 12yr old purely kid bad spiderman try fictional blend reality clearly 12yr old</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>purely kid bad spiderman try fictional blend reality clearly 12yr old</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>purely kid bad spiderman try fictional movie blend reality clearly 12yr old purely kid bad spiderman try fictional blend reality clearly 12yr old purely kid bad spiderman try fictional blend reality clearly 12yr old</t>
+          <t>purely kid bad spiderman try fictional movie blend reality clearly 12yr old purely kid bad spiderman try fictional blend reality clearly 12yr old [SEP]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5427,20 +4147,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5462,14 +4172,10 @@
           <t>okay completely terrible mistake terrible okay completely terrible mistake terrible</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>okay completely terrible mistake terrible</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>okay completely terrible mistake terrible okay completely terrible mistake terrible okay completely terrible mistake terrible</t>
+          <t>okay completely terrible mistake terrible okay completely terrible mistake terrible [SEP]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5484,20 +4190,10 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5521,12 +4217,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>boring lacking believe 170 million dollar budget think 10 million dollar budget look vin diesel probably spend 2 hour studio easy 100 grand probably writing bad direction bad lot acting bad bad writing direction like chris pratt think great actor great impressed voice bradley cooper sound like impressive voice honestly steal reason m ridiculous 5 dave bautista performance hilarious reason create steal actually create likable good line</t>
+          <t>ENTLBL_PERSON ENTTXT_chris_pratt</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>bite dust thoroughly look forward see good review hear end end like action film bore lacking not believe 170 million dollar budget think 10 million dollar budget look vin diesel probably spend 2 hour studio easy 100 grand probably writing bad direction bad lot acting bad bad writing direction like chris pratt think great actor not great impressed voice bradley cooper sound like impressive voice honestly steal reason m give ridiculous 5 dave bautista performance hilarious reason create steal actually create likable good line bite dust thoroughly look forward good review hear end end like action bore lacking believe 170 million dollar budget think 10 million dollar budget look vin diesel probably spend 2 hour studio easy 100 grand probably writing bad direction bad lot acting bad bad writing direction like chris pratt think great actor great impressed voice bradley cooper sound like impressive voice honestly steal reason m ridiculous 5 dave bautista performance hilarious reason create steal actually create likable good line boring lacking believe 170 million dollar budget think 10 million dollar budget look vin diesel probably spend 2 hour studio easy 100 grand probably writing bad direction bad lot acting bad bad writing direction like chris pratt think great actor great impressed voice bradley cooper sound like impressive voice honestly steal reason m ridiculous 5 dave bautista performance hilarious reason create steal actually create likable good line</t>
+          <t>bite dust thoroughly look forward see good review hear end end like action film bore lacking not believe 170 million dollar budget think 10 million dollar budget look vin diesel probably spend 2 hour studio easy 100 grand probably writing bad direction bad lot acting bad bad writing direction like chris pratt think great actor not great impressed voice bradley cooper sound like impressive voice honestly steal reason m give ridiculous 5 dave bautista performance hilarious reason create steal actually create likable good line bite dust thoroughly look forward good review hear end end like action bore lacking believe 170 million dollar budget think 10 million dollar budget look vin diesel probably spend 2 hour studio easy 100 grand probably writing bad direction bad lot acting bad bad writing direction like chris pratt think great actor great impressed voice bradley cooper sound like impressive voice honestly steal reason m ridiculous 5 dave bautista performance hilarious reason create steal actually create likable good line [SEP] ENTLBL_PERSON ENTTXT_chris_pratt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5541,20 +4237,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5578,12 +4264,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>fun capital f summer blockbuster hype train roll straight good advertise chiseled jaw grim determine brow crowd superhero year think need like remind great loose fun genre fact superhero stretch span number different class pluck fitting element pack beautifully odd curious colorful bouquet read comic_strip life know uncommon filmed adaptation near kind boundless imagination possible print page guardian galaxy gust fresh air time screen brim rich detail superior dash inconsequential world building oodle hint wink close think hollywood come flash sense joy wonder inherent medium broad audience real treat drink enjoy help admire ball far left field create wholly different present status quo admire appreciate ride</t>
+          <t>ENTLBL_ORG ENTTXT_indiana_jones</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>fun capital f summer blockbuster hype train not roll straight good advertise chiseled jaw grim determine brow crowd superhero year think need like remind great loose fun genre fact call superhero stretch span number different class pluck fitting element pack beautifully odd curious colorful bouquet star war indiana jones thor glowing hunk science fiction adventure taste restraint ticklish funny bone set apart having read comic_strip life know uncommon filmed adaptation near kind boundless imagination possible print page guardian galaxy gust fresh air time screen brim rich detail superior dash inconsequential world building oodle hint wink close think hollywood come flash sense joy wonder inherent medium broad audience real treat drink enjoy not help admire ball take far left field create wholly different present status quo admire appreciate ride fun capital f summer blockbuster hype train roll straight good advertise chiseled jaw grim determine brow crowd superhero year think need like remind great loose fun genre fact superhero stretch span number different class pluck fitting element pack beautifully odd curious colorful bouquet star war indiana jones thor glowing hunk science fiction adventure taste restraint ticklish funny bone set apart having read comic_strip life know uncommon filmed adaptation near kind boundless imagination possible print page guardian galaxy gust fresh air time screen brim rich detail superior dash inconsequential world building oodle hint wink close think hollywood come flash sense joy wonder inherent medium broad audience real treat drink enjoy help admire ball far left field create wholly different present status quo admire appreciate ride fun capital f summer blockbuster hype train roll straight good advertise chiseled jaw grim determine brow crowd superhero year think need like remind great loose fun genre fact superhero stretch span number different class pluck fitting element pack beautifully odd curious colorful bouquet read comic_strip life know uncommon filmed adaptation near kind boundless imagination possible print page guardian galaxy gust fresh air time screen brim rich detail superior dash inconsequential world building oodle hint wink close think hollywood come flash sense joy wonder inherent medium broad audience real treat drink enjoy help admire ball far left field create wholly different present status quo admire appreciate ride</t>
+          <t>fun capital f summer blockbuster hype train not roll straight good advertise chiseled jaw grim determine brow crowd superhero year think need like remind great loose fun genre fact call superhero stretch span number different class pluck fitting element pack beautifully odd curious colorful bouquet star war indiana jones thor glowing hunk science fiction adventure taste restraint ticklish funny bone set apart having read comic_strip life know uncommon filmed adaptation near kind boundless imagination possible print page guardian galaxy gust fresh air time screen brim rich detail superior dash inconsequential world building oodle hint wink close think hollywood come flash sense joy wonder inherent medium broad audience real treat drink enjoy not help admire ball take far left field create wholly different present status quo admire appreciate ride fun capital f summer blockbuster hype train roll straight good advertise chiseled jaw grim determine brow crowd superhero year think need like remind great loose fun genre fact superhero stretch span number different class pluck fitting element pack beautifully odd curious colorful bouquet star war indiana jones thor glowing hunk science fiction adventure taste restraint ticklish funny bone set apart having read comic_strip life know uncommon filmed adaptation near kind boundless imagination possible print page guardian galaxy gust fresh air time screen brim rich detail superior dash inconsequential world building oodle hint wink close think hollywood come flash sense joy wonder inherent medium broad audience real treat drink enjoy help admire ball far left field create wholly different present status quo admire appreciate ride [SEP] ENTLBL_ORG ENTTXT_indiana_jones</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5598,20 +4284,10 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -5633,14 +4309,10 @@
           <t>marvel inner chi shang chi arguably original entertaining origin marvel deliver time come slowly start superhero fatigue side aisle deliver spectacle family drama feel shakespearean time way want live action version mulan inner chi shang chi arguably original entertaining origin deliver time come slowly start superhero fatigue aisle deliver spectacle family drama feel shakespearean time way want live action version mulan</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>inner chi shang chi arguably original entertaining origin deliver time come slowly start superhero fatigue aisle deliver spectacle family drama feel shakespearean time way want live action version mulan</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>marvel inner chi shang chi arguably original entertaining origin marvel deliver time come slowly start superhero fatigue side aisle deliver spectacle family drama feel shakespearean time way want live action version mulan inner chi shang chi arguably original entertaining origin deliver time come slowly start superhero fatigue aisle deliver spectacle family drama feel shakespearean time way want live action version mulan inner chi shang chi arguably original entertaining origin deliver time come slowly start superhero fatigue aisle deliver spectacle family drama feel shakespearean time way want live action version mulan</t>
+          <t>marvel inner chi shang chi arguably original entertaining origin marvel deliver time come slowly start superhero fatigue side aisle deliver spectacle family drama feel shakespearean time way want live action version mulan inner chi shang chi arguably original entertaining origin deliver time come slowly start superhero fatigue aisle deliver spectacle family drama feel shakespearean time way want live action version mulan [SEP]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5655,20 +4327,10 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -5692,12 +4354,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>harrison ford little young play president reach point look phone akin action prime time bathroom break cinema mediocre good structure plot complete mess rewrite bunch time anthony mackie good 80 script fault poor job harrison ford include expect bad slop release lately come laugh bad laugh matter snooze f</t>
+          <t>ENTLBL_ORG ENTTXT_ford ENTLBL_PERSON ENTTXT_anthony_mackie</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>not harrison ford little young play president reach point look phone akin action prime time bathroom break cinema mediocre good structure plot complete mess rewrite bunch time anthony mackie good 80 script fault poor job harrison ford include expect not bad slop release lately come movie laugh bad laugh matter snooze f harrison ford little young play president reach point look phone akin action prime time bathroom break cinema mediocre good structure plot complete mess rewrite bunch time anthony mackie good 80 script fault poor job harrison ford include expect bad slop release lately come laugh bad laugh matter snooze f harrison ford little young play president reach point look phone akin action prime time bathroom break cinema mediocre good structure plot complete mess rewrite bunch time anthony mackie good 80 script fault poor job harrison ford include expect bad slop release lately come laugh bad laugh matter snooze f</t>
+          <t>not harrison ford little young play president reach point look phone akin action prime time bathroom break cinema mediocre good structure plot complete mess rewrite bunch time anthony mackie good 80 script fault poor job harrison ford include expect not bad slop release lately come movie laugh bad laugh matter snooze f harrison ford little young play president reach point look phone akin action prime time bathroom break cinema mediocre good structure plot complete mess rewrite bunch time anthony mackie good 80 script fault poor job harrison ford include expect bad slop release lately come laugh bad laugh matter snooze f [SEP] ENTLBL_ORG ENTTXT_ford ENTLBL_PERSON ENTTXT_anthony_mackie</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5712,20 +4374,10 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5749,12 +4401,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>chance save galaxy twice sequel divisive fan people like decide rewatch opinion change like 2 2017   great soundtrack kick lot ass hear song acting cast pretty damn good issue writing like new addition cast kurt russell ego pom klementieff mantis sylvester stallone stakar ogor standout yondu udonta nice redemption arc help guardian stop villain good line dialogue father boy daddy death yondu emotional heartbreaking moment cinematic emotional wreck honor death finally action sequence lot fun 2 2017   team like constantly argue like dumb child humor land awkward listen thing baby groot annoying people argument cute feel nebula redemption arc ve good feel force narrative lot line delivery stiff angry villain underwhelming sovereign people forgettable barely beg question place taserface dumb cinematic ass beat easily finally kurt russell ego reveal main villain plot twist tell kill million star lord sibling mother reason choose team dad despite tell ego trust look stupid 2 2017 bad mcu big disappointment cinematic want original instead</t>
+          <t>ENTLBL_PERSON ENTTXT_russell_ego ENTLBL_PERSON ENTTXT_kurt_russell_ego_reveal</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>chance save galaxy twice guardian galaxy 2014 big surprise people good movie cinematic sequel divisive fan people not like decide rewatch opinion change not like positive guardian galaxy vol 2 2017   great soundtrack kick lot ass hear song acting cast pretty damn good issue writing like new addition cast kurt russell ego pom klementieff mantis sylvester stallone stakar ogor standout yondu udonta get nice redemption arc help guardian stop villain good line dialogue father boy not daddy death yondu emotional heartbreaking moment cinematic emotional wreck watch honor death finally action sequence lot fun negative guardian galaxy vol 2 2017   team not like constantly argue like dumb child humor not land awkward watch listen thing baby groot annoying people argument cute not feel nebula go redemption arc ve good feel force narrative lot line delivery stiff angry villain underwhelming sovereign people forgettable barely beg question place taserface dumb cinematic get ass beat easily finally kurt russell ego reveal main villain plot twist tell kill million star lord sibling mother reason choose team dad despite tell ego not trust make look stupid overall guardian galaxy vol 2 2017 bad movie mcu big disappointment cinematic make want original instead chance save galaxy twice guardian galaxy 2014 big surprise people good cinematic sequel divisive fan people like decide rewatch opinion change like positive guardian galaxy vol 2 2017   great soundtrack kick lot ass hear song acting cast pretty damn good issue writing like new addition cast kurt russell ego pom klementieff mantis sylvester stallone stakar ogor standout yondu udonta nice redemption arc help guardian stop villain good line dialogue father boy daddy death yondu emotional heartbreaking moment cinematic emotional wreck honor death finally action sequence lot fun negative guardian galaxy vol 2 2017   team like constantly argue like dumb child humor land awkward listen thing baby groot annoying people argument cute feel nebula redemption arc ve good feel force narrative lot line delivery stiff angry villain underwhelming sovereign people forgettable barely beg question place taserface dumb cinematic ass beat easily finally kurt russell ego reveal main villain plot twist tell kill million star lord sibling mother reason choose team dad despite tell ego trust look stupid overall guardian galaxy vol 2 2017 bad mcu big disappointment cinematic want original instead chance save galaxy twice sequel divisive fan people like decide rewatch opinion change like 2 2017   great soundtrack kick lot ass hear song acting cast pretty damn good issue writing like new addition cast kurt russell ego pom klementieff mantis sylvester stallone stakar ogor standout yondu udonta nice redemption arc help guardian stop villain good line dialogue father boy daddy death yondu emotional heartbreaking moment cinematic emotional wreck honor death finally action sequence lot fun 2 2017   team like constantly argue like dumb child humor land awkward listen thing baby groot annoying people argument cute feel nebula redemption arc ve good feel force narrative lot line delivery stiff angry villain underwhelming sovereign people forgettable barely beg question place taserface dumb cinematic ass beat easily finally kurt russell ego reveal main villain plot twist tell kill million star lord sibling mother reason choose team dad despite tell ego trust look stupid 2 2017 bad mcu big disappointment cinematic want original instead</t>
+          <t>chance save galaxy twice guardian galaxy 2014 big surprise people good movie cinematic sequel divisive fan people not like decide rewatch opinion change not like positive guardian galaxy vol 2 2017   great soundtrack kick lot ass hear song acting cast pretty damn good issue writing like new addition cast kurt russell ego pom klementieff mantis sylvester stallone stakar ogor standout yondu udonta get nice redemption arc help guardian stop villain good line dialogue father boy not daddy death yondu emotional heartbreaking moment cinematic emotional wreck watch honor death finally action sequence lot fun negative guardian galaxy vol 2 2017   team not like constantly argue like dumb child humor not land awkward watch listen thing baby groot annoying people argument cute not feel nebula go redemption arc ve good feel force narrative lot line delivery stiff angry villain underwhelming sovereign people forgettable barely beg question place taserface dumb cinematic get ass beat easily finally kurt russell ego reveal main villain plot twist tell kill million star lord sibling mother reason choose team dad despite tell ego not trust make look stupid overall guardian galaxy vol 2 2017 bad movie mcu big disappointment cinematic make want original instead chance save galaxy twice guardian galaxy 2014 big surprise people good cinematic sequel divisive fan people like decide rewatch opinion change like positive guardian galaxy vol 2 2017   great soundtrack kick lot ass hear song acting cast pretty damn good issue writing like new addition cast kurt russell ego pom klementieff mantis sylvester stallone stakar ogor standout yondu udonta nice redemption arc help guardian stop villain good line dialogue father boy daddy death yondu emotional heartbreaking moment cinematic emotional wreck honor death finally action sequence lot fun negative guardian galaxy vol 2 2017   team like constantly argue like dumb child humor land awkward listen thing baby groot annoying people argument cute feel nebula redemption arc ve good feel force narrative lot line delivery stiff angry villain underwhelming sovereign people forgettable barely beg question place taserface dumb cinematic ass beat easily finally kurt russell ego reveal main villain plot twist tell kill million star lord sibling mother reason choose team dad despite tell ego trust look stupid overall guardian galaxy vol 2 2017 bad mcu big disappointment cinematic want original instead [SEP] ENTLBL_PERSON ENTTXT_russell_ego ENTLBL_PERSON ENTTXT_kurt_russell_ego_reveal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5769,20 +4421,10 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -5804,14 +4446,10 @@
           <t>unique direction real 2 set plot bar come great fight unique direction team unique direction real 2 set plot bar come great fight unique direction team</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>unique direction real 2 set plot bar come</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>unique direction real 2 set plot bar come great fight unique direction team unique direction real 2 set plot bar come great fight unique direction team unique direction real 2 set plot bar come</t>
+          <t>unique direction real 2 set plot bar come great fight unique direction team unique direction real 2 set plot bar come great fight unique direction team [SEP]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5826,20 +4464,10 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -5861,14 +4489,10 @@
           <t>good thing computer generate imagery honestly not know get rating 4 imdb terrible original movie well term act coherence jump thing make sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original movie good thing computer generate imagery honestly know rating 4 imdb terrible original term act coherence jump thing sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>good thing computer generate imagery honestly know rating 4 imdb terrible original term act coherence jump thing sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>good thing computer generate imagery honestly not know get rating 4 imdb terrible original movie well term act coherence jump thing make sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original movie good thing computer generate imagery honestly know rating 4 imdb terrible original term act coherence jump thing sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original good thing computer generate imagery honestly know rating 4 imdb terrible original term act coherence jump thing sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original</t>
+          <t>good thing computer generate imagery honestly not know get rating 4 imdb terrible original movie well term act coherence jump thing make sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original movie good thing computer generate imagery honestly know rating 4 imdb terrible original term act coherence jump thing sense feel like rush little time leave audience unable enjoy plot connection acting horrible enjoy original [SEP]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5883,20 +4507,10 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -5920,12 +4534,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>far enjoyable d lead believe m particularly strong fan select certainly follow disney series 2 hour plenty humour way bridge grow hero young generation hand powerful superhero misunderstood hug company rare change feel bit long explore point glossed carol clearly wrestle lose memory bury emotion need companionship reconciliation monica definitely detail skrull need kree think annihilator end day theatre enjoy look cinema right</t>
+          <t>ENTLBL_PERSON ENTTXT_generation_brie ENTLBL_PERSON ENTTXT_nick_fury ENTLBL_PERSON ENTTXT_monica ENTLBL_PERSON ENTTXT_nick_fury_point_care_captain ENTLBL_ORG ENTTXT_kree</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>far enjoyable d lead believe not m particularly strong fan see select film certainly follow disney series arm minor background knowledge existence miss surprisingly easy follow contrast dr strange multiverse madness previous see   2 hour plenty humour way bridge grow hero young generation brie larson portray captain perfectly hand powerful superhero misunderstood hug company nick fury say point care captain grief rare change feel bit long explore point glossed carol clearly wrestle lose memory bury emotion need companionship reconciliation monica definitely detail skrull say not need kree think annihilator end day theatre enjoy look cinema right far enjoyable d lead believe m particularly strong fan select certainly follow disney series arm minor background knowledge existence miss surprisingly easy follow contrast dr strange multiverse madness previous   2 hour plenty humour way bridge grow hero young generation brie larson portray captain perfectly hand powerful superhero misunderstood hug company nick fury point care captain grief rare change feel bit long explore point glossed carol clearly wrestle lose memory bury emotion need companionship reconciliation monica definitely detail skrull need kree think annihilator end day theatre enjoy look cinema right far enjoyable d lead believe m particularly strong fan select certainly follow disney series 2 hour plenty humour way bridge grow hero young generation hand powerful superhero misunderstood hug company rare change feel bit long explore point glossed carol clearly wrestle lose memory bury emotion need companionship reconciliation monica definitely detail skrull need kree think annihilator end day theatre enjoy look cinema right</t>
+          <t>far enjoyable d lead believe not m particularly strong fan see select film certainly follow disney series arm minor background knowledge existence miss surprisingly easy follow contrast dr strange multiverse madness previous see   2 hour plenty humour way bridge grow hero young generation brie larson portray captain perfectly hand powerful superhero misunderstood hug company nick fury say point care captain grief rare change feel bit long explore point glossed carol clearly wrestle lose memory bury emotion need companionship reconciliation monica definitely detail skrull say not need kree think annihilator end day theatre enjoy look cinema right far enjoyable d lead believe m particularly strong fan select certainly follow disney series arm minor background knowledge existence miss surprisingly easy follow contrast dr strange multiverse madness previous   2 hour plenty humour way bridge grow hero young generation brie larson portray captain perfectly hand powerful superhero misunderstood hug company nick fury point care captain grief rare change feel bit long explore point glossed carol clearly wrestle lose memory bury emotion need companionship reconciliation monica definitely detail skrull need kree think annihilator end day theatre enjoy look cinema right [SEP] ENTLBL_PERSON ENTTXT_generation_brie ENTLBL_PERSON ENTTXT_nick_fury ENTLBL_PERSON ENTTXT_monica ENTLBL_PERSON ENTTXT_nick_fury_point_care_captain ENTLBL_ORG ENTTXT_kree</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5940,20 +4554,10 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -5977,12 +4581,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>tony stark billionaire industrialistengineer work am3rcn military industrial complex purpose save am3rcn r3gm3 people evil force 1st afghan 2nd russian 3rd pakistani portray villain bn ld3n gddf stand am3rcn bullying mention z0nt scamfraud wr 0n t3rr0r mention sense whatsoever maker want am3rcn r3gm3 liberator reality oppressor large portion am3rcn r3gm3s economy dependent military industrial complex engage endless war</t>
+          <t>ENTLBL_ORG ENTTXT_propaganda_iron_franchise_collection_perfectly_serve ENTLBL_PERSON ENTTXT_tony_stark ENTLBL_PERSON ENTTXT_am3rcn ENTLBL_PERSON ENTTXT_ld3n_gddf ENTLBL_PERSON ENTTXT_am3rcn_bullying ENTLBL_PERSON ENTTXT_z0nt ENTLBL_PERSON ENTTXT_james_rhode_iron ENTLBL_PERSON ENTTXT_ld3n</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>propaganda iron franchise collection perfectly serve imperial narrative am3rcn r3gm3 tony stark billionaire industrialistengineer work am3rcn military industrial complex purpose save am3rcn r3gm3 people call evil force iron bear afghanistan 1st afghan 2nd russian 3rd pakistani portray villain name bn ld3n gddf stand am3rcn bullying mention call z0nt scamfraud wr 0n t3rr0r mention colonel james rhode iron suit visit small sewing factory pakistan woman fully cover suddenly escape place see thank liberate not sense whatsoever maker want am3rcn r3gm3 liberator reality oppressor large portion am3rcn r3gm3s economy dependent military industrial complex engage endless war propaganda iron franchise collection perfectly serve imperial narrative am3rcn r3gm3 tony stark billionaire industrialistengineer work am3rcn military industrial complex purpose save am3rcn r3gm3 people evil force iron bear afghanistan 1st afghan 2nd russian 3rd pakistani portray villain bn ld3n gddf stand am3rcn bullying mention z0nt scamfraud wr 0n t3rr0r mention colonel james rhode iron suit visit small sewing factory pakistan woman fully cover suddenly escape place thank liberate sense whatsoever maker want am3rcn r3gm3 liberator reality oppressor large portion am3rcn r3gm3s economy dependent military industrial complex engage endless war tony stark billionaire industrialistengineer work am3rcn military industrial complex purpose save am3rcn r3gm3 people evil force 1st afghan 2nd russian 3rd pakistani portray villain bn ld3n gddf stand am3rcn bullying mention z0nt scamfraud wr 0n t3rr0r mention sense whatsoever maker want am3rcn r3gm3 liberator reality oppressor large portion am3rcn r3gm3s economy dependent military industrial complex engage endless war</t>
+          <t>propaganda iron franchise collection perfectly serve imperial narrative am3rcn r3gm3 tony stark billionaire industrialistengineer work am3rcn military industrial complex purpose save am3rcn r3gm3 people call evil force iron bear afghanistan 1st afghan 2nd russian 3rd pakistani portray villain name bn ld3n gddf stand am3rcn bullying mention call z0nt scamfraud wr 0n t3rr0r mention colonel james rhode iron suit visit small sewing factory pakistan woman fully cover suddenly escape place see thank liberate not sense whatsoever maker want am3rcn r3gm3 liberator reality oppressor large portion am3rcn r3gm3s economy dependent military industrial complex engage endless war propaganda iron franchise collection perfectly serve imperial narrative am3rcn r3gm3 tony stark billionaire industrialistengineer work am3rcn military industrial complex purpose save am3rcn r3gm3 people evil force iron bear afghanistan 1st afghan 2nd russian 3rd pakistani portray villain bn ld3n gddf stand am3rcn bullying mention z0nt scamfraud wr 0n t3rr0r mention colonel james rhode iron suit visit small sewing factory pakistan woman fully cover suddenly escape place thank liberate sense whatsoever maker want am3rcn r3gm3 liberator reality oppressor large portion am3rcn r3gm3s economy dependent military industrial complex engage endless war [SEP] ENTLBL_ORG ENTTXT_propaganda_iron_franchise_collection_perfectly_serve ENTLBL_PERSON ENTTXT_tony_stark ENTLBL_PERSON ENTTXT_am3rcn ENTLBL_PERSON ENTTXT_ld3n_gddf ENTLBL_PERSON ENTTXT_am3rcn_bullying ENTLBL_PERSON ENTTXT_z0nt ENTLBL_PERSON ENTTXT_james_rhode_iron ENTLBL_PERSON ENTTXT_ld3n</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5992,25 +4596,15 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>NEGATIVE</t>
+          <t>POSITIVE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -6034,12 +4628,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>comic relief guess expect comic book company think acting par good instance poor relationship obey extend law physics inexcusable ill try precisely explain sentiment 1 logic aircraft carrier fly runway ship supposedly capable fly possible ship like fly possible flying craft need runway scientist review script hand 2 scant liner robert downey jrs annoying guess addadhd try appeal multitude addadhd fan screen need dr bannerhulk useknowledge gain hand wave supposedly touch sensitive screen mr downey obsess wave hand enjoy samuel jackson respond lame navigator excuse navigation system reinitialize sun left genuine moment mediocrity probably impact title earning enthused catch sequel maybe worth netflix video store rental theater ticket</t>
+          <t>ENTLBL_PERSON ENTTXT_robert_downey_jrs ENTLBL_PERSON ENTTXT_samuel_jackson</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>comic relief guess expect not comic book company think acting par good instance poor relationship obey extend law physics inexcusable ill try precisely explain sentiment 1 logic have aircraft carrier fly runway ship supposedly capable fly possible ship like fly not possible flying craft not need runway scientist review script hand 2 scant liner robert downey jrs annoying well guess addadhd try appeal multitude addadhd fan 3 hand wave computer screen remind bad attempt impress viewer occur minority report hand wave meaningful minimal screen need dr bannerhulk get useknowledge gain hand wave supposedly touch sensitive screen mr downey obsess wave hand enjoy samuel jackson respond lame navigator excuse navigation system reinitialize say sun left genuine moment expect superior plot complexity thor sadly disappoint rehash independence style special effect lame alien invader mediocrity probably not impact title earning will not enthused catch sequel maybe worth netflix video store rental theater ticket comic relief guess expect comic book company think acting par good instance poor relationship obey extend law physics inexcusable ill try precisely explain sentiment 1 logic aircraft carrier fly runway ship supposedly capable fly possible ship like fly possible flying craft need runway scientist review script hand 2 scant liner robert downey jrs annoying guess addadhd try appeal multitude addadhd fan 3 hand wave computer screen remind bad attempt impress viewer occur minority report hand wave meaningful minimal screen need dr bannerhulk useknowledge gain hand wave supposedly touch sensitive screen mr downey obsess wave hand enjoy samuel jackson respond lame navigator excuse navigation system reinitialize sun left genuine moment expect superior plot complexity thor sadly disappoint rehash independence style special effect lame alien invader mediocrity probably impact title earning enthused catch sequel maybe worth netflix video store rental theater ticket comic relief guess expect comic book company think acting par good instance poor relationship obey extend law physics inexcusable ill try precisely explain sentiment 1 logic aircraft carrier fly runway ship supposedly capable fly possible ship like fly possible flying craft need runway scientist review script hand 2 scant liner robert downey jrs annoying guess addadhd try appeal multitude addadhd fan screen need dr bannerhulk useknowledge gain hand wave supposedly touch sensitive screen mr downey obsess wave hand enjoy samuel jackson respond lame navigator excuse navigation system reinitialize sun left genuine moment mediocrity probably impact title earning enthused catch sequel maybe worth netflix video store rental theater ticket</t>
+          <t>comic relief guess expect not comic book company think acting par good instance poor relationship obey extend law physics inexcusable ill try precisely explain sentiment 1 logic have aircraft carrier fly runway ship supposedly capable fly possible ship like fly not possible flying craft not need runway scientist review script hand 2 scant liner robert downey jrs annoying well guess addadhd try appeal multitude addadhd fan 3 hand wave computer screen remind bad attempt impress viewer occur minority report hand wave meaningful minimal screen need dr bannerhulk get useknowledge gain hand wave supposedly touch sensitive screen mr downey obsess wave hand enjoy samuel jackson respond lame navigator excuse navigation system reinitialize say sun left genuine moment expect superior plot complexity thor sadly disappoint rehash independence style special effect lame alien invader mediocrity probably not impact title earning will not enthused catch sequel maybe worth netflix video store rental theater ticket comic relief guess expect comic book company think acting par good instance poor relationship obey extend law physics inexcusable ill try precisely explain sentiment 1 logic aircraft carrier fly runway ship supposedly capable fly possible ship like fly possible flying craft need runway scientist review script hand 2 scant liner robert downey jrs annoying guess addadhd try appeal multitude addadhd fan 3 hand wave computer screen remind bad attempt impress viewer occur minority report hand wave meaningful minimal screen need dr bannerhulk useknowledge gain hand wave supposedly touch sensitive screen mr downey obsess wave hand enjoy samuel jackson respond lame navigator excuse navigation system reinitialize sun left genuine moment expect superior plot complexity thor sadly disappoint rehash independence style special effect lame alien invader mediocrity probably impact title earning enthused catch sequel maybe worth netflix video store rental theater ticket [SEP] ENTLBL_PERSON ENTTXT_robert_downey_jrs ENTLBL_PERSON ENTTXT_samuel_jackson</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6054,20 +4648,10 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6091,12 +4675,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>shallow tasty horsoderve tray mean line invisible showcase new underdeveloped super powerful little explanation action active diverse zero central white actor diverse matter good craft easy follow woman karen especially kid repeatedly confuse good beat foe save day power proficient highly train superhero confuse beginning actual development obvious goal oh goal evil villain villain misunderstood woman king know rule communicate powerful weapon eye toy advance confusing line eventually pointless final revelation little material beginning end jump plot point lose important cute factor attempt explore deep meaning actually visually explain event develop empathy nick furry add decoration real contribution good action event funny line fake emotion bad camera cut jump nonsense people enjoy leave disappointed shallow pointless journey</t>
+          <t>ENTLBL_PERSON ENTTXT_nick_furry</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>shallow tasty horsoderve tray mean line invisible showcase new underdeveloped super powerful little explanation film action active diverse zero central white actor diverse matter good craft easy follow not woman karen especially kid repeatedly say confuse good beat foe save day show power proficient highly train superhero confuse beginning actual development obvious goal show oh say goal show evil villain not villain misunderstood woman king not know rule communicate powerful weapon eye toy advance confusing line eventually pointless final revelation little material beginning end jump plot point lose important cute factor attempt explore deep meaning actually visually explain event develop empathy nick furry add decoration real contribution good action event funny line fake emotion bad camera cut jump nonsense people enjoy leave disappointed shallow pointless journey shallow tasty horsoderve tray mean line invisible showcase new underdeveloped super powerful little explanation action active diverse zero central white actor diverse matter good craft easy follow woman karen especially kid repeatedly confuse good beat foe save day power proficient highly train superhero confuse beginning actual development obvious goal oh goal evil villain villain misunderstood woman king know rule communicate powerful weapon eye toy advance confusing line eventually pointless final revelation little material beginning end jump plot point lose important cute factor attempt explore deep meaning actually visually explain event develop empathy nick furry add decoration real contribution good action event funny line fake emotion bad camera cut jump nonsense people enjoy leave disappointed shallow pointless journey shallow tasty horsoderve tray mean line invisible showcase new underdeveloped super powerful little explanation action active diverse zero central white actor diverse matter good craft easy follow woman karen especially kid repeatedly confuse good beat foe save day power proficient highly train superhero confuse beginning actual development obvious goal oh goal evil villain villain misunderstood woman king know rule communicate powerful weapon eye toy advance confusing line eventually pointless final revelation little material beginning end jump plot point lose important cute factor attempt explore deep meaning actually visually explain event develop empathy nick furry add decoration real contribution good action event funny line fake emotion bad camera cut jump nonsense people enjoy leave disappointed shallow pointless journey</t>
+          <t>shallow tasty horsoderve tray mean line invisible showcase new underdeveloped super powerful little explanation film action active diverse zero central white actor diverse matter good craft easy follow not woman karen especially kid repeatedly say confuse good beat foe save day show power proficient highly train superhero confuse beginning actual development obvious goal show oh say goal show evil villain not villain misunderstood woman king not know rule communicate powerful weapon eye toy advance confusing line eventually pointless final revelation little material beginning end jump plot point lose important cute factor attempt explore deep meaning actually visually explain event develop empathy nick furry add decoration real contribution good action event funny line fake emotion bad camera cut jump nonsense people enjoy leave disappointed shallow pointless journey shallow tasty horsoderve tray mean line invisible showcase new underdeveloped super powerful little explanation action active diverse zero central white actor diverse matter good craft easy follow woman karen especially kid repeatedly confuse good beat foe save day power proficient highly train superhero confuse beginning actual development obvious goal oh goal evil villain villain misunderstood woman king know rule communicate powerful weapon eye toy advance confusing line eventually pointless final revelation little material beginning end jump plot point lose important cute factor attempt explore deep meaning actually visually explain event develop empathy nick furry add decoration real contribution good action event funny line fake emotion bad camera cut jump nonsense people enjoy leave disappointed shallow pointless journey [SEP] ENTLBL_PERSON ENTTXT_nick_furry</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6111,20 +4695,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6146,14 +4720,10 @@
           <t>nope m love actor performance excellent expect plus great liner like beginning deadpool say 206 bone human body 207 watch polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd nope m love actor performance excellent expect plus great liner like beginning deadpool 206 bone human body 207 polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>nope m love actor performance excellent expect plus great liner like beginning deadpool 206 bone human body 207 polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>nope m love actor performance excellent expect plus great liner like beginning deadpool say 206 bone human body 207 watch polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd nope m love actor performance excellent expect plus great liner like beginning deadpool 206 bone human body 207 polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd nope m love actor performance excellent expect plus great liner like beginning deadpool 206 bone human body 207 polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd</t>
+          <t>nope m love actor performance excellent expect plus great liner like beginning deadpool say 206 bone human body 207 watch polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd nope m love actor performance excellent expect plus great liner like beginning deadpool 206 bone human body 207 polly ann funny audience expect profanity ok appropriate situation gratuitous like filler aside like   exercise adhd cinema nope m franchise evolve effort rehash old unnecessary dialogue swear ridiculous storyline grab dollar adhd crowd [SEP]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6168,20 +4738,10 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6203,14 +4763,10 @@
           <t>tired high school spiderman acting fine plot not bad m ridiculously tired wishy washy teenage angst pathetic high school spider see huge stretch movie spiderman infantile high school student grow hell start act like mature person stop make high school musical version spider tired high school spiderman acting fine plot bad m ridiculously tired wishy washy teenage angst pathetic high school spider huge stretch spiderman infantile high school student grow hell start act like mature person stop high school musical version spider</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>tired high school spiderman acting fine plot bad m ridiculously tired wishy washy teenage angst pathetic high school spider huge stretch spiderman infantile high school student grow hell start act like mature person stop high school musical version spider</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>tired high school spiderman acting fine plot not bad m ridiculously tired wishy washy teenage angst pathetic high school spider see huge stretch movie spiderman infantile high school student grow hell start act like mature person stop make high school musical version spider tired high school spiderman acting fine plot bad m ridiculously tired wishy washy teenage angst pathetic high school spider huge stretch spiderman infantile high school student grow hell start act like mature person stop high school musical version spider tired high school spiderman acting fine plot bad m ridiculously tired wishy washy teenage angst pathetic high school spider huge stretch spiderman infantile high school student grow hell start act like mature person stop high school musical version spider</t>
+          <t>tired high school spiderman acting fine plot not bad m ridiculously tired wishy washy teenage angst pathetic high school spider see huge stretch movie spiderman infantile high school student grow hell start act like mature person stop make high school musical version spider tired high school spiderman acting fine plot bad m ridiculously tired wishy washy teenage angst pathetic high school spider huge stretch spiderman infantile high school student grow hell start act like mature person stop high school musical version spider [SEP]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6225,20 +4781,10 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6260,14 +4806,10 @@
           <t>total abomination not pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set marvel reboot decade way forward guy captain america include upcoming new movie disney brain pivot make bucky new captain america late wish find good thing abomination unfortunately not bad bad minute disgusting plain piss zero star rating sweep razzie award total abomination pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set reboot decade way forward guy captain america include upcoming new disney brain pivot bucky new captain america late wish find good thing abomination unfortunately bad bad minute disgusting plain piss zero star rating sweep razzie award</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>total abomination pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set reboot decade way forward guy captain america include upcoming new disney brain pivot bucky new captain america late wish find good thing abomination unfortunately bad bad minute disgusting plain piss zero star rating sweep razzie award</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>total abomination not pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set marvel reboot decade way forward guy captain america include upcoming new movie disney brain pivot make bucky new captain america late wish find good thing abomination unfortunately not bad bad minute disgusting plain piss zero star rating sweep razzie award total abomination pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set reboot decade way forward guy captain america include upcoming new disney brain pivot bucky new captain america late wish find good thing abomination unfortunately bad bad minute disgusting plain piss zero star rating sweep razzie award total abomination pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set reboot decade way forward guy captain america include upcoming new disney brain pivot bucky new captain america late wish find good thing abomination unfortunately bad bad minute disgusting plain piss zero star rating sweep razzie award</t>
+          <t>total abomination not pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set marvel reboot decade way forward guy captain america include upcoming new movie disney brain pivot make bucky new captain america late wish find good thing abomination unfortunately not bad bad minute disgusting plain piss zero star rating sweep razzie award total abomination pardon pun terribly stupid fight ridiculous acting horrible absolutely true blacktain america bad set reboot decade way forward guy captain america include upcoming new disney brain pivot bucky new captain america late wish find good thing abomination unfortunately bad bad minute disgusting plain piss zero star rating sweep razzie award [SEP]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6282,20 +4824,10 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6317,14 +4849,10 @@
           <t>like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen not compute waswell write nicely direct not like villain involve villain america go home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen compute waswell write nicely direct like villain involve villain america home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen compute waswell write nicely direct like villain involve villain america home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen not compute waswell write nicely direct not like villain involve villain america go home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen compute waswell write nicely direct like villain involve villain america home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen compute waswell write nicely direct like villain involve villain america home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol</t>
+          <t>like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen not compute waswell write nicely direct not like villain involve villain america go home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol like idea wakanda powerful sense ancient time suppose hi tech country rule world africa instead hide   wakanda mention enemy worry absolutely sense 10x advanced world big flaw comic_strip poor country africa theirs hi tech civilization dress like cavemen compute waswell write nicely direct like villain involve villain america home retake wakanda lol hilarious   pretty terrible write like writer include tiny america connection relevance audience america lol [SEP]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6339,20 +4867,10 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6374,14 +4892,10 @@
           <t>let play count cliche seriously believe review year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party keep oh drunk people funny know funny destroy stuff yeah let face one mortality not tony stark die get veiny stuff bad industrialist expose love interest hide big secret bad guy not shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve see time boring point let play count cliche seriously believe review year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party oh drunk people funny know funny destroy stuff yeah let face mortality tony stark die veiny stuff bad industrialist expose love interest hide big secret bad guy shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve time boring point</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>let play count cliche seriously believe review   year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party oh drunk people funny know funny destroy stuff yeah let face mortality tony stark die veiny stuff bad industrialist expose love interest hide big secret bad guy shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve time boring point</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>let play count cliche seriously believe review year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party keep oh drunk people funny know funny destroy stuff yeah let face one mortality not tony stark die get veiny stuff bad industrialist expose love interest hide big secret bad guy not shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve see time boring point let play count cliche seriously believe review year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party oh drunk people funny know funny destroy stuff yeah let face mortality tony stark die veiny stuff bad industrialist expose love interest hide big secret bad guy shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve time boring point let play count cliche seriously believe review   year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party oh drunk people funny know funny destroy stuff yeah let face mortality tony stark die veiny stuff bad industrialist expose love interest hide big secret bad guy shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve time boring point</t>
+          <t>let play count cliche seriously believe review year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party keep oh drunk people funny know funny destroy stuff yeah let face one mortality not tony stark die get veiny stuff bad industrialist expose love interest hide big secret bad guy not shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve see time boring point let play count cliche seriously believe review year wow northpointmjm ah sound like ass let beg differ review pretty check mess drunk party oh drunk people funny know funny destroy stuff yeah let face mortality tony stark die veiny stuff bad industrialist expose love interest hide big secret bad guy shoot straight 90 pound supposedly hot chick kick ass guy time size etc ve time boring point [SEP]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6396,20 +4910,10 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6433,12 +4937,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>trash excess effect completely boring spend bad buck entire life buy ticket theater handle trash sorry lover suck begin end buy ticket reference 87 average imdb meter publish completely disappointing ill care trust meter actually imdb problem perfect example human dumb love insult tell job geek think business seek profound ll regret sure considerable huge war explosion sound effect complete enemy cinema effect use good like avatar time guess way business earn lot money ironic start believe human rule submit deny love example</t>
+          <t>ENTLBL_ORG ENTTXT_disappointing_ill_care_trust_meter</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>trash excess effect completely boring spend bad buck entire life buy ticket theater not handle trash sorry lover suck begin end buy ticket take reference 87 average imdb meter publish completely disappointing ill care trust meter actually imdb problem perfect example human dumb love insult tell job geek think business seek profound story ll regret sure considerable huge war explosion sound effect complete enemy cinema effect good like avatar time guess way make business earn lot money ironic watch start believe human rule submit deny love example trash excess effect completely boring spend bad buck entire life buy ticket theater handle trash sorry lover suck begin end buy ticket reference 87 average imdb meter publish completely disappointing ill care trust meter actually imdb problem perfect example human dumb love insult tell job geek think business seek profound ll regret sure considerable huge war explosion sound effect complete enemy cinema effect use good like avatar time guess way business earn lot money ironic start believe human rule submit deny love example trash excess effect completely boring spend bad buck entire life buy ticket theater handle trash sorry lover suck begin end buy ticket reference 87 average imdb meter publish completely disappointing ill care trust meter actually imdb problem perfect example human dumb love insult tell job geek think business seek profound ll regret sure considerable huge war explosion sound effect complete enemy cinema effect use good like avatar time guess way business earn lot money ironic start believe human rule submit deny love example</t>
+          <t>trash excess effect completely boring spend bad buck entire life buy ticket theater not handle trash sorry lover suck begin end buy ticket take reference 87 average imdb meter publish completely disappointing ill care trust meter actually imdb problem perfect example human dumb love insult tell job geek think business seek profound story ll regret sure considerable huge war explosion sound effect complete enemy cinema effect good like avatar time guess way make business earn lot money ironic watch start believe human rule submit deny love example trash excess effect completely boring spend bad buck entire life buy ticket theater handle trash sorry lover suck begin end buy ticket reference 87 average imdb meter publish completely disappointing ill care trust meter actually imdb problem perfect example human dumb love insult tell job geek think business seek profound ll regret sure considerable huge war explosion sound effect complete enemy cinema effect use good like avatar time guess way business earn lot money ironic start believe human rule submit deny love example [SEP] ENTLBL_ORG ENTTXT_disappointing_ill_care_trust_meter</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6453,20 +4957,10 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6488,14 +4982,10 @@
           <t>bla get silly interested anymore lose interest 20 minute bye bye silly verse bla silly interested anymore lose interest 20 minute bye bye silly verse</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>bla silly interested anymore lose interest 20 minute bye bye silly verse</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>bla get silly interested anymore lose interest 20 minute bye bye silly verse bla silly interested anymore lose interest 20 minute bye bye silly verse bla silly interested anymore lose interest 20 minute bye bye silly verse</t>
+          <t>bla get silly interested anymore lose interest 20 minute bye bye silly verse bla silly interested anymore lose interest 20 minute bye bye silly verse [SEP]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6510,20 +5000,10 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6545,14 +5025,10 @@
           <t>hype live hype contain spoiler safe hard 10 maybe m give 10 excited go come maybe drop 9 tick box action right thing happen personally not expect set future film get real hype future film amazing young old nerd enjoy entire family highly recommend hype live hype contain spoiler safe hard 10 maybe m 10 excited come maybe drop 9 tick box action right thing happen personally expect set future real hype future amazing young old nerd enjoy entire family highly recommend</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>hype live hype contain spoiler safe hard 10 maybe m 10 excited come maybe drop 9 tick box action right thing happen personally expect set future real hype future amazing young old nerd enjoy entire family highly recommend</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>hype live hype contain spoiler safe hard 10 maybe m give 10 excited go come maybe drop 9 tick box action right thing happen personally not expect set future film get real hype future film amazing young old nerd enjoy entire family highly recommend hype live hype contain spoiler safe hard 10 maybe m 10 excited come maybe drop 9 tick box action right thing happen personally expect set future real hype future amazing young old nerd enjoy entire family highly recommend hype live hype contain spoiler safe hard 10 maybe m 10 excited come maybe drop 9 tick box action right thing happen personally expect set future real hype future amazing young old nerd enjoy entire family highly recommend</t>
+          <t>hype live hype contain spoiler safe hard 10 maybe m give 10 excited go come maybe drop 9 tick box action right thing happen personally not expect set future film get real hype future film amazing young old nerd enjoy entire family highly recommend hype live hype contain spoiler safe hard 10 maybe m 10 excited come maybe drop 9 tick box action right thing happen personally expect set future real hype future amazing young old nerd enjoy entire family highly recommend [SEP]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6567,22 +5043,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
         </is>
       </c>
     </row>
@@ -6602,14 +5068,10 @@
           <t>hate yawn good way good know little try include detail movie review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind watch bad guy bad guy matrix boring poorly direct m sure great m go sequel m sure like trick pony good thing far movie spider xman boring make mad want force like not sleeper avoid hate yawn good way good know little try include detail review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind bad guy bad guy matrix boring poorly direct m sure great m sequel m sure like trick pony good thing far spider xman boring mad want force like sleeper avoid</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>hate yawn good way good know little try include detail review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind poorly direct m sure great m sequel m sure like trick pony good thing far spider xman boring mad want force like sleeper avoid</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>hate yawn good way good know little try include detail movie review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind watch bad guy bad guy matrix boring poorly direct m sure great m go sequel m sure like trick pony good thing far movie spider xman boring make mad want force like not sleeper avoid hate yawn good way good know little try include detail review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind bad guy bad guy matrix boring poorly direct m sure great m sequel m sure like trick pony good thing far spider xman boring mad want force like sleeper avoid hate yawn good way good know little try include detail review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind poorly direct m sure great m sequel m sure like trick pony good thing far spider xman boring mad want force like sleeper avoid</t>
+          <t>hate yawn good way good know little try include detail movie review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind watch bad guy bad guy matrix boring poorly direct m sure great m go sequel m sure like trick pony good thing far movie spider xman boring make mad want force like not sleeper avoid hate yawn good way good know little try include detail review suck m shy include detail andor spoiler superhero love set 40 love action love ummm 4 star soooooo bloody boring action quick kind lame lame goofy way super flat pop bore mind bad guy bad guy matrix boring poorly direct m sure great m sequel m sure like trick pony good thing far spider xman boring mad want force like sleeper avoid [SEP]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6624,20 +5086,10 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6661,12 +5113,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>way spoil know captain america gun fight explosion like michael bay premise american superman science lot experiment 1940 invent atom bomb etc scientist super soldier list option steve rogers cliche think emotion witty charming standard save day super hero enjoin use brain instead brawn scarce bland remember uncle ben scientist   lois lane female main tommy lee jones stereotypical colonel dialogue fault   good friend lot development actually think anysteve roger stay exactly reach profound understanding fight lot blow thing m joke 70 80 explosion gun fight know title</t>
+          <t>ENTLBL_PERSON ENTTXT_steve ENTLBL_PERSON ENTTXT_michael_bay ENTLBL_PERSON ENTTXT_lois_lane ENTLBL_PERSON ENTTXT_tommy_lee_jones ENTLBL_PERSON ENTTXT_steve_rogers_cliche ENTLBL_PERSON ENTTXT_roger</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>not bad thor steve rogers bit cliche 1940 cliche common way spoil know captain america gun fight explosion like michael bay premise american superman science lot experiment 1940 invent atom bomb etc scientist make super soldier list option steve rogers not cliche not think not emotion witty charming standard save day super heroi enjoin brain instead brawn scarce bland not remember name uncle ben scientist lois lane female main tommy lee jones stereotypical colonel dialogue fault   good friend lot development actually think not anysteve roger stay exactly not reach profound understanding fight lot blow thing m joke 70 80 explosion gun fight set like thor know title bad thor steve rogers bit cliche 1940 cliche common way spoil know captain america gun fight explosion like michael bay premise american superman science lot experiment 1940 invent atom bomb etc scientist super soldier list option steve rogers cliche think emotion witty charming standard save day super heroi enjoin use brain instead brawn scarce bland remember uncle ben scientist lois lane female main tommy lee jones stereotypical colonel dialogue fault   good friend lot development actually think anysteve roger stay exactly reach profound understanding fight lot blow thing m joke 70 80 explosion gun fight set like thor know title way spoil know captain america gun fight explosion like michael bay premise american superman science lot experiment 1940 invent atom bomb etc scientist super soldier list option steve rogers cliche think emotion witty charming standard save day super hero enjoin use brain instead brawn scarce bland remember uncle ben scientist   lois lane female main tommy lee jones stereotypical colonel dialogue fault   good friend lot development actually think anysteve roger stay exactly reach profound understanding fight lot blow thing m joke 70 80 explosion gun fight know title</t>
+          <t>not bad thor steve rogers bit cliche 1940 cliche common way spoil know captain america gun fight explosion like michael bay premise american superman science lot experiment 1940 invent atom bomb etc scientist make super soldier list option steve rogers not cliche not think not emotion witty charming standard save day super heroi enjoin brain instead brawn scarce bland not remember name uncle ben scientist lois lane female main tommy lee jones stereotypical colonel dialogue fault   good friend lot development actually think not anysteve roger stay exactly not reach profound understanding fight lot blow thing m joke 70 80 explosion gun fight set like thor know title bad thor steve rogers bit cliche 1940 cliche common way spoil know captain america gun fight explosion like michael bay premise american superman science lot experiment 1940 invent atom bomb etc scientist super soldier list option steve rogers cliche think emotion witty charming standard save day super heroi enjoin use brain instead brawn scarce bland remember uncle ben scientist lois lane female main tommy lee jones stereotypical colonel dialogue fault   good friend lot development actually think anysteve roger stay exactly reach profound understanding fight lot blow thing m joke 70 80 explosion gun fight set like thor know title [SEP] ENTLBL_PERSON ENTTXT_steve ENTLBL_PERSON ENTTXT_michael_bay ENTLBL_PERSON ENTTXT_lois_lane ENTLBL_PERSON ENTTXT_tommy_lee_jones ENTLBL_PERSON ENTTXT_steve_rogers_cliche ENTLBL_PERSON ENTTXT_roger</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6681,20 +5133,10 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6716,14 +5158,10 @@
           <t>talk not listen naysayer solid not depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit well computer generate imagery need tad well not let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use talk listen naysayer solid depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit computer generate imagery need tad let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>talk listen naysayer solid depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit computer generate imagery need tad let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>talk not listen naysayer solid not depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit well computer generate imagery need tad well not let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use talk listen naysayer solid depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit computer generate imagery need tad let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use talk listen naysayer solid depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit computer generate imagery need tad let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use</t>
+          <t>talk not listen naysayer solid not depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit well computer generate imagery need tad well not let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use talk listen naysayer solid depend cameo action build pace element mystery maintain underlaying spy fiction element superhero refreshing believe actor specific role lot justice cinematic overall balanced way production design bit computer generate imagery need tad let good cohesive write conceive spark interest cinematic like romulus alien gargantuan mistake good use [SEP]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6738,20 +5176,10 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6775,12 +5203,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>wakanda expectation death chadwick boseman long poor feel unrealistic science fiction r p mr boseman feel wrong force accurate feel like forever finish bad acting help dialogue poor performance weak boring waste time save time money favor wakanda sequel believe rating pretty bad bad</t>
+          <t>ENTLBL_PERSON ENTTXT_wakanda_expectation ENTLBL_PERSON ENTTXT_chadwick_boseman</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>wakanda expectation death chadwick boseman long poor feel unrealistic science fiction r p mr boseman feel wrong force accurate feel like forever finish bad acting help dialogue poor performance weak boring waste time save time money favor not watch wakanda sequel not believe rating pretty bad bad movie wakanda expectation death chadwick boseman long poor feel unrealistic science fiction r p mr boseman feel wrong force accurate feel like forever finish bad acting help dialogue poor performance weak boring waste time save time money favor wakanda sequel believe rating pretty bad bad wakanda expectation death chadwick boseman long poor feel unrealistic science fiction r p mr boseman feel wrong force accurate feel like forever finish bad acting help dialogue poor performance weak boring waste time save time money favor wakanda sequel believe rating pretty bad bad</t>
+          <t>wakanda expectation death chadwick boseman long poor feel unrealistic science fiction r p mr boseman feel wrong force accurate feel like forever finish bad acting help dialogue poor performance weak boring waste time save time money favor not watch wakanda sequel not believe rating pretty bad bad movie wakanda expectation death chadwick boseman long poor feel unrealistic science fiction r p mr boseman feel wrong force accurate feel like forever finish bad acting help dialogue poor performance weak boring waste time save time money favor wakanda sequel believe rating pretty bad bad [SEP] ENTLBL_PERSON ENTTXT_wakanda_expectation ENTLBL_PERSON ENTTXT_chadwick_boseman</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6795,20 +5223,10 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6832,12 +5250,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>highly underrated theater opening weekend rewatche disneyi appreciate accomplish time able achieve lead actor spectacular journey grieve acceptance actor fantastic job feel genuine emotion shuris particular grow angela bassettwhat amazing performance queenaward worthy love underrated gem 2022</t>
+          <t>ENTLBL_PERSON ENTTXT_angela</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>highly underrated see theater opening weekend rewatche disneyi appreciate accomplish see time able achieve lead actor spectacular journey grieve acceptance actor fantastic job feel genuine emotion shuris particular grow angela bassettwhat amazing performance queenaward worthy love underrated gem 2022 highly underrated theater opening weekend rewatche disneyi appreciate accomplish time able achieve lead actor spectacular journey grieve acceptance actor fantastic job feel genuine emotion shuris particular grow angela bassettwhat amazing performance queenaward worthy love underrated gem 2022 highly underrated theater opening weekend rewatche disneyi appreciate accomplish time able achieve lead actor spectacular journey grieve acceptance actor fantastic job feel genuine emotion shuris particular grow angela bassettwhat amazing performance queenaward worthy love underrated gem 2022</t>
+          <t>highly underrated see theater opening weekend rewatche disneyi appreciate accomplish see time able achieve lead actor spectacular journey grieve acceptance actor fantastic job feel genuine emotion shuris particular grow angela bassettwhat amazing performance queenaward worthy love underrated gem 2022 highly underrated theater opening weekend rewatche disneyi appreciate accomplish time able achieve lead actor spectacular journey grieve acceptance actor fantastic job feel genuine emotion shuris particular grow angela bassettwhat amazing performance queenaward worthy love underrated gem 2022 [SEP] ENTLBL_PERSON ENTTXT_angela</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6852,20 +5270,10 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -6887,14 +5295,10 @@
           <t>disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity</t>
-        </is>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity</t>
+          <t>disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity disappointing end relieve end les mis want barricade fight liberty equality fraternity lost opportunity [SEP]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6909,20 +5313,10 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -6946,12 +5340,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>good great entertaining live predecessor miss wow factor producer decide essential vol 1 drax repeat joke twice repeatedly dance action baby groot minute racoon joke bit flat family issue discuss time yondu star lord ego drax gamora nebulaetc long yondu funeral   result fresh vivid vol 1</t>
+          <t>ENTLBL_PERSON ENTTXT_ego_drax_gamora</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>good great entertaining live predecessor miss wow factor producer decide essential vol 1 drax repeat joke twice repeatedly dance action baby groot minute racoon joke bit flat family issue discuss time yondu star lord ego drax gamora nebulaetc long yondu funeral   result fresh vivid vol 1 good great entertaining live predecessor miss wow factor producer decide essential vol 1 drax repeat joke twice repeatedly dance action baby groot minute racoon joke bit flat family issue discuss time yondu star lord ego drax gamora nebulaetc long yondu funeral   result fresh vivid vol 1 good great entertaining live predecessor miss wow factor producer decide essential vol 1 drax repeat joke twice repeatedly dance action baby groot minute racoon joke bit flat family issue discuss time yondu star lord ego drax gamora nebulaetc long yondu funeral   result fresh vivid vol 1</t>
+          <t>good great entertaining live predecessor miss wow factor producer decide essential vol 1 drax repeat joke twice repeatedly dance action baby groot minute racoon joke bit flat family issue discuss time yondu star lord ego drax gamora nebulaetc long yondu funeral   result fresh vivid vol 1 good great entertaining live predecessor miss wow factor producer decide essential vol 1 drax repeat joke twice repeatedly dance action baby groot minute racoon joke bit flat family issue discuss time yondu star lord ego drax gamora nebulaetc long yondu funeral   result fresh vivid vol 1 [SEP] ENTLBL_PERSON ENTTXT_ego_drax_gamora</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6966,20 +5360,10 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -7003,12 +5387,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>deserve crush shoe okay formulaic load old tripe feature boring cocksure dumb supposedly charming hero bless super power deserve bore death turgid hour special effect plot write postage stamp anybody think bit comedyexcept lame joke sign post mile away deserve punctuate ba dumb tish snare drum ant lousy idea lousy 2 hour life threat end   ant return bother</t>
+          <t>ENTLBL_PERSON ENTTXT_al</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>deserve crush shoe okay formulaic load old tripe feature boring cocksure dumb supposedly charming hero bless super power not deserve bore death turgid hour special effect plot write postage stamp iron green lantern et al anybody think bit comedyexcept lame joke sign post mile away deserve punctuate ba dumb tish snare drum ant lousy idea lousy 2 hour life threat end ant return not bother deserve crush shoe okay formulaic load old tripe feature boring cocksure dumb supposedly charming hero bless super power deserve bore death turgid hour special effect plot write postage stamp iron green lantern et al anybody think bit comedyexcept lame joke sign post mile away deserve punctuate ba dumb tish snare drum ant lousy idea lousy 2 hour life threat end ant return bother deserve crush shoe okay formulaic load old tripe feature boring cocksure dumb supposedly charming hero bless super power deserve bore death turgid hour special effect plot write postage stamp anybody think bit comedyexcept lame joke sign post mile away deserve punctuate ba dumb tish snare drum ant lousy idea lousy 2 hour life threat end   ant return bother</t>
+          <t>deserve crush shoe okay formulaic load old tripe feature boring cocksure dumb supposedly charming hero bless super power not deserve bore death turgid hour special effect plot write postage stamp iron green lantern et al anybody think bit comedyexcept lame joke sign post mile away deserve punctuate ba dumb tish snare drum ant lousy idea lousy 2 hour life threat end ant return not bother deserve crush shoe okay formulaic load old tripe feature boring cocksure dumb supposedly charming hero bless super power deserve bore death turgid hour special effect plot write postage stamp iron green lantern et al anybody think bit comedyexcept lame joke sign post mile away deserve punctuate ba dumb tish snare drum ant lousy idea lousy 2 hour life threat end ant return bother [SEP] ENTLBL_PERSON ENTTXT_al</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7023,20 +5407,10 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7058,14 +5432,10 @@
           <t>think go to well lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary one well get bad guardian galaxy expect alot get good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript not hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think think lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary bad guardian galaxy expect alot good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>think lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary bad guardian galaxy expect alot good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>think go to well lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary one well get bad guardian galaxy expect alot get good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript not hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think think lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary bad guardian galaxy expect alot good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think think lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary bad guardian galaxy expect alot good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think</t>
+          <t>think go to well lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary one well get bad guardian galaxy expect alot get good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript not hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think think lame summarise bad actor abit childish miss basic logic lame boring exaggerate long unnecessary bad guardian galaxy expect alot good moment watchable abit cute abit sad rarely funny silly laugh bad manuscript hope word great franchise 3 pretty bad unfortunately recommend big fan franchise worth 2 h 30 min rap franchise end think [SEP]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -7080,20 +5450,10 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7117,12 +5477,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>american miltary propoganda work start high school think captain america theatre brother dad history buff able enjoy captain america people like slow start superhero stuff time happen enjoy find willing rewatch especially brother grow realize military propoganda want enjoy plenty action mix ww2 imagine chris evans captain america great year role</t>
+          <t>ENTLBL_PERSON ENTTXT_dad_history ENTLBL_PERSON ENTTXT_buff ENTLBL_ORG ENTTXT_chris_evans_captain</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>american miltary propoganda work start watch movie high school think captain america one get theatre brother dad history buff able enjoy captain america people movie like slow start superhero stuff take time happen enjoy find willing rewatch especially brother grow realize military propoganda want enjoy plenty action mix ww2 not imagine chris evans captain america great see year role american miltary propoganda work start high school think captain america theatre brother dad history buff able enjoy captain america people like slow start superhero stuff time happen enjoy find willing rewatch especially brother grow realize military propoganda want enjoy plenty action mix ww2 imagine chris evans captain america great year role american miltary propoganda work start high school think captain america theatre brother dad history buff able enjoy captain america people like slow start superhero stuff time happen enjoy find willing rewatch especially brother grow realize military propoganda want enjoy plenty action mix ww2 imagine chris evans captain america great year role</t>
+          <t>american miltary propoganda work start watch movie high school think captain america one get theatre brother dad history buff able enjoy captain america people movie like slow start superhero stuff take time happen enjoy find willing rewatch especially brother grow realize military propoganda want enjoy plenty action mix ww2 not imagine chris evans captain america great see year role american miltary propoganda work start high school think captain america theatre brother dad history buff able enjoy captain america people like slow start superhero stuff time happen enjoy find willing rewatch especially brother grow realize military propoganda want enjoy plenty action mix ww2 imagine chris evans captain america great year role [SEP] ENTLBL_PERSON ENTTXT_dad_history ENTLBL_PERSON ENTTXT_buff ENTLBL_ORG ENTTXT_chris_evans_captain</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7137,20 +5497,10 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -7174,12 +5524,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>captain america brave new world know know thunderbolt power power friend family   know action action action   like explane background small flash good favorite wyatt russell fall sentry nerfe thoery think sentry power 1000 explode sun comic_strip million explode sun think happen probably dr doom sentry inject serum sentry powerfull forget memory thunderbolt ruler sector battelworld</t>
+          <t>ENTLBL_PERSON ENTTXT_wyatt_russell_fall</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>well captain america brave new world like well captain america brave new world know know thunderbolt power power friend family   know action well action action   like explane background small flash good favorite wyatt russell fall sentry nerfe thoery think show sentry power 1000 explode sun comic_strip million explode sun think happen probably dr doom sentry inject serum sentry powerfull forget memory thunderbolt ruler sector battelworld captain america brave new world like captain america brave new world know know thunderbolt power power friend family   know action action action   like explane background small flash good favorite wyatt russell fall sentry nerfe thoery think sentry power 1000 explode sun comic_strip million explode sun think happen probably dr doom sentry inject serum sentry powerfull forget memory thunderbolt ruler sector battelworld captain america brave new world know know thunderbolt power power friend family   know action action action   like explane background small flash good favorite wyatt russell fall sentry nerfe thoery think sentry power 1000 explode sun comic_strip million explode sun think happen probably dr doom sentry inject serum sentry powerfull forget memory thunderbolt ruler sector battelworld</t>
+          <t>well captain america brave new world like well captain america brave new world know know thunderbolt power power friend family   know action well action action   like explane background small flash good favorite wyatt russell fall sentry nerfe thoery think show sentry power 1000 explode sun comic_strip million explode sun think happen probably dr doom sentry inject serum sentry powerfull forget memory thunderbolt ruler sector battelworld captain america brave new world like captain america brave new world know know thunderbolt power power friend family   know action action action   like explane background small flash good favorite wyatt russell fall sentry nerfe thoery think sentry power 1000 explode sun comic_strip million explode sun think happen probably dr doom sentry inject serum sentry powerfull forget memory thunderbolt ruler sector battelworld [SEP] ENTLBL_PERSON ENTTXT_wyatt_russell_fall</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7194,20 +5544,10 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -7229,14 +5569,10 @@
           <t>hard confuse reason dumb found probably havnt see gaurdian galaxy movie   doctor strange black panther captain america civil war hard track   way overblown computer generate imagery opinion not patch assemble inclusion certain interesting overall dissapointe bad ending hard confuse reason dumb found probably havnt gaurdian galaxy   doctor strange black panther captain america civil war hard track   way overblown computer generate imagery opinion patch assemble inclusion certain interesting overall dissapointe bad ending</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>hard confuse</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>hard confuse reason dumb found probably havnt see gaurdian galaxy movie   doctor strange black panther captain america civil war hard track   way overblown computer generate imagery opinion not patch assemble inclusion certain interesting overall dissapointe bad ending hard confuse reason dumb found probably havnt gaurdian galaxy   doctor strange black panther captain america civil war hard track   way overblown computer generate imagery opinion patch assemble inclusion certain interesting overall dissapointe bad ending hard confuse</t>
+          <t>hard confuse reason dumb found probably havnt see gaurdian galaxy movie   doctor strange black panther captain america civil war hard track   way overblown computer generate imagery opinion not patch assemble inclusion certain interesting overall dissapointe bad ending hard confuse reason dumb found probably havnt gaurdian galaxy   doctor strange black panther captain america civil war hard track   way overblown computer generate imagery opinion patch assemble inclusion certain interesting overall dissapointe bad ending [SEP]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7251,20 +5587,10 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7288,12 +5614,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>bad boring stupid plot idiotic unsympathetic protagonist bad action bad computer generate imagery spear usefull place cinematic catastrophic ending catastrophic phase 4 goodbye oh need 400 wow 2hours 40 feel actually bore lot thing awake stupid plot unlikeable behave like moron time death war stake consequencesmean switch brain try like present impossible ask 250 m   dollar   seriously 1 look</t>
+          <t>ENTLBL_ORG ENTTXT_moron_time_death_war</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>bad boring stupid plot idiotic unsympathetic protagonist bad action bad computer generate imagery spear usefull place cinematic catastrophic ending catastrophic phase 4 goodbye oh need 400 wow 2hours 40 feel actually get bore lot thing keep awake stupid plot unlikeable behave like moron time death war stake consequencesmean switch brain try like present impossible ask 250 m   dollar   seriously 1 look well bad boring stupid plot idiotic unsympathetic protagonist bad action bad computer generate imagery spear usefull place cinematic catastrophic ending catastrophic phase 4 goodbye oh need 400 wow 2hours 40 feel actually bore lot thing awake stupid plot unlikeable behave like moron time death war stake consequencesmean switch brain try like present impossible ask 250 m   dollar   seriously 1 look bad boring stupid plot idiotic unsympathetic protagonist bad action bad computer generate imagery spear usefull place cinematic catastrophic ending catastrophic phase 4 goodbye oh need 400 wow 2hours 40 feel actually bore lot thing awake stupid plot unlikeable behave like moron time death war stake consequencesmean switch brain try like present impossible ask 250 m   dollar   seriously 1 look</t>
+          <t>bad boring stupid plot idiotic unsympathetic protagonist bad action bad computer generate imagery spear usefull place cinematic catastrophic ending catastrophic phase 4 goodbye oh need 400 wow 2hours 40 feel actually get bore lot thing keep awake stupid plot unlikeable behave like moron time death war stake consequencesmean switch brain try like present impossible ask 250 m   dollar   seriously 1 look well bad boring stupid plot idiotic unsympathetic protagonist bad action bad computer generate imagery spear usefull place cinematic catastrophic ending catastrophic phase 4 goodbye oh need 400 wow 2hours 40 feel actually bore lot thing awake stupid plot unlikeable behave like moron time death war stake consequencesmean switch brain try like present impossible ask 250 m   dollar   seriously 1 look [SEP] ENTLBL_ORG ENTTXT_moron_time_death_war</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7308,20 +5634,10 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7343,14 +5659,10 @@
           <t>great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 black panther definitely disappoint start finish amazing action great great introduce lot new stuff great job say acting great definitely recommend see bad thing end not add second preview credit end huge deal bad thing believe deserve 83 great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 black panther definitely disappoint start finish amazing action great great introduce lot new stuff great job acting great definitely recommend bad thing end add second preview credit end huge deal bad thing believe deserve 83</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 action great great introduce lot new stuff great job acting great definitely recommend bad thing end add second preview credit end huge deal bad thing believe deserve 83</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 black panther definitely disappoint start finish amazing action great great introduce lot new stuff great job say acting great definitely recommend see bad thing end not add second preview credit end huge deal bad thing believe deserve 83 great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 black panther definitely disappoint start finish amazing action great great introduce lot new stuff great job acting great definitely recommend bad thing end add second preview credit end huge deal bad thing believe deserve 83 great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 action great great introduce lot new stuff great job acting great definitely recommend bad thing end add second preview credit end huge deal bad thing believe deserve 83</t>
+          <t>great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 black panther definitely disappoint start finish amazing action great great introduce lot new stuff great job say acting great definitely recommend see bad thing end not add second preview credit end huge deal bad thing believe deserve 83 great introduce new stuff great acrion amazing imdb rating kinda low believe deserve 83 black panther definitely disappoint start finish amazing action great great introduce lot new stuff great job acting great definitely recommend bad thing end add second preview credit end huge deal bad thing believe deserve 83 [SEP]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7365,20 +5677,10 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -7402,12 +5704,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>expect actually hat director james gunn styling job visual special effect incredible non human look amazingly real blend perfectly surrounding action flawles good blend action suspense humor entertainment value 1010 visual   1010 oh rocket favorite guardian bradley cooper voice uhmmm vin diesel cast voice groot literally sentence time groot course groot end ok sentence learn record sentence use playback notice</t>
+          <t>ENTLBL_ORG ENTTXT_big_superhero_fan ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_ORG ENTTXT_uhmmm_vin_diesel</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>well expect actually m big superhero fan actually expect like thoroughly entertain hat director james gunn styling job visual special effect incredible non human look amazingly real blend perfectly surrounding action flawles good blend action suspense humor entertainment value 1010 visual   1010 oh rocket favorite guardian bradley cooper voice uhmmm vin diesel cast voice groot literally sentence say time groot course groot end ok sentence learn record sentence playback notice expect actually m big superhero fan actually expect like thoroughly entertain hat director james gunn styling job visual special effect incredible non human look amazingly real blend perfectly surrounding action flawles good blend action suspense humor entertainment value 1010 visual   1010 oh rocket favorite guardian bradley cooper voice uhmmm vin diesel cast voice groot literally sentence time groot course groot end ok sentence learn record sentence use playback notice expect actually hat director james gunn styling job visual special effect incredible non human look amazingly real blend perfectly surrounding action flawles good blend action suspense humor entertainment value 1010 visual   1010 oh rocket favorite guardian bradley cooper voice uhmmm vin diesel cast voice groot literally sentence time groot course groot end ok sentence learn record sentence use playback notice</t>
+          <t>well expect actually m big superhero fan actually expect like thoroughly entertain hat director james gunn styling job visual special effect incredible non human look amazingly real blend perfectly surrounding action flawles good blend action suspense humor entertainment value 1010 visual   1010 oh rocket favorite guardian bradley cooper voice uhmmm vin diesel cast voice groot literally sentence say time groot course groot end ok sentence learn record sentence playback notice expect actually m big superhero fan actually expect like thoroughly entertain hat director james gunn styling job visual special effect incredible non human look amazingly real blend perfectly surrounding action flawles good blend action suspense humor entertainment value 1010 visual   1010 oh rocket favorite guardian bradley cooper voice uhmmm vin diesel cast voice groot literally sentence time groot course groot end ok sentence learn record sentence use playback notice [SEP] ENTLBL_ORG ENTTXT_big_superhero_fan ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_ORG ENTTXT_uhmmm_vin_diesel</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7422,20 +5724,10 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -7457,14 +5749,10 @@
           <t>boring movie movie stereotypical american action film bright pretty color boring sleep worthy like rest mcu simpleton boring stereotypical american action bright pretty color boring sleep worthy like rest mcu simpleton</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>boring stereotypical american action bright pretty color boring sleep worthy like rest mcu simpleton</t>
-        </is>
-      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>boring movie movie stereotypical american action film bright pretty color boring sleep worthy like rest mcu simpleton boring stereotypical american action bright pretty color boring sleep worthy like rest mcu simpleton boring stereotypical american action bright pretty color boring sleep worthy like rest mcu simpleton</t>
+          <t>boring movie movie stereotypical american action film bright pretty color boring sleep worthy like rest mcu simpleton boring stereotypical american action bright pretty color boring sleep worthy like rest mcu simpleton [SEP]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7479,20 +5767,10 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7514,14 +5792,10 @@
           <t>terribly bad million mile comic book childish childish humour terribly bad earth let terribly bad million mile comic book childish childish humour terribly bad earth let</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>terribly bad million mile comic book childish childish humour terribly bad earth let</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>terribly bad million mile comic book childish childish humour terribly bad earth let terribly bad million mile comic book childish childish humour terribly bad earth let terribly bad million mile comic book childish childish humour terribly bad earth let</t>
+          <t>terribly bad million mile comic book childish childish humour terribly bad earth let terribly bad million mile comic book childish childish humour terribly bad earth let [SEP]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7536,20 +5810,10 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7573,12 +5837,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>holy ish mess far enjoyable unfortunately decline continue good label infinity war change thing 4 year old try funny fail half a55ed slapstick good actress play kamala girl unfortunately big talent add insult injury suffer bad dialogue write babble ramble suppose kidsteenage nonsense truly unbearable unnecessary annoying face slapstick singing dance hat musical episode   chance fortunately super weak beginning long realize skip</t>
+          <t>ENTLBL_PERSON ENTTXT_kamala</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>holy ish mess far enjoyable unfortunately decline movie continue not good label infinity war marvel not change thing call 4 year old try funny fail half a55ed slapstick good actress play kamala girl unfortunately big talent add insult injury suffer bad dialogue write babble ramble suppose kidsteenage nonsense truly unbearable unnecessary annoying face slapstick singing dance hat musical episode   lazy uninspired look back supposedly happen captain piece junk chance fortunately super weak beginning will not long realize well skip holy ish mess far enjoyable unfortunately decline continue good label infinity war change thing 4 year old try funny fail half a55ed slapstick good actress play kamala girl unfortunately big talent add insult injury suffer bad dialogue write babble ramble suppose kidsteenage nonsense truly unbearable unnecessary annoying face slapstick singing dance hat musical episode   lazy uninspired look supposedly happen captain piece junk chance fortunately super weak beginning long realize skip holy ish mess far enjoyable unfortunately decline continue good label infinity war change thing 4 year old try funny fail half a55ed slapstick good actress play kamala girl unfortunately big talent add insult injury suffer bad dialogue write babble ramble suppose kidsteenage nonsense truly unbearable unnecessary annoying face slapstick singing dance hat musical episode   chance fortunately super weak beginning long realize skip</t>
+          <t>holy ish mess far enjoyable unfortunately decline movie continue not good label infinity war marvel not change thing call 4 year old try funny fail half a55ed slapstick good actress play kamala girl unfortunately big talent add insult injury suffer bad dialogue write babble ramble suppose kidsteenage nonsense truly unbearable unnecessary annoying face slapstick singing dance hat musical episode   lazy uninspired look back supposedly happen captain piece junk chance fortunately super weak beginning will not long realize well skip holy ish mess far enjoyable unfortunately decline continue good label infinity war change thing 4 year old try funny fail half a55ed slapstick good actress play kamala girl unfortunately big talent add insult injury suffer bad dialogue write babble ramble suppose kidsteenage nonsense truly unbearable unnecessary annoying face slapstick singing dance hat musical episode   lazy uninspired look supposedly happen captain piece junk chance fortunately super weak beginning long realize skip [SEP] ENTLBL_PERSON ENTTXT_kamala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7593,20 +5857,10 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7628,14 +5882,10 @@
           <t>oh dear oh dear earth crp consider entertainment feel rob hour lifetime get nominate oscar bad year award apart cool computer generate imagery effect pitiful waste time oh dear oh dear earth crp consider entertainment feel rob hour lifetime nominate oscar bad year award apart cool computer generate imagery effect pitiful waste time</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>oh dear oh dear earth crp consider entertainment feel rob hour lifetime bad year award apart cool computer generate imagery effect pitiful waste time</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>oh dear oh dear earth crp consider entertainment feel rob hour lifetime get nominate oscar bad year award apart cool computer generate imagery effect pitiful waste time oh dear oh dear earth crp consider entertainment feel rob hour lifetime nominate oscar bad year award apart cool computer generate imagery effect pitiful waste time oh dear oh dear earth crp consider entertainment feel rob hour lifetime bad year award apart cool computer generate imagery effect pitiful waste time</t>
+          <t>oh dear oh dear earth crp consider entertainment feel rob hour lifetime get nominate oscar bad year award apart cool computer generate imagery effect pitiful waste time oh dear oh dear earth crp consider entertainment feel rob hour lifetime nominate oscar bad year award apart cool computer generate imagery effect pitiful waste time [SEP]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7650,20 +5900,10 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7685,14 +5925,10 @@
           <t>world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time</t>
+          <t>world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time world robot super soldier doctor strange bring new table magic feel little refreshing main treat probably special effect way ahead ultimately offer new plot thing million time [SEP]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7707,20 +5943,10 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7744,12 +5970,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>good comic book ve believe hype great numerous reason director choose job bring iconic super team comic_strip life joss whedon time time know run astonishing x team dynamic firefly work work magic max reason great cast good performance stand mark ruffalo bruce bannerhulk second tom hiddleston loki enjoy ed norton banner feel miss likability mark ruffalo likability reason action final epic battle rival robot trash chicago transformer 3 way cool great action come favorite beginning loki steal tesseractcosmic cube bunch shield agent include nick fury hawkeye plot fairly simplistic shone dynamic final verdict possibly good summer 2012 assemble</t>
+          <t>ENTLBL_PERSON ENTTXT_max ENTLBL_PERSON ENTTXT_hiddleston ENTLBL_PERSON ENTTXT_ed_norton ENTLBL_PERSON ENTTXT_mark_ruffalo_likability ENTLBL_PERSON ENTTXT_tom_hiddleston ENTLBL_PERSON ENTTXT_nick_fury</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>good comic book movie ve see not say believe hype great numerous reason director choose job bring iconic super team comic_strip lifejoss whedon show time time know run astonishing x man team dynamic firefly work work magic max reason great cast good performance stand mark ruffalo bruce bannerhulk second tom hiddleston loki enjoy ed norton banner feel miss likability mark ruffalo likability tom hiddleston loki great villain sinister aura well thor reason action final epic battle rival robot trash chicago transformer 3 way cool great action come favorite beginning loki steal tesseractcosmic cube take bunch shield agent include nick fury hawkeye plot fairly simplistic make shone dynamic final verdict possibly good summer 2012 assemble good comic book ve believe hype great numerous reason director choose job bring iconic super team comic_strip lifejoss whedon time time know run astonishing x team dynamic firefly work work magic max reason great cast good performance stand mark ruffalo bruce bannerhulk second tom hiddleston loki enjoy ed norton banner feel miss likability mark ruffalo likability tom hiddleston loki great villain sinister aura thor reason action final epic battle rival robot trash chicago transformer 3 way cool great action come favorite beginning loki steal tesseractcosmic cube bunch shield agent include nick fury hawkeye plot fairly simplistic shone dynamic final verdict possibly good summer 2012 assemble good comic book ve believe hype great numerous reason director choose job bring iconic super team comic_strip life joss whedon time time know run astonishing x team dynamic firefly work work magic max reason great cast good performance stand mark ruffalo bruce bannerhulk second tom hiddleston loki enjoy ed norton banner feel miss likability mark ruffalo likability reason action final epic battle rival robot trash chicago transformer 3 way cool great action come favorite beginning loki steal tesseractcosmic cube bunch shield agent include nick fury hawkeye plot fairly simplistic shone dynamic final verdict possibly good summer 2012 assemble</t>
+          <t>good comic book movie ve see not say believe hype great numerous reason director choose job bring iconic super team comic_strip lifejoss whedon show time time know run astonishing x man team dynamic firefly work work magic max reason great cast good performance stand mark ruffalo bruce bannerhulk second tom hiddleston loki enjoy ed norton banner feel miss likability mark ruffalo likability tom hiddleston loki great villain sinister aura well thor reason action final epic battle rival robot trash chicago transformer 3 way cool great action come favorite beginning loki steal tesseractcosmic cube take bunch shield agent include nick fury hawkeye plot fairly simplistic make shone dynamic final verdict possibly good summer 2012 assemble good comic book ve believe hype great numerous reason director choose job bring iconic super team comic_strip lifejoss whedon time time know run astonishing x team dynamic firefly work work magic max reason great cast good performance stand mark ruffalo bruce bannerhulk second tom hiddleston loki enjoy ed norton banner feel miss likability mark ruffalo likability tom hiddleston loki great villain sinister aura thor reason action final epic battle rival robot trash chicago transformer 3 way cool great action come favorite beginning loki steal tesseractcosmic cube bunch shield agent include nick fury hawkeye plot fairly simplistic shone dynamic final verdict possibly good summer 2012 assemble [SEP] ENTLBL_PERSON ENTTXT_max ENTLBL_PERSON ENTTXT_hiddleston ENTLBL_PERSON ENTTXT_ed_norton ENTLBL_PERSON ENTTXT_mark_ruffalo_likability ENTLBL_PERSON ENTTXT_tom_hiddleston ENTLBL_PERSON ENTTXT_nick_fury</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7764,20 +5990,10 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -7799,14 +6015,10 @@
           <t>pretty good introduction bad obviously hype endgame go hard beat time overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday not see totally open mind pretty good introduction bad obviously hype endgame hard beat time overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday totally open mind</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>pretty good introduction bad overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday totally open mind</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>pretty good introduction bad obviously hype endgame go hard beat time overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday not see totally open mind pretty good introduction bad obviously hype endgame hard beat time overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday totally open mind pretty good introduction bad overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday totally open mind</t>
+          <t>pretty good introduction bad obviously hype endgame go hard beat time overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday not see totally open mind pretty good introduction bad obviously hype endgame hard beat time overall plot setup good hopefully sequel continue cliffhanger post credit point roadmap maybe doomsday totally open mind [SEP]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7821,20 +6033,10 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7856,14 +6058,10 @@
           <t>refreshing journey non traditional fan get eyeful beauty style culture backdrop long anticipated superhero get big screen traditional fan m sure not fighting crash noise conflict go satisfy todays adrenaline addiction allow shift realize fact experience not culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther not superhero action beginning mythology legend refreshing journey non traditional fan eyeful beauty style culture backdrop long anticipated superhero big screen traditional fan m sure fighting crash noise conflict satisfy todays adrenaline addiction allow shift realize fact experience culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther superhero action beginning mythology legend</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>refreshing journey non traditional fan eyeful beauty style culture backdrop long anticipated superhero big screen traditional fan m sure fighting crash noise conflict satisfy todays adrenaline addiction allow shift realize fact experience culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther superhero action beginning mythology legend</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>refreshing journey non traditional fan get eyeful beauty style culture backdrop long anticipated superhero get big screen traditional fan m sure not fighting crash noise conflict go satisfy todays adrenaline addiction allow shift realize fact experience not culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther not superhero action beginning mythology legend refreshing journey non traditional fan eyeful beauty style culture backdrop long anticipated superhero big screen traditional fan m sure fighting crash noise conflict satisfy todays adrenaline addiction allow shift realize fact experience culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther superhero action beginning mythology legend refreshing journey non traditional fan eyeful beauty style culture backdrop long anticipated superhero big screen traditional fan m sure fighting crash noise conflict satisfy todays adrenaline addiction allow shift realize fact experience culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther superhero action beginning mythology legend</t>
+          <t>refreshing journey non traditional fan get eyeful beauty style culture backdrop long anticipated superhero get big screen traditional fan m sure not fighting crash noise conflict go satisfy todays adrenaline addiction allow shift realize fact experience not culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther not superhero action beginning mythology legend refreshing journey non traditional fan eyeful beauty style culture backdrop long anticipated superhero big screen traditional fan m sure fighting crash noise conflict satisfy todays adrenaline addiction allow shift realize fact experience culture foreign lot america calmness steely keenness strategy cool collect demeanor new appreciate appreciate aspect work art young old remember generation like early day superman black panther superhero action beginning mythology legend [SEP]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7878,20 +6076,10 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -7915,12 +6103,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>near perfect interpretation minor problem near match imagine perfect interpretation work art different medium canon rank number probably doctor strange favourite comic capture psychedelic aspect original perfectly use interstellar overdrive soundtrack minor dislike ancient play white woman actually think change ancient gender inspire tilda swinton brilliant role hard asian actor choose role dislike opening sequence start big action sequence day know connection main little impact impress cgi far opening sequence leave cutting room floor start stephen strange hospital opening sequence apart feel computer generate imagery earn place doctor strange perfectly integrate visual reflect steve ditkos style far add enjoyment hope standalone doctor strange help feel ill serve mere team member ensemble effort</t>
+          <t>ENTLBL_ORG ENTTXT_tilda_swinton ENTLBL_PERSON ENTTXT_steve_ditkos</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>near perfect interpretation minor problem near match imagine go not perfect give someone interpretation work art different medium canon film rank number probably doctor strange favourite comic sixty capture psychedelic aspect original perfectly interstellar overdrive soundtrack minor dislike ancient play white woman actually think change ancient one gender inspire tilda swinton brilliant role hard asian actor not choose role dislike opening sequence film start big action sequence day not know connection main little impact impress cgi far opening sequence leave cutting room floor start stephen strange hospital opening sequence apart feel computer generate imagery earn place doctor strange perfectly integrate visual reflect steve ditkos style add enjoyment hope standalone doctor strange movie not help feel ill serve mere team member ensemble effort near perfect interpretation minor problem near match imagine perfect interpretation work art different medium canon rank number probably doctor strange favourite comic capture psychedelic aspect original perfectly use interstellar overdrive soundtrack minor dislike ancient play white woman actually think change ancient gender inspire tilda swinton brilliant role hard asian actor choose role dislike opening sequence start big action sequence day know connection main little impact impress cgi far opening sequence leave cutting room floor start stephen strange hospital opening sequence apart feel computer generate imagery earn place doctor strange perfectly integrate visual reflect steve ditkos style far add enjoyment hope standalone doctor strange help feel ill serve mere team member ensemble effort near perfect interpretation minor problem near match imagine perfect interpretation work art different medium canon rank number probably doctor strange favourite comic capture psychedelic aspect original perfectly use interstellar overdrive soundtrack minor dislike ancient play white woman actually think change ancient gender inspire tilda swinton brilliant role hard asian actor choose role dislike opening sequence start big action sequence day know connection main little impact impress cgi far opening sequence leave cutting room floor start stephen strange hospital opening sequence apart feel computer generate imagery earn place doctor strange perfectly integrate visual reflect steve ditkos style far add enjoyment hope standalone doctor strange help feel ill serve mere team member ensemble effort</t>
+          <t>near perfect interpretation minor problem near match imagine go not perfect give someone interpretation work art different medium canon film rank number probably doctor strange favourite comic sixty capture psychedelic aspect original perfectly interstellar overdrive soundtrack minor dislike ancient play white woman actually think change ancient one gender inspire tilda swinton brilliant role hard asian actor not choose role dislike opening sequence film start big action sequence day not know connection main little impact impress cgi far opening sequence leave cutting room floor start stephen strange hospital opening sequence apart feel computer generate imagery earn place doctor strange perfectly integrate visual reflect steve ditkos style add enjoyment hope standalone doctor strange movie not help feel ill serve mere team member ensemble effort near perfect interpretation minor problem near match imagine perfect interpretation work art different medium canon rank number probably doctor strange favourite comic capture psychedelic aspect original perfectly use interstellar overdrive soundtrack minor dislike ancient play white woman actually think change ancient gender inspire tilda swinton brilliant role hard asian actor choose role dislike opening sequence start big action sequence day know connection main little impact impress cgi far opening sequence leave cutting room floor start stephen strange hospital opening sequence apart feel computer generate imagery earn place doctor strange perfectly integrate visual reflect steve ditkos style far add enjoyment hope standalone doctor strange help feel ill serve mere team member ensemble effort [SEP] ENTLBL_ORG ENTTXT_tilda_swinton ENTLBL_PERSON ENTTXT_steve_ditkos</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7935,20 +6123,10 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -7970,14 +6148,10 @@
           <t>intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience deliver robocop 1987 big large poignant loss robocop wife family deliver alien 1986 hi tech individual warfare alien factor actually provide intimate civil war 1861 1864 angle terminator 2 judgment day 1991 alien factor iron not provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience deliver robocop 1987 big large poignant loss robocop wife family deliver alien 1986 hi tech individual warfare alien factor actually provide intimate civil war 1861 1864 angle terminator 2 judgment day 1991 alien factor iron provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience iron provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience deliver robocop 1987 big large poignant loss robocop wife family deliver alien 1986 hi tech individual warfare alien factor actually provide intimate civil war 1861 1864 angle terminator 2 judgment day 1991 alien factor iron not provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience deliver robocop 1987 big large poignant loss robocop wife family deliver alien 1986 hi tech individual warfare alien factor actually provide intimate civil war 1861 1864 angle terminator 2 judgment day 1991 alien factor iron provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience iron provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star</t>
+          <t>intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience deliver robocop 1987 big large poignant loss robocop wife family deliver alien 1986 hi tech individual warfare alien factor actually provide intimate civil war 1861 1864 angle terminator 2 judgment day 1991 alien factor iron not provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star intelligent super hero action 4 2008 step normal superhero fact spoiled rich technology discover conscience deliver robocop 1987 big large poignant loss robocop wife family deliver alien 1986 hi tech individual warfare alien factor actually provide intimate civil war 1861 1864 angle terminator 2 judgment day 1991 alien factor iron provide nature everyman common perspective level mass audience identify spiderman franchise personal relational boy girl conflict iron truly intellectual conscience remain spiderman focus universal experience additional unnecessary flashback sequence like batman begin 2005 contemporary honor 2008 allow underdevelopment familial relationship important iron worth ticket allow gloss overlook important flash underneath seven star [SEP]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7992,20 +6166,10 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -8027,14 +6191,10 @@
           <t>good ve well like think careful choice director time actress good ve like think careful choice director time actress</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>good ve like think careful choice director time actress</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>good ve well like think careful choice director time actress good ve like think careful choice director time actress good ve like think careful choice director time actress</t>
+          <t>good ve well like think careful choice director time actress good ve like think careful choice director time actress [SEP]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8049,20 +6209,10 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -8084,14 +6234,10 @@
           <t>bad cinematic charcter clear motif ultron bad computer generate imagery bad cinematic charcter clear motif ultron bad computer generate imagery</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>bad cinematic charcter clear motif ultron bad computer generate imagery</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>bad cinematic charcter clear motif ultron bad computer generate imagery bad cinematic charcter clear motif ultron bad computer generate imagery bad cinematic charcter clear motif ultron bad computer generate imagery</t>
+          <t>bad cinematic charcter clear motif ultron bad computer generate imagery bad cinematic charcter clear motif ultron bad computer generate imagery [SEP]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8106,20 +6252,10 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8143,12 +6279,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>expect usual avengermarvel quality high hope black widow level script act action grandeur early opening plot exciting 10 minute fall flat recover imho halfway convinced scarlet johansson create buzz spinoff know director cate shortland want find past uninspire poor act direct fault kid final time time time true testament great black widow ill shame love scarlet johansson role real meh moment d hop rachel weisz olga kurylenko great lift sleep face twice tiny line try deliver florence pugh obviously set return spinoff m bucket new know extra bucket milk cow dry bone hop connection original print money m feed new good unique superhero replace cookie cutter feminist replacement good mileage vary ve review range nil max mind black widow d gladly miss despite love scarlet johansson actor great good script good director know jon favreau super busy continue awesome need reign taika waititi comedy variant gather try fail hard ps speak russian abysmal despite supposedly russians mean spend weekend speech coach teach line correctly russian far great feel like comedy action flick</t>
+          <t>ENTLBL_PERSON ENTTXT_imho_halfway ENTLBL_PERSON ENTTXT_rachel_weisz_olga_kurylenko ENTLBL_PERSON ENTTXT_max ENTLBL_ORG ENTTXT_ps</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>not expect usual avengermarvel quality high hope black widow level script act action grandeur early movie iron thor captain america instead get feel like zero connection like people not see previous movie let work production opening plot exciting 10 minute fall flat recover imho halfway convinced scarlet johansson create buzz spinoff not know director cate shortland want find movie past uninspire poor act direct whatever fault kid watch movie final time time time true testament great movie black widow ill shame love scarlet johansson role real meh moment d hop rachel weisz olga kurylenko great part lift sleep show face twice tiny line try deliver florence pugh obviously set return spinoff m put bucket new one know extra bucket milk cow dry bone hop connection original movie print money m get feed new movie go good unique superhero movie replace cookie cutter feminist replacement good one mileage vary ve see review range nil max mind black widow d gladly miss despite love scarlet johansson actor great good script good director know jon favreau super busy not go continue make awesome movie need reign taika waititi comedy variant gather try fail hard ps speak russian abysmal despite supposedly russians mean not spend weekend speech coach teach line correctly russian far great feel like comedy action flick expect usual avengermarvel quality high hope black widow level script act action grandeur early iron thor captain america instead feel like zero connection like people previous let work production opening plot exciting 10 minute fall flat recover imho halfway convinced scarlet johansson create buzz spinoff know director cate shortland want find past uninspire poor act direct fault kid final time time time true testament great black widow ill shame love scarlet johansson role real meh moment d hop rachel weisz olga kurylenko great lift sleep face twice tiny line try deliver florence pugh obviously set return spinoff m bucket new know extra bucket milk cow dry bone hop connection original print money m feed new good unique superhero replace cookie cutter feminist replacement good mileage vary ve review range nil max mind black widow d gladly miss despite love scarlet johansson actor great good script good director know jon favreau super busy continue awesome need reign taika waititi comedy variant gather try fail hard ps speak russian abysmal despite supposedly russians mean spend weekend speech coach teach line correctly russian far great feel like comedy action flick expect usual avengermarvel quality high hope black widow level script act action grandeur early opening plot exciting 10 minute fall flat recover imho halfway convinced scarlet johansson create buzz spinoff know director cate shortland want find past uninspire poor act direct fault kid final time time time true testament great black widow ill shame love scarlet johansson role real meh moment d hop rachel weisz olga kurylenko great lift sleep face twice tiny line try deliver florence pugh obviously set return spinoff m bucket new know extra bucket milk cow dry bone hop connection original print money m feed new good unique superhero replace cookie cutter feminist replacement good mileage vary ve review range nil max mind black widow d gladly miss despite love scarlet johansson actor great good script good director know jon favreau super busy continue awesome need reign taika waititi comedy variant gather try fail hard ps speak russian abysmal despite supposedly russians mean spend weekend speech coach teach line correctly russian far great feel like comedy action flick</t>
+          <t>not expect usual avengermarvel quality high hope black widow level script act action grandeur early movie iron thor captain america instead get feel like zero connection like people not see previous movie let work production opening plot exciting 10 minute fall flat recover imho halfway convinced scarlet johansson create buzz spinoff not know director cate shortland want find movie past uninspire poor act direct whatever fault kid watch movie final time time time true testament great movie black widow ill shame love scarlet johansson role real meh moment d hop rachel weisz olga kurylenko great part lift sleep show face twice tiny line try deliver florence pugh obviously set return spinoff m put bucket new one know extra bucket milk cow dry bone hop connection original movie print money m get feed new movie go good unique superhero movie replace cookie cutter feminist replacement good one mileage vary ve see review range nil max mind black widow d gladly miss despite love scarlet johansson actor great good script good director know jon favreau super busy not go continue make awesome movie need reign taika waititi comedy variant gather try fail hard ps speak russian abysmal despite supposedly russians mean not spend weekend speech coach teach line correctly russian far great feel like comedy action flick expect usual avengermarvel quality high hope black widow level script act action grandeur early iron thor captain america instead feel like zero connection like people previous let work production opening plot exciting 10 minute fall flat recover imho halfway convinced scarlet johansson create buzz spinoff know director cate shortland want find past uninspire poor act direct fault kid final time time time true testament great black widow ill shame love scarlet johansson role real meh moment d hop rachel weisz olga kurylenko great lift sleep face twice tiny line try deliver florence pugh obviously set return spinoff m bucket new know extra bucket milk cow dry bone hop connection original print money m feed new good unique superhero replace cookie cutter feminist replacement good mileage vary ve review range nil max mind black widow d gladly miss despite love scarlet johansson actor great good script good director know jon favreau super busy continue awesome need reign taika waititi comedy variant gather try fail hard ps speak russian abysmal despite supposedly russians mean spend weekend speech coach teach line correctly russian far great feel like comedy action flick [SEP] ENTLBL_PERSON ENTTXT_imho_halfway ENTLBL_PERSON ENTTXT_rachel_weisz_olga_kurylenko ENTLBL_PERSON ENTTXT_max ENTLBL_ORG ENTTXT_ps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8163,20 +6299,10 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8200,12 +6326,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>dislike time travel case question 7 10 rating usually like break star assign review star 1 costume disclaimer biased section maybe list use work entertainment costuming year continually dump forget pay extra attention quality detail costume piece time think develop costume case know kind lot lead role play mean creative work twice hard normal honestly trailer shot team time travel team suit super excite evident lot time development attention detail know version hero costume exquisitely 2008 actually consider star category yay costume 2 care obviously studio string money ve throw repeatedly yes star care start 3 performance quality   difficult large ensemble cast yes concentrate main team survive lot lead time compare lead m try explain lead believe performance quality poor course good love actor actress tear extra feel   help cry think moment like amazing feel relate wow happen okay russo brother great balance talent star 4 cinematic yes star 5 music 6 star 21 arch 2008 come think star good job 7 feel yes feel feel performance thing star 8 originality difficult base creation stan lee jack kirby technically original exception fact create interconnect 11 year time like original category star evident sort time travel happen order save snappeddusted satisfied play ve twice question feel answer joke time travel original   shrug 9 entertainment star likely 10 9 star</t>
+          <t>ENTLBL_PERSON ENTTXT_stan_lee_jack_kirby</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>dislike time travel case question 7 10 rating usually like break star assign review star 1 costume disclaimer biased section maybe list work entertainment costuming year continually dump forget pay extra attention quality detail costume piece time think develop costume case not know kind lot lead role play mean creative work twice hard normal honestly see trailer shot team time travel team suit get super excite evident lot time development attention detail go know version hero costume exquisitely 2008 actually consider star category yay costume 2 care obviously studio string take money ve throw repeatedly yes star care start not pick comic book iron release theatre 3 performance quality   difficult large ensemble cast yes concentrate main team survive lot lead time compare film lead m try explain lead believe performance quality poor course good love actor actress tear extra feel not   not help not cry think moment like amazing feel relate wow not happen okay russo brother great balance talent star 4 cinematic yes star 5 music honestly notice music team star 6 star 21 arch 2008 come think star good job 7 feel yes feel feel go performance thing not think moment peak emotion exception cut cap sling thor hammer star 8 originality difficult film base creation stan lee jack kirby technically not original exception fact create interconnect film 11 year time like original film category star evident sort time travel happen order save snappeddusted satisfied play ve see twice question feel not go answer plan answer shot far home spinoff put new disney streaming service november joke time travel film original shrug 9 entertainment star likely 10 9 star dislike time travel case question 7 10 rating usually like break star assign review star 1 costume disclaimer biased section maybe list use work entertainment costuming year continually dump forget pay extra attention quality detail costume piece time think develop costume case know kind lot lead role play mean creative work twice hard normal honestly trailer shot team time travel team suit super excite evident lot time development attention detail know version hero costume exquisitely 2008 actually consider star category yay costume 2 care obviously studio string money ve throw repeatedly yes star care start pick comic book iron release theatre 3 performance quality   difficult large ensemble cast yes concentrate main team survive lot lead time compare lead m try explain lead believe performance quality poor course good love actor actress tear extra feel   help cry think moment like amazing feel relate wow happen okay russo brother great balance talent star 4 cinematic yes star 5 music honestly notice music team star 6 star 21 arch 2008 come think star good job 7 feel yes feel feel performance thing think moment peak emotion exception cut cap sling thor hammer star 8 originality difficult base creation stan lee jack kirby technically original exception fact create interconnect 11 year time like original category star evident sort time travel happen order save snappeddusted satisfied play ve twice question feel answer plan answer shot far home spinoff new disney streaming service november joke time travel original shrug 9 entertainment star likely 10 9 star dislike time travel case question 7 10 rating usually like break star assign review star 1 costume disclaimer biased section maybe list use work entertainment costuming year continually dump forget pay extra attention quality detail costume piece time think develop costume case know kind lot lead role play mean creative work twice hard normal honestly trailer shot team time travel team suit super excite evident lot time development attention detail know version hero costume exquisitely 2008 actually consider star category yay costume 2 care obviously studio string money ve throw repeatedly yes star care start 3 performance quality   difficult large ensemble cast yes concentrate main team survive lot lead time compare lead m try explain lead believe performance quality poor course good love actor actress tear extra feel   help cry think moment like amazing feel relate wow happen okay russo brother great balance talent star 4 cinematic yes star 5 music 6 star 21 arch 2008 come think star good job 7 feel yes feel feel performance thing star 8 originality difficult base creation stan lee jack kirby technically original exception fact create interconnect 11 year time like original category star evident sort time travel happen order save snappeddusted satisfied play ve twice question feel answer joke time travel original   shrug 9 entertainment star likely 10 9 star</t>
+          <t>dislike time travel case question 7 10 rating usually like break star assign review star 1 costume disclaimer biased section maybe list work entertainment costuming year continually dump forget pay extra attention quality detail costume piece time think develop costume case not know kind lot lead role play mean creative work twice hard normal honestly see trailer shot team time travel team suit get super excite evident lot time development attention detail go know version hero costume exquisitely 2008 actually consider star category yay costume 2 care obviously studio string take money ve throw repeatedly yes star care start not pick comic book iron release theatre 3 performance quality   difficult large ensemble cast yes concentrate main team survive lot lead time compare film lead m try explain lead believe performance quality poor course good love actor actress tear extra feel not   not help not cry think moment like amazing feel relate wow not happen okay russo brother great balance talent star 4 cinematic yes star 5 music honestly notice music team star 6 star 21 arch 2008 come think star good job 7 feel yes feel feel go performance thing not think moment peak emotion exception cut cap sling thor hammer star 8 originality difficult film base creation stan lee jack kirby technically not original exception fact create interconnect film 11 year time like original film category star evident sort time travel happen order save snappeddusted satisfied play ve see twice question feel not go answer plan answer shot far home spinoff put new disney streaming service november joke time travel film original shrug 9 entertainment star likely 10 9 star dislike time travel case question 7 10 rating usually like break star assign review star 1 costume disclaimer biased section maybe list use work entertainment costuming year continually dump forget pay extra attention quality detail costume piece time think develop costume case know kind lot lead role play mean creative work twice hard normal honestly trailer shot team time travel team suit super excite evident lot time development attention detail know version hero costume exquisitely 2008 actually consider star category yay costume 2 care obviously studio string money ve throw repeatedly yes star care start pick comic book iron release theatre 3 performance quality   difficult large ensemble cast yes concentrate main team survive lot lead time compare lead m try explain lead believe performance quality poor course good love actor actress tear extra feel   help cry think moment like amazing feel relate wow happen okay russo brother great balance talent star 4 cinematic yes star 5 music honestly notice music team star 6 star 21 arch 2008 come think star good job 7 feel yes feel feel performance thing think moment peak emotion exception cut cap sling thor hammer star 8 originality difficult base creation stan lee jack kirby technically original exception fact create interconnect 11 year time like original category star evident sort time travel happen order save snappeddusted satisfied play ve twice question feel answer plan answer shot far home spinoff new disney streaming service november joke time travel original shrug 9 entertainment star likely 10 9 star [SEP] ENTLBL_PERSON ENTTXT_stan_lee_jack_kirby</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8220,20 +6346,10 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8255,14 +6371,10 @@
           <t>well kind appreciate fact take time build solid relation not mean like superhero interesting predictable kind appreciate fact time build solid relation mean like superhero interesting predictable</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>kind appreciate fact time build solid relation mean like superhero interesting predictable</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>well kind appreciate fact take time build solid relation not mean like superhero interesting predictable kind appreciate fact time build solid relation mean like superhero interesting predictable kind appreciate fact time build solid relation mean like superhero interesting predictable</t>
+          <t>well kind appreciate fact take time build solid relation not mean like superhero interesting predictable kind appreciate fact time build solid relation mean like superhero interesting predictable [SEP]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8277,20 +6389,10 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8314,12 +6416,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>amazing superhero symphony fist pumping like fanatic editing whirlwind action seamlessly interweave large life battle drive moment narrative heart strength seamless blending individual hero cohesive team dynamic superhero jigsaw puzzle fit flawlessly weakness occasionally plot hover edge hey superhero extravaganza love way music alan silvestris score pulse heroism swell iconic entrance save world crescendo cinematography capture grandeur soar height stark tower depth lokis mischief message celebration teamwork diversity idea disparate hero come great good good superhero salute exhilarate entertainment assemble earth mighty hero assemble solid spot pantheon superhero epic</t>
+          <t>ENTLBL_PERSON ENTTXT_robert_downey_jrs_snarky_tony ENTLBL_PERSON ENTTXT_stark_scarlett_johansson_kick ENTLBL_PERSON ENTTXT_alan_silvestris</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>amazing superhero symphony fist pumping like fanatic ensemble cast robert downey jrs snarky tony stark scarlett johansson kick ass black widow powerhouse charisma chemistry hero shin right editing whirlwind action seamlessly interweave large life battle drive moment narrative heart strength seamless blending individual hero story cohesive team dynamic superhero jigsaw puzzle fit flawlessly weakness occasionally plot hover edge hey superhero extravaganza love way music alan silvestris score pulse heroism swell iconic entrance save world crescendo cinematography capture grandeur soar height stark tower depth lokis mischief message celebration teamwork diversity idea disparate hero come great good good superhero salute exhilarate entertainment assemble earth mighty hero assemble solid spot pantheon superhero epic amazing superhero symphony fist pumping like fanatic ensemble cast robert downey jrs snarky tony stark scarlett johansson kick ass black widow powerhouse charisma chemistry hero shin right editing whirlwind action seamlessly interweave large life battle drive moment narrative heart strength seamless blending individual hero cohesive team dynamic superhero jigsaw puzzle fit flawlessly weakness occasionally plot hover edge hey superhero extravaganza love way music alan silvestris score pulse heroism swell iconic entrance save world crescendo cinematography capture grandeur soar height stark tower depth lokis mischief message celebration teamwork diversity idea disparate hero come great good good superhero salute exhilarate entertainment assemble earth mighty hero assemble solid spot pantheon superhero epic amazing superhero symphony fist pumping like fanatic editing whirlwind action seamlessly interweave large life battle drive moment narrative heart strength seamless blending individual hero cohesive team dynamic superhero jigsaw puzzle fit flawlessly weakness occasionally plot hover edge hey superhero extravaganza love way music alan silvestris score pulse heroism swell iconic entrance save world crescendo cinematography capture grandeur soar height stark tower depth lokis mischief message celebration teamwork diversity idea disparate hero come great good good superhero salute exhilarate entertainment assemble earth mighty hero assemble solid spot pantheon superhero epic</t>
+          <t>amazing superhero symphony fist pumping like fanatic ensemble cast robert downey jrs snarky tony stark scarlett johansson kick ass black widow powerhouse charisma chemistry hero shin right editing whirlwind action seamlessly interweave large life battle drive moment narrative heart strength seamless blending individual hero story cohesive team dynamic superhero jigsaw puzzle fit flawlessly weakness occasionally plot hover edge hey superhero extravaganza love way music alan silvestris score pulse heroism swell iconic entrance save world crescendo cinematography capture grandeur soar height stark tower depth lokis mischief message celebration teamwork diversity idea disparate hero come great good good superhero salute exhilarate entertainment assemble earth mighty hero assemble solid spot pantheon superhero epic amazing superhero symphony fist pumping like fanatic ensemble cast robert downey jrs snarky tony stark scarlett johansson kick ass black widow powerhouse charisma chemistry hero shin right editing whirlwind action seamlessly interweave large life battle drive moment narrative heart strength seamless blending individual hero cohesive team dynamic superhero jigsaw puzzle fit flawlessly weakness occasionally plot hover edge hey superhero extravaganza love way music alan silvestris score pulse heroism swell iconic entrance save world crescendo cinematography capture grandeur soar height stark tower depth lokis mischief message celebration teamwork diversity idea disparate hero come great good good superhero salute exhilarate entertainment assemble earth mighty hero assemble solid spot pantheon superhero epic [SEP] ENTLBL_PERSON ENTTXT_robert_downey_jrs_snarky_tony ENTLBL_PERSON ENTTXT_stark_scarlett_johansson_kick ENTLBL_PERSON ENTTXT_alan_silvestris</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8334,20 +6436,10 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -8369,14 +6461,10 @@
           <t>okay supposedly good superhero 2025 not think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif not question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay well okay supposedly good superhero 2025 think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>okay supposedly good superhero 2025 think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>okay supposedly good superhero 2025 not think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif not question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay well okay supposedly good superhero 2025 think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay okay supposedly good superhero 2025 think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay</t>
+          <t>okay supposedly good superhero 2025 not think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif not question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay well okay supposedly good superhero 2025 think illogical action poorly write dialogue comprehensible motif forever development virtually nonexistent motif question let explain feel like house cat buy random food hardware store tell eat die bad action computer generate imagery good describe okay [SEP]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8391,20 +6479,10 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8426,14 +6504,10 @@
           <t>enjoyable worthy not matter say bad captain worthy enjoyable introduce captain prior endgame hate say bad think captain marvel plot unsatisfying direct enjoyable worthy matter bad captain worthy enjoyable introduce captain prior endgame hate bad think captain plot unsatisfying direct</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>enjoyable worthy matter bad captain worthy enjoyable introduce captain prior endgame hate bad think captain plot unsatisfying direct</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>enjoyable worthy not matter say bad captain worthy enjoyable introduce captain prior endgame hate say bad think captain marvel plot unsatisfying direct enjoyable worthy matter bad captain worthy enjoyable introduce captain prior endgame hate bad think captain plot unsatisfying direct enjoyable worthy matter bad captain worthy enjoyable introduce captain prior endgame hate bad think captain plot unsatisfying direct</t>
+          <t>enjoyable worthy not matter say bad captain worthy enjoyable introduce captain prior endgame hate say bad think captain marvel plot unsatisfying direct enjoyable worthy matter bad captain worthy enjoyable introduce captain prior endgame hate bad think captain plot unsatisfying direct [SEP]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8448,20 +6522,10 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8485,12 +6549,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>subatomic space opera episode fifth phase mcus multiverse saga thirty cinematic ant wasp quantumania subatomic space opera continue ant franchise great imagination efficiency stellar cast create large galactic family actress actor new generation hollywood legend bill murray michael douglas michelle pfeiffer dimension creature realm setting infinite possibility multiverse limit constitute imagination creator</t>
+          <t>ENTLBL_PERSON ENTTXT_bill_murray ENTLBL_PERSON ENTTXT_michael_douglas_michelle</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>subatomic space opera episode fifth phase mcus multiverse saga thirty cinematic ant wasp quantumania subatomic space opera continue ant franchise great imagination efficiency stellar cast create large galactic family actress actor new generation hollywood legend bill murray michael douglas michelle pfeiffer dimension creature realm setting universe infinite possibility multiverse limit constitute imagination creator subatomic space opera episode fifth phase mcus multiverse saga thirty cinematic ant wasp quantumania subatomic space opera continue ant franchise great imagination efficiency stellar cast create large galactic family actress actor new generation hollywood legend bill murray michael douglas michelle pfeiffer dimension creature realm setting infinite possibility multiverse limit constitute imagination creator subatomic space opera episode fifth phase mcus multiverse saga thirty cinematic ant wasp quantumania subatomic space opera continue ant franchise great imagination efficiency stellar cast create large galactic family actress actor new generation hollywood legend bill murray michael douglas michelle pfeiffer dimension creature realm setting infinite possibility multiverse limit constitute imagination creator</t>
+          <t>subatomic space opera episode fifth phase mcus multiverse saga thirty cinematic ant wasp quantumania subatomic space opera continue ant franchise great imagination efficiency stellar cast create large galactic family actress actor new generation hollywood legend bill murray michael douglas michelle pfeiffer dimension creature realm setting universe infinite possibility multiverse limit constitute imagination creator subatomic space opera episode fifth phase mcus multiverse saga thirty cinematic ant wasp quantumania subatomic space opera continue ant franchise great imagination efficiency stellar cast create large galactic family actress actor new generation hollywood legend bill murray michael douglas michelle pfeiffer dimension creature realm setting infinite possibility multiverse limit constitute imagination creator [SEP] ENTLBL_PERSON ENTTXT_bill_murray ENTLBL_PERSON ENTTXT_michael_douglas_michelle</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8505,20 +6569,10 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -8542,12 +6596,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>substantial convert fan mcu fair good struggle cinematic sacrifice depth human interest exchange effect gimmick escapism sadly convert fairly rat consider ps dimensional development believable acting storyline engage half descend mindless action section hold end prop quality soundtrack</t>
+          <t>ENTLBL_ORG ENTTXT_ps_dimensional_development_believable</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>substantial convert not fan mcu fair good film struggle cinematic sacrifice depth human interest exchange effect gimmick escapism sadly convert well film fairly rat consider PS dimensional development believable acting storyline engage half descend mindless action section hold end prop quality soundtrack substantial convert fan mcu fair good struggle cinematic sacrifice depth human interest exchange effect gimmick escapism sadly convert fairly rat consider ps dimensional development believable acting storyline engage half descend mindless action section hold end prop quality soundtrack substantial convert fan mcu fair good struggle cinematic sacrifice depth human interest exchange effect gimmick escapism sadly convert fairly rat consider ps dimensional development believable acting storyline engage half descend mindless action section hold end prop quality soundtrack</t>
+          <t>substantial convert not fan mcu fair good film struggle cinematic sacrifice depth human interest exchange effect gimmick escapism sadly convert well film fairly rat consider PS dimensional development believable acting storyline engage half descend mindless action section hold end prop quality soundtrack substantial convert fan mcu fair good struggle cinematic sacrifice depth human interest exchange effect gimmick escapism sadly convert fairly rat consider ps dimensional development believable acting storyline engage half descend mindless action section hold end prop quality soundtrack [SEP] ENTLBL_ORG ENTTXT_ps_dimensional_development_believable</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8562,20 +6616,10 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8597,14 +6641,10 @@
           <t>love cuz look long time ago not remember thing love cuz look long time ago remember thing</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>love cuz look long time ago remember thing</t>
-        </is>
-      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>love cuz look long time ago not remember thing love cuz look long time ago remember thing love cuz look long time ago remember thing</t>
+          <t>love cuz look long time ago not remember thing love cuz look long time ago remember thing [SEP]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8619,20 +6659,10 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8654,14 +6684,10 @@
           <t>disney series think issue series episode go nuance eternal relationship journey time feel get nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes story deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited story disney series think issue series episode nuance eternal relationship journey time feel nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>disney series think issue series episode nuance eternal relationship journey time feel nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited</t>
-        </is>
-      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>disney series think issue series episode go nuance eternal relationship journey time feel get nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes story deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited story disney series think issue series episode nuance eternal relationship journey time feel nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited disney series think issue series episode nuance eternal relationship journey time feel nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited</t>
+          <t>disney series think issue series episode go nuance eternal relationship journey time feel get nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes story deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited story disney series think issue series episode nuance eternal relationship journey time feel nice powerful cut limit run time consider single chloe zhao great job clamor new lore cinematic perfect casting unique crisp feel bored yes deserve time need develop feel series great series help audience pace actually enjoy nuance vfx good cinematic love excited [SEP]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8676,20 +6702,10 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -8713,12 +6729,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>fun fresh space adventure guardian galaxy direct james gunn refreshing addition cinematic blend humor action quirky ensemble follow peter quill chris pratt   abduct earth child grow space fare rogue star lord form unlikely alliance group misfit fierce gamora zoe saldana   literal drax destroyer dave bautista   wisecracking rocket raccoon voice bradley cooper   lovable tree like groot voice vin diesel   charm lie offbeat humor chemistry main soundtrack fill classic 70 80 hit add nostalgic energetic vibe complement tone visual effect stunning bring vibrant diverse galaxy life plot revolve familiar battle save powerful villain development camaraderie stand member guardian bring backstory personality create dynamic entertaining heartfelt guardian galaxy successfully blend action comedy heart enjoyable unique entry superhero genre</t>
+          <t>ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_peter_quill ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_fierce_gamora ENTLBL_PERSON ENTTXT_saldana ENTLBL_PERSON ENTTXT_dave_bautista</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>fun fresh space adventure guardian galaxy direct james gunn refreshing addition cinematic blend humor action quirky ensemble follow peter quill chris pratt   abduct earth child grow space fare rogue star lord form unlikely alliance group misfit fierce gamora zoe saldana   literal drax destroyer dave bautista   wisecracking rocket raccoon voice bradley cooper   lovable tree like groot voice vin diesel   movie charm lie offbeat humor chemistry main soundtrack fill classic 70 80 hit add nostalgic energetic vibe complement film tone visual effect stunning bring vibrant diverse galaxy life plot revolve familiar battle save powerful villain development camaraderie stand member guardian bring backstory personality create dynamic entertaining heartfelt guardian galaxy successfully blend action comedy heart make enjoyable unique entry superhero genre fun fresh space adventure guardian galaxy direct james gunn refreshing addition cinematic blend humor action quirky ensemble follow peter quill chris pratt   abduct earth child grow space fare rogue star lord form unlikely alliance group misfit fierce gamora zoe saldana   literal drax destroyer dave bautista   wisecracking rocket raccoon voice bradley cooper   lovable tree like groot voice vin diesel   charm lie offbeat humor chemistry main soundtrack fill classic 70 80 hit add nostalgic energetic vibe complement tone visual effect stunning bring vibrant diverse galaxy life plot revolve familiar battle save powerful villain development camaraderie stand member guardian bring backstory personality create dynamic entertaining heartfelt guardian galaxy successfully blend action comedy heart enjoyable unique entry superhero genre fun fresh space adventure guardian galaxy direct james gunn refreshing addition cinematic blend humor action quirky ensemble follow peter quill chris pratt   abduct earth child grow space fare rogue star lord form unlikely alliance group misfit fierce gamora zoe saldana   literal drax destroyer dave bautista   wisecracking rocket raccoon voice bradley cooper   lovable tree like groot voice vin diesel   charm lie offbeat humor chemistry main soundtrack fill classic 70 80 hit add nostalgic energetic vibe complement tone visual effect stunning bring vibrant diverse galaxy life plot revolve familiar battle save powerful villain development camaraderie stand member guardian bring backstory personality create dynamic entertaining heartfelt guardian galaxy successfully blend action comedy heart enjoyable unique entry superhero genre</t>
+          <t>fun fresh space adventure guardian galaxy direct james gunn refreshing addition cinematic blend humor action quirky ensemble follow peter quill chris pratt   abduct earth child grow space fare rogue star lord form unlikely alliance group misfit fierce gamora zoe saldana   literal drax destroyer dave bautista   wisecracking rocket raccoon voice bradley cooper   lovable tree like groot voice vin diesel   movie charm lie offbeat humor chemistry main soundtrack fill classic 70 80 hit add nostalgic energetic vibe complement film tone visual effect stunning bring vibrant diverse galaxy life plot revolve familiar battle save powerful villain development camaraderie stand member guardian bring backstory personality create dynamic entertaining heartfelt guardian galaxy successfully blend action comedy heart make enjoyable unique entry superhero genre fun fresh space adventure guardian galaxy direct james gunn refreshing addition cinematic blend humor action quirky ensemble follow peter quill chris pratt   abduct earth child grow space fare rogue star lord form unlikely alliance group misfit fierce gamora zoe saldana   literal drax destroyer dave bautista   wisecracking rocket raccoon voice bradley cooper   lovable tree like groot voice vin diesel   charm lie offbeat humor chemistry main soundtrack fill classic 70 80 hit add nostalgic energetic vibe complement tone visual effect stunning bring vibrant diverse galaxy life plot revolve familiar battle save powerful villain development camaraderie stand member guardian bring backstory personality create dynamic entertaining heartfelt guardian galaxy successfully blend action comedy heart enjoyable unique entry superhero genre [SEP] ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_peter_quill ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_fierce_gamora ENTLBL_PERSON ENTTXT_saldana ENTLBL_PERSON ENTTXT_dave_bautista</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8733,20 +6749,10 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -8770,12 +6776,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>unwatchable actress untalented uncharismatic bad hardcore fan try disappointed samuel l jackson save</t>
+          <t>ENTLBL_PERSON ENTTXT_samuel_l_jackson</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>unwatchable actress untalented uncharismatic bad hardcore fan try disappointed samuel l jackson save unwatchable actress untalented uncharismatic bad hardcore fan try disappointed samuel l jackson save unwatchable actress untalented uncharismatic bad hardcore fan try disappointed samuel l jackson save</t>
+          <t>unwatchable actress untalented uncharismatic bad hardcore fan try disappointed samuel l jackson save unwatchable actress untalented uncharismatic bad hardcore fan try disappointed samuel l jackson save [SEP] ENTLBL_PERSON ENTTXT_samuel_l_jackson</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8790,20 +6796,10 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8827,12 +6823,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>nowcrazy big issue opinion comic_strip giant cluster mess great exist kid right new young spiderboy dumb   feel series assasin girl stupid super hero average joe strong alien cmon hollywood speak spiderboy deserve strength pull glove thano hand easily plot pull unknown leave table dr strange work sloppily term thing reason asgard set tree powerful think head clash like galactus big enemy fox buy disney lead xman join big bad good luck</t>
+          <t>ENTLBL_PERSON ENTTXT_joe ENTLBL_PERSON ENTTXT_joe_strong ENTLBL_ORG ENTTXT_cmon_hollywood</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>well nowcrazy marvel big issue opinion comic_strip giant cluster mess great not exist black panther yawn second iron pure stupid 3rd banner kid right new young spiderboy dumb   feel not series assasin girl stupid super hero average joe move strong alien cmon hollywood speak spiderboy not deserve call strength pull glove thano hand easily say plot pull unknown leave table dr strange antman strange toono real explanation thing like reality stone work sloppily term thing thor good reason asgard set tree powerful think head clash like galactus big enemy fox buy disney lead xman join get big bad good luck nowcrazy big issue opinion comic_strip giant cluster mess great exist black panther yawn second iron pure stupid 3rd banner kid right new young spiderboy dumb   feel series assasin girl stupid super hero average joe strong alien cmon hollywood speak spiderboy deserve strength pull glove thano hand easily plot pull unknown leave table dr strange antman strange toono real explanation thing like reality stone work sloppily term thing thor good reason asgard set tree powerful think head clash like galactus big enemy fox buy disney lead xman join big bad good luck nowcrazy big issue opinion comic_strip giant cluster mess great exist kid right new young spiderboy dumb   feel series assasin girl stupid super hero average joe strong alien cmon hollywood speak spiderboy deserve strength pull glove thano hand easily plot pull unknown leave table dr strange work sloppily term thing reason asgard set tree powerful think head clash like galactus big enemy fox buy disney lead xman join big bad good luck</t>
+          <t>well nowcrazy marvel big issue opinion comic_strip giant cluster mess great not exist black panther yawn second iron pure stupid 3rd banner kid right new young spiderboy dumb   feel not series assasin girl stupid super hero average joe move strong alien cmon hollywood speak spiderboy not deserve call strength pull glove thano hand easily say plot pull unknown leave table dr strange antman strange toono real explanation thing like reality stone work sloppily term thing thor good reason asgard set tree powerful think head clash like galactus big enemy fox buy disney lead xman join get big bad good luck nowcrazy big issue opinion comic_strip giant cluster mess great exist black panther yawn second iron pure stupid 3rd banner kid right new young spiderboy dumb   feel series assasin girl stupid super hero average joe strong alien cmon hollywood speak spiderboy deserve strength pull glove thano hand easily plot pull unknown leave table dr strange antman strange toono real explanation thing like reality stone work sloppily term thing thor good reason asgard set tree powerful think head clash like galactus big enemy fox buy disney lead xman join big bad good luck [SEP] ENTLBL_PERSON ENTTXT_joe ENTLBL_PERSON ENTTXT_joe_strong ENTLBL_ORG ENTTXT_cmon_hollywood</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8847,20 +6843,10 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8884,12 +6870,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>hilarious flawed union deadpool   wolverine review highly anticipated pairing deadpool wolverine finally hit screen deliver abundance laughter action fall short truly exceptional pacing scripting issue standout aspect return hugh jackman wolverine slip iconic role ease presence welcome addition chemistry ryan reynolds deadpool undeniable reynold shin merc mouth bring signature wit irreverence role opening set tone showcase impressive action sequence seamlessly blend humor intensity tone maintain plenty laugh loud moment leave audience entertain moment feel stretched overly reliant reynold quick wit exhausting time primary issue scripting dialogue hilarious ryan reynolds line feel heavy handed shorten edit flow particularly noticeable second act pacing begin drag overabundance exposition meandering subplot despite flaw strength lie ability balance humor heart dynamic deadpool wolverine genuinely engaging banter highlight action sequence choreographed visually stunning making immersive viewing experience conclusion deadpool   wolverine enjoyable plenty laugh exciting moment fall short truly exceptional scripting pace issue tight editing concise dialogue reach potential nonetheless fan find plenty love chemistry jackman reynold compelling rat good recommendation fan deadpool wolverine enjoy action comedy healthy dose irreverence definitely worth viewer seek streamlined narrative find slightly disappointed</t>
+          <t>ENTLBL_ORG ENTTXT_hugh_jackman ENTLBL_ORG ENTTXT_merc</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>hilarious flawed union deadpool   wolverine review highly anticipated pairing deadpool wolverine finally hit screen deliver abundance laughter action fall short truly exceptional pacing scripting issue standout aspect return hugh jackman wolverine slip iconic role ease presence welcome addition chemistry ryan reynolds deadpool undeniable reynold shin merc mouth bring signature wit irreverence role opening set tone showcase impressive action sequence seamlessly blend humor intensity tone maintain plenty laugh loud moment leave audience entertain moment feel stretched overly reliant reynold quick wit exhausting time primary issue scripting dialogue hilarious ryan reynolds line feel heavy handed shorten edit well flow particularly noticeable film second act pacing begin drag overabundance exposition meandering subplot despite flaw film strength lie ability balance humor heart dynamic deadpool wolverine genuinely engaging banter film highlight action sequence choreographed visually stunning making immersive viewing experience conclusion deadpool   wolverine enjoyable plenty laugh exciting moment fall short truly exceptional scripting pace issue tight editing concise dialogue reach potential nonetheless fan find plenty love chemistry jackman reynold make compelling rat good recommendation fan deadpool wolverine enjoy action comedy healthy dose irreverence definitely worth watch viewer seek streamlined narrative find slightly disappointed hilarious flawed union deadpool   wolverine review highly anticipated pairing deadpool wolverine finally hit screen deliver abundance laughter action fall short truly exceptional pacing scripting issue standout aspect return hugh jackman wolverine slip iconic role ease presence welcome addition chemistry ryan reynolds deadpool undeniable reynold shin merc mouth bring signature wit irreverence role opening set tone showcase impressive action sequence seamlessly blend humor intensity tone maintain plenty laugh loud moment leave audience entertain moment feel stretched overly reliant reynold quick wit exhausting time primary issue scripting dialogue hilarious ryan reynolds line feel heavy handed shorten edit flow particularly noticeable second act pacing begin drag overabundance exposition meandering subplot despite flaw strength lie ability balance humor heart dynamic deadpool wolverine genuinely engaging banter highlight action sequence choreographed visually stunning making immersive viewing experience conclusion deadpool   wolverine enjoyable plenty laugh exciting moment fall short truly exceptional scripting pace issue tight editing concise dialogue reach potential nonetheless fan find plenty love chemistry jackman reynold compelling rat good recommendation fan deadpool wolverine enjoy action comedy healthy dose irreverence definitely worth viewer seek streamlined narrative find slightly disappointed hilarious flawed union deadpool   wolverine review highly anticipated pairing deadpool wolverine finally hit screen deliver abundance laughter action fall short truly exceptional pacing scripting issue standout aspect return hugh jackman wolverine slip iconic role ease presence welcome addition chemistry ryan reynolds deadpool undeniable reynold shin merc mouth bring signature wit irreverence role opening set tone showcase impressive action sequence seamlessly blend humor intensity tone maintain plenty laugh loud moment leave audience entertain moment feel stretched overly reliant reynold quick wit exhausting time primary issue scripting dialogue hilarious ryan reynolds line feel heavy handed shorten edit flow particularly noticeable second act pacing begin drag overabundance exposition meandering subplot despite flaw strength lie ability balance humor heart dynamic deadpool wolverine genuinely engaging banter highlight action sequence choreographed visually stunning making immersive viewing experience conclusion deadpool   wolverine enjoyable plenty laugh exciting moment fall short truly exceptional scripting pace issue tight editing concise dialogue reach potential nonetheless fan find plenty love chemistry jackman reynold compelling rat good recommendation fan deadpool wolverine enjoy action comedy healthy dose irreverence definitely worth viewer seek streamlined narrative find slightly disappointed</t>
+          <t>hilarious flawed union deadpool   wolverine review highly anticipated pairing deadpool wolverine finally hit screen deliver abundance laughter action fall short truly exceptional pacing scripting issue standout aspect return hugh jackman wolverine slip iconic role ease presence welcome addition chemistry ryan reynolds deadpool undeniable reynold shin merc mouth bring signature wit irreverence role opening set tone showcase impressive action sequence seamlessly blend humor intensity tone maintain plenty laugh loud moment leave audience entertain moment feel stretched overly reliant reynold quick wit exhausting time primary issue scripting dialogue hilarious ryan reynolds line feel heavy handed shorten edit well flow particularly noticeable film second act pacing begin drag overabundance exposition meandering subplot despite flaw film strength lie ability balance humor heart dynamic deadpool wolverine genuinely engaging banter film highlight action sequence choreographed visually stunning making immersive viewing experience conclusion deadpool   wolverine enjoyable plenty laugh exciting moment fall short truly exceptional scripting pace issue tight editing concise dialogue reach potential nonetheless fan find plenty love chemistry jackman reynold make compelling rat good recommendation fan deadpool wolverine enjoy action comedy healthy dose irreverence definitely worth watch viewer seek streamlined narrative find slightly disappointed hilarious flawed union deadpool   wolverine review highly anticipated pairing deadpool wolverine finally hit screen deliver abundance laughter action fall short truly exceptional pacing scripting issue standout aspect return hugh jackman wolverine slip iconic role ease presence welcome addition chemistry ryan reynolds deadpool undeniable reynold shin merc mouth bring signature wit irreverence role opening set tone showcase impressive action sequence seamlessly blend humor intensity tone maintain plenty laugh loud moment leave audience entertain moment feel stretched overly reliant reynold quick wit exhausting time primary issue scripting dialogue hilarious ryan reynolds line feel heavy handed shorten edit flow particularly noticeable second act pacing begin drag overabundance exposition meandering subplot despite flaw strength lie ability balance humor heart dynamic deadpool wolverine genuinely engaging banter highlight action sequence choreographed visually stunning making immersive viewing experience conclusion deadpool   wolverine enjoyable plenty laugh exciting moment fall short truly exceptional scripting pace issue tight editing concise dialogue reach potential nonetheless fan find plenty love chemistry jackman reynold compelling rat good recommendation fan deadpool wolverine enjoy action comedy healthy dose irreverence definitely worth viewer seek streamlined narrative find slightly disappointed [SEP] ENTLBL_ORG ENTTXT_hugh_jackman ENTLBL_ORG ENTTXT_merc</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8904,20 +6890,10 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -8941,12 +6917,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>expect boring sick enoughthe political beespecially super hero sensitive guy extremely peaceful like external politic past year iron tool powerful administration pretty bad recap special effect interesting build acting good jeff bridges robert downey junior fantastic general consider average robert robert   straightforward feel emotion political message think world past year especially beginning turn   course mature category teenager deeply detail overall boring bad</t>
+          <t>ENTLBL_PERSON ENTTXT_jeff_bridges ENTLBL_PERSON ENTTXT_robert_downey_junior ENTLBL_PERSON ENTTXT_robert_robert___straightforward ENTLBL_PERSON ENTTXT_robert_robert___straightforward_feel</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>expect boring sick enoughthe political not beespecially super hero sensitive guy extremely peaceful not like external politic past year well iron tool powerful administration pretty bad recap special effect interesting build acting good jeff bridges robert downey junior fantastic general consider average robert robert   straightforward not feel emotion see political message think world past year especially beginning turn   course mature category teenager deeply detail overall boring bad expect boring sick enoughthe political beespecially super hero sensitive guy extremely peaceful like external politic past year iron tool powerful administration pretty bad recap special effect interesting build acting good jeff bridges robert downey junior fantastic general consider average robert robert   straightforward feel emotion political message think world past year especially beginning turn   course mature category teenager deeply detail overall boring bad expect boring sick enoughthe political beespecially super hero sensitive guy extremely peaceful like external politic past year iron tool powerful administration pretty bad recap special effect interesting build acting good jeff bridges robert downey junior fantastic general consider average robert robert   straightforward feel emotion political message think world past year especially beginning turn   course mature category teenager deeply detail overall boring bad</t>
+          <t>expect boring sick enoughthe political not beespecially super hero sensitive guy extremely peaceful not like external politic past year well iron tool powerful administration pretty bad recap special effect interesting build acting good jeff bridges robert downey junior fantastic general consider average robert robert   straightforward not feel emotion see political message think world past year especially beginning turn   course mature category teenager deeply detail overall boring bad expect boring sick enoughthe political beespecially super hero sensitive guy extremely peaceful like external politic past year iron tool powerful administration pretty bad recap special effect interesting build acting good jeff bridges robert downey junior fantastic general consider average robert robert   straightforward feel emotion political message think world past year especially beginning turn   course mature category teenager deeply detail overall boring bad [SEP] ENTLBL_PERSON ENTTXT_jeff_bridges ENTLBL_PERSON ENTTXT_robert_downey_junior ENTLBL_PERSON ENTTXT_robert_robert___straightforward ENTLBL_PERSON ENTTXT_robert_robert___straightforward_feel</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8961,20 +6937,10 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -8998,12 +6964,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>fairly simplistic steve rogers skinny boy kick lot heart big german scientist discover eventually enlist army 12th try super soldier program superhero captain america main villain johann schmidt whilst outrageous villain sadly boring place like worthy adversary captain america</t>
+          <t>ENTLBL_PERSON ENTTXT_steve ENTLBL_ORG ENTTXT_superhero ENTLBL_PERSON ENTTXT_villain_johann</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>fairly simplistic steve rogers skinny boy get kick lot heart big german scientist discover eventually enlist army 12th try super soldier program superhero captain america main villain johann schmidt whilst outrageous villain sadly boring place like worthy adversary captain america establish favourite cinematic future leader wear heart sleeve die countryworld second thought fairly simplistic steve rogers skinny boy kick lot heart big german scientist discover eventually enlist army 12th try super soldier program superhero captain america main villain johann schmidt whilst outrageous villain sadly boring place like worthy adversary captain america establish favourite cinematic future leader wear heart sleeve die countryworld second thought fairly simplistic steve rogers skinny boy kick lot heart big german scientist discover eventually enlist army 12th try super soldier program superhero captain america main villain johann schmidt whilst outrageous villain sadly boring place like worthy adversary captain america</t>
+          <t>fairly simplistic steve rogers skinny boy get kick lot heart big german scientist discover eventually enlist army 12th try super soldier program superhero captain america main villain johann schmidt whilst outrageous villain sadly boring place like worthy adversary captain america establish favourite cinematic future leader wear heart sleeve die countryworld second thought fairly simplistic steve rogers skinny boy kick lot heart big german scientist discover eventually enlist army 12th try super soldier program superhero captain america main villain johann schmidt whilst outrageous villain sadly boring place like worthy adversary captain america establish favourite cinematic future leader wear heart sleeve die countryworld second thought [SEP] ENTLBL_PERSON ENTTXT_steve ENTLBL_ORG ENTTXT_superhero ENTLBL_PERSON ENTTXT_villain_johann</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -9018,20 +6984,10 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9053,14 +7009,10 @@
           <t>understand hype not understand masterpiece not set standard serviceable well people remember fondly completely escape provide original guardian galaxy comic_strip suck hard understand hype understand masterpiece set standard serviceable people remember fondly completely escape provide original guardian galaxy comic_strip suck hard</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>understand hype understand masterpiece set standard serviceable people remember fondly completely escape provide original guardian galaxy comic_strip suck hard</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>understand hype not understand masterpiece not set standard serviceable well people remember fondly completely escape provide original guardian galaxy comic_strip suck hard understand hype understand masterpiece set standard serviceable people remember fondly completely escape provide original guardian galaxy comic_strip suck hard understand hype understand masterpiece set standard serviceable people remember fondly completely escape provide original guardian galaxy comic_strip suck hard</t>
+          <t>understand hype not understand masterpiece not set standard serviceable well people remember fondly completely escape provide original guardian galaxy comic_strip suck hard understand hype understand masterpiece set standard serviceable people remember fondly completely escape provide original guardian galaxy comic_strip suck hard [SEP]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9075,20 +7027,10 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9112,12 +7054,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>new york newyork iron 3 freakinglegendary ous start phase 2 robert downey junior wereyou alwayswe know away trick toy money suit fix mechanic   mandarinnever comingreally guy pearce great job gwyneth outstanding shane black hat shane black know anxiety attack start phase 2</t>
+          <t>ENTLBL_PERSON ENTTXT_robert_downey</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>nothing new york nothing newyork see iron 3 freakinglegendary ous start phase 2 robert downey junior wereyou alwayswe know away trick toy money suit fix mechanic   mandarinnever see comingreally guy pearce great job gwyneth outstanding shane black hat shane black not know anxiety attack end iron trilogy start phase 2 not thing not away   iron new york newyork iron 3 freakinglegendary ous start phase 2 robert downey junior wereyou alwayswe know away trick toy money suit fix mechanic   mandarinnever comingreally guy pearce great job gwyneth outstanding shane black hat shane black know anxiety attack end iron trilogy start phase 2 thing away   iron new york newyork iron 3 freakinglegendary ous start phase 2 robert downey junior wereyou alwayswe know away trick toy money suit fix mechanic   mandarinnever comingreally guy pearce great job gwyneth outstanding shane black hat shane black know anxiety attack start phase 2</t>
+          <t>nothing new york nothing newyork see iron 3 freakinglegendary ous start phase 2 robert downey junior wereyou alwayswe know away trick toy money suit fix mechanic   mandarinnever see comingreally guy pearce great job gwyneth outstanding shane black hat shane black not know anxiety attack end iron trilogy start phase 2 not thing not away   iron new york newyork iron 3 freakinglegendary ous start phase 2 robert downey junior wereyou alwayswe know away trick toy money suit fix mechanic   mandarinnever comingreally guy pearce great job gwyneth outstanding shane black hat shane black know anxiety attack end iron trilogy start phase 2 thing away   iron [SEP] ENTLBL_PERSON ENTTXT_robert_downey</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -9132,20 +7074,10 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9167,14 +7099,10 @@
           <t>enjoyable action romp improve thor nicely pace excellent action eagerness clear audience go big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula enjoyable action romp improve thor nicely pace excellent action eagerness clear audience big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>nicely pace excellent action eagerness clear audience big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>enjoyable action romp improve thor nicely pace excellent action eagerness clear audience go big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula enjoyable action romp improve thor nicely pace excellent action eagerness clear audience big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula nicely pace excellent action eagerness clear audience big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula</t>
+          <t>enjoyable action romp improve thor nicely pace excellent action eagerness clear audience go big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula enjoyable action romp improve thor nicely pace excellent action eagerness clear audience big action early lot chaotic noise like peaceful abandon building catch interest stay catch coherent instantly noticeable plot hole hope typical superhero nice surprise good woah moment performance good certainly formulaic use formula [SEP]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -9189,20 +7117,10 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9226,12 +7144,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>bore action flat storyline force drama black widow completely forgettable merit black widow quickly devolve formula checklist people florence pugh highlight star sure intend yelena interesting instead natasha chemistry pugh johansson decent initial fight widow task master cool family drama force dinner table flat comedy drama order create artificial conflict main cast task master eventually seat forced family drama reveal end predictable action disappointing aspect exciting fight quick cut hide stunt double list actor big money effort learn choreography understand heck fight constant reminder m stunt double fight 3rd act computer generate imagery battle happen natasha turn computer generate imagery bore action dull lifeless problem action slick bore style grit black widow disney afraid chance tone style instead solo suspense fill ground million time miss opportunity ground superhero feel real sort like nolan batman trilogy eventually end black widow overlong final battle super happy natasha change hair color happy leave theatre yawn black widow pure formula chance deviate path set year previous convenient tidy want roll eye black widow gasp excitement tremble suspense tear invest comfort food black widow thing likely easy right dumb review like review sad look review imdb dislike differ opinion fit category m sure black widow high production value equal substance love black widow hate f9 difference</t>
+          <t>ENTLBL_ORG ENTTXT_f9</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>bore action flat storyline force drama black widow completely forgettable merit black widow quickly devolve formula checklist people say florence pugh highlight say star sure intend yelena interesting instead natasha chemistry pugh johansson decent initial fight widow task master cool family drama force dinner table move flat comedy drama order create artificial conflict main cast task master eventually take seat forced family drama reveal end predictable action disappointing aspect exciting well movie fight quick cut hide stunt double list actor big money not effort learn choreography understand heck go fight constant reminder m watch stunt double take fight 3rd act computer generate imagery battle happen natasha turn computer generate imagery bore action dull lifeless problem action slick bore style grit black widow disney afraid chance tone style instead make solo suspense fill ground see million time miss opportunity ground superhero feel real sort like nolan batman trilogy eventually end black widow overlong final battle super happy natasha change hair color happy leave theatre yawn black widow pure formula take chance deviate path set year previous film convenient tidy want roll eye black widow gasp excitement tremble suspense tear invest comfort food black widow thing likely easy right dumb review like review sad look review imdb dislike differ opinion fit category m sure black widow high production value equal substance love black widow hate f9 difference bore action flat storyline force drama black widow completely forgettable merit black widow quickly devolve formula checklist people florence pugh highlight star sure intend yelena interesting instead natasha chemistry pugh johansson decent initial fight widow task master cool family drama force dinner table flat comedy drama order create artificial conflict main cast task master eventually seat forced family drama reveal end predictable action disappointing aspect exciting fight quick cut hide stunt double list actor big money effort learn choreography understand heck fight constant reminder m stunt double fight 3rd act computer generate imagery battle happen natasha turn computer generate imagery bore action dull lifeless problem action slick bore style grit black widow disney afraid chance tone style instead solo suspense fill ground million time miss opportunity ground superhero feel real sort like nolan batman trilogy eventually end black widow overlong final battle super happy natasha change hair color happy leave theatre yawn black widow pure formula chance deviate path set year previous convenient tidy want roll eye black widow gasp excitement tremble suspense tear invest comfort food black widow thing likely easy right dumb review like review sad look review imdb dislike differ opinion fit category m sure black widow high production value equal substance love black widow hate f9 difference bore action flat storyline force drama black widow completely forgettable merit black widow quickly devolve formula checklist people florence pugh highlight star sure intend yelena interesting instead natasha chemistry pugh johansson decent initial fight widow task master cool family drama force dinner table flat comedy drama order create artificial conflict main cast task master eventually seat forced family drama reveal end predictable action disappointing aspect exciting fight quick cut hide stunt double list actor big money effort learn choreography understand heck fight constant reminder m stunt double fight 3rd act computer generate imagery battle happen natasha turn computer generate imagery bore action dull lifeless problem action slick bore style grit black widow disney afraid chance tone style instead solo suspense fill ground million time miss opportunity ground superhero feel real sort like nolan batman trilogy eventually end black widow overlong final battle super happy natasha change hair color happy leave theatre yawn black widow pure formula chance deviate path set year previous convenient tidy want roll eye black widow gasp excitement tremble suspense tear invest comfort food black widow thing likely easy right dumb review like review sad look review imdb dislike differ opinion fit category m sure black widow high production value equal substance love black widow hate f9 difference</t>
+          <t>bore action flat storyline force drama black widow completely forgettable merit black widow quickly devolve formula checklist people say florence pugh highlight say star sure intend yelena interesting instead natasha chemistry pugh johansson decent initial fight widow task master cool family drama force dinner table move flat comedy drama order create artificial conflict main cast task master eventually take seat forced family drama reveal end predictable action disappointing aspect exciting well movie fight quick cut hide stunt double list actor big money not effort learn choreography understand heck go fight constant reminder m watch stunt double take fight 3rd act computer generate imagery battle happen natasha turn computer generate imagery bore action dull lifeless problem action slick bore style grit black widow disney afraid chance tone style instead make solo suspense fill ground see million time miss opportunity ground superhero feel real sort like nolan batman trilogy eventually end black widow overlong final battle super happy natasha change hair color happy leave theatre yawn black widow pure formula take chance deviate path set year previous film convenient tidy want roll eye black widow gasp excitement tremble suspense tear invest comfort food black widow thing likely easy right dumb review like review sad look review imdb dislike differ opinion fit category m sure black widow high production value equal substance love black widow hate f9 difference bore action flat storyline force drama black widow completely forgettable merit black widow quickly devolve formula checklist people florence pugh highlight star sure intend yelena interesting instead natasha chemistry pugh johansson decent initial fight widow task master cool family drama force dinner table flat comedy drama order create artificial conflict main cast task master eventually seat forced family drama reveal end predictable action disappointing aspect exciting fight quick cut hide stunt double list actor big money effort learn choreography understand heck fight constant reminder m stunt double fight 3rd act computer generate imagery battle happen natasha turn computer generate imagery bore action dull lifeless problem action slick bore style grit black widow disney afraid chance tone style instead solo suspense fill ground million time miss opportunity ground superhero feel real sort like nolan batman trilogy eventually end black widow overlong final battle super happy natasha change hair color happy leave theatre yawn black widow pure formula chance deviate path set year previous convenient tidy want roll eye black widow gasp excitement tremble suspense tear invest comfort food black widow thing likely easy right dumb review like review sad look review imdb dislike differ opinion fit category m sure black widow high production value equal substance love black widow hate f9 difference [SEP] ENTLBL_ORG ENTTXT_f9</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9246,20 +7164,10 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9281,14 +7189,10 @@
           <t>fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide movie good moment cameo plentiful handle give fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic film plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit not push boundary storytelling development ve see previous deadpool film laugh action fan service will not disappoint look depth compelling narrative leave feel bit unsatisfied good time movie alcohol require cinematic savior hop fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide good moment cameo plentiful handle fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit push boundary storytelling development ve previous deadpool laugh action fan service disappoint look depth compelling narrative leave feel bit unsatisfied good time alcohol require cinematic savior hop</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide good moment cameo plentiful handle fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit push boundary storytelling development ve previous deadpool laugh action fan service disappoint look depth compelling narrative leave feel bit unsatisfied good time alcohol require cinematic savior hop</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide movie good moment cameo plentiful handle give fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic film plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit not push boundary storytelling development ve see previous deadpool film laugh action fan service will not disappoint look depth compelling narrative leave feel bit unsatisfied good time movie alcohol require cinematic savior hop fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide good moment cameo plentiful handle fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit push boundary storytelling development ve previous deadpool laugh action fan service disappoint look depth compelling narrative leave feel bit unsatisfied good time alcohol require cinematic savior hop fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide good moment cameo plentiful handle fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit push boundary storytelling development ve previous deadpool laugh action fan service disappoint look depth compelling narrative leave feel bit unsatisfied good time alcohol require cinematic savior hop</t>
+          <t>fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide movie good moment cameo plentiful handle give fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic film plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit not push boundary storytelling development ve see previous deadpool film laugh action fan service will not disappoint look depth compelling narrative leave feel bit unsatisfied good time movie alcohol require cinematic savior hop fun uneven mashup deadpool   wolverine deliver mix high energy action crude humor feel like love letter fan bit chaotic mess ryan reynolds hugh jackmans chemistry glue hold banter dynamic genuinely entertaining provide good moment cameo plentiful handle fan fox delightful send integrate plot action particularly car fight execute flair making visually satisfying sequence recent cinematic plot feel like afterthought overshadow barrage cameo humor thin narrative thread exist string gag surprise guest humor hit miss plenty laughter relentless cursing juvenile gag wear thin viewer feel like attempt prove r rating enhance feel self aware detriment fourth wall break meta commentary pull experience enhance deadpool   wolverine fun somewhat overwhelming ride celebration inhabit push boundary storytelling development ve previous deadpool laugh action fan service disappoint look depth compelling narrative leave feel bit unsatisfied good time alcohol require cinematic savior hop [SEP]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -9303,20 +7207,10 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9338,14 +7232,10 @@
           <t>different people   spoiler   not rave review infinity war yes action great yes special effect great yes pretty good balance different see favourite meet favourite great not understand people rave end   spoiler reminder   give know film pipeline spidey guardian main kill pointless know go resurrect infinity war 2 new stand film release   time reversal diving soul stone   simply mean go resurrect know thano like insignificant blip radar possibly get undo jarring not believe second death real ie black panther spidey guardian   know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people say end aiw heart wrench gullible people know m kind viewer not critique m watch like enjoy experience absorb event unfold aiw not work writer bite way chew want rate 2 star m disappointed ending mention lot good thing different people   spoiler   rave review infinity war yes action great yes special effect great yes pretty good balance different favourite meet favourite great understand people rave end   spoiler reminder   know pipeline spidey guardian main kill pointless know resurrect infinity war 2 new stand release   time reversal diving soul stone   simply mean resurrect know thano like insignificant blip radar possibly undo jarring believe second death real ie black panther spidey guardian   know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people end aiw heart wrench gullible people know m kind viewer critique m like enjoy experience absorb event unfold aiw work writer bite way chew want rate 2 star m disappointed ending mention lot good thing</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>different people   spoiler   rave review infinity war yes action great yes special effect great yes pretty good balance different favourite meet favourite great understand people rave end   spoiler reminder   know pipeline spidey guardian main kill pointless know resurrect infinity war 2 new stand release   time reversal diving soul stone   simply mean resurrect know thano like insignificant blip radar possibly undo jarring believe second death real ie know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people end aiw heart wrench gullible people know m kind viewer critique m like enjoy experience absorb event unfold aiw work writer bite way chew want rate 2 star m disappointed ending mention lot good thing</t>
-        </is>
-      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>different people   spoiler   not rave review infinity war yes action great yes special effect great yes pretty good balance different see favourite meet favourite great not understand people rave end   spoiler reminder   give know film pipeline spidey guardian main kill pointless know go resurrect infinity war 2 new stand film release   time reversal diving soul stone   simply mean go resurrect know thano like insignificant blip radar possibly get undo jarring not believe second death real ie black panther spidey guardian   know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people say end aiw heart wrench gullible people know m kind viewer not critique m watch like enjoy experience absorb event unfold aiw not work writer bite way chew want rate 2 star m disappointed ending mention lot good thing different people   spoiler   rave review infinity war yes action great yes special effect great yes pretty good balance different favourite meet favourite great understand people rave end   spoiler reminder   know pipeline spidey guardian main kill pointless know resurrect infinity war 2 new stand release   time reversal diving soul stone   simply mean resurrect know thano like insignificant blip radar possibly undo jarring believe second death real ie black panther spidey guardian   know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people end aiw heart wrench gullible people know m kind viewer critique m like enjoy experience absorb event unfold aiw work writer bite way chew want rate 2 star m disappointed ending mention lot good thing different people   spoiler   rave review infinity war yes action great yes special effect great yes pretty good balance different favourite meet favourite great understand people rave end   spoiler reminder   know pipeline spidey guardian main kill pointless know resurrect infinity war 2 new stand release   time reversal diving soul stone   simply mean resurrect know thano like insignificant blip radar possibly undo jarring believe second death real ie know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people end aiw heart wrench gullible people know m kind viewer critique m like enjoy experience absorb event unfold aiw work writer bite way chew want rate 2 star m disappointed ending mention lot good thing</t>
+          <t>different people   spoiler   not rave review infinity war yes action great yes special effect great yes pretty good balance different see favourite meet favourite great not understand people rave end   spoiler reminder   give know film pipeline spidey guardian main kill pointless know go resurrect infinity war 2 new stand film release   time reversal diving soul stone   simply mean go resurrect know thano like insignificant blip radar possibly get undo jarring not believe second death real ie black panther spidey guardian   know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people say end aiw heart wrench gullible people know m kind viewer not critique m watch like enjoy experience absorb event unfold aiw not work writer bite way chew want rate 2 star m disappointed ending mention lot good thing different people   spoiler   rave review infinity war yes action great yes special effect great yes pretty good balance different favourite meet favourite great understand people rave end   spoiler reminder   know pipeline spidey guardian main kill pointless know resurrect infinity war 2 new stand release   time reversal diving soul stone   simply mean resurrect know thano like insignificant blip radar possibly undo jarring believe second death real ie black panther spidey guardian   know resurrect kill tension kill atmosphere mean cry parker know come time end credit stinger roll death occur snarl contemptuously screen bitterly disappointed honestly mean wholeheartedly feel like twilight super cool battle essentially dream happen plot device stunned hear people end aiw heart wrench gullible people know m kind viewer critique m like enjoy experience absorb event unfold aiw work writer bite way chew want rate 2 star m disappointed ending mention lot good thing [SEP]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9360,20 +7250,10 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9395,14 +7275,10 @@
           <t>magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor one early late viewer knowledge ve see cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people see long open mind concept superhero magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor early late viewer knowledge ve cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people long open mind concept superhero</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor early late viewer knowledge ve cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people long open mind concept superhero</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor one early late viewer knowledge ve see cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people see long open mind concept superhero magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor early late viewer knowledge ve cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people long open mind concept superhero magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor early late viewer knowledge ve cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people long open mind concept superhero</t>
+          <t>magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor one early late viewer knowledge ve see cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people see long open mind concept superhero magnificent return form action fight physical struggle hope superhero shin emotional core viewer familiar comic_strip encounter huge surprise term plot good minor early late viewer knowledge ve cinematic twist plot action explosion chase punch etc gravy compare resonantly movingly handle theme stand performance pugh pullman strong ensemble performance round cinematic fan d tentatively recommend people long open mind concept superhero [SEP]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9417,20 +7293,10 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9452,14 +7318,10 @@
           <t>tedious poorly film comic_strip good especially captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little exclusion incredible hulk thor considerable mistake villain non descript not interesting menacing opinion tony starkiron give screen time plot revolve huge disappointment tedious poorly comic_strip good especially captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little exclusion incredible hulk thor considerable mistake villain non descript interesting menacing opinion tony starkiron screen time plot revolve huge disappointment</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>tedious poorly captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little villain non descript interesting menace huge disappointment</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>tedious poorly film comic_strip good especially captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little exclusion incredible hulk thor considerable mistake villain non descript not interesting menacing opinion tony starkiron give screen time plot revolve huge disappointment tedious poorly comic_strip good especially captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little exclusion incredible hulk thor considerable mistake villain non descript interesting menacing opinion tony starkiron screen time plot revolve huge disappointment tedious poorly captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little villain non descript interesting menace huge disappointment</t>
+          <t>tedious poorly film comic_strip good especially captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little exclusion incredible hulk thor considerable mistake villain non descript not interesting menacing opinion tony starkiron give screen time plot revolve huge disappointment tedious poorly comic_strip good especially captain america civil war boring confusingly plot poorly act ending settle regard divide law restrict movement superhero hardly continuity narrative flat tyre dread computer generate imagery precious little exclusion incredible hulk thor considerable mistake villain non descript interesting menacing opinion tony starkiron screen time plot revolve huge disappointment [SEP]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9474,20 +7336,10 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9509,14 +7361,10 @@
           <t>not like end start strong end sad opinion end kind rough detail upcoming film series watch complete series chronological order black widow come 29th april not completely not enjoy not like end end like capture bandit assign not want not like end enjoy like end start strong end sad opinion end kind rough detail upcoming series complete series chronological order black widow come 29th april completely enjoy like end end like capture bandit assign want like end enjoy</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>like end start strong end sad opinion end kind rough detail upcoming series completely enjoy like end end like capture bandit assign want like end enjoy</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>not like end start strong end sad opinion end kind rough detail upcoming film series watch complete series chronological order black widow come 29th april not completely not enjoy not like end end like capture bandit assign not want not like end enjoy like end start strong end sad opinion end kind rough detail upcoming series complete series chronological order black widow come 29th april completely enjoy like end end like capture bandit assign want like end enjoy like end start strong end sad opinion end kind rough detail upcoming series completely enjoy like end end like capture bandit assign want like end enjoy</t>
+          <t>not like end start strong end sad opinion end kind rough detail upcoming film series watch complete series chronological order black widow come 29th april not completely not enjoy not like end end like capture bandit assign not want not like end enjoy like end start strong end sad opinion end kind rough detail upcoming series complete series chronological order black widow come 29th april completely enjoy like end end like capture bandit assign want like end enjoy [SEP]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9531,20 +7379,10 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9568,12 +7406,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>unpack brilliance iron 3 iron 3 direct shane black 2013 superhero thriller delve complexity tony stark expose vulnerability insecurity game changer cinematic offer fresh introspective perspective iconic superhero try find way cope anxiety ptsd new threat emerge form mandarin terrorist use advanced technology wreak havoc world time vulnerable tony grapple inner demon support cast include gwyneth paltrow don cheadle guy pearce deliver solid performance add depth action sequence iron 3 impressive cinematic standout aspect iron 3 exploration theme trauma vulnerability psychological effect superhero tony stark struggle anxiety ptsd relatable human iron 3 thought provoking visually stunning fan cinematic impressive action sequence solid performance exploration complex theme game changer superhero genre overall iron 3 brilliant offer unique think provoke perspective superhero genre impressive action sequence solid performance exploration complex theme fan cinematic</t>
+          <t>ENTLBL_PERSON ENTTXT_robert_downey_jr_shin ENTLBL_PERSON ENTTXT_gwyneth_paltrow_don ENTLBL_PERSON ENTTXT_tony_stark_struggle_anxiety_ptsd</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>unpack brilliance iron 3 iron 3 direct shane black 2013 superhero thriller delve complexity tony stark expose vulnerability insecurity game changer cinematic offer fresh introspective perspective iconic superhero take place event tony stark struggle come term trauma experience alien invasion try find way cope anxiety ptsd new threat emerge form mandarin terrorist advanced technology wreak havoc world robert downey jr shin tony starkiron bring signature wit charm role time vulnerable tony grapple inner demon support cast include gwyneth paltrow don cheadle guy pearce deliver solid performance add depth action sequence iron 3 impressive cinematic movie visual stunning iron suit look sleek advanced film climax feature epic battle iron mandarin minion thrill visually stunning standout aspect iron 3 exploration theme trauma vulnerability psychological effect superhero show tony stark struggle anxiety ptsd make relatable human touch theme identity tony stark grapple question iron suit iron 3 thought provoking visually stunning fan cinematic impressive action sequence solid performance exploration complex theme game changer superhero genre overall iron 3 brilliant offer unique think provoke perspective superhero genre impressive action sequence solid performance exploration complex theme fan cinematic unpack brilliance iron 3 iron 3 direct shane black 2013 superhero thriller delve complexity tony stark expose vulnerability insecurity game changer cinematic offer fresh introspective perspective iconic superhero place event tony stark struggle come term trauma experience alien invasion try find way cope anxiety ptsd new threat emerge form mandarin terrorist use advanced technology wreak havoc world robert downey jr shin tony starkiron bring signature wit charm role time vulnerable tony grapple inner demon support cast include gwyneth paltrow don cheadle guy pearce deliver solid performance add depth action sequence iron 3 impressive cinematic visual stunning iron suit look sleek advanced climax feature epic battle iron mandarin minion thrill visually stunning standout aspect iron 3 exploration theme trauma vulnerability psychological effect superhero tony stark struggle anxiety ptsd relatable human touch theme identity tony stark grapple question iron suit iron 3 thought provoking visually stunning fan cinematic impressive action sequence solid performance exploration complex theme game changer superhero genre overall iron 3 brilliant offer unique think provoke perspective superhero genre impressive action sequence solid performance exploration complex theme fan cinematic unpack brilliance iron 3 iron 3 direct shane black 2013 superhero thriller delve complexity tony stark expose vulnerability insecurity game changer cinematic offer fresh introspective perspective iconic superhero try find way cope anxiety ptsd new threat emerge form mandarin terrorist use advanced technology wreak havoc world time vulnerable tony grapple inner demon support cast include gwyneth paltrow don cheadle guy pearce deliver solid performance add depth action sequence iron 3 impressive cinematic standout aspect iron 3 exploration theme trauma vulnerability psychological effect superhero tony stark struggle anxiety ptsd relatable human iron 3 thought provoking visually stunning fan cinematic impressive action sequence solid performance exploration complex theme game changer superhero genre overall iron 3 brilliant offer unique think provoke perspective superhero genre impressive action sequence solid performance exploration complex theme fan cinematic</t>
+          <t>unpack brilliance iron 3 iron 3 direct shane black 2013 superhero thriller delve complexity tony stark expose vulnerability insecurity game changer cinematic offer fresh introspective perspective iconic superhero take place event tony stark struggle come term trauma experience alien invasion try find way cope anxiety ptsd new threat emerge form mandarin terrorist advanced technology wreak havoc world robert downey jr shin tony starkiron bring signature wit charm role time vulnerable tony grapple inner demon support cast include gwyneth paltrow don cheadle guy pearce deliver solid performance add depth action sequence iron 3 impressive cinematic movie visual stunning iron suit look sleek advanced film climax feature epic battle iron mandarin minion thrill visually stunning standout aspect iron 3 exploration theme trauma vulnerability psychological effect superhero show tony stark struggle anxiety ptsd make relatable human touch theme identity tony stark grapple question iron suit iron 3 thought provoking visually stunning fan cinematic impressive action sequence solid performance exploration complex theme game changer superhero genre overall iron 3 brilliant offer unique think provoke perspective superhero genre impressive action sequence solid performance exploration complex theme fan cinematic unpack brilliance iron 3 iron 3 direct shane black 2013 superhero thriller delve complexity tony stark expose vulnerability insecurity game changer cinematic offer fresh introspective perspective iconic superhero place event tony stark struggle come term trauma experience alien invasion try find way cope anxiety ptsd new threat emerge form mandarin terrorist use advanced technology wreak havoc world robert downey jr shin tony starkiron bring signature wit charm role time vulnerable tony grapple inner demon support cast include gwyneth paltrow don cheadle guy pearce deliver solid performance add depth action sequence iron 3 impressive cinematic visual stunning iron suit look sleek advanced climax feature epic battle iron mandarin minion thrill visually stunning standout aspect iron 3 exploration theme trauma vulnerability psychological effect superhero tony stark struggle anxiety ptsd relatable human touch theme identity tony stark grapple question iron suit iron 3 thought provoking visually stunning fan cinematic impressive action sequence solid performance exploration complex theme game changer superhero genre overall iron 3 brilliant offer unique think provoke perspective superhero genre impressive action sequence solid performance exploration complex theme fan cinematic [SEP] ENTLBL_PERSON ENTTXT_robert_downey_jr_shin ENTLBL_PERSON ENTTXT_gwyneth_paltrow_don ENTLBL_PERSON ENTTXT_tony_stark_struggle_anxiety_ptsd</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9588,20 +7426,10 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9625,12 +7453,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>enjoyable mixed bag black widow mix view near end beginningopene credit pretty good care family time action sequence veer ff territory chase sequence moment play dark dramatically think elevate play laugh mcu scarlet johansson reliable role natasha romanov like florence pugh sister stand david harbour steal screen task master huge disappointment read opening credit fan recognise like happen realise easily</t>
+          <t>ENTLBL_PERSON ENTTXT_david_harbour</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>enjoyable mixed bag get black widow mix view end cinematic movie like ultron iron 3 thor 2 near end beginningopene credit pretty good make care family time action sequence veer ff territory take chase sequence moment play dark dramatically think elevate play laugh mcu scarlet johansson reliable role natasha romanov like florence pugh sister stand david harbour not give steal screen task master huge disappointment read name opening credit fan recognise like happen realise easily enjoyable mixed bag black widow mix view end cinematic like ultron iron 3 thor 2 near end beginningopene credit pretty good care family time action sequence veer ff territory chase sequence moment play dark dramatically think elevate play laugh mcu scarlet johansson reliable role natasha romanov like florence pugh sister stand david harbour steal screen task master huge disappointment read opening credit fan recognise like happen realise easily enjoyable mixed bag black widow mix view near end beginningopene credit pretty good care family time action sequence veer ff territory chase sequence moment play dark dramatically think elevate play laugh mcu scarlet johansson reliable role natasha romanov like florence pugh sister stand david harbour steal screen task master huge disappointment read opening credit fan recognise like happen realise easily</t>
+          <t>enjoyable mixed bag get black widow mix view end cinematic movie like ultron iron 3 thor 2 near end beginningopene credit pretty good make care family time action sequence veer ff territory take chase sequence moment play dark dramatically think elevate play laugh mcu scarlet johansson reliable role natasha romanov like florence pugh sister stand david harbour not give steal screen task master huge disappointment read name opening credit fan recognise like happen realise easily enjoyable mixed bag black widow mix view end cinematic like ultron iron 3 thor 2 near end beginningopene credit pretty good care family time action sequence veer ff territory chase sequence moment play dark dramatically think elevate play laugh mcu scarlet johansson reliable role natasha romanov like florence pugh sister stand david harbour steal screen task master huge disappointment read opening credit fan recognise like happen realise easily [SEP] ENTLBL_PERSON ENTTXT_david_harbour</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9645,20 +7473,10 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9682,12 +7500,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>way narrative address discussion evolution humanity representation diversity different follow group super power come earth specific mission celestial arishem voice david kaye   end threat deviant monster process help humanity evolve involve conflict arrive world dawn human civilization time immerse planet culture cling mix protege lack tone change rampant fanservice immense need connect cinematic cinematic generate lot friction fan producer lover raise important question example worth follow share moviesserie need connected independent eternal come promise great freshness saturate mainly count chloe zhao head project director screenwriter win oscar nomadland good picture good director fact kevin feige executive producer allow zhao work lot freedom despite product eternal positively differentiate count director creative vision wide open aspect mixture astronaut god gnosticism superhero work zhao choose brake action know new protagonist depth relate world live essential connect patience cinematic demand audience big point fight 10 minute unbridle rush need relationship human thing come near divine slow pace different formula present decade result interesting important thing eternal truly captivate dynamic god set origin protagonist easy task especially know public great merit eternal able present develop immortal dedicate good script know affectionate understand member group personality way world team hero eternal large diverse cast varied history genre irregular normal come different personality age different genre sersis gemma chan passion humanity kingos kumail nanjiani narcissism goblin lia mchugh frustration nature new hero portray unique personality set apart rest equally interesting captivate highlight moment mix typical humor particularity work richard maddens ikaris great despite actor limit performance main challenge script reconcile wide range strong cast highlight develop relevant succeed little screen time appear feel lack depth central present interesting contexts background personality follow simple archetype create impression hero necessarily mean bad overall dynamic member work chemistry charismatic time dynamic key work real tension script group defeat deviant save world different way look humanity mission ve clash conflict work people need care eternal time relationship explore eternal hit brake use mcu instead action sequence plot celerity sense urgency dedicate relationship ikaris sersi justify mutual admiration gilgamesh don lee thena angelina jolie explain druig barry keoghan disagree brother method narrative linear alternate present day important moment human history forth flashback way time follow trajectory hero lead situation definitely break standard set care lot tell inflate cinematic reference warning upcoming influence present unfortunately negative way needlessly tune serve bring comic relief bad funny work totally break rhythm long seriously furthermore inconsistency difficult swallow especially involve reason deviant exist impression leave end alien purpose compose action yes problem eternal digital effect impressive arm interesting secondary arouse feeling semi villain poorly explore feeling place despite script notable hole duration excessively long deliver good engaging bring freshness badly need thank chloe zhao eternal personality remarkable great direction actor director bring naturalistic perspective filming value detail combat choreography advantage ability eternal visual impact offer compose impactful stunning real location eternal beautiful term look message union love convey viewer soundtrack noteworthy complete epic setting emphasize emotional moment punctuate amplify effect happen screen peculiar point despite soberer contemplative tone use mcu long afraid reference disney franchise competitor dc comic_strip respond fan ask question like eternal help fight thano interesting direct honest wide open answer big screen addition way narrative address discussion evolution humanity representation diversity different banal production lead case feature genre eternal slip deliver solid work care illustrious stranger dynamic god sustain plot twist conflict necessary weight impact design come future cinematic tremendous success bring like chloe zhao bring identity body soul project wrong intervene connect cinematic director screenwriter vision essential good attach mcu remain continue bring zhao professional good exactly need director bring personality trait public expectation anxiety great monster create struggle tame audience sure find eternal interesting thing cinematic offer long time</t>
+          <t>ENTLBL_PERSON ENTTXT_david_kaye ENTLBL_PERSON ENTTXT_kevin ENTLBL_PERSON ENTTXT_richard_maddens ENTLBL_PERSON ENTTXT_don_lee_thena_angelina_jolie_explain ENTLBL_PERSON ENTTXT_barry_keoghan ENTLBL_ORG ENTTXT_linear</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>way narrative address discussion evolution humanity representation diversity make different film follow group super power being come earth specific mission give celestial arishem voice david kaye   end threat deviant monster process help humanity evolve involve conflict arrive world dawn human civilization time immerse planet culture cling mix protege lack tone change rampant fanservice immense need connect cinematic cinematic generate lot friction fan producer lover raise important question example worth follow share moviesserie need connected not independent eternal come promise give great freshness saturate mainly count chloe zhao head project director screenwriter win oscar nomadland good picture good director fact kevin feige executive producer allow zhao work lot freedom despite product eternal positively differentiate count director creative vision wide open aspect mixture astronaut god gnosticism superhero work zhao choose brake action know new protagonist depth relate world live essential connect take patience cinematic demand audience big point fight 10 minute unbridle rush need relationship human thing come near divine being slow pace different formula present decade result interesting story important thing eternal make truly captivate dynamic marvel god set origin protagonist easy task especially know public great merit eternal able present develop immortal being dedicate good script know affectionate understand member group personality way see world team hero eternal large diverse cast varied history genre irregular normal come different personality age different genre sersis gemma chan passion humanity kingos kumail nanjiani narcissism goblin lia mchugh frustration nature new hero portray unique personality set apart rest equally interesting captivate highlight moment mix typical humor particularity work well richard maddens ikaris great despite actor limit performance main challenge script reconcile wide range strong cast highlight develop make relevant succeed little screen time appear feel lack depth central present interesting contexts background personality follow simple archetype create impression hero not necessarily mean bad overall dynamic member work chemistry charismatic time dynamic key make work real tension script not group defeat deviant save world different way look humanity mission ve give clash conflict work people need care eternal say take time relationship explore eternal hit brake see mcu instead have action sequence plot celerity sense urgency dedicate show relationship ikaris sersi justify mutual admiration gilgamesh don lee thena angelina jolie explain druig barry keoghan disagree brother method narrative linear alternate present day important moment human history go forth flashback way time follow trajectory hero get lead situation definitely break standard set care lot tell inflate cinematic reference warning upcoming movie influence present unfortunately negative way needlessly tune serve bring comic relief bad funny work totally break rhythm long take seriously furthermore inconsistency difficult swallow especially involve reason deviant exist impression leave end alien being purpose compose action yes problem eternal digital effect impressive arm interesting secondary not arouse feeling semi villain poorly explore feeling not place despite script have notable hole film duration excessively long deliver good engaging bring freshness badly need thank chloe zhao eternal film personality remarkable great direction actor director bring naturalistic perspective filming value detail full combat choreography take advantage ability eternal visual impact offer compose impactful stunning film real location eternal beautiful term look message union love convey viewer soundtrack noteworthy complete epic setting emphasize emotional moment punctuate amplify effect happen screen peculiar point despite soberer contemplative tone mcu long afraid reference disney franchise competitor dc comic_strip respond fan ask question like not eternal help fight thano interesting direct honest wide open answer big screen addition way narrative address discussion evolution humanity representation diversity make different banal production lead case feature film genre eternal slip deliver solid work make care illustrious stranger dynamic god sustain plot make twist conflict necessary weight impact design come future cinematic tremendous success bring like chloe zhao bring identity body soul project wrong intervene connect cinematic director screenwriter vision essential good have attach mcu remain see continue bring zhao professional good exactly film need director bring personality trait film shadow create endgame problem phase 4 public expectation anxiety great monster create struggle tame audience sure find eternal interesting thing cinematic offer long time way narrative address discussion evolution humanity representation diversity different follow group super power come earth specific mission celestial arishem voice david kaye   end threat deviant monster process help humanity evolve involve conflict arrive world dawn human civilization time immerse planet culture cling mix protege lack tone change rampant fanservice immense need connect cinematic cinematic generate lot friction fan producer lover raise important question example worth follow share moviesserie need connected independent eternal come promise great freshness saturate mainly count chloe zhao head project director screenwriter win oscar nomadland good picture good director fact kevin feige executive producer allow zhao work lot freedom despite product eternal positively differentiate count director creative vision wide open aspect mixture astronaut god gnosticism superhero work zhao choose brake action know new protagonist depth relate world live essential connect patience cinematic demand audience big point fight 10 minute unbridle rush need relationship human thing come near divine slow pace different formula present decade result interesting important thing eternal truly captivate dynamic god set origin protagonist easy task especially know public great merit eternal able present develop immortal dedicate good script know affectionate understand member group personality way world team hero eternal large diverse cast varied history genre irregular normal come different personality age different genre sersis gemma chan passion humanity kingos kumail nanjiani narcissism goblin lia mchugh frustration nature new hero portray unique personality set apart rest equally interesting captivate highlight moment mix typical humor particularity work richard maddens ikaris great despite actor limit performance main challenge script reconcile wide range strong cast highlight develop relevant succeed little screen time appear feel lack depth central present interesting contexts background personality follow simple archetype create impression hero necessarily mean bad overall dynamic member work chemistry charismatic time dynamic key work real tension script group defeat deviant save world different way look humanity mission ve clash conflict work people need care eternal time relationship explore eternal hit brake use mcu instead action sequence plot celerity sense urgency dedicate relationship ikaris sersi justify mutual admiration gilgamesh don lee thena angelina jolie explain druig barry keoghan disagree brother method narrative linear alternate present day important moment human history forth flashback way time follow trajectory hero lead situation definitely break standard set care lot tell inflate cinematic reference warning upcoming influence present unfortunately negative way needlessly tune serve bring comic relief bad funny work totally break rhythm long seriously furthermore inconsistency difficult swallow especially involve reason deviant exist impression leave end alien purpose compose action yes problem eternal digital effect impressive arm interesting secondary arouse feeling semi villain poorly explore feeling place despite script notable hole duration excessively long deliver good engaging bring freshness badly need thank chloe zhao eternal personality remarkable great direction actor director bring naturalistic perspective filming value detail combat choreography advantage ability eternal visual impact offer compose impactful stunning real location eternal beautiful term look message union love convey viewer soundtrack noteworthy complete epic setting emphasize emotional moment punctuate amplify effect happen screen peculiar point despite soberer contemplative tone use mcu long afraid reference disney franchise competitor dc comic_strip respond fan ask question like eternal help fight thano interesting direct honest wide open answer big screen addition way narrative address discussion evolution humanity representation diversity different banal production lead case feature genre eternal slip deliver solid work care illustrious stranger dynamic god sustain plot twist conflict necessary weight impact design come future cinematic tremendous success bring like chloe zhao bring identity body soul project wrong intervene connect cinematic director screenwriter vision essential good attach mcu remain continue bring zhao professional good exactly need director bring personality trait shadow create endgame problem phase 4 public expectation anxiety great monster create struggle tame audience sure find eternal interesting thing cinematic offer long time way narrative address discussion evolution humanity representation diversity different follow group super power come earth specific mission celestial arishem voice david kaye   end threat deviant monster process help humanity evolve involve conflict arrive world dawn human civilization time immerse planet culture cling mix protege lack tone change rampant fanservice immense need connect cinematic cinematic generate lot friction fan producer lover raise important question example worth follow share moviesserie need connected independent eternal come promise great freshness saturate mainly count chloe zhao head project director screenwriter win oscar nomadland good picture good director fact kevin feige executive producer allow zhao work lot freedom despite product eternal positively differentiate count director creative vision wide open aspect mixture astronaut god gnosticism superhero work zhao choose brake action know new protagonist depth relate world live essential connect patience cinematic demand audience big point fight 10 minute unbridle rush need relationship human thing come near divine slow pace different formula present decade result interesting important thing eternal truly captivate dynamic god set origin protagonist easy task especially know public great merit eternal able present develop immortal dedicate good script know affectionate understand member group personality way world team hero eternal large diverse cast varied history genre irregular normal come different personality age different genre sersis gemma chan passion humanity kingos kumail nanjiani narcissism goblin lia mchugh frustration nature new hero portray unique personality set apart rest equally interesting captivate highlight moment mix typical humor particularity work richard maddens ikaris great despite actor limit performance main challenge script reconcile wide range strong cast highlight develop relevant succeed little screen time appear feel lack depth central present interesting contexts background personality follow simple archetype create impression hero necessarily mean bad overall dynamic member work chemistry charismatic time dynamic key work real tension script group defeat deviant save world different way look humanity mission ve clash conflict work people need care eternal time relationship explore eternal hit brake use mcu instead action sequence plot celerity sense urgency dedicate relationship ikaris sersi justify mutual admiration gilgamesh don lee thena angelina jolie explain druig barry keoghan disagree brother method narrative linear alternate present day important moment human history forth flashback way time follow trajectory hero lead situation definitely break standard set care lot tell inflate cinematic reference warning upcoming influence present unfortunately negative way needlessly tune serve bring comic relief bad funny work totally break rhythm long seriously furthermore inconsistency difficult swallow especially involve reason deviant exist impression leave end alien purpose compose action yes problem eternal digital effect impressive arm interesting secondary arouse feeling semi villain poorly explore feeling place despite script notable hole duration excessively long deliver good engaging bring freshness badly need thank chloe zhao eternal personality remarkable great direction actor director bring naturalistic perspective filming value detail combat choreography advantage ability eternal visual impact offer compose impactful stunning real location eternal beautiful term look message union love convey viewer soundtrack noteworthy complete epic setting emphasize emotional moment punctuate amplify effect happen screen peculiar point despite soberer contemplative tone use mcu long afraid reference disney franchise competitor dc comic_strip respond fan ask question like eternal help fight thano interesting direct honest wide open answer big screen addition way narrative address discussion evolution humanity representation diversity different banal production lead case feature genre eternal slip deliver solid work care illustrious stranger dynamic god sustain plot twist conflict necessary weight impact design come future cinematic tremendous success bring like chloe zhao bring identity body soul project wrong intervene connect cinematic director screenwriter vision essential good attach mcu remain continue bring zhao professional good exactly need director bring personality trait public expectation anxiety great monster create struggle tame audience sure find eternal interesting thing cinematic offer long time</t>
+          <t>way narrative address discussion evolution humanity representation diversity make different film follow group super power being come earth specific mission give celestial arishem voice david kaye   end threat deviant monster process help humanity evolve involve conflict arrive world dawn human civilization time immerse planet culture cling mix protege lack tone change rampant fanservice immense need connect cinematic cinematic generate lot friction fan producer lover raise important question example worth follow share moviesserie need connected not independent eternal come promise give great freshness saturate mainly count chloe zhao head project director screenwriter win oscar nomadland good picture good director fact kevin feige executive producer allow zhao work lot freedom despite product eternal positively differentiate count director creative vision wide open aspect mixture astronaut god gnosticism superhero work zhao choose brake action know new protagonist depth relate world live essential connect take patience cinematic demand audience big point fight 10 minute unbridle rush need relationship human thing come near divine being slow pace different formula present decade result interesting story important thing eternal make truly captivate dynamic marvel god set origin protagonist easy task especially know public great merit eternal able present develop immortal being dedicate good script know affectionate understand member group personality way see world team hero eternal large diverse cast varied history genre irregular normal come different personality age different genre sersis gemma chan passion humanity kingos kumail nanjiani narcissism goblin lia mchugh frustration nature new hero portray unique personality set apart rest equally interesting captivate highlight moment mix typical humor particularity work well richard maddens ikaris great despite actor limit performance main challenge script reconcile wide range strong cast highlight develop make relevant succeed little screen time appear feel lack depth central present interesting contexts background personality follow simple archetype create impression hero not necessarily mean bad overall dynamic member work chemistry charismatic time dynamic key make work real tension script not group defeat deviant save world different way look humanity mission ve give clash conflict work people need care eternal say take time relationship explore eternal hit brake see mcu instead have action sequence plot celerity sense urgency dedicate show relationship ikaris sersi justify mutual admiration gilgamesh don lee thena angelina jolie explain druig barry keoghan disagree brother method narrative linear alternate present day important moment human history go forth flashback way time follow trajectory hero get lead situation definitely break standard set care lot tell inflate cinematic reference warning upcoming movie influence present unfortunately negative way needlessly tune serve bring comic relief bad funny work totally break rhythm long take seriously furthermore inconsistency difficult swallow especially involve reason deviant exist impression leave end alien being purpose compose action yes problem eternal digital effect impressive arm interesting secondary not arouse feeling semi villain poorly explore feeling not place despite script have notable hole film duration excessively long deliver good engaging bring freshness badly need thank chloe zhao eternal film personality remarkable great direction actor director bring naturalistic perspective filming value detail full combat choreography take advantage ability eternal visual impact offer compose impactful stunning film real location eternal beautiful term look message union love convey viewer soundtrack noteworthy complete epic setting emphasize emotional moment punctuate amplify effect happen screen peculiar point despite soberer contemplative tone mcu long afraid reference disney franchise competitor dc comic_strip respond fan ask question like not eternal help fight thano interesting direct honest wide open answer big screen addition way narrative address discussion evolution humanity representation diversity make different banal production lead case feature film genre eternal slip deliver solid work make care illustrious stranger dynamic god sustain plot make twist conflict necessary weight impact design come future cinematic tremendous success bring like chloe zhao bring identity body soul project wrong intervene connect cinematic director screenwriter vision essential good have attach mcu remain see continue bring zhao professional good exactly film need director bring personality trait film shadow create endgame problem phase 4 public expectation anxiety great monster create struggle tame audience sure find eternal interesting thing cinematic offer long time way narrative address discussion evolution humanity representation diversity different follow group super power come earth specific mission celestial arishem voice david kaye   end threat deviant monster process help humanity evolve involve conflict arrive world dawn human civilization time immerse planet culture cling mix protege lack tone change rampant fanservice immense need connect cinematic cinematic generate lot friction fan producer lover raise important question example worth follow share moviesserie need connected independent eternal come promise great freshness saturate mainly count chloe zhao head project director screenwriter win oscar nomadland good picture good director fact kevin feige executive producer allow zhao work lot freedom despite product eternal positively differentiate count director creative vision wide open aspect mixture astronaut god gnosticism superhero work zhao choose brake action know new protagonist depth relate world live essential connect patience cinematic demand audience big point fight 10 minute unbridle rush need relationship human thing come near divine slow pace different formula present decade result interesting important thing eternal truly captivate dynamic god set origin protagonist easy task especially know public great merit eternal able present develop immortal dedicate good script know affectionate understand member group personality way world team hero eternal large diverse cast varied history genre irregular normal come different personality age different genre sersis gemma chan passion humanity kingos kumail nanjiani narcissism goblin lia mchugh frustration nature new hero portray unique personality set apart rest equally interesting captivate highlight moment mix typical humor particularity work richard maddens ikaris great despite actor limit performance main challenge script reconcile wide range strong cast highlight develop relevant succeed little screen time appear feel lack depth central present interesting contexts background personality follow simple archetype create impression hero necessarily mean bad overall dynamic member work chemistry charismatic time dynamic key work real tension script group defeat deviant save world different way look humanity mission ve clash conflict work people need care eternal time relationship explore eternal hit brake use mcu instead action sequence plot celerity sense urgency dedicate relationship ikaris sersi justify mutual admiration gilgamesh don lee thena angelina jolie explain druig barry keoghan disagree brother method narrative linear alternate present day important moment human history forth flashback way time follow trajectory hero lead situation definitely break standard set care lot tell inflate cinematic reference warning upcoming influence present unfortunately negative way needlessly tune serve bring comic relief bad funny work totally break rhythm long seriously furthermore inconsistency difficult swallow especially involve reason deviant exist impression leave end alien purpose compose action yes problem eternal digital effect impressive arm interesting secondary arouse feeling semi villain poorly explore feeling place despite script notable hole duration excessively long deliver good engaging bring freshness badly need thank chloe zhao eternal personality remarkable great direction actor director bring naturalistic perspective filming value detail combat choreography advantage ability eternal visual impact offer compose impactful stunning real location eternal beautiful term look message union love convey viewer soundtrack noteworthy complete epic setting emphasize emotional moment punctuate amplify effect happen screen peculiar point despite soberer contemplative tone use mcu long afraid reference disney franchise competitor dc comic_strip respond fan ask question like eternal help fight thano interesting direct honest wide open answer big screen addition way narrative address discussion evolution humanity representation diversity different banal production lead case feature genre eternal slip deliver solid work care illustrious stranger dynamic god sustain plot twist conflict necessary weight impact design come future cinematic tremendous success bring like chloe zhao bring identity body soul project wrong intervene connect cinematic director screenwriter vision essential good attach mcu remain continue bring zhao professional good exactly need director bring personality trait shadow create endgame problem phase 4 public expectation anxiety great monster create struggle tame audience sure find eternal interesting thing cinematic offer long time [SEP] ENTLBL_PERSON ENTTXT_david_kaye ENTLBL_PERSON ENTTXT_kevin ENTLBL_PERSON ENTTXT_richard_maddens ENTLBL_PERSON ENTTXT_don_lee_thena_angelina_jolie_explain ENTLBL_PERSON ENTTXT_barry_keoghan ENTLBL_ORG ENTTXT_linear</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9702,20 +7520,10 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9739,12 +7547,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>boring alr buck like finish tell thing happen hate try cool antagonist speak language cause separate reality cause care care villain motivation suppose care save grace loki honestly like thing think legit entertain word m glad push continue</t>
+          <t>ENTLBL_PERSON ENTTXT_grace_loki</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>boring alr keep buck boring not have thing thor lore cool instead kinda cover ignore annoy like finish not tell thing happen hate movie try cool antagonist speak language cause separate reality make cause not care not care villain motivation suppose care save grace loki honestly like thing think legit entertain word m glad push continue boring alr buck boring thing thor lore cool instead kinda cover ignore annoy like finish tell thing happen hate try cool antagonist speak language cause separate reality cause care care villain motivation suppose care save grace loki honestly like thing think legit entertain word m glad push continue boring alr buck like finish tell thing happen hate try cool antagonist speak language cause separate reality cause care care villain motivation suppose care save grace loki honestly like thing think legit entertain word m glad push continue</t>
+          <t>boring alr keep buck boring not have thing thor lore cool instead kinda cover ignore annoy like finish not tell thing happen hate movie try cool antagonist speak language cause separate reality make cause not care not care villain motivation suppose care save grace loki honestly like thing think legit entertain word m glad push continue boring alr buck boring thing thor lore cool instead kinda cover ignore annoy like finish tell thing happen hate try cool antagonist speak language cause separate reality cause care care villain motivation suppose care save grace loki honestly like thing think legit entertain word m glad push continue [SEP] ENTLBL_PERSON ENTTXT_grace_loki</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9759,20 +7567,10 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9796,12 +7594,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>strange literally unusual mcu action pack cinematic pacing great creativity wonderful problem feature illuminati real letdown feature bunch great previously unseen wonderful patrick stewart reprise role   sadly kill pretty quickly good outweighs bad original classic great world building maybe use humor certainly new idea viewer m glad long short</t>
+          <t>ENTLBL_PERSON ENTTXT_patrick_stewart</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>strange literally unusual film mcu basic premise wanda try replace child doctor strange stop action pack cinematic pacing great creativity wonderful say problem feature illuminati real letdown feature bunch great previously unseen wonderful patrick stewart reprise role   sadly kill pretty quickly good outweighs bad original classic great world building maybe humor certainly see new idea viewer m glad not long short strange literally unusual mcu basic premise wanda try replace child doctor strange stop action pack cinematic pacing great creativity wonderful problem feature illuminati real letdown feature bunch great previously unseen wonderful patrick stewart reprise role   sadly kill pretty quickly good outweighs bad original classic great world building maybe use humor certainly new idea viewer m glad long short strange literally unusual mcu action pack cinematic pacing great creativity wonderful problem feature illuminati real letdown feature bunch great previously unseen wonderful patrick stewart reprise role   sadly kill pretty quickly good outweighs bad original classic great world building maybe use humor certainly new idea viewer m glad long short</t>
+          <t>strange literally unusual film mcu basic premise wanda try replace child doctor strange stop action pack cinematic pacing great creativity wonderful say problem feature illuminati real letdown feature bunch great previously unseen wonderful patrick stewart reprise role   sadly kill pretty quickly good outweighs bad original classic great world building maybe humor certainly see new idea viewer m glad not long short strange literally unusual mcu basic premise wanda try replace child doctor strange stop action pack cinematic pacing great creativity wonderful problem feature illuminati real letdown feature bunch great previously unseen wonderful patrick stewart reprise role   sadly kill pretty quickly good outweighs bad original classic great world building maybe use humor certainly new idea viewer m glad long short [SEP] ENTLBL_PERSON ENTTXT_patrick_stewart</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9816,20 +7614,10 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9853,12 +7641,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>fondue start wwii origin chris evans play steve roger puny 4f lie way military science experiment tommy lee jones play excellent colonel kid shark rogers 90 pound weakling display intellect courage gut select military secret program transform muscular super hero roger transform captain america use recruiting tool tommy lee doubt 90 pound weakling course thing change rest hard figure read comic_strip combine action drama light comedy light romance good act good dialogue good frickin laser beam swearing nudity sex</t>
+          <t>ENTLBL_PERSON ENTTXT_chris_evans ENTLBL_PERSON ENTTXT_steve_roger_puny ENTLBL_PERSON ENTTXT_tommy_lee_jones ENTLBL_ORG ENTTXT_nazi_hugo ENTLBL_PERSON ENTTXT_darth_maul ENTLBL_PERSON ENTTXT_tommy_lee_doubt ENTLBL_PERSON ENTTXT_samuel_l_jackson_iron</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>fondue start wwii origin chris evans play steve roger puny 4f lie way military science experiment tommy lee jones play excellent colonel evil nazi hugo weaving believe darth maul plan world conquest shark frickin laser beam kid shark rogers 90 pound weakling display intellect courage gut select military secret program transform muscular super hero special effect good know action hero not jump car roof roger transform captain america recruiting tool tommy lee doubt 90 pound weakling course thing change rest not hard figure not read comic_strip end utilize eyed samuel l jackson iron 2 hint ultimate sequel provide not dead combine action drama light comedy light romance good act good dialogue good frickin laser beam swearing nudity sex fondue start wwii origin chris evans play steve roger puny 4f lie way military science experiment tommy lee jones play excellent colonel evil nazi hugo weaving believe darth maul plan world conquest use shark frickin laser beam kid shark rogers 90 pound weakling display intellect courage gut select military secret program transform muscular super hero special effect good know action hero jump car roof roger transform captain america use recruiting tool tommy lee doubt 90 pound weakling course thing change rest hard figure read comic_strip end utilize eyed samuel l jackson iron 2 hint ultimate sequel provide dead combine action drama light comedy light romance good act good dialogue good frickin laser beam swearing nudity sex fondue start wwii origin chris evans play steve roger puny 4f lie way military science experiment tommy lee jones play excellent colonel kid shark rogers 90 pound weakling display intellect courage gut select military secret program transform muscular super hero roger transform captain america use recruiting tool tommy lee doubt 90 pound weakling course thing change rest hard figure read comic_strip combine action drama light comedy light romance good act good dialogue good frickin laser beam swearing nudity sex</t>
+          <t>fondue start wwii origin chris evans play steve roger puny 4f lie way military science experiment tommy lee jones play excellent colonel evil nazi hugo weaving believe darth maul plan world conquest shark frickin laser beam kid shark rogers 90 pound weakling display intellect courage gut select military secret program transform muscular super hero special effect good know action hero not jump car roof roger transform captain america recruiting tool tommy lee doubt 90 pound weakling course thing change rest not hard figure not read comic_strip end utilize eyed samuel l jackson iron 2 hint ultimate sequel provide not dead combine action drama light comedy light romance good act good dialogue good frickin laser beam swearing nudity sex fondue start wwii origin chris evans play steve roger puny 4f lie way military science experiment tommy lee jones play excellent colonel evil nazi hugo weaving believe darth maul plan world conquest use shark frickin laser beam kid shark rogers 90 pound weakling display intellect courage gut select military secret program transform muscular super hero special effect good know action hero jump car roof roger transform captain america use recruiting tool tommy lee doubt 90 pound weakling course thing change rest hard figure read comic_strip end utilize eyed samuel l jackson iron 2 hint ultimate sequel provide dead combine action drama light comedy light romance good act good dialogue good frickin laser beam swearing nudity sex [SEP] ENTLBL_PERSON ENTTXT_chris_evans ENTLBL_PERSON ENTTXT_steve_roger_puny ENTLBL_PERSON ENTTXT_tommy_lee_jones ENTLBL_ORG ENTTXT_nazi_hugo ENTLBL_PERSON ENTTXT_darth_maul ENTLBL_PERSON ENTTXT_tommy_lee_doubt ENTLBL_PERSON ENTTXT_samuel_l_jackson_iron</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9873,20 +7661,10 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -9910,12 +7688,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>lackluster sequel fail shine let talk thor dark world sum word underwhelme theme family dynamic loyalty touch add new try epic end feel tired uninspired support cast include natalie portman tom hiddleston waste role forgettable villain malekith particularly disappointing suppose menacing powerful threat come generic bad guy real motivation pace sluggish long stretch exposition action fail engage dialog clunky exposition dump feel like trust audience follow rate 5 10 complete disaster special effect impressive moment manage genuinely entertaining overall thor dark world lackluster forgettable entry cinematic terrible far great die hard fan enjoyment superhero</t>
+          <t>ENTLBL_PERSON ENTTXT_chris_hemsworth_good ENTLBL_PERSON ENTTXT_tom_hiddleston</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>lackluster sequel fail shine let talk thor dark world sum word underwhelme plot feel like rehash ve see thor thor need save world case powerful enemy threaten destroy theme family dynamic loyalty touch not add new try epic end feel tired uninspired acting fine chris hemsworth good carry thor not save lackluster script support cast include natalie portman tom hiddleston waste role forgettable villain malekith particularly disappointing suppose menacing powerful threat come generic bad guy real motivation pace sluggish long stretch exposition action fail engage dialog clunky exposition dump make feel like not trust audience follow rate 5 10 complete disaster special effect impressive moment manage genuinely entertaining overall thor dark world lackluster forgettable entry cinematic terrible far great die hard fan enjoyment well superhero movie lackluster sequel fail shine let talk thor dark world sum word underwhelme plot feel like rehash ve thor thor need save world case powerful enemy threaten destroy theme family dynamic loyalty touch add new try epic end feel tired uninspired acting fine chris hemsworth good carry thor save lackluster script support cast include natalie portman tom hiddleston waste role forgettable villain malekith particularly disappointing suppose menacing powerful threat come generic bad guy real motivation pace sluggish long stretch exposition action fail engage dialog clunky exposition dump feel like trust audience follow rate 5 10 complete disaster special effect impressive moment manage genuinely entertaining overall thor dark world lackluster forgettable entry cinematic terrible far great die hard fan enjoyment superhero lackluster sequel fail shine let talk thor dark world sum word underwhelme theme family dynamic loyalty touch add new try epic end feel tired uninspired support cast include natalie portman tom hiddleston waste role forgettable villain malekith particularly disappointing suppose menacing powerful threat come generic bad guy real motivation pace sluggish long stretch exposition action fail engage dialog clunky exposition dump feel like trust audience follow rate 5 10 complete disaster special effect impressive moment manage genuinely entertaining overall thor dark world lackluster forgettable entry cinematic terrible far great die hard fan enjoyment superhero</t>
+          <t>lackluster sequel fail shine let talk thor dark world sum word underwhelme plot feel like rehash ve see thor thor need save world case powerful enemy threaten destroy theme family dynamic loyalty touch not add new try epic end feel tired uninspired acting fine chris hemsworth good carry thor not save lackluster script support cast include natalie portman tom hiddleston waste role forgettable villain malekith particularly disappointing suppose menacing powerful threat come generic bad guy real motivation pace sluggish long stretch exposition action fail engage dialog clunky exposition dump make feel like not trust audience follow rate 5 10 complete disaster special effect impressive moment manage genuinely entertaining overall thor dark world lackluster forgettable entry cinematic terrible far great die hard fan enjoyment well superhero movie lackluster sequel fail shine let talk thor dark world sum word underwhelme plot feel like rehash ve thor thor need save world case powerful enemy threaten destroy theme family dynamic loyalty touch add new try epic end feel tired uninspired acting fine chris hemsworth good carry thor save lackluster script support cast include natalie portman tom hiddleston waste role forgettable villain malekith particularly disappointing suppose menacing powerful threat come generic bad guy real motivation pace sluggish long stretch exposition action fail engage dialog clunky exposition dump feel like trust audience follow rate 5 10 complete disaster special effect impressive moment manage genuinely entertaining overall thor dark world lackluster forgettable entry cinematic terrible far great die hard fan enjoyment superhero [SEP] ENTLBL_PERSON ENTTXT_chris_hemsworth_good ENTLBL_PERSON ENTTXT_tom_hiddleston</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -9930,20 +7708,10 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -9965,14 +7733,10 @@
           <t>great great funny good end credit movie great great funny good end credit</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>great great funny good end credit</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>great great funny good end credit movie great great funny good end credit great great funny good end credit</t>
+          <t>great great funny good end credit movie great great funny good end credit [SEP]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -9987,20 +7751,10 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10024,12 +7778,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>good effort great d excellent 30 minute point hulk liv tylers betty ross performance excellent edward norton excellent bruce banner plus tim roth william hurt outstanding support role theirs liv tyler bad actress absolutely note useless liv tyler performance matter unbelievable wooden want knock unconscious screen time whatsoever contribute pump wooden dialogue visual effect notch final battle hulk abomination eye popping design craft virtually hulk stand facial expression breathtakingly realistic script work fail provide emotional pull generally lack development work dialogue introduce fail afterward state previously 40 minute incredible hulk notch emotional satisfy good bit work great format like 2003s hulk</t>
+          <t>ENTLBL_PERSON ENTTXT_edward_norton ENTLBL_PERSON ENTTXT_bruce_banner ENTLBL_PERSON ENTTXT_tim_roth ENTLBL_PERSON ENTTXT_william_hurt</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>good effort great d excellent 30 minute point hulk see liv tylers betty ross performance excellent edward norton excellent bruce banner plus tim roth william hurt outstanding support role theirs liv tyler bad actress absolutely note useless liv tyler performance not matter well unbelievable wooden want knock unconscious screen time whatsoever contribute pump wooden dialogue visual effect notch final battle hulk abomination eye popping design craft virtually hulk stand facial expression breathtakingly realistic script work not fail provide emotional pull generally have lack development work well dialogue introduce fail afterward state previously 40 minute incredible hulk notch emotional satisfy good bit work not great not format like 2003s hulk good effort great d excellent 30 minute point hulk liv tylers betty ross performance excellent edward norton excellent bruce banner plus tim roth william hurt outstanding support role theirs liv tyler bad actress absolutely note useless liv tyler performance matter unbelievable wooden want knock unconscious screen time whatsoever contribute pump wooden dialogue visual effect notch final battle hulk abomination eye popping design craft virtually hulk stand facial expression breathtakingly realistic script work fail provide emotional pull generally lack development work dialogue introduce fail afterward state previously 40 minute incredible hulk notch emotional satisfy good bit work great format like 2003s hulk good effort great d excellent 30 minute point hulk liv tylers betty ross performance excellent edward norton excellent bruce banner plus tim roth william hurt outstanding support role theirs liv tyler bad actress absolutely note useless liv tyler performance matter unbelievable wooden want knock unconscious screen time whatsoever contribute pump wooden dialogue visual effect notch final battle hulk abomination eye popping design craft virtually hulk stand facial expression breathtakingly realistic script work fail provide emotional pull generally lack development work dialogue introduce fail afterward state previously 40 minute incredible hulk notch emotional satisfy good bit work great format like 2003s hulk</t>
+          <t>good effort great d excellent 30 minute point hulk see liv tylers betty ross performance excellent edward norton excellent bruce banner plus tim roth william hurt outstanding support role theirs liv tyler bad actress absolutely note useless liv tyler performance not matter well unbelievable wooden want knock unconscious screen time whatsoever contribute pump wooden dialogue visual effect notch final battle hulk abomination eye popping design craft virtually hulk stand facial expression breathtakingly realistic script work not fail provide emotional pull generally have lack development work well dialogue introduce fail afterward state previously 40 minute incredible hulk notch emotional satisfy good bit work not great not format like 2003s hulk good effort great d excellent 30 minute point hulk liv tylers betty ross performance excellent edward norton excellent bruce banner plus tim roth william hurt outstanding support role theirs liv tyler bad actress absolutely note useless liv tyler performance matter unbelievable wooden want knock unconscious screen time whatsoever contribute pump wooden dialogue visual effect notch final battle hulk abomination eye popping design craft virtually hulk stand facial expression breathtakingly realistic script work fail provide emotional pull generally lack development work dialogue introduce fail afterward state previously 40 minute incredible hulk notch emotional satisfy good bit work great format like 2003s hulk [SEP] ENTLBL_PERSON ENTTXT_edward_norton ENTLBL_PERSON ENTTXT_bruce_banner ENTLBL_PERSON ENTTXT_tim_roth ENTLBL_PERSON ENTTXT_william_hurt</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -10044,20 +7798,10 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10081,12 +7825,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>self awareness great humour laugh rag tag bunch galaxian american fantasy action comedy boy abduct alien grow mercenary far flung galaxy join band misfit battle timelord intent destruction bubblegum science fiction comedy anarchic feel edge zip z wisp star war new hope ether healthy dose wink audience wit chris pratt bring charisma good turn david bautista big brut fail understand metaphor absurdity long credit writer director funny dazzling adventure</t>
+          <t>ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_david_bautista</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>self awareness great humour laugh rag tag bunch galaxian american fantasy action comedy boy abduct alien grow mercenary far flung galaxy join band misfit battle timelord intent destruction bubblegum science fiction comedy anarchic feel edge zip z wisp star war new hope ether healthy dose wink audience wit chris pratt bring charisma good turn david bautista big brut fail understand metaphor absurdity keep move long credit writer director funny dazzling adventure self awareness great humour laugh rag tag bunch galaxian american fantasy action comedy boy abduct alien grow mercenary far flung galaxy join band misfit battle timelord intent destruction bubblegum science fiction comedy anarchic feel edge zip z wisp star war new hope ether healthy dose wink audience wit chris pratt bring charisma good turn david bautista big brut fail understand metaphor absurdity long credit writer director funny dazzling adventure self awareness great humour laugh rag tag bunch galaxian american fantasy action comedy boy abduct alien grow mercenary far flung galaxy join band misfit battle timelord intent destruction bubblegum science fiction comedy anarchic feel edge zip z wisp star war new hope ether healthy dose wink audience wit chris pratt bring charisma good turn david bautista big brut fail understand metaphor absurdity long credit writer director funny dazzling adventure</t>
+          <t>self awareness great humour laugh rag tag bunch galaxian american fantasy action comedy boy abduct alien grow mercenary far flung galaxy join band misfit battle timelord intent destruction bubblegum science fiction comedy anarchic feel edge zip z wisp star war new hope ether healthy dose wink audience wit chris pratt bring charisma good turn david bautista big brut fail understand metaphor absurdity keep move long credit writer director funny dazzling adventure self awareness great humour laugh rag tag bunch galaxian american fantasy action comedy boy abduct alien grow mercenary far flung galaxy join band misfit battle timelord intent destruction bubblegum science fiction comedy anarchic feel edge zip z wisp star war new hope ether healthy dose wink audience wit chris pratt bring charisma good turn david bautista big brut fail understand metaphor absurdity long credit writer director funny dazzling adventure [SEP] ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_david_bautista</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -10101,20 +7845,10 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10138,12 +7872,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>thor tastic thor ragnarok fun entertaining great performance tessa thompson cate blanchett tom hiddleston chris hemsworth usual fan base oppose tell infinity stone sub plot run worth</t>
+          <t>ENTLBL_PERSON ENTTXT_tom_hiddleston ENTLBL_PERSON ENTTXT_chris</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>thor tastic thor ragnarok fun entertaining remind lot guardian galaxy 2 great performance tessa thompson cate blanchett tom hiddleston chris hemsworth usual fan base oppose tell infinity stone sub plot run movie worth thor tastic thor ragnarok fun entertaining remind lot guardian galaxy 2 great performance tessa thompson cate blanchett tom hiddleston chris hemsworth usual fan base oppose tell infinity stone sub plot run worth thor tastic thor ragnarok fun entertaining great performance tessa thompson cate blanchett tom hiddleston chris hemsworth usual fan base oppose tell infinity stone sub plot run worth</t>
+          <t>thor tastic thor ragnarok fun entertaining remind lot guardian galaxy 2 great performance tessa thompson cate blanchett tom hiddleston chris hemsworth usual fan base oppose tell infinity stone sub plot run movie worth thor tastic thor ragnarok fun entertaining remind lot guardian galaxy 2 great performance tessa thompson cate blanchett tom hiddleston chris hemsworth usual fan base oppose tell infinity stone sub plot run worth [SEP] ENTLBL_PERSON ENTTXT_tom_hiddleston ENTLBL_PERSON ENTTXT_chris</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -10158,20 +7892,10 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10195,12 +7919,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>amazing expect casting great chemistry combination different verse personality set success relatable expect superhero bring aspect common alcohol abuse loneliness abuse kinda end feel like big redemption arc complaint true introspection understandable action great fight hold big thing appreciation nerf sentrys think thing lightly spoiler hopefully continue magnitude future overall m impressed</t>
+          <t>ENTLBL_PERSON ENTTXT_kinda</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>amazing not expect amazing get to consistent flop previous year huge success endgame close ve get actual level casting great chemistry combination different verse personality set success relatable expect give superhero bring aspect common alcohol abuse loneliness abuse kinda end feel like big redemption arc complaint not true introspection understandable action great fight not hold big thing appreciation not nerf sentrys think put thing lightly give spoiler direction expect thor love   thunder hopefully continue get movie magnitude future overall m impressed amazing expect amazing consistent flop previous year huge success endgame close ve actual level casting great chemistry combination different verse personality set success relatable expect superhero bring aspect common alcohol abuse loneliness abuse kinda end feel like big redemption arc complaint true introspection understandable action great fight hold big thing appreciation nerf sentrys think thing lightly spoiler direction expect thor love   thunder hopefully continue magnitude future overall m impressed amazing expect casting great chemistry combination different verse personality set success relatable expect superhero bring aspect common alcohol abuse loneliness abuse kinda end feel like big redemption arc complaint true introspection understandable action great fight hold big thing appreciation nerf sentrys think thing lightly spoiler hopefully continue magnitude future overall m impressed</t>
+          <t>amazing not expect amazing get to consistent flop previous year huge success endgame close ve get actual level casting great chemistry combination different verse personality set success relatable expect give superhero bring aspect common alcohol abuse loneliness abuse kinda end feel like big redemption arc complaint not true introspection understandable action great fight not hold big thing appreciation not nerf sentrys think put thing lightly give spoiler direction expect thor love   thunder hopefully continue get movie magnitude future overall m impressed amazing expect amazing consistent flop previous year huge success endgame close ve actual level casting great chemistry combination different verse personality set success relatable expect superhero bring aspect common alcohol abuse loneliness abuse kinda end feel like big redemption arc complaint true introspection understandable action great fight hold big thing appreciation nerf sentrys think thing lightly spoiler direction expect thor love   thunder hopefully continue magnitude future overall m impressed [SEP] ENTLBL_PERSON ENTTXT_kinda</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -10215,20 +7939,10 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10252,12 +7966,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>incredible reboot hulk franchise fair negative response audience critic ang lee hulk   incredible hulk completely different way ang lee   drama ambition   simple mindless popcorn action flick obvious problem lie screenplay   lack originality   cliche barely write   maybe reason actor interesting nice joke easter egg hulk fan cameo stan lee   cameo lou ferrigno   joke pant   lonely theme   bland direction louis letterier help   awful cgi edward norton good actor   actor tim ruth terribly weak parody william hurt nice general ross   especially consider stuck dimensional role bad performance certainly belong liv tyler   cast scientist betty ross   unbelievable   dramatic performance laugh fan hulk pleased   viewer disappointed boring   impress audience substance   interesting action pretty forgettable die hard comic book fan 210</t>
+          <t>ENTLBL_PERSON ENTTXT_ang_lee_hulk ENTLBL_PERSON ENTTXT_ang_lee___drama ENTLBL_PERSON ENTTXT_stan_lee___cameo_lou_ferrigno ENTLBL_PERSON ENTTXT_edward_norton ENTLBL_PERSON ENTTXT_tim_ruth ENTLBL_PERSON ENTTXT_william_hurt ENTLBL_PERSON ENTTXT_betty_ross ENTLBL_PRODUCT ENTTXT_210</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>incredible reboot hulk franchise fair negative response audience critic ang lee hulk incredible hulk go completely different way ang lee   drama ambition   simple mindless popcorn action flick obvious problem lie screenplay   lack originality   cliche barely write   maybe reason actor not interesting nice joke easter egg hulk fan cameo stan lee   cameo lou ferrigno   joke pant   lonely theme   bland direction louis letterier not help   awful cgi edward norton good actor   not actor tim ruth terribly weak parody william hurt nice general ross   especially consider stuck dimensional role bad performance certainly belong liv tyler   cast scientist betty ross   unbelievable   dramatic performance give laugh fan hulk pleased   viewer disappointed boring   get impress audience substance   interesting action pretty forgettable die hard comic book fan 210 incredible reboot hulk franchise fair negative response audience critic ang lee hulk incredible hulk completely different way ang lee   drama ambition   simple mindless popcorn action flick obvious problem lie screenplay   lack originality   cliche barely write   maybe reason actor interesting nice joke easter egg hulk fan cameo stan lee   cameo lou ferrigno   joke pant   lonely theme   bland direction louis letterier help   awful cgi edward norton good actor   actor tim ruth terribly weak parody william hurt nice general ross   especially consider stuck dimensional role bad performance certainly belong liv tyler   cast scientist betty ross   unbelievable   dramatic performance laugh fan hulk pleased   viewer disappointed boring   impress audience substance   interesting action pretty forgettable die hard comic book fan 210 incredible reboot hulk franchise fair negative response audience critic ang lee hulk   incredible hulk completely different way ang lee   drama ambition   simple mindless popcorn action flick obvious problem lie screenplay   lack originality   cliche barely write   maybe reason actor interesting nice joke easter egg hulk fan cameo stan lee   cameo lou ferrigno   joke pant   lonely theme   bland direction louis letterier help   awful cgi edward norton good actor   actor tim ruth terribly weak parody william hurt nice general ross   especially consider stuck dimensional role bad performance certainly belong liv tyler   cast scientist betty ross   unbelievable   dramatic performance laugh fan hulk pleased   viewer disappointed boring   impress audience substance   interesting action pretty forgettable die hard comic book fan 210</t>
+          <t>incredible reboot hulk franchise fair negative response audience critic ang lee hulk incredible hulk go completely different way ang lee   drama ambition   simple mindless popcorn action flick obvious problem lie screenplay   lack originality   cliche barely write   maybe reason actor not interesting nice joke easter egg hulk fan cameo stan lee   cameo lou ferrigno   joke pant   lonely theme   bland direction louis letterier not help   awful cgi edward norton good actor   not actor tim ruth terribly weak parody william hurt nice general ross   especially consider stuck dimensional role bad performance certainly belong liv tyler   cast scientist betty ross   unbelievable   dramatic performance give laugh fan hulk pleased   viewer disappointed boring   get impress audience substance   interesting action pretty forgettable die hard comic book fan 210 incredible reboot hulk franchise fair negative response audience critic ang lee hulk incredible hulk completely different way ang lee   drama ambition   simple mindless popcorn action flick obvious problem lie screenplay   lack originality   cliche barely write   maybe reason actor interesting nice joke easter egg hulk fan cameo stan lee   cameo lou ferrigno   joke pant   lonely theme   bland direction louis letterier help   awful cgi edward norton good actor   actor tim ruth terribly weak parody william hurt nice general ross   especially consider stuck dimensional role bad performance certainly belong liv tyler   cast scientist betty ross   unbelievable   dramatic performance laugh fan hulk pleased   viewer disappointed boring   impress audience substance   interesting action pretty forgettable die hard comic book fan 210 [SEP] ENTLBL_PERSON ENTTXT_ang_lee_hulk ENTLBL_PERSON ENTTXT_ang_lee___drama ENTLBL_PERSON ENTTXT_stan_lee___cameo_lou_ferrigno ENTLBL_PERSON ENTTXT_edward_norton ENTLBL_PERSON ENTTXT_tim_ruth ENTLBL_PERSON ENTTXT_william_hurt ENTLBL_PERSON ENTTXT_betty_ross ENTLBL_PRODUCT ENTTXT_210</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -10272,20 +7986,10 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10309,12 +8013,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>fun visually stunning ride flaw ant wasp quantumania franchise bold new direction diving deep quantum realm dazzle visual large life stake paul rudd remain effortlessly charming scott lang balance humor action perfectly big highlight jonathan majors kang conqueror presence command elevate quantum realm visual spectacle fill imaginative creature environment feel straight science fiction epic stumble area plot element feel rushed certain deserve development despite flaw quantumania entertaining entry mcu offer thrilling mix action comedy world building set stage future franchise solid cinematic fan reach height predecessor</t>
+          <t>ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_scott_lang ENTLBL_PERSON ENTTXT_jonathan_majors_kang</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>fun visually stunning ride flaw ant wasp quantumania take franchise bold new direction diving deep quantum realm dazzle visual large life stake paul rudd remain effortlessly charming scott lang balance humor action perfectly big highlight jonathan majors kang conqueror presence command elevate quantum realm visual spectacle fill imaginative creature environment feel straight science fiction epic stumble area humor strength ant film not land previous installment plot element feel rushed certain deserve development despite flaw quantumania entertaining entry mcu offer thrilling mix action comedy world building set stage future franchise solid cinematic fan not reach height predecessor fun visually stunning ride flaw ant wasp quantumania franchise bold new direction diving deep quantum realm dazzle visual large life stake paul rudd remain effortlessly charming scott lang balance humor action perfectly big highlight jonathan majors kang conqueror presence command elevate quantum realm visual spectacle fill imaginative creature environment feel straight science fiction epic stumble area humor strength ant land previous installment plot element feel rushed certain deserve development despite flaw quantumania entertaining entry mcu offer thrilling mix action comedy world building set stage future franchise solid cinematic fan reach height predecessor fun visually stunning ride flaw ant wasp quantumania franchise bold new direction diving deep quantum realm dazzle visual large life stake paul rudd remain effortlessly charming scott lang balance humor action perfectly big highlight jonathan majors kang conqueror presence command elevate quantum realm visual spectacle fill imaginative creature environment feel straight science fiction epic stumble area plot element feel rushed certain deserve development despite flaw quantumania entertaining entry mcu offer thrilling mix action comedy world building set stage future franchise solid cinematic fan reach height predecessor</t>
+          <t>fun visually stunning ride flaw ant wasp quantumania take franchise bold new direction diving deep quantum realm dazzle visual large life stake paul rudd remain effortlessly charming scott lang balance humor action perfectly big highlight jonathan majors kang conqueror presence command elevate quantum realm visual spectacle fill imaginative creature environment feel straight science fiction epic stumble area humor strength ant film not land previous installment plot element feel rushed certain deserve development despite flaw quantumania entertaining entry mcu offer thrilling mix action comedy world building set stage future franchise solid cinematic fan not reach height predecessor fun visually stunning ride flaw ant wasp quantumania franchise bold new direction diving deep quantum realm dazzle visual large life stake paul rudd remain effortlessly charming scott lang balance humor action perfectly big highlight jonathan majors kang conqueror presence command elevate quantum realm visual spectacle fill imaginative creature environment feel straight science fiction epic stumble area humor strength ant land previous installment plot element feel rushed certain deserve development despite flaw quantumania entertaining entry mcu offer thrilling mix action comedy world building set stage future franchise solid cinematic fan reach height predecessor [SEP] ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_scott_lang ENTLBL_PERSON ENTTXT_jonathan_majors_kang</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -10329,20 +8033,10 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10366,12 +8060,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>great laugh laugh head chuckle cat repetitive way cast brie larson captain honestly mistake hate actor actor emotion change plot point great hate want good bad second bad</t>
+          <t>ENTLBL_PERSON ENTTXT_brie_larson ENTLBL_PERSON ENTTXT_robert_downey_jr_iron ENTLBL_PERSON ENTTXT_samuel_jackson_paul_rudd_evangeline_lilly</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>great part laugh laugh head part chuckle part cat repetitive third way cast brie larson captain honestly mistake hate actor actor example robert downey jr iron impossible imagine play emotion change call example benedict cumberbatch doctor strange samuel jackson paul rudd evangeline lilly list go plot point great hate want good movie bad second bad great laugh laugh head chuckle cat repetitive way cast brie larson captain honestly mistake hate actor actor example robert downey jr iron impossible imagine play emotion change example benedict cumberbatch doctor strange samuel jackson paul rudd evangeline lilly list plot point great hate want good bad second bad great laugh laugh head chuckle cat repetitive way cast brie larson captain honestly mistake hate actor actor emotion change plot point great hate want good bad second bad</t>
+          <t>great part laugh laugh head part chuckle part cat repetitive third way cast brie larson captain honestly mistake hate actor actor example robert downey jr iron impossible imagine play emotion change call example benedict cumberbatch doctor strange samuel jackson paul rudd evangeline lilly list go plot point great hate want good movie bad second bad great laugh laugh head chuckle cat repetitive way cast brie larson captain honestly mistake hate actor actor example robert downey jr iron impossible imagine play emotion change example benedict cumberbatch doctor strange samuel jackson paul rudd evangeline lilly list plot point great hate want good bad second bad [SEP] ENTLBL_PERSON ENTTXT_brie_larson ENTLBL_PERSON ENTTXT_robert_downey_jr_iron ENTLBL_PERSON ENTTXT_samuel_jackson_paul_rudd_evangeline_lilly</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -10386,20 +8080,10 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10421,14 +8105,10 @@
           <t>not imagine level genius take recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius go director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially not help notice potential homage pay different science fiction movie television show western past recent expression love business sir love hang witness work someday imagine level genius recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially help notice potential homage pay different science fiction television western past recent expression love business sir love hang witness work someday</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>imagine level genius recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially help notice potential homage pay different science fiction television western past recent expression love business sir love hang witness work someday</t>
-        </is>
-      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>not imagine level genius take recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius go director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially not help notice potential homage pay different science fiction movie television show western past recent expression love business sir love hang witness work someday imagine level genius recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially help notice potential homage pay different science fiction television western past recent expression love business sir love hang witness work someday imagine level genius recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially help notice potential homage pay different science fiction television western past recent expression love business sir love hang witness work someday</t>
+          <t>not imagine level genius take recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius go director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially not help notice potential homage pay different science fiction movie television show western past recent expression love business sir love hang witness work someday imagine level genius recognize work genius perfect end magnificent trilogy excitement adventure emotion work pure genius director writer work inspiration chemistry actor perfect casting actor fit like dream theme park base trilogy especially help notice potential homage pay different science fiction television western past recent expression love business sir love hang witness work someday [SEP]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -10443,20 +8123,10 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10480,12 +8150,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>oops negative people hear like talk raccoon tree hmmmnot interested think able pull come prove wrong thing happen ant announce guess ant sound intimidating impressive right fight visually understand skill pretty badass start tie knot past succeed beautifully cross future event interesting plot development inside mcu paul rudd handles scott lang chris pratt handle peter quill connect guy second michael douglas evangeline lilly fantastic job play hank pym hope van dyne backstorie great addition franchise guy steal michael pena play luis hilarious little thing bother corey stoll darren cross bad actor definitely feel old old villain progress role villain issue inside cinematic aside loki alexander pierce villain sound feel different yellowjacket big threat butthurt guy try prove short ant awesome immerse delightful mess cinematic certainly great time</t>
+          <t>ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_scott_lang ENTLBL_PERSON ENTTXT_chris_pratt_handle_peter_quill ENTLBL_PERSON ENTTXT_michael_douglas_evangeline_lilly ENTLBL_PERSON ENTTXT_van_dyne ENTLBL_PERSON ENTTXT_michael_pena ENTLBL_PERSON ENTTXT_luis_hilarious ENTLBL_PERSON ENTTXT_corey_stoll_darren</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>oops guardian galaxy announce kind reaction trigger negative people hear like talk raccoon tree hmmmnot interested fan comic book like go forward not think able pull come prove wrong thing happen ant announce guess ant not sound intimidating impressive right fight visually understand skill pretty badass start tie knot past movie go succeed beautifully cross future event interesting plot development inside mcu paul rudd handles scott lang chris pratt handle peter quill connect guy second michael douglas evangeline lilly fantastic job play hank pym hope van dyne backstorie great addition franchise guy steal make well michael pena play luis hilarious little thing bother corey stoll darren cross say bad actor definitely feel old old villain progress role villain issue inside cinematic aside loki alexander pierce villain sound feel different yellowjacket not big threat butthurt guy try prove well short ant awesome immerse delightful mess cinematic certainly great time oops guardian galaxy announce kind reaction trigger negative people hear like talk raccoon tree hmmmnot interested fan comic book like forward think able pull come prove wrong thing happen ant announce guess ant sound intimidating impressive right fight visually understand skill pretty badass start tie knot past succeed beautifully cross future event interesting plot development inside mcu paul rudd handles scott lang chris pratt handle peter quill connect guy second michael douglas evangeline lilly fantastic job play hank pym hope van dyne backstorie great addition franchise guy steal michael pena play luis hilarious little thing bother corey stoll darren cross bad actor definitely feel old old villain progress role villain issue inside cinematic aside loki alexander pierce villain sound feel different yellowjacket big threat butthurt guy try prove short ant awesome immerse delightful mess cinematic certainly great time oops negative people hear like talk raccoon tree hmmmnot interested think able pull come prove wrong thing happen ant announce guess ant sound intimidating impressive right fight visually understand skill pretty badass start tie knot past succeed beautifully cross future event interesting plot development inside mcu paul rudd handles scott lang chris pratt handle peter quill connect guy second michael douglas evangeline lilly fantastic job play hank pym hope van dyne backstorie great addition franchise guy steal michael pena play luis hilarious little thing bother corey stoll darren cross bad actor definitely feel old old villain progress role villain issue inside cinematic aside loki alexander pierce villain sound feel different yellowjacket big threat butthurt guy try prove short ant awesome immerse delightful mess cinematic certainly great time</t>
+          <t>oops guardian galaxy announce kind reaction trigger negative people hear like talk raccoon tree hmmmnot interested fan comic book like go forward not think able pull come prove wrong thing happen ant announce guess ant not sound intimidating impressive right fight visually understand skill pretty badass start tie knot past movie go succeed beautifully cross future event interesting plot development inside mcu paul rudd handles scott lang chris pratt handle peter quill connect guy second michael douglas evangeline lilly fantastic job play hank pym hope van dyne backstorie great addition franchise guy steal make well michael pena play luis hilarious little thing bother corey stoll darren cross say bad actor definitely feel old old villain progress role villain issue inside cinematic aside loki alexander pierce villain sound feel different yellowjacket not big threat butthurt guy try prove well short ant awesome immerse delightful mess cinematic certainly great time oops guardian galaxy announce kind reaction trigger negative people hear like talk raccoon tree hmmmnot interested fan comic book like forward think able pull come prove wrong thing happen ant announce guess ant sound intimidating impressive right fight visually understand skill pretty badass start tie knot past succeed beautifully cross future event interesting plot development inside mcu paul rudd handles scott lang chris pratt handle peter quill connect guy second michael douglas evangeline lilly fantastic job play hank pym hope van dyne backstorie great addition franchise guy steal michael pena play luis hilarious little thing bother corey stoll darren cross bad actor definitely feel old old villain progress role villain issue inside cinematic aside loki alexander pierce villain sound feel different yellowjacket big threat butthurt guy try prove short ant awesome immerse delightful mess cinematic certainly great time [SEP] ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_scott_lang ENTLBL_PERSON ENTTXT_chris_pratt_handle_peter_quill ENTLBL_PERSON ENTTXT_michael_douglas_evangeline_lilly ENTLBL_PERSON ENTTXT_van_dyne ENTLBL_PERSON ENTTXT_michael_pena ENTLBL_PERSON ENTTXT_luis_hilarious ENTLBL_PERSON ENTTXT_corey_stoll_darren</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -10500,20 +8170,10 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10535,14 +8195,10 @@
           <t>worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep watch blake lively strongly present movie joke understand condition reynold contract truth bad deadpool series worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep blake lively strongly present joke understand condition reynold contract truth bad deadpool series</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep blake lively strongly present joke understand condition reynold contract truth bad deadpool series</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep watch blake lively strongly present movie joke understand condition reynold contract truth bad deadpool series worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep blake lively strongly present joke understand condition reynold contract truth bad deadpool series worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep blake lively strongly present joke understand condition reynold contract truth bad deadpool series</t>
+          <t>worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep watch blake lively strongly present movie joke understand condition reynold contract truth bad deadpool series worst deadpool   strange enter cinema wolverine collection cheap sexual unfunny joke plus bloody   scenario event fast miss sentence pay attention wolverine bad version hugh jackman great save long useless feel bored point sleep blake lively strongly present joke understand condition reynold contract truth bad deadpool series [SEP]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -10557,20 +8213,10 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10592,14 +8238,10 @@
           <t>poor comparison fun look messy not perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust see 911 go step actually collapse skyscraper pancake method result poor comparison fun look messy perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust 911 step far actually collapse skyscraper pancake method result</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>poor comparison fun look messy perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust 911 step far actually collapse skyscraper pancake method result</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>poor comparison fun look messy not perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust see 911 go step actually collapse skyscraper pancake method result poor comparison fun look messy perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust 911 step far actually collapse skyscraper pancake method result poor comparison fun look messy perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust 911 step far actually collapse skyscraper pancake method result</t>
+          <t>poor comparison fun look messy not perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust see 911 go step actually collapse skyscraper pancake method result poor comparison fun look messy perfect polished point clear creative vision sensible arc disjointed writing editing particularly surround scarlet witch dream sequence inspire oddly difficult track fight seemingly warp place minimal continuity especially end ultron weak villain nonchalant attitude human foiblesquirk distinctly odd motive obligatory 911 reference obligatory mention offencive extremely poor taste superhero day disturbingly oblige include terrify citizen run advance cloud concrete dust 911 step far actually collapse skyscraper pancake method result [SEP]</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -10614,20 +8256,10 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10649,14 +8281,10 @@
           <t>boring new spider extremely boring low comedy action thing oversaturate     worth time money boring new spider extremely boring low comedy action thing oversaturate     worth time money</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>boring new spider extremely boring low comedy action thing oversaturate     worth time money</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>boring new spider extremely boring low comedy action thing oversaturate     worth time money boring new spider extremely boring low comedy action thing oversaturate     worth time money boring new spider extremely boring low comedy action thing oversaturate     worth time money</t>
+          <t>boring new spider extremely boring low comedy action thing oversaturate     worth time money boring new spider extremely boring low comedy action thing oversaturate     worth time money [SEP]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -10671,20 +8299,10 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10708,12 +8326,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>like read weekly issue comic realize resemble comic_strip use purchase kid spidey fight villain focus filler love life bring comic_strip life great chemistry romance tom holland peter parker zendaya mj fulfill purpose gyllenhaal explore goodsmartcrazy bad guy potential</t>
+          <t>ENTLBL_PERSON ENTTXT_peter_parker_zendaya</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>like read weekly issue comic go realize resemble comic_strip purchase kid spidey fight villain focus filler love life bring comic_strip life great chemistry romance tom holland peter parker zendaya mj fulfill purpose pretty solid spider year exceed homecoming emotion humor great casting plot gyllenhaal explore goodsmartcrazy bad guy show potential like read weekly issue comic realize resemble comic_strip use purchase kid spidey fight villain focus filler love life bring comic_strip life great chemistry romance tom holland peter parker zendaya mj fulfill purpose pretty solid spider year exceed homecoming emotion humor great casting plot gyllenhaal explore goodsmartcrazy bad guy potential like read weekly issue comic realize resemble comic_strip use purchase kid spidey fight villain focus filler love life bring comic_strip life great chemistry romance tom holland peter parker zendaya mj fulfill purpose gyllenhaal explore goodsmartcrazy bad guy potential</t>
+          <t>like read weekly issue comic go realize resemble comic_strip purchase kid spidey fight villain focus filler love life bring comic_strip life great chemistry romance tom holland peter parker zendaya mj fulfill purpose pretty solid spider year exceed homecoming emotion humor great casting plot gyllenhaal explore goodsmartcrazy bad guy show potential like read weekly issue comic realize resemble comic_strip use purchase kid spidey fight villain focus filler love life bring comic_strip life great chemistry romance tom holland peter parker zendaya mj fulfill purpose pretty solid spider year exceed homecoming emotion humor great casting plot gyllenhaal explore goodsmartcrazy bad guy potential [SEP] ENTLBL_PERSON ENTTXT_peter_parker_zendaya</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -10728,20 +8346,10 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -10763,14 +8371,10 @@
           <t>73 non doctor strange fan rating rating person watch doctor strange time interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random one die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth watch especially cinemas sound quality computer generate imagery god tier 73 non doctor strange fan rating rating person doctor strange time interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth especially cinemas sound quality computer generate imagery god tier</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth especially cinemas sound quality computer generate imagery god tier</t>
-        </is>
-      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>73 non doctor strange fan rating rating person watch doctor strange time interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random one die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth watch especially cinemas sound quality computer generate imagery god tier 73 non doctor strange fan rating rating person doctor strange time interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth especially cinemas sound quality computer generate imagery god tier interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth especially cinemas sound quality computer generate imagery god tier</t>
+          <t>73 non doctor strange fan rating rating person watch doctor strange time interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random one die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth watch especially cinemas sound quality computer generate imagery god tier 73 non doctor strange fan rating rating person doctor strange time interesting grab attention quickly love action non stop insanity quickly come realisation lack lack total 4 random die moment step wanda addition lack multiverse world d love action explore problem villain likeable good guy love wanda far strong emotion feel pain generally good worth especially cinemas sound quality computer generate imagery god tier [SEP]</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -10785,20 +8389,10 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10822,12 +8416,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>force soon normal viewer fan m pretty underwhelmed think force second unbaked raw soon 1 try base multiple properly introduce feel like pose great ve civil war feel like try yeah look important like hell feel force confrontation plot mixed forge expect superhero feel like terrible hard spider feel like trailer need hype want advertise new let drop 2 fight feel bad quality un creativity feel like try seriously compare rest captain america work dynamic fight joke etc thing blank uninteresting camera shot simply 2 warmachine war machine gatle gun rocket basically iron gunpowder version chase slow gliding guy basically un arm comparison iron armor accidentally shoot vision sky know vision range sure precision force range use vision mixed let try hide pretty whelm honest 3 think notice script problem plot hole overall feel business business feel lot choice good lot bore strong main fe video footage base camera like middle 1991 perfect let forget   think actual plot let hate unknown reason viewer want fight yeah beat like fight perfect constantly feel try   ohhh good fan feeling flow recommend maybe hardcore fan</t>
+          <t>ENTLBL_ORG ENTTXT_un</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>force soon normal viewer fan m pretty underwhelmed think force second unbaked raw soon 1 try base multiple not properly introduce feel like pose great ve get civil war feel like try yeah look important like hell feels force confrontation plot mixed forge expect superhero feel like terrible hard spider feel like trailer need hype want advertise new let drop 2 fight feel bad lack comparison hulk vs iron ii get   quality un creativity feel like not try seriously compare rest captain america work dynamic fight off joke etc thing blank uninteresting camera shot simply 2 warmachine war machine gatle gun rocket basically iron gunpowder version chase slow gliding guy basically un arm comparison iron armor get accidentally shoot vision sky know vision range sure precision force range not vision mixed let try hide pretty whelm honest 3 not think not notice script problem plot hole overall feel business business go feel lot choice good lot bore story strong main fe video footage base camera like middle 1991 perfect let forget think actual plot let hate unknown reason viewer want fight yeah beat like fight m sure hear people rant captain america super soldier able fight iron buky iron hand iron chest comic_strip not perfect constantly feel not try ohhh good fan feeling flow not recommend maybe hardcore fan force soon normal viewer fan m pretty underwhelmed think force second unbaked raw soon 1 try base multiple properly introduce feel like pose great ve civil war feel like try yeah look important like hell feels force confrontation plot mixed forge expect superhero feel like terrible hard spider feel like trailer need hype want advertise new let drop 2 fight feel bad lack comparison hulk vs iron ii   quality un creativity feel like try seriously compare rest captain america work dynamic fight joke etc thing blank uninteresting camera shot simply 2 warmachine war machine gatle gun rocket basically iron gunpowder version chase slow gliding guy basically un arm comparison iron armor accidentally shoot vision sky know vision range sure precision force range use vision mixed let try hide pretty whelm honest 3 think notice script problem plot hole overall feel business business feel lot choice good lot bore strong main fe video footage base camera like middle 1991 perfect let forget think actual plot let hate unknown reason viewer want fight yeah beat like fight m sure hear people rant captain america super soldier able fight iron buky iron hand iron chest comic_strip perfect constantly feel try ohhh good fan feeling flow recommend maybe hardcore fan force soon normal viewer fan m pretty underwhelmed think force second unbaked raw soon 1 try base multiple properly introduce feel like pose great ve civil war feel like try yeah look important like hell feel force confrontation plot mixed forge expect superhero feel like terrible hard spider feel like trailer need hype want advertise new let drop 2 fight feel bad quality un creativity feel like try seriously compare rest captain america work dynamic fight joke etc thing blank uninteresting camera shot simply 2 warmachine war machine gatle gun rocket basically iron gunpowder version chase slow gliding guy basically un arm comparison iron armor accidentally shoot vision sky know vision range sure precision force range use vision mixed let try hide pretty whelm honest 3 think notice script problem plot hole overall feel business business feel lot choice good lot bore strong main fe video footage base camera like middle 1991 perfect let forget   think actual plot let hate unknown reason viewer want fight yeah beat like fight perfect constantly feel try   ohhh good fan feeling flow recommend maybe hardcore fan</t>
+          <t>force soon normal viewer fan m pretty underwhelmed think force second unbaked raw soon 1 try base multiple not properly introduce feel like pose great ve get civil war feel like try yeah look important like hell feels force confrontation plot mixed forge expect superhero feel like terrible hard spider feel like trailer need hype want advertise new let drop 2 fight feel bad lack comparison hulk vs iron ii get   quality un creativity feel like not try seriously compare rest captain america work dynamic fight off joke etc thing blank uninteresting camera shot simply 2 warmachine war machine gatle gun rocket basically iron gunpowder version chase slow gliding guy basically un arm comparison iron armor get accidentally shoot vision sky know vision range sure precision force range not vision mixed let try hide pretty whelm honest 3 not think not notice script problem plot hole overall feel business business go feel lot choice good lot bore story strong main fe video footage base camera like middle 1991 perfect let forget think actual plot let hate unknown reason viewer want fight yeah beat like fight m sure hear people rant captain america super soldier able fight iron buky iron hand iron chest comic_strip not perfect constantly feel not try ohhh good fan feeling flow not recommend maybe hardcore fan force soon normal viewer fan m pretty underwhelmed think force second unbaked raw soon 1 try base multiple properly introduce feel like pose great ve civil war feel like try yeah look important like hell feels force confrontation plot mixed forge expect superhero feel like terrible hard spider feel like trailer need hype want advertise new let drop 2 fight feel bad lack comparison hulk vs iron ii   quality un creativity feel like try seriously compare rest captain america work dynamic fight joke etc thing blank uninteresting camera shot simply 2 warmachine war machine gatle gun rocket basically iron gunpowder version chase slow gliding guy basically un arm comparison iron armor accidentally shoot vision sky know vision range sure precision force range use vision mixed let try hide pretty whelm honest 3 think notice script problem plot hole overall feel business business feel lot choice good lot bore strong main fe video footage base camera like middle 1991 perfect let forget think actual plot let hate unknown reason viewer want fight yeah beat like fight m sure hear people rant captain america super soldier able fight iron buky iron hand iron chest comic_strip perfect constantly feel try ohhh good fan feeling flow recommend maybe hardcore fan [SEP] ENTLBL_ORG ENTTXT_un</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -10842,20 +8436,10 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10879,12 +8463,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>waste time money joss whedon finish main thought head earth joss whedon write direct bland dimensional shoot em joss whedon humorless computer generate imagery f handle number robotic hollywood hack look forward moon excitement thought typical jump cut scream video game pretty joke flat dialogue embarrass think scarlett johannsson charming usually like bad incredibly watchable mark ruffalo render total snooze possible robert downey sarcastic fun god good real letdown like potential greatness flatten super dumb hollywood crap machine</t>
+          <t>ENTLBL_PERSON ENTTXT_joss_whedon ENTLBL_ORG ENTTXT_joss_whedon_humorless ENTLBL_PERSON ENTTXT_scarlett_johannsson ENTLBL_PERSON ENTTXT_robert_downey_sarcastic</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>waste time money joss whedon finish watch main thought head earth joss whedon write whedon master witty earthy dialogue watch buffy angel firefly know direct action powerful interpersonal connection direct bland dimensional shoot em joss whedon humorless computer generate imagery f handle number robotic hollywood hack look forward moon excitement thought not typical jump cut scream video game pretty joke flat dialogue embarrass think scarlett johannsson charming usually not like bad incredibly watchable mark ruffalo render total snooze possible robert downey sarcastic fun god good real letdown like potential greatness flatten super dumb hollywood crap machine waste time money joss whedon finish main thought head earth joss whedon write whedon master witty earthy dialogue buffy angel firefly know direct action powerful interpersonal connection direct bland dimensional shoot em joss whedon humorless computer generate imagery f handle number robotic hollywood hack look forward moon excitement thought typical jump cut scream video game pretty joke flat dialogue embarrass think scarlett johannsson charming usually like bad incredibly watchable mark ruffalo render total snooze possible robert downey sarcastic fun god good real letdown like potential greatness flatten super dumb hollywood crap machine waste time money joss whedon finish main thought head earth joss whedon write direct bland dimensional shoot em joss whedon humorless computer generate imagery f handle number robotic hollywood hack look forward moon excitement thought typical jump cut scream video game pretty joke flat dialogue embarrass think scarlett johannsson charming usually like bad incredibly watchable mark ruffalo render total snooze possible robert downey sarcastic fun god good real letdown like potential greatness flatten super dumb hollywood crap machine</t>
+          <t>waste time money joss whedon finish watch main thought head earth joss whedon write whedon master witty earthy dialogue watch buffy angel firefly know direct action powerful interpersonal connection direct bland dimensional shoot em joss whedon humorless computer generate imagery f handle number robotic hollywood hack look forward moon excitement thought not typical jump cut scream video game pretty joke flat dialogue embarrass think scarlett johannsson charming usually not like bad incredibly watchable mark ruffalo render total snooze possible robert downey sarcastic fun god good real letdown like potential greatness flatten super dumb hollywood crap machine waste time money joss whedon finish main thought head earth joss whedon write whedon master witty earthy dialogue buffy angel firefly know direct action powerful interpersonal connection direct bland dimensional shoot em joss whedon humorless computer generate imagery f handle number robotic hollywood hack look forward moon excitement thought typical jump cut scream video game pretty joke flat dialogue embarrass think scarlett johannsson charming usually like bad incredibly watchable mark ruffalo render total snooze possible robert downey sarcastic fun god good real letdown like potential greatness flatten super dumb hollywood crap machine [SEP] ENTLBL_PERSON ENTTXT_joss_whedon ENTLBL_ORG ENTTXT_joss_whedon_humorless ENTLBL_PERSON ENTTXT_scarlett_johannsson ENTLBL_PERSON ENTTXT_robert_downey_sarcastic</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -10899,20 +8483,10 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10936,12 +8510,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>cut anticipate rush day release d cinema bated week past decide time describe good unlikely begin cinema find bored laugh mean laugh suppose comedy leave confuse decision walk half way unsure huge hype complete let decide chance release dvd realise wrong fan know previous plot fail explain development aware find wrack brain remember thing comic_strip generic superhero new special realise unconventional view feel lot people enjoy feel guess die hard fan claim dislike big superhero time</t>
+          <t>ENTLBL_PERSON ENTTXT_suppose_comedy_leave_confuse</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>not cut anticipate rush day release d cinema bated week past decide time describe good see unlikely begin cinema find bored laugh part mean laugh suppose comedy leave confuse decision walk half way unsure huge hype complete let decide chance release dvd realise go wrong fan know previous plot fail explain development aware find have wrack brain remember thing comic_strip generic superhero new special realise unconventional view feel lot people enjoy feel guess die hard fan not claim dislike big superhero time cut anticipate rush day release d cinema bated week past decide time describe good unlikely begin cinema find bored laugh mean laugh suppose comedy leave confuse decision walk half way unsure huge hype complete let decide chance release dvd realise wrong fan know previous plot fail explain development aware find wrack brain remember thing comic_strip generic superhero new special realise unconventional view feel lot people enjoy feel guess die hard fan claim dislike big superhero time cut anticipate rush day release d cinema bated week past decide time describe good unlikely begin cinema find bored laugh mean laugh suppose comedy leave confuse decision walk half way unsure huge hype complete let decide chance release dvd realise wrong fan know previous plot fail explain development aware find wrack brain remember thing comic_strip generic superhero new special realise unconventional view feel lot people enjoy feel guess die hard fan claim dislike big superhero time</t>
+          <t>not cut anticipate rush day release d cinema bated week past decide time describe good see unlikely begin cinema find bored laugh part mean laugh suppose comedy leave confuse decision walk half way unsure huge hype complete let decide chance release dvd realise go wrong fan know previous plot fail explain development aware find have wrack brain remember thing comic_strip generic superhero new special realise unconventional view feel lot people enjoy feel guess die hard fan not claim dislike big superhero time cut anticipate rush day release d cinema bated week past decide time describe good unlikely begin cinema find bored laugh mean laugh suppose comedy leave confuse decision walk half way unsure huge hype complete let decide chance release dvd realise wrong fan know previous plot fail explain development aware find wrack brain remember thing comic_strip generic superhero new special realise unconventional view feel lot people enjoy feel guess die hard fan claim dislike big superhero time [SEP] ENTLBL_PERSON ENTTXT_suppose_comedy_leave_confuse</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -10956,20 +8530,10 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -10993,12 +8557,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>typically overlong long super hero fight villain pow bang like suffer psychoanalysis session realize famous awhile course forever 90 minute day hard find hour long forever hard time understand kick hour brainy young lady assemble sophisticated armored suit like ironman wakanda screw nail pack cigarette think isolated landlocked country suddenly waterway big flow battleship find ramble like</t>
+          <t>ENTLBL_ORG ENTTXT_ironman_wakanda</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>typically overlong long super hero fight villain pow bang like suffer psychoanalysis session realize famous awhile course go forever 90 minute day hard find hour long forever hard time understand kick hour brainy young lady assemble sophisticated armored suit like ironman wakanda screw nail pack cigarette think isolated landlocked country suddenly waterway big flow battleship find ramble like watch typically overlong long super hero fight villain pow bang like suffer psychoanalysis session realize famous awhile course forever 90 minute day hard find hour long forever hard time understand kick hour brainy young lady assemble sophisticated armored suit like ironman wakanda screw nail pack cigarette think isolated landlocked country suddenly waterway big flow battleship find ramble like typically overlong long super hero fight villain pow bang like suffer psychoanalysis session realize famous awhile course forever 90 minute day hard find hour long forever hard time understand kick hour brainy young lady assemble sophisticated armored suit like ironman wakanda screw nail pack cigarette think isolated landlocked country suddenly waterway big flow battleship find ramble like</t>
+          <t>typically overlong long super hero fight villain pow bang like suffer psychoanalysis session realize famous awhile course go forever 90 minute day hard find hour long forever hard time understand kick hour brainy young lady assemble sophisticated armored suit like ironman wakanda screw nail pack cigarette think isolated landlocked country suddenly waterway big flow battleship find ramble like watch typically overlong long super hero fight villain pow bang like suffer psychoanalysis session realize famous awhile course forever 90 minute day hard find hour long forever hard time understand kick hour brainy young lady assemble sophisticated armored suit like ironman wakanda screw nail pack cigarette think isolated landlocked country suddenly waterway big flow battleship find ramble like [SEP] ENTLBL_ORG ENTTXT_ironman_wakanda</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -11013,20 +8577,10 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11048,14 +8602,10 @@
           <t>good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book film spider exemplify worth penny theatre good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book spider exemplify worth penny theatre</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book spider exemplify worth penny theatre</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book film spider exemplify worth penny theatre good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book spider exemplify worth penny theatre good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book spider exemplify worth penny theatre</t>
+          <t>good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book film spider exemplify worth penny theatre good spider want join crowd theatre love relax husband enjoy especially new despite fact love moment spider mans youthful charming simultaneously badass super hero nail head holland vulnerability charisma carry refresh tone comic book spider exemplify worth penny theatre [SEP]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -11070,20 +8620,10 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -11105,14 +8645,10 @@
           <t>long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically hundred handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest black panther good bad well disappointing long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest black panther good bad disappointing</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest disappointing</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically hundred handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest black panther good bad well disappointing long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest black panther good bad disappointing long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest disappointing</t>
+          <t>long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically hundred handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest black panther good bad well disappointing long boring disappointing massively underwhelme drag 2 hour excitement plot point mean meaningfull feel totally underwhelming like death mother point underwhelming meaningless plot totally insignificant add end wakandans sacrifice basically handful soldier peace attack capital killing thousand civilian consequence bit killmonger feel unfinished like rest black panther good bad disappointing [SEP]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -11127,20 +8663,10 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11162,14 +8688,10 @@
           <t>bad spiderman not know start m shock bad like 10 12 year old completely fail grab attention hour manage lot go screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh bad spiderman know start m shock bad like 10 12 year old completely fail grab attention hour manage lot screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>bad spiderman know start m shock bad like 10 12 year old completely fail grab attention hour manage lot screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>bad spiderman not know start m shock bad like 10 12 year old completely fail grab attention hour manage lot go screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh bad spiderman know start m shock bad like 10 12 year old completely fail grab attention hour manage lot screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh bad spiderman know start m shock bad like 10 12 year old completely fail grab attention hour manage lot screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh</t>
+          <t>bad spiderman not know start m shock bad like 10 12 year old completely fail grab attention hour manage lot go screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh bad spiderman know start m shock bad like 10 12 year old completely fail grab attention hour manage lot screen consistently plain boring unbelievable unconvincing finally prefer old spider kid big meh [SEP]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11184,20 +8706,10 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11221,12 +8733,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>weak script lazy direction poor audience enjoy cleverly write viewer brain resting title feel accomplished big feel uncomfortable die guardian galaxy reason know specific group hero marketing image build feeling change people positive comment pretty excited idea brain rest enjoyable know m   disappointment chris pratt sympathy desperately look melancholic mix tape rocket raccoon try lift humor amusing episode overall want care neytiri oh mean gamora cold distant feel spend hour desperate attempt cast attention focus enjoy vin diesel brilliant performance know poor script james gunn feel inspire cast sarah michelle gellar friend maybe fact jar superhero turn cinema disappoint bit doubt production come</t>
+          <t>ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_gamora ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_sarah_michelle ENTLBL_PERSON ENTTXT_chris_pratt_sympathy</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>weak script lazy direction poor audience enjoy film cleverly write viewer brain resting title make feel accomplished big not feel uncomfortable not die guardian galaxy reason not know specific group hero marketing image build give feeling not change people positive comment watch pretty excited idea brain rest enjoyable know m go   disappointment chris pratt not sympathy desperately look melancholic mix tape rocket raccoon try lift humor amusing episode overall not want care neytiri oh mean gamora cold distant feel spend hour watch desperate attempt cast get attention focus enjoy vin diesel brilliant performance not know poor script james gunn not feel inspire cast sarah michelle gellar friend maybe fact jar superhero turn cinema disappoint bit doubt production come weak script lazy direction poor audience enjoy cleverly write viewer brain resting title feel accomplished big feel uncomfortable die guardian galaxy reason know specific group hero marketing image build feeling change people positive comment pretty excited idea brain rest enjoyable know m   disappointment chris pratt sympathy desperately look melancholic mix tape rocket raccoon try lift humor amusing episode overall want care neytiri oh mean gamora cold distant feel spend hour desperate attempt cast attention focus enjoy vin diesel brilliant performance know poor script james gunn feel inspire cast sarah michelle gellar friend maybe fact jar superhero turn cinema disappoint bit doubt production come weak script lazy direction poor audience enjoy cleverly write viewer brain resting title feel accomplished big feel uncomfortable die guardian galaxy reason know specific group hero marketing image build feeling change people positive comment pretty excited idea brain rest enjoyable know m   disappointment chris pratt sympathy desperately look melancholic mix tape rocket raccoon try lift humor amusing episode overall want care neytiri oh mean gamora cold distant feel spend hour desperate attempt cast attention focus enjoy vin diesel brilliant performance know poor script james gunn feel inspire cast sarah michelle gellar friend maybe fact jar superhero turn cinema disappoint bit doubt production come</t>
+          <t>weak script lazy direction poor audience enjoy film cleverly write viewer brain resting title make feel accomplished big not feel uncomfortable not die guardian galaxy reason not know specific group hero marketing image build give feeling not change people positive comment watch pretty excited idea brain rest enjoyable know m go   disappointment chris pratt not sympathy desperately look melancholic mix tape rocket raccoon try lift humor amusing episode overall not want care neytiri oh mean gamora cold distant feel spend hour watch desperate attempt cast get attention focus enjoy vin diesel brilliant performance not know poor script james gunn not feel inspire cast sarah michelle gellar friend maybe fact jar superhero turn cinema disappoint bit doubt production come weak script lazy direction poor audience enjoy cleverly write viewer brain resting title feel accomplished big feel uncomfortable die guardian galaxy reason know specific group hero marketing image build feeling change people positive comment pretty excited idea brain rest enjoyable know m   disappointment chris pratt sympathy desperately look melancholic mix tape rocket raccoon try lift humor amusing episode overall want care neytiri oh mean gamora cold distant feel spend hour desperate attempt cast attention focus enjoy vin diesel brilliant performance know poor script james gunn feel inspire cast sarah michelle gellar friend maybe fact jar superhero turn cinema disappoint bit doubt production come [SEP] ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_gamora ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_sarah_michelle ENTLBL_PERSON ENTTXT_chris_pratt_sympathy</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11241,20 +8753,10 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11278,12 +8780,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>good iron probably bad superhero long time expectation iron 2i enjoy love iron like flow feel like like tony stark post cold war america stay true comic_strip time deviate comic_strip stamp fresh like great carry carry tony stark millionaire millionaire douche bag larry ellison cameo cement stark combination steve job meet batman complete mac fest fully realize great largely absent ivan vankos fully flesh partially mickey rourke great performance like justin hammer actually sympathize smarmy jackass tony stark totally unlikable underdog sure chest kill stark time root like hope millionaire like lose come realization party count   change pepper pott lack sophistication overall terrence howard great james rhode actually smart choice avoid don cheadle material lack thereof work hop explain growth james rhode instead rhode inexplicably able use suit deliver military send climax fan comic book expect like spider 2 dark knight superman return like transformer revenge fall bad turn mind worry plot enjoyable</t>
+          <t>ENTLBL_EVENT ENTTXT_post_cold_war_america ENTLBL_PERSON ENTTXT_larry_ellison ENTLBL_PERSON ENTTXT_steve_job_meet_batman ENTLBL_ORG ENTTXT_justin ENTLBL_PERSON ENTTXT_james_rhode ENTLBL_PERSON ENTTXT_larry_ellison_cameo ENTLBL_PERSON ENTTXT_howard_great_james_rhode</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>good iron probably bad superhero movie long time expectation go iron 2i enjoy love iron like flow feel like take like tony stark post cold war america stay true comic_strip time deviate comic_strip stamp fresh like great carry carry tony stark millionaire put millionaire douche bag larry ellison cameo cement stark combination steve job meet batman complete mac fest not fully realize excuse explosion cool iron suit great largely absent ivan vankos fully flesh partially mickey rourke great performance like justin hammer actually sympathize smarmy jackass new natashanatalieblack widow non issue void impression tony stark totally unlikable underdog not sure chest kill alcohol kill yes vaguely reference demon bottle storyline comic_strip   stark time make root like hope get millionaire like lose come realization party not count   change pepper pott lack sophistication overall terrence howard not great james rhode actually smart choice avoid don cheadle material lack thereof work not explain able jump iron suit use hop explain growth james rhode instead rhode inexplicably able use suit deliver military send climax fan comic book movie not expect like spider 2 dark knight superman return like transformer revenge fall bad turn mind not worry plot movie enjoyable good iron probably bad superhero long time expectation iron 2i enjoy love iron like flow feel like like tony stark post cold war america stay true comic_strip time deviate comic_strip stamp fresh like great carry carry tony stark millionaire millionaire douche bag larry ellison cameo cement stark combination steve job meet batman complete mac fest fully realize excuse explosion cool iron suit great largely absent ivan vankos fully flesh partially mickey rourke great performance like justin hammer actually sympathize smarmy jackass new natashanatalieblack widow non issue void impression tony stark totally unlikable underdog sure chest kill alcohol kill yes vaguely reference demon bottle storyline comic_strip   stark time root like hope millionaire like lose come realization party count   change pepper pott lack sophistication overall terrence howard great james rhode actually smart choice avoid don cheadle material lack thereof work explain able jump iron suit use hop explain growth james rhode instead rhode inexplicably able use suit deliver military send climax fan comic book expect like spider 2 dark knight superman return like transformer revenge fall bad turn mind worry plot enjoyable good iron probably bad superhero long time expectation iron 2i enjoy love iron like flow feel like like tony stark post cold war america stay true comic_strip time deviate comic_strip stamp fresh like great carry carry tony stark millionaire millionaire douche bag larry ellison cameo cement stark combination steve job meet batman complete mac fest fully realize great largely absent ivan vankos fully flesh partially mickey rourke great performance like justin hammer actually sympathize smarmy jackass tony stark totally unlikable underdog sure chest kill stark time root like hope millionaire like lose come realization party count   change pepper pott lack sophistication overall terrence howard great james rhode actually smart choice avoid don cheadle material lack thereof work hop explain growth james rhode instead rhode inexplicably able use suit deliver military send climax fan comic book expect like spider 2 dark knight superman return like transformer revenge fall bad turn mind worry plot enjoyable</t>
+          <t>good iron probably bad superhero movie long time expectation go iron 2i enjoy love iron like flow feel like take like tony stark post cold war america stay true comic_strip time deviate comic_strip stamp fresh like great carry carry tony stark millionaire put millionaire douche bag larry ellison cameo cement stark combination steve job meet batman complete mac fest not fully realize excuse explosion cool iron suit great largely absent ivan vankos fully flesh partially mickey rourke great performance like justin hammer actually sympathize smarmy jackass new natashanatalieblack widow non issue void impression tony stark totally unlikable underdog not sure chest kill alcohol kill yes vaguely reference demon bottle storyline comic_strip   stark time make root like hope get millionaire like lose come realization party not count   change pepper pott lack sophistication overall terrence howard not great james rhode actually smart choice avoid don cheadle material lack thereof work not explain able jump iron suit use hop explain growth james rhode instead rhode inexplicably able use suit deliver military send climax fan comic book movie not expect like spider 2 dark knight superman return like transformer revenge fall bad turn mind not worry plot movie enjoyable good iron probably bad superhero long time expectation iron 2i enjoy love iron like flow feel like like tony stark post cold war america stay true comic_strip time deviate comic_strip stamp fresh like great carry carry tony stark millionaire millionaire douche bag larry ellison cameo cement stark combination steve job meet batman complete mac fest fully realize excuse explosion cool iron suit great largely absent ivan vankos fully flesh partially mickey rourke great performance like justin hammer actually sympathize smarmy jackass new natashanatalieblack widow non issue void impression tony stark totally unlikable underdog sure chest kill alcohol kill yes vaguely reference demon bottle storyline comic_strip   stark time root like hope millionaire like lose come realization party count   change pepper pott lack sophistication overall terrence howard great james rhode actually smart choice avoid don cheadle material lack thereof work explain able jump iron suit use hop explain growth james rhode instead rhode inexplicably able use suit deliver military send climax fan comic book expect like spider 2 dark knight superman return like transformer revenge fall bad turn mind worry plot enjoyable [SEP] ENTLBL_EVENT ENTTXT_post_cold_war_america ENTLBL_PERSON ENTTXT_larry_ellison ENTLBL_PERSON ENTTXT_steve_job_meet_batman ENTLBL_ORG ENTTXT_justin ENTLBL_PERSON ENTTXT_james_rhode ENTLBL_PERSON ENTTXT_larry_ellison_cameo ENTLBL_PERSON ENTTXT_howard_great_james_rhode</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11298,20 +8800,10 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11333,14 +8825,10 @@
           <t>poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad marvel legacy poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad legacy</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad legacy</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad marvel legacy poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad legacy poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad legacy</t>
+          <t>poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad marvel legacy poor extremely lazy writing weak direction disappointing plot robotic act force dialog deviant common appearance sad legacy [SEP]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11355,20 +8843,10 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11390,14 +8868,10 @@
           <t>disappointed   see trailer not impressed hype get buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial started look promising 10 minute get weird fast curious opinion 40 minute super stupid boring get well fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute not think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person disappointed   trailer impressed hype buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial started look promising 10 minute weird fast curious opinion 40 minute super stupid boring fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>disappointed   trailer impressed hype buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial start look promising 10 minute weird fast curious opinion 40 minute super stupid boring fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>disappointed   see trailer not impressed hype get buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial started look promising 10 minute get weird fast curious opinion 40 minute super stupid boring get well fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute not think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person disappointed   trailer impressed hype buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial started look promising 10 minute weird fast curious opinion 40 minute super stupid boring fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person disappointed   trailer impressed hype buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial start look promising 10 minute weird fast curious opinion 40 minute super stupid boring fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person</t>
+          <t>disappointed   see trailer not impressed hype get buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial started look promising 10 minute get weird fast curious opinion 40 minute super stupid boring get well fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute not think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person disappointed   trailer impressed hype buy ticket online afternoon new theater recliner seat rush time sit lease 30 minute commercial started look promising 10 minute weird fast curious opinion 40 minute super stupid boring fight bp american black dude come life african dialect mishmash dependency computer generate imagery etc korean car chase bad poorly execute think people die drench blood gather pic callander help run away etc super immature execution esp beginning way black white person [SEP]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11412,20 +8886,10 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11449,12 +8913,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>bad completely stupid minute feel little bit dumber constantly opposite sane person planet line exist new random overused trope pretty guess happen time producer great actor totally actually learn captain america likely ill like mind blow human stupid race seriously stress waste time like properly slightly moderately retard</t>
+          <t>ENTLBL_PERSON ENTTXT_tommy_lee_samuel</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>bad see completely stupid minute watch make feel little bit dumber constantly opposite sane person planet line exist new random overused trope pretty guess go happen time bad piece hollywood bullshit see fantastic producer great actor totally want tommy lee samuel l great sunset limit actually learn move captain america likely ill like mind blow human stupid race seriously stress waste time like properly slightly moderately retard bad completely stupid minute feel little bit dumber constantly opposite sane person planet line exist new random overused trope pretty guess happen time bad piece hollywood bullshit fantastic producer great actor totally want tommy lee samuel l great sunset limit actually learn captain america likely ill like mind blow human stupid race seriously stress waste time like properly slightly moderately retard bad completely stupid minute feel little bit dumber constantly opposite sane person planet line exist new random overused trope pretty guess happen time producer great actor totally actually learn captain america likely ill like mind blow human stupid race seriously stress waste time like properly slightly moderately retard</t>
+          <t>bad see completely stupid minute watch make feel little bit dumber constantly opposite sane person planet line exist new random overused trope pretty guess go happen time bad piece hollywood bullshit see fantastic producer great actor totally want tommy lee samuel l great sunset limit actually learn move captain america likely ill like mind blow human stupid race seriously stress waste time like properly slightly moderately retard bad completely stupid minute feel little bit dumber constantly opposite sane person planet line exist new random overused trope pretty guess happen time bad piece hollywood bullshit fantastic producer great actor totally want tommy lee samuel l great sunset limit actually learn captain america likely ill like mind blow human stupid race seriously stress waste time like properly slightly moderately retard [SEP] ENTLBL_PERSON ENTTXT_tommy_lee_samuel</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11469,20 +8933,10 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11504,14 +8958,10 @@
           <t>fanfiction type script script disjoint shallow feel fanfiction ish guess big issue not see disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat not go see bad movie ill 6 star oh important thing end credit midcredit leave 5 minute early movie fanfiction type script script disjoint shallow feel fanfiction ish guess big issue disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat bad ill 6 star oh important thing end credit midcredit leave 5 minute early</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>fanfiction type script script disjoint shallow feel fanfiction ish guess big issue disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat bad ill 6 star oh important thing end credit midcredit leave 5 minute early</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>fanfiction type script script disjoint shallow feel fanfiction ish guess big issue not see disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat not go see bad movie ill 6 star oh important thing end credit midcredit leave 5 minute early movie fanfiction type script script disjoint shallow feel fanfiction ish guess big issue disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat bad ill 6 star oh important thing end credit midcredit leave 5 minute early fanfiction type script script disjoint shallow feel fanfiction ish guess big issue disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat bad ill 6 star oh important thing end credit midcredit leave 5 minute early</t>
+          <t>fanfiction type script script disjoint shallow feel fanfiction ish guess big issue not see disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat not go see bad movie ill 6 star oh important thing end credit midcredit leave 5 minute early movie fanfiction type script script disjoint shallow feel fanfiction ish guess big issue disney ms person development sorry disney m line pocket cent minor play attempt humor family ms fall flat place outside stand let flerkin eat bad ill 6 star oh important thing end credit midcredit leave 5 minute early [SEP]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11526,20 +8976,10 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11563,12 +9003,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>visual feast horror horror aspect horror probably visually violent obviously open lot possibility future franchise ill let find great introduction cameo lot sam raimis previous superhero expect total departure rest mcu</t>
+          <t>ENTLBL_PERSON ENTTXT_sam_raimis</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>visual feast doctor strange heavily dependent visual call horror horror aspect not horror probably visually violent obviously open lot possibility future franchise ill let find great introduction cameo lot back sam raimis previous movie superhero not expect total departure rest mcu visual feast doctor strange heavily dependent visual horror horror aspect horror probably visually violent obviously open lot possibility future franchise ill let find great introduction cameo lot sam raimis previous superhero expect total departure rest mcu visual feast horror horror aspect horror probably visually violent obviously open lot possibility future franchise ill let find great introduction cameo lot sam raimis previous superhero expect total departure rest mcu</t>
+          <t>visual feast doctor strange heavily dependent visual call horror horror aspect not horror probably visually violent obviously open lot possibility future franchise ill let find great introduction cameo lot back sam raimis previous movie superhero not expect total departure rest mcu visual feast doctor strange heavily dependent visual horror horror aspect horror probably visually violent obviously open lot possibility future franchise ill let find great introduction cameo lot sam raimis previous superhero expect total departure rest mcu [SEP] ENTLBL_PERSON ENTTXT_sam_raimis</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11583,20 +9023,10 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11620,12 +9050,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>ensemble act fall short hype 2012 summer blockbuster title garner attention praise direct joss whedon superhero ensemble mark amazing moment mcu bring iconic spectacle action mayhem undeniably entertain hard ignore linger feeling reputation overstate impact success lean heavily presentation hero collective camaraderie course action pack set piece technical standpoint hit right note special effect choreographed battle visual spectacle cater fan explosive action superhuman feat joss whedon direction seamlessly juggle ensemble cast allow hero showcase signature power personality quirk triumph overshadow pressing question substance beneath surface narrative ambition match technical prowess lean heavily tried true formula hero initially clash differ viewpoint unite common threat formulaic structure staple superhero storytelling fail provide depth nuance elevate mere popcorn entertainment key criticism direct lack profound theme underlie message unlike cinematic counterpart delve complex moral dilemma societal reflection predominantly rest laurel spectacle thrill beloved share screen humor enjoyable occasionally undercut moment carry weight development backseat action orient focus hero bring charisma table arc largely remain confine establish personas moment introspection growth tend fleet leave audience hungry substantial evolution conclusion mean bad status cornerstone cinematic deserve consider pioneer feat assemble beloved grand scale reputation game changer overshadow shortcoming entertaining deliver promise action hero camaraderie lack deep thematic exploration depth prevent ascend echelon true cinematic greatness</t>
+          <t>ENTLBL_ORG ENTTXT_whedon_superhero</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ensemble act fall short hype 2012 summer blockbuster title garner attention praise direct joss whedon superhero ensemble mark amazing moment mcu bring iconic spectacle action mayhem undeniably entertain hard ignore linger feeling film reputation overstate impact premise simple entice earth mighty hero iron captain america thor hulk black widow hawkeye join force thwart alien invasion orchestrate loki film success lean heavily presentation hero collective camaraderie course action pack set piece technical standpoint hit right note special effect choreographed battle visual spectacle cater fan explosive action superhuman feat joss whedon direction seamlessly juggle ensemble cast allow hero showcase signature power personality quirk triumph overshadow pressing question substance beneath surface film narrative ambition not match technical prowess lean heavily tried true formula hero initially clash differ viewpoint unite common threat formulaic structure staple superhero storytelling fail provide depth nuance elevate mere popcorn entertainment key criticism direct lack profound theme underlie message unlike cinematic counterpart delve complex moral dilemma societal reflection predominantly rest laurel spectacle thrill see beloved share screen film humor enjoyable occasionally undercut moment carry weight development take backseat film action orient focus hero bring charisma table arc largely remain confine establish personas moment introspection growth tend fleet leave audience hungry substantial evolution conclusion mean bad status cornerstone cinematic deserve consider pioneer feat assemble beloved grand scale film reputation game changer overshadow shortcoming entertaining deliver promise action hero camaraderie lack deep thematic exploration depth prevent ascend echelon true cinematic greatness ensemble act fall short hype 2012 summer blockbuster title garner attention praise direct joss whedon superhero ensemble mark amazing moment mcu bring iconic spectacle action mayhem undeniably entertain hard ignore linger feeling reputation overstate impact premise simple entice earth mighty hero iron captain america thor hulk black widow hawkeye join force thwart alien invasion orchestrate loki success lean heavily presentation hero collective camaraderie course action pack set piece technical standpoint hit right note special effect choreographed battle visual spectacle cater fan explosive action superhuman feat joss whedon direction seamlessly juggle ensemble cast allow hero showcase signature power personality quirk triumph overshadow pressing question substance beneath surface narrative ambition match technical prowess lean heavily tried true formula hero initially clash differ viewpoint unite common threat formulaic structure staple superhero storytelling fail provide depth nuance elevate mere popcorn entertainment key criticism direct lack profound theme underlie message unlike cinematic counterpart delve complex moral dilemma societal reflection predominantly rest laurel spectacle thrill beloved share screen humor enjoyable occasionally undercut moment carry weight development backseat action orient focus hero bring charisma table arc largely remain confine establish personas moment introspection growth tend fleet leave audience hungry substantial evolution conclusion mean bad status cornerstone cinematic deserve consider pioneer feat assemble beloved grand scale reputation game changer overshadow shortcoming entertaining deliver promise action hero camaraderie lack deep thematic exploration depth prevent ascend echelon true cinematic greatness ensemble act fall short hype 2012 summer blockbuster title garner attention praise direct joss whedon superhero ensemble mark amazing moment mcu bring iconic spectacle action mayhem undeniably entertain hard ignore linger feeling reputation overstate impact success lean heavily presentation hero collective camaraderie course action pack set piece technical standpoint hit right note special effect choreographed battle visual spectacle cater fan explosive action superhuman feat joss whedon direction seamlessly juggle ensemble cast allow hero showcase signature power personality quirk triumph overshadow pressing question substance beneath surface narrative ambition match technical prowess lean heavily tried true formula hero initially clash differ viewpoint unite common threat formulaic structure staple superhero storytelling fail provide depth nuance elevate mere popcorn entertainment key criticism direct lack profound theme underlie message unlike cinematic counterpart delve complex moral dilemma societal reflection predominantly rest laurel spectacle thrill beloved share screen humor enjoyable occasionally undercut moment carry weight development backseat action orient focus hero bring charisma table arc largely remain confine establish personas moment introspection growth tend fleet leave audience hungry substantial evolution conclusion mean bad status cornerstone cinematic deserve consider pioneer feat assemble beloved grand scale reputation game changer overshadow shortcoming entertaining deliver promise action hero camaraderie lack deep thematic exploration depth prevent ascend echelon true cinematic greatness</t>
+          <t>ensemble act fall short hype 2012 summer blockbuster title garner attention praise direct joss whedon superhero ensemble mark amazing moment mcu bring iconic spectacle action mayhem undeniably entertain hard ignore linger feeling film reputation overstate impact premise simple entice earth mighty hero iron captain america thor hulk black widow hawkeye join force thwart alien invasion orchestrate loki film success lean heavily presentation hero collective camaraderie course action pack set piece technical standpoint hit right note special effect choreographed battle visual spectacle cater fan explosive action superhuman feat joss whedon direction seamlessly juggle ensemble cast allow hero showcase signature power personality quirk triumph overshadow pressing question substance beneath surface film narrative ambition not match technical prowess lean heavily tried true formula hero initially clash differ viewpoint unite common threat formulaic structure staple superhero storytelling fail provide depth nuance elevate mere popcorn entertainment key criticism direct lack profound theme underlie message unlike cinematic counterpart delve complex moral dilemma societal reflection predominantly rest laurel spectacle thrill see beloved share screen film humor enjoyable occasionally undercut moment carry weight development take backseat film action orient focus hero bring charisma table arc largely remain confine establish personas moment introspection growth tend fleet leave audience hungry substantial evolution conclusion mean bad status cornerstone cinematic deserve consider pioneer feat assemble beloved grand scale film reputation game changer overshadow shortcoming entertaining deliver promise action hero camaraderie lack deep thematic exploration depth prevent ascend echelon true cinematic greatness ensemble act fall short hype 2012 summer blockbuster title garner attention praise direct joss whedon superhero ensemble mark amazing moment mcu bring iconic spectacle action mayhem undeniably entertain hard ignore linger feeling reputation overstate impact premise simple entice earth mighty hero iron captain america thor hulk black widow hawkeye join force thwart alien invasion orchestrate loki success lean heavily presentation hero collective camaraderie course action pack set piece technical standpoint hit right note special effect choreographed battle visual spectacle cater fan explosive action superhuman feat joss whedon direction seamlessly juggle ensemble cast allow hero showcase signature power personality quirk triumph overshadow pressing question substance beneath surface narrative ambition match technical prowess lean heavily tried true formula hero initially clash differ viewpoint unite common threat formulaic structure staple superhero storytelling fail provide depth nuance elevate mere popcorn entertainment key criticism direct lack profound theme underlie message unlike cinematic counterpart delve complex moral dilemma societal reflection predominantly rest laurel spectacle thrill beloved share screen humor enjoyable occasionally undercut moment carry weight development backseat action orient focus hero bring charisma table arc largely remain confine establish personas moment introspection growth tend fleet leave audience hungry substantial evolution conclusion mean bad status cornerstone cinematic deserve consider pioneer feat assemble beloved grand scale reputation game changer overshadow shortcoming entertaining deliver promise action hero camaraderie lack deep thematic exploration depth prevent ascend echelon true cinematic greatness [SEP] ENTLBL_ORG ENTTXT_whedon_superhero</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -11640,20 +9070,10 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -11677,12 +9097,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>want place steal sht age ultron amaze theater little know ant albeit small extent different reason ant definitely 5 cinematic tie winter soldier place fan action spectacular shrink dynamic utilize hero villain alike intriguing especially quantum level know microverse canon   prefer clear direct hand hand combat oppose scott punch opponent ease miniature level action overall pleasing like state minor appearance falcon welcome addition include short fight final fight pretty spectacular lack steve vs bucky tws term hand hand combat simply fact usage everyday item weapon shrink grow concept battle oh yea appreciate concept ant assist order scott probably funniest action unlike humor humor ant feel fluent seamless remarkably hilarious personal favorite funny type definitely inclusion thomas tank engine toy climax literally balloon previously hand sized toy actual railroad funny fact thomas eye motion   action humor factor discuss aside bring point yellowjacket appear literally act disappointing eye sufficient kill enjoyment solid 85 910 definitely especially fan</t>
+          <t>ENTLBL_ORG ENTTXT_scott_punch ENTLBL_PERSON ENTTXT_steve_vs_bucky_tws_term ENTLBL_PERSON ENTTXT_thomas_eye_motion</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>want place steal sht age ultron amaze see theater little know ant albeit small extent different reason see ant definitely 5 cinematic film tie winter soldier place fan action spectacular film shrink dynamic utilize hero villain alike intriguing especially take quantum level know microverse canon   prefer clear direct hand hand combat oppose scott punch opponent ease miniature level action overall pleasing like state minor appearance falcon welcome addition include short fight final fight pretty spectacular lack see steve vs bucky tws term hand hand combat simply fact usage everyday item weapon shrink grow concept battle oh yea appreciate concept ant assist order scott probably funniest action see little quip joke film look like episode spongebob unlike humor movie humor ant feel fluent seamless remarkably hilarious personal favorite funny type definitely inclusion thomas tank engine toy climax literally balloon previously hand sized toy actual railroad funny fact thomas eye motion   action humor factor discuss aside humorous enjoyable villain darren cross thoroughly oddly similar stane ironman 2008 bring point yellowjacket appear literally act disappointing eye sufficient kill enjoyment solid 85 910 definitely especially fan want place steal sht age ultron amaze theater little know ant albeit small extent different reason ant definitely 5 cinematic tie winter soldier place fan action spectacular shrink dynamic utilize hero villain alike intriguing especially quantum level know microverse canon   prefer clear direct hand hand combat oppose scott punch opponent ease miniature level action overall pleasing like state minor appearance falcon welcome addition include short fight final fight pretty spectacular lack steve vs bucky tws term hand hand combat simply fact usage everyday item weapon shrink grow concept battle oh yea appreciate concept ant assist order scott probably funniest action little quip joke look like episode spongebob unlike humor humor ant feel fluent seamless remarkably hilarious personal favorite funny type definitely inclusion thomas tank engine toy climax literally balloon previously hand sized toy actual railroad funny fact thomas eye motion   action humor factor discuss aside humorous enjoyable villain darren cross thoroughly oddly similar stane ironman 2008 bring point yellowjacket appear literally act disappointing eye sufficient kill enjoyment solid 85 910 definitely especially fan want place steal sht age ultron amaze theater little know ant albeit small extent different reason ant definitely 5 cinematic tie winter soldier place fan action spectacular shrink dynamic utilize hero villain alike intriguing especially quantum level know microverse canon   prefer clear direct hand hand combat oppose scott punch opponent ease miniature level action overall pleasing like state minor appearance falcon welcome addition include short fight final fight pretty spectacular lack steve vs bucky tws term hand hand combat simply fact usage everyday item weapon shrink grow concept battle oh yea appreciate concept ant assist order scott probably funniest action unlike humor humor ant feel fluent seamless remarkably hilarious personal favorite funny type definitely inclusion thomas tank engine toy climax literally balloon previously hand sized toy actual railroad funny fact thomas eye motion   action humor factor discuss aside bring point yellowjacket appear literally act disappointing eye sufficient kill enjoyment solid 85 910 definitely especially fan</t>
+          <t>want place steal sht age ultron amaze see theater little know ant albeit small extent different reason see ant definitely 5 cinematic film tie winter soldier place fan action spectacular film shrink dynamic utilize hero villain alike intriguing especially take quantum level know microverse canon   prefer clear direct hand hand combat oppose scott punch opponent ease miniature level action overall pleasing like state minor appearance falcon welcome addition include short fight final fight pretty spectacular lack see steve vs bucky tws term hand hand combat simply fact usage everyday item weapon shrink grow concept battle oh yea appreciate concept ant assist order scott probably funniest action see little quip joke film look like episode spongebob unlike humor movie humor ant feel fluent seamless remarkably hilarious personal favorite funny type definitely inclusion thomas tank engine toy climax literally balloon previously hand sized toy actual railroad funny fact thomas eye motion   action humor factor discuss aside humorous enjoyable villain darren cross thoroughly oddly similar stane ironman 2008 bring point yellowjacket appear literally act disappointing eye sufficient kill enjoyment solid 85 910 definitely especially fan want place steal sht age ultron amaze theater little know ant albeit small extent different reason ant definitely 5 cinematic tie winter soldier place fan action spectacular shrink dynamic utilize hero villain alike intriguing especially quantum level know microverse canon   prefer clear direct hand hand combat oppose scott punch opponent ease miniature level action overall pleasing like state minor appearance falcon welcome addition include short fight final fight pretty spectacular lack steve vs bucky tws term hand hand combat simply fact usage everyday item weapon shrink grow concept battle oh yea appreciate concept ant assist order scott probably funniest action little quip joke look like episode spongebob unlike humor humor ant feel fluent seamless remarkably hilarious personal favorite funny type definitely inclusion thomas tank engine toy climax literally balloon previously hand sized toy actual railroad funny fact thomas eye motion   action humor factor discuss aside humorous enjoyable villain darren cross thoroughly oddly similar stane ironman 2008 bring point yellowjacket appear literally act disappointing eye sufficient kill enjoyment solid 85 910 definitely especially fan [SEP] ENTLBL_ORG ENTTXT_scott_punch ENTLBL_PERSON ENTTXT_steve_vs_bucky_tws_term ENTLBL_PERSON ENTTXT_thomas_eye_motion</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -11697,20 +9117,10 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -11732,14 +9142,10 @@
           <t>good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak</t>
+          <t>good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak good concept poorly execute hype serve tedious example poor script play genre lot great eye candy sizzle steak [SEP]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -11754,20 +9160,10 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11791,12 +9187,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>mean hype praise surround cap late adventure curious finally dare risk establish goofy embarrassing tone course crowd blockbuster critic bash certain flaw rabid fan suddenly enter defensive fanatic stance refuse accept criticism frankly care m comic book fanboy m superhero fanboy m certainly big fan countless dumb blockbuster nowadays basically m m completely honest fully aware good thing let credit substantial improvement certain area guess installment utterance exit mouth liner quip excessiveness begin feel like exact personality witty smug happen seriously recurrence thankfully small extent drama intrigue time knowactually feel like superhero parody fact winter soldier fresh superhero genre suddenly present espionage thriller implement bit suspense mystery plot surprised discover unnecessary screen romance toss big shocker hollywood   wait mean captain america stumble bar catch eye horny blonde stimulate pointless interfere arc rest happen focus threat large ensemble involve instead follow incredibly intense entertaining action sequence monumental set piece introduce fine close quarter combat non stop gunplay addition related find arc shield outcome utterly fascinating big militaristic organization draw interesting parallel america undeniably aggressive agency foreign policy consider notion completely flip thing cast shield nother evil light pleasant risk studio compelling conception lack variance hydra shield people brainwash think belligerent organization end different target essentially method perfectly exemplified line negotiate enemy early ve applaud let dirty know excited spy thriller new chapter turn erase fact studio learn produce unpredictable high stake superhero far face enormous conflictthreat mean end world irony actuality absolutely peril feel spoiler studio scared kill major minor insert form loss danger situation actually discern villain prove formidable think villain point cause shocking permanent damage societyinstitution kill major infuriating constantly tease idea significant kill point return later nonsensical excuse like revive thank deus ex machina silly scheme plan believe death transpire totally real kill suspense espionage thriller absolutely need continue honestly find captain america captivate frankly necessary superhero   oh look m powerful rebound shield creativeness construction distinction separate superhero completely unrelated note post credit totally waste lame captain america winter soldier clearly vast improvement predecessor smart thoughtful plot merging thriller genre suffer damn lack originality end lack impactful truly threaten villain</t>
+          <t>ENTLBL_PERSON ENTTXT_variance_hydra_shield</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>cap widow fury boy year mess iron 3 proceed mediocre thor 2 expectation not low movie mean hype praise surround cap late adventure curious finally dare risk establish goofy embarrassing tone course crowd please blockbuster critic bash certain flaw rabid fan suddenly enter defensive fanatic stance refuse accept criticism frankly not care m comic book fanboy m superhero fanboy m certainly big fan countless dumb blockbuster nowadays basically m say m go completely honest fully aware say good thing let credit substantial improvement certain area guess follow not pervade poorly write humor like iron 3 thor 2 installment utterance exit mouth liner quip excessiveness begin feel like exact personality witty smug take happen seriously give recurrence thankfully small extent drama intrigue time knowactually make feel like superhero parody fact winter soldier fresh superhero genre suddenly present espionage thriller implement bit suspense mystery plot surprised discover unnecessary screen romance toss big shocker hollywood   wait mean captain america not stumble bar catch eye horny blonde stimulate pointless interfere arc rest happen focus threat large ensemble involve instead follow incredibly intense entertaining action sequence monumental set piece introduce fine close quarter combat non stop gunplay definitely amusing captain america fight peer thor iron addition related find arc shield outcome utterly fascinating big militaristic organization draw interesting parallel america undeniably aggressive agency foreign policy consider notion completely flip thing cast shield nother evil light pleasant risk studio take compelling conception lack variance hydra shield people brainwash think belligerent organization well end different target essentially method perfectly exemplified line not negotiate enemy take early ve applaud let dirty know everyone excited spy thriller new chapter turn not erase fact studio not learn produce unpredictable high stake superhero far face enormous conflictthreat mean end world irony actuality absolutely peril feel spoiler studio scared kill major minor insert form loss danger situation actually discern villain prove formidable not think villain point cause shocking permanent damage societyinstitution kill major make infuriating constantly tease idea significant kill point return later nonsensical excuse like revive thank deus ex machina silly scheme plan believe death transpire totally real kill suspense espionage thriller absolutely need continue honestly not find captain america captivate frankly necessary superhero oh look m powerful rebound shield creativeness construction distinction separate superhero completely unrelated note post credit totally waste lame captain america winter soldier clearly vast improvement predecessor smart thoughtful plot merging thriller genre suffer damn lack originality end lack impactful truly threaten villain cap widow fury boy year mess iron 3 proceed mediocre thor 2 expectation low mean hype praise surround cap late adventure curious finally dare risk establish goofy embarrassing tone course crowd blockbuster critic bash certain flaw rabid fan suddenly enter defensive fanatic stance refuse accept criticism frankly care m comic book fanboy m superhero fanboy m certainly big fan countless dumb blockbuster nowadays basically m m completely honest fully aware good thing let credit substantial improvement certain area guess follow pervade poorly write humor like iron 3 thor 2 installment utterance exit mouth liner quip excessiveness begin feel like exact personality witty smug happen seriously recurrence thankfully small extent drama intrigue time knowactually feel like superhero parody fact winter soldier fresh superhero genre suddenly present espionage thriller implement bit suspense mystery plot surprised discover unnecessary screen romance toss big shocker hollywood   wait mean captain america stumble bar catch eye horny blonde stimulate pointless interfere arc rest happen focus threat large ensemble involve instead follow incredibly intense entertaining action sequence monumental set piece introduce fine close quarter combat non stop gunplay definitely amusing captain america fight peer thor iron addition related find arc shield outcome utterly fascinating big militaristic organization draw interesting parallel america undeniably aggressive agency foreign policy consider notion completely flip thing cast shield nother evil light pleasant risk studio compelling conception lack variance hydra shield people brainwash think belligerent organization end different target essentially method perfectly exemplified line negotiate enemy early ve applaud let dirty know excited spy thriller new chapter turn erase fact studio learn produce unpredictable high stake superhero far face enormous conflictthreat mean end world irony actuality absolutely peril feel spoiler studio scared kill major minor insert form loss danger situation actually discern villain prove formidable think villain point cause shocking permanent damage societyinstitution kill major infuriating constantly tease idea significant kill point return later nonsensical excuse like revive thank deus ex machina silly scheme plan believe death transpire totally real kill suspense espionage thriller absolutely need continue honestly find captain america captivate frankly necessary superhero oh look m powerful rebound shield creativeness construction distinction separate superhero completely unrelated note post credit totally waste lame captain america winter soldier clearly vast improvement predecessor smart thoughtful plot merging thriller genre suffer damn lack originality end lack impactful truly threaten villain mean hype praise surround cap late adventure curious finally dare risk establish goofy embarrassing tone course crowd blockbuster critic bash certain flaw rabid fan suddenly enter defensive fanatic stance refuse accept criticism frankly care m comic book fanboy m superhero fanboy m certainly big fan countless dumb blockbuster nowadays basically m m completely honest fully aware good thing let credit substantial improvement certain area guess installment utterance exit mouth liner quip excessiveness begin feel like exact personality witty smug happen seriously recurrence thankfully small extent drama intrigue time knowactually feel like superhero parody fact winter soldier fresh superhero genre suddenly present espionage thriller implement bit suspense mystery plot surprised discover unnecessary screen romance toss big shocker hollywood   wait mean captain america stumble bar catch eye horny blonde stimulate pointless interfere arc rest happen focus threat large ensemble involve instead follow incredibly intense entertaining action sequence monumental set piece introduce fine close quarter combat non stop gunplay addition related find arc shield outcome utterly fascinating big militaristic organization draw interesting parallel america undeniably aggressive agency foreign policy consider notion completely flip thing cast shield nother evil light pleasant risk studio compelling conception lack variance hydra shield people brainwash think belligerent organization end different target essentially method perfectly exemplified line negotiate enemy early ve applaud let dirty know excited spy thriller new chapter turn erase fact studio learn produce unpredictable high stake superhero far face enormous conflictthreat mean end world irony actuality absolutely peril feel spoiler studio scared kill major minor insert form loss danger situation actually discern villain prove formidable think villain point cause shocking permanent damage societyinstitution kill major infuriating constantly tease idea significant kill point return later nonsensical excuse like revive thank deus ex machina silly scheme plan believe death transpire totally real kill suspense espionage thriller absolutely need continue honestly find captain america captivate frankly necessary superhero   oh look m powerful rebound shield creativeness construction distinction separate superhero completely unrelated note post credit totally waste lame captain america winter soldier clearly vast improvement predecessor smart thoughtful plot merging thriller genre suffer damn lack originality end lack impactful truly threaten villain</t>
+          <t>cap widow fury boy year mess iron 3 proceed mediocre thor 2 expectation not low movie mean hype praise surround cap late adventure curious finally dare risk establish goofy embarrassing tone course crowd please blockbuster critic bash certain flaw rabid fan suddenly enter defensive fanatic stance refuse accept criticism frankly not care m comic book fanboy m superhero fanboy m certainly big fan countless dumb blockbuster nowadays basically m say m go completely honest fully aware say good thing let credit substantial improvement certain area guess follow not pervade poorly write humor like iron 3 thor 2 installment utterance exit mouth liner quip excessiveness begin feel like exact personality witty smug take happen seriously give recurrence thankfully small extent drama intrigue time knowactually make feel like superhero parody fact winter soldier fresh superhero genre suddenly present espionage thriller implement bit suspense mystery plot surprised discover unnecessary screen romance toss big shocker hollywood   wait mean captain america not stumble bar catch eye horny blonde stimulate pointless interfere arc rest happen focus threat large ensemble involve instead follow incredibly intense entertaining action sequence monumental set piece introduce fine close quarter combat non stop gunplay definitely amusing captain america fight peer thor iron addition related find arc shield outcome utterly fascinating big militaristic organization draw interesting parallel america undeniably aggressive agency foreign policy consider notion completely flip thing cast shield nother evil light pleasant risk studio take compelling conception lack variance hydra shield people brainwash think belligerent organization well end different target essentially method perfectly exemplified line not negotiate enemy take early ve applaud let dirty know everyone excited spy thriller new chapter turn not erase fact studio not learn produce unpredictable high stake superhero far face enormous conflictthreat mean end world irony actuality absolutely peril feel spoiler studio scared kill major minor insert form loss danger situation actually discern villain prove formidable not think villain point cause shocking permanent damage societyinstitution kill major make infuriating constantly tease idea significant kill point return later nonsensical excuse like revive thank deus ex machina silly scheme plan believe death transpire totally real kill suspense espionage thriller absolutely need continue honestly not find captain america captivate frankly necessary superhero oh look m powerful rebound shield creativeness construction distinction separate superhero completely unrelated note post credit totally waste lame captain america winter soldier clearly vast improvement predecessor smart thoughtful plot merging thriller genre suffer damn lack originality end lack impactful truly threaten villain cap widow fury boy year mess iron 3 proceed mediocre thor 2 expectation low mean hype praise surround cap late adventure curious finally dare risk establish goofy embarrassing tone course crowd blockbuster critic bash certain flaw rabid fan suddenly enter defensive fanatic stance refuse accept criticism frankly care m comic book fanboy m superhero fanboy m certainly big fan countless dumb blockbuster nowadays basically m m completely honest fully aware good thing let credit substantial improvement certain area guess follow pervade poorly write humor like iron 3 thor 2 installment utterance exit mouth liner quip excessiveness begin feel like exact personality witty smug happen seriously recurrence thankfully small extent drama intrigue time knowactually feel like superhero parody fact winter soldier fresh superhero genre suddenly present espionage thriller implement bit suspense mystery plot surprised discover unnecessary screen romance toss big shocker hollywood   wait mean captain america stumble bar catch eye horny blonde stimulate pointless interfere arc rest happen focus threat large ensemble involve instead follow incredibly intense entertaining action sequence monumental set piece introduce fine close quarter combat non stop gunplay definitely amusing captain america fight peer thor iron addition related find arc shield outcome utterly fascinating big militaristic organization draw interesting parallel america undeniably aggressive agency foreign policy consider notion completely flip thing cast shield nother evil light pleasant risk studio compelling conception lack variance hydra shield people brainwash think belligerent organization end different target essentially method perfectly exemplified line negotiate enemy early ve applaud let dirty know excited spy thriller new chapter turn erase fact studio learn produce unpredictable high stake superhero far face enormous conflictthreat mean end world irony actuality absolutely peril feel spoiler studio scared kill major minor insert form loss danger situation actually discern villain prove formidable think villain point cause shocking permanent damage societyinstitution kill major infuriating constantly tease idea significant kill point return later nonsensical excuse like revive thank deus ex machina silly scheme plan believe death transpire totally real kill suspense espionage thriller absolutely need continue honestly find captain america captivate frankly necessary superhero oh look m powerful rebound shield creativeness construction distinction separate superhero completely unrelated note post credit totally waste lame captain america winter soldier clearly vast improvement predecessor smart thoughtful plot merging thriller genre suffer damn lack originality end lack impactful truly threaten villain [SEP] ENTLBL_PERSON ENTTXT_variance_hydra_shield</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -11811,20 +9207,10 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11846,14 +9232,10 @@
           <t>fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like watch saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall not enjoy get bored unecessary slash fight deadpool end stupid thing see screen fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall enjoy bored unecessary slash fight deadpool end stupid thing screen</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall enjoy bored unecessary slash fight deadpool end stupid thing screen</t>
-        </is>
-      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like watch saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall not enjoy get bored unecessary slash fight deadpool end stupid thing see screen fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall enjoy bored unecessary slash fight deadpool end stupid thing screen fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall enjoy bored unecessary slash fight deadpool end stupid thing screen</t>
+          <t>fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like watch saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall not enjoy get bored unecessary slash fight deadpool end stupid thing see screen fan service absent material thw save cinematic follow actual plot hugh jackman great different different energy ryan reynold ryan reynold expect joke come mouth open storyline unecessary like saturday night live episode different sketch introduce elektra blade awesome gambit need sure overall enjoy bored unecessary slash fight deadpool end stupid thing screen [SEP]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -11868,20 +9250,10 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11905,12 +9277,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>cinematic failure potential good interesting nothis mediocre failure able interesting cinematic endgame bad bad alot potential like idea introduce thunderbolt cinematic cheap rehash instead new creative cool usual day disney hire director action science fiction fun cool anymore good thing sentry especially idea bad thing script direct red hulk imagine actually like james gunn ve perfect director like ve fun exciting cool dialogue cool action sadly good director clueless action interesting intense action scenethis boring problem cinematic couple year hire director good action director writer actually write new interesting rehashed formula ve love hop introduce red hulk perfect opportunity use aswell like thunderbolt assemble ross contact valentina team expendable agent break super prison gather team minus sentry ofc cause idea ross know locate valentina want hand project succeed odd ros sentry asset chase ofc bucky valentina backstab team sentry retrieve valentina turn sentry time thunderbolt true leader ross aka red hulk epic fight rest team end dead fight yelena sentry bucky void talk sentry later doomsday yelena bucky join new cap america reform instead new lame bs thunderbolt actually come leader ross thunderboltsomething like hop ve interesting watchbut miss opportunity usual day disney shot exactly dilemma eternal wrong director wrong script writer boring lame instead fun cool science fiction action gunn manage turn guardian galaxy intowell manage ff4 right atleast mess end thunderbolt sense director ff4 clue ship end thunderbolt sense eithergood job chargeget cinematic soon loose fan</t>
+          <t>ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_ross_aka ENTLBL_ORG ENTTXT_new_cap_america_reform</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>cinematic failure potential good interesting nothis mediocre failure not able interesting cinematic endgame bad bad say alot potential like idea introduce thunderbolt cinematic cheap rehash instead new creative cool not usual day disney hire director not action science fiction fun cool anymore good thing sentry especially idea bad thing script direct red hulk imagine actually like james gunn ve perfect director like ve fun exciting cool dialogue cool action sadly good director clueless action not interesting intense action scenethis boring problem cinematic couple year not hire director good action director writer actually write new interesting rehashed formula ve love hop introduce red hulk perfect opportunity use aswell like thunderbolt assemble ross having contact valentina team expendable agent break super prison gather team minus sentry ofc cause idea ross know locate valentina want hand project succeed odd ros take sentry asset get chase ofc bucky valentina backstab team sentry go to retrieve valentina turn sentry time thunderbolt true leader ross aka red hulk epic fight rest team end dead fight yelena sentry bucky void talk sentry take show later doomsday yelena bucky join new cap america reform instead new lame bs thunderbolt actually come leader ross thunderboltsomething like hop ve well interesting watchbut miss opportunity usual day disney make shot exactly dilemma eternal wrong director wrong script writer boring lame instead fun cool science fiction action gunn manage turn guardian galaxy intowell manage ff4 right atleast mess end thunderbolt not make sense director ff4 clue ship show end thunderbolt movie make sense eithergood job one chargeget cinematic soon loose fan cinematic failure potential good interesting nothis mediocre failure able interesting cinematic endgame bad bad alot potential like idea introduce thunderbolt cinematic cheap rehash instead new creative cool usual day disney hire director action science fiction fun cool anymore good thing sentry especially idea bad thing script direct red hulk imagine actually like james gunn ve perfect director like ve fun exciting cool dialogue cool action sadly good director clueless action interesting intense action scenethis boring problem cinematic couple year hire director good action director writer actually write new interesting rehashed formula ve love hop introduce red hulk perfect opportunity use aswell like thunderbolt assemble ross having contact valentina team expendable agent break super prison gather team minus sentry ofc cause idea ross know locate valentina want hand project succeed odd ros sentry asset chase ofc bucky valentina backstab team sentry retrieve valentina turn sentry time thunderbolt true leader ross aka red hulk epic fight rest team end dead fight yelena sentry bucky void talk sentry later doomsday yelena bucky join new cap america reform instead new lame bs thunderbolt actually come leader ross thunderboltsomething like hop ve interesting watchbut miss opportunity usual day disney shot exactly dilemma eternal wrong director wrong script writer boring lame instead fun cool science fiction action gunn manage turn guardian galaxy intowell manage ff4 right atleast mess end thunderbolt sense director ff4 clue ship end thunderbolt sense eithergood job chargeget cinematic soon loose fan cinematic failure potential good interesting nothis mediocre failure able interesting cinematic endgame bad bad alot potential like idea introduce thunderbolt cinematic cheap rehash instead new creative cool usual day disney hire director action science fiction fun cool anymore good thing sentry especially idea bad thing script direct red hulk imagine actually like james gunn ve perfect director like ve fun exciting cool dialogue cool action sadly good director clueless action interesting intense action scenethis boring problem cinematic couple year hire director good action director writer actually write new interesting rehashed formula ve love hop introduce red hulk perfect opportunity use aswell like thunderbolt assemble ross contact valentina team expendable agent break super prison gather team minus sentry ofc cause idea ross know locate valentina want hand project succeed odd ros sentry asset chase ofc bucky valentina backstab team sentry retrieve valentina turn sentry time thunderbolt true leader ross aka red hulk epic fight rest team end dead fight yelena sentry bucky void talk sentry later doomsday yelena bucky join new cap america reform instead new lame bs thunderbolt actually come leader ross thunderboltsomething like hop ve interesting watchbut miss opportunity usual day disney shot exactly dilemma eternal wrong director wrong script writer boring lame instead fun cool science fiction action gunn manage turn guardian galaxy intowell manage ff4 right atleast mess end thunderbolt sense director ff4 clue ship end thunderbolt sense eithergood job chargeget cinematic soon loose fan</t>
+          <t>cinematic failure potential good interesting nothis mediocre failure not able interesting cinematic endgame bad bad say alot potential like idea introduce thunderbolt cinematic cheap rehash instead new creative cool not usual day disney hire director not action science fiction fun cool anymore good thing sentry especially idea bad thing script direct red hulk imagine actually like james gunn ve perfect director like ve fun exciting cool dialogue cool action sadly good director clueless action not interesting intense action scenethis boring problem cinematic couple year not hire director good action director writer actually write new interesting rehashed formula ve love hop introduce red hulk perfect opportunity use aswell like thunderbolt assemble ross having contact valentina team expendable agent break super prison gather team minus sentry ofc cause idea ross know locate valentina want hand project succeed odd ros take sentry asset get chase ofc bucky valentina backstab team sentry go to retrieve valentina turn sentry time thunderbolt true leader ross aka red hulk epic fight rest team end dead fight yelena sentry bucky void talk sentry take show later doomsday yelena bucky join new cap america reform instead new lame bs thunderbolt actually come leader ross thunderboltsomething like hop ve well interesting watchbut miss opportunity usual day disney make shot exactly dilemma eternal wrong director wrong script writer boring lame instead fun cool science fiction action gunn manage turn guardian galaxy intowell manage ff4 right atleast mess end thunderbolt not make sense director ff4 clue ship show end thunderbolt movie make sense eithergood job one chargeget cinematic soon loose fan cinematic failure potential good interesting nothis mediocre failure able interesting cinematic endgame bad bad alot potential like idea introduce thunderbolt cinematic cheap rehash instead new creative cool usual day disney hire director action science fiction fun cool anymore good thing sentry especially idea bad thing script direct red hulk imagine actually like james gunn ve perfect director like ve fun exciting cool dialogue cool action sadly good director clueless action interesting intense action scenethis boring problem cinematic couple year hire director good action director writer actually write new interesting rehashed formula ve love hop introduce red hulk perfect opportunity use aswell like thunderbolt assemble ross having contact valentina team expendable agent break super prison gather team minus sentry ofc cause idea ross know locate valentina want hand project succeed odd ros sentry asset chase ofc bucky valentina backstab team sentry retrieve valentina turn sentry time thunderbolt true leader ross aka red hulk epic fight rest team end dead fight yelena sentry bucky void talk sentry later doomsday yelena bucky join new cap america reform instead new lame bs thunderbolt actually come leader ross thunderboltsomething like hop ve interesting watchbut miss opportunity usual day disney shot exactly dilemma eternal wrong director wrong script writer boring lame instead fun cool science fiction action gunn manage turn guardian galaxy intowell manage ff4 right atleast mess end thunderbolt sense director ff4 clue ship end thunderbolt sense eithergood job chargeget cinematic soon loose fan [SEP] ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_ross_aka ENTLBL_ORG ENTTXT_new_cap_america_reform</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -11925,20 +9297,10 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -11960,14 +9322,10 @@
           <t>cinematic marathon 2019 9 thoroughly dissatisfied disappoint entirety terrible captain dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop cinematic marathon 2019 9 thoroughly dissatisfied disappoint entirety terrible captain dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>cinematic marathon 2019 9 thoroughly dissatisfied disappoint entirety terrible captain dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop cinematic marathon 2019 9 thoroughly dissatisfied disappoint entirety terrible captain dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop</t>
+          <t>cinematic marathon 2019 9 thoroughly dissatisfied disappoint entirety terrible captain dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop cinematic marathon 2019 9 thoroughly dissatisfied disappoint entirety terrible captain dreadful script crummy direction thor dark world fail deliver decent entry cinematic editing department horrendous job mishmashe important time feel like endless boring hodgepodge loop [SEP]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -11982,20 +9340,10 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12017,14 +9365,10 @@
           <t>dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed</t>
-        </is>
-      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed</t>
+          <t>dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed dull purposeless bore poor development predictable real plot pretentious effect lousy love jane thor expect production disappointed [SEP]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -12039,20 +9383,10 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12076,12 +9410,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>embarrassment ant regret know fantastic predecessor earth think use green screen kind mix build set 98 green screen overkill cgi horrendously bad return daren intergalactic emotionally fragile humpty dumpty weaponize suit stretch face like disturbing poorly computer generate imagery look like 1995 amazing cameo bill murray find nail janet dyne quantum realm hank apparently cheat wife basically destroy sweet image marriage high normal clearly suffer lack vision production ruin potential future ant release</t>
+          <t>ENTLBL_PERSON ENTTXT_bill_murray</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>embarrassment ant film regret see know fantastic predecessor earth think movie use green screen kind mix build set 98 green screen overkill cgi horrendously bad return daren intergalactic emotionally fragile humpty dumpty weaponize suit stretch face like disturbing poorly computer generate imagery look like 1995 amazing cameo bill murray find nail janet dyne quantum realm hank apparently cheat wife basically destroy sweet image marriage high normal clearly suffer lack vision production ruin potential future ant film release will not see embarrassment ant regret know fantastic predecessor earth think use green screen kind mix build set 98 green screen overkill cgi horrendously bad return daren intergalactic emotionally fragile humpty dumpty weaponize suit stretch face like disturbing poorly computer generate imagery look like 1995 amazing cameo bill murray find nail janet dyne quantum realm hank apparently cheat wife basically destroy sweet image marriage high normal clearly suffer lack vision production ruin potential future ant release embarrassment ant regret know fantastic predecessor earth think use green screen kind mix build set 98 green screen overkill cgi horrendously bad return daren intergalactic emotionally fragile humpty dumpty weaponize suit stretch face like disturbing poorly computer generate imagery look like 1995 amazing cameo bill murray find nail janet dyne quantum realm hank apparently cheat wife basically destroy sweet image marriage high normal clearly suffer lack vision production ruin potential future ant release</t>
+          <t>embarrassment ant film regret see know fantastic predecessor earth think movie use green screen kind mix build set 98 green screen overkill cgi horrendously bad return daren intergalactic emotionally fragile humpty dumpty weaponize suit stretch face like disturbing poorly computer generate imagery look like 1995 amazing cameo bill murray find nail janet dyne quantum realm hank apparently cheat wife basically destroy sweet image marriage high normal clearly suffer lack vision production ruin potential future ant film release will not see embarrassment ant regret know fantastic predecessor earth think use green screen kind mix build set 98 green screen overkill cgi horrendously bad return daren intergalactic emotionally fragile humpty dumpty weaponize suit stretch face like disturbing poorly computer generate imagery look like 1995 amazing cameo bill murray find nail janet dyne quantum realm hank apparently cheat wife basically destroy sweet image marriage high normal clearly suffer lack vision production ruin potential future ant release [SEP] ENTLBL_PERSON ENTTXT_bill_murray</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12096,20 +9430,10 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12131,14 +9455,10 @@
           <t>pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment film like dark knight series set standard superhero film deep thoughtful person comment guardian galaxy challenge standard generally not like dogma dogma fact deep one trigger deep emotion provoke thought inspire audience help audience learn help audience learn well audience like think involuntarily recall remember high score deep film course different people different opinion deepness not comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn well unfortunately guardian galaxy not feel way time great film comment guardian galaxy great light hearted comedy not think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon say later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous wizard oz 1939   feel creepy prison prison feel like noisy second hand market not find joke funny not know line know intend people laugh not feel entertain improper moment guardian galaxy place time great list joke play 250 list great film mediocrity manifest month release drop 20 place 250 list 34th 54th time go likely drop enthusiasm fade initial surge great film like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment like dark knight series set standard superhero deep thoughtful person far comment guardian galaxy challenge standard generally like dogma dogma fact deep trigger deep emotion provoke thought inspire audience help audience learn help audience learn audience like think involuntarily recall remember high score deep course different people different opinion deepness comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn unfortunately guardian galaxy feel way time great comment guardian galaxy great light hearted comedy think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous wizard oz 1939   feel creepy prison prison feel like noisy second hand market find joke funny know line know intend people laugh feel entertain improper moment guardian galaxy place time great list joke play 250 list great mediocrity manifest month release drop 20 place 250 list 34th 54th time likely drop far enthusiasm fade initial surge great like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment like dark knight series set standard superhero deep thoughtful person far comment guardian galaxy challenge standard generally like dogma dogma fact deep trigger deep emotion provoke thought inspire audience help audience learn help audience learn audience like think involuntarily recall remember high score deep course different people different opinion deepness comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn unfortunately guardian galaxy feel way time great comment guardian galaxy great light hearted comedy think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous prison feel like noisy second hand market find joke funny know line know intend people laugh feel entertain improper moment guardian galaxy place time great list joke play 250 list great mediocrity manifest month release drop 20 place 250 list 34th 54th time likely drop far enthusiasm fade initial surge great like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list</t>
-        </is>
-      </c>
+      <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment film like dark knight series set standard superhero film deep thoughtful person comment guardian galaxy challenge standard generally not like dogma dogma fact deep one trigger deep emotion provoke thought inspire audience help audience learn help audience learn well audience like think involuntarily recall remember high score deep film course different people different opinion deepness not comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn well unfortunately guardian galaxy not feel way time great film comment guardian galaxy great light hearted comedy not think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon say later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous wizard oz 1939   feel creepy prison prison feel like noisy second hand market not find joke funny not know line know intend people laugh not feel entertain improper moment guardian galaxy place time great list joke play 250 list great film mediocrity manifest month release drop 20 place 250 list 34th 54th time go likely drop enthusiasm fade initial surge great film like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment like dark knight series set standard superhero deep thoughtful person far comment guardian galaxy challenge standard generally like dogma dogma fact deep trigger deep emotion provoke thought inspire audience help audience learn help audience learn audience like think involuntarily recall remember high score deep course different people different opinion deepness comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn unfortunately guardian galaxy feel way time great comment guardian galaxy great light hearted comedy think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous wizard oz 1939   feel creepy prison prison feel like noisy second hand market find joke funny know line know intend people laugh feel entertain improper moment guardian galaxy place time great list joke play 250 list great mediocrity manifest month release drop 20 place 250 list 34th 54th time likely drop far enthusiasm fade initial surge great like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment like dark knight series set standard superhero deep thoughtful person far comment guardian galaxy challenge standard generally like dogma dogma fact deep trigger deep emotion provoke thought inspire audience help audience learn help audience learn audience like think involuntarily recall remember high score deep course different people different opinion deepness comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn unfortunately guardian galaxy feel way time great comment guardian galaxy great light hearted comedy think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous prison feel like noisy second hand market find joke funny know line know intend people laugh feel entertain improper moment guardian galaxy place time great list joke play 250 list great mediocrity manifest month release drop 20 place 250 list 34th 54th time likely drop far enthusiasm fade initial surge great like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list</t>
+          <t>pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment film like dark knight series set standard superhero film deep thoughtful person comment guardian galaxy challenge standard generally not like dogma dogma fact deep one trigger deep emotion provoke thought inspire audience help audience learn help audience learn well audience like think involuntarily recall remember high score deep film course different people different opinion deepness not comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn well unfortunately guardian galaxy not feel way time great film comment guardian galaxy great light hearted comedy not think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon say later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous wizard oz 1939   feel creepy prison prison feel like noisy second hand market not find joke funny not know line know intend people laugh not feel entertain improper moment guardian galaxy place time great list joke play 250 list great film mediocrity manifest month release drop 20 place 250 list 34th 54th time go likely drop enthusiasm fade initial surge great film like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list pretentious mediocre guardian galaxy mediocre pretence future sneak embrace past try comedy fail trigger deep emotion inside humour context properly develop purpose existence figure confusing ill comment detail triggering deep emotion humour follow 2 paragraph comment like dark knight series set standard superhero deep thoughtful person far comment guardian galaxy challenge standard generally like dogma dogma fact deep trigger deep emotion provoke thought inspire audience help audience learn help audience learn audience like think involuntarily recall remember high score deep course different people different opinion deepness comment deepness guardian galaxy comment trigger deep emotion provoke thought inspire help learn learn unfortunately guardian galaxy feel way time great comment guardian galaxy great light hearted comedy think agree great humour exist context right context plain hilarious context brilliant joke guardian galaxy humour run context example raccoon later ask prisoner prosthetic leg joke convey clever play heartless joke partner time try portray figure raccoon unfazed great danger situation look dangerous wizard oz 1939   feel creepy prison prison feel like noisy second hand market find joke funny know line know intend people laugh feel entertain improper moment guardian galaxy place time great list joke play 250 list great mediocrity manifest month release drop 20 place 250 list 34th 54th time likely drop far enthusiasm fade initial surge great like father 1993   beautiful mind 2001 etc 250 list gradually rise emerge time great list contrary guardian galaxy gradually drop 250 list [SEP]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -12153,20 +9473,10 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12190,12 +9500,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>amazing black panther amazing entry cinematic offer typical superhero significance entertainment resonate deeply audience seek representation cultural empowerment feature entirely black cast celebrate african culture audience rare opportunity reflect global stage disney major risk approach pay deliver thrill meaningful excel visually stylistically wakanda render stunning futuristic african nation seamlessly blend tradition cut edge technology costume design production value computer generate imagery contribute world feel immersive alive director ryan coogler balance spectacle substance create culturally rich action pack performance standout michael b jordan killmonger deliver compelling villain performance mcu bring depth personal motivation elevate typical antagonist trope support cast include lupita nyongo danai gurira letitia wright add emotional weight complexity round feel ground despite fantastical element black panther succeed thematically explore identity responsibility legacy touch social political issue feel heavy hand impact screen inspire conversation representation inclusion empowerment hollywood ultimately black panther landmark thrilling visually stunning culturally significant blend superhero action truly matter cinematic moment remember year come</t>
+          <t>ENTLBL_PERSON ENTTXT_chadwick_boseman ENTLBL_PERSON ENTTXT_michael_b_jordan_killmonger ENTLBL_PERSON ENTTXT_gurira_letitia_wright ENTLBL_PERSON ENTTXT_gravita_king</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>amazing black panther amazing entry cinematic offer typical superhero significance go entertainment resonate deeply audience seek representation cultural empowerment feature entirely black cast celebrate african culture give audience rare opportunity reflect global stage disney take major risk approach pay deliver thrill meaningful excel visually stylistically wakanda render stunning futuristic african nation seamlessly blend tradition cut edge technology costume design production value computer generate imagery contribute world feel immersive alive director ryan coogler balance spectacle substance create culturally rich action pack performance standout chadwick boseman embody tchalla quiet authority gravita make king heroic relatable michael b jordan killmonger deliver compelling villain performance mcu bring depth personal motivation elevate typical antagonist trope support cast include lupita nyongo danai gurira letitia wright add emotional weight complexity round feels ground despite fantastical element black panther succeed thematically explore identity responsibility legacy touch social political issue feel heavy hand impact go screen inspire conversation representation inclusion empowerment hollywood ultimately black panther landmark thrilling visually stunning culturally significant blend superhero action truly matter cinematic moment remember year come amazing black panther amazing entry cinematic offer typical superhero significance entertainment resonate deeply audience seek representation cultural empowerment feature entirely black cast celebrate african culture audience rare opportunity reflect global stage disney major risk approach pay deliver thrill meaningful excel visually stylistically wakanda render stunning futuristic african nation seamlessly blend tradition cut edge technology costume design production value computer generate imagery contribute world feel immersive alive director ryan coogler balance spectacle substance create culturally rich action pack performance standout chadwick boseman embody tchalla quiet authority gravita king heroic relatable michael b jordan killmonger deliver compelling villain performance mcu bring depth personal motivation elevate typical antagonist trope support cast include lupita nyongo danai gurira letitia wright add emotional weight complexity round feels ground despite fantastical element black panther succeed thematically explore identity responsibility legacy touch social political issue feel heavy hand impact screen inspire conversation representation inclusion empowerment hollywood ultimately black panther landmark thrilling visually stunning culturally significant blend superhero action truly matter cinematic moment remember year come amazing black panther amazing entry cinematic offer typical superhero significance entertainment resonate deeply audience seek representation cultural empowerment feature entirely black cast celebrate african culture audience rare opportunity reflect global stage disney major risk approach pay deliver thrill meaningful excel visually stylistically wakanda render stunning futuristic african nation seamlessly blend tradition cut edge technology costume design production value computer generate imagery contribute world feel immersive alive director ryan coogler balance spectacle substance create culturally rich action pack performance standout michael b jordan killmonger deliver compelling villain performance mcu bring depth personal motivation elevate typical antagonist trope support cast include lupita nyongo danai gurira letitia wright add emotional weight complexity round feel ground despite fantastical element black panther succeed thematically explore identity responsibility legacy touch social political issue feel heavy hand impact screen inspire conversation representation inclusion empowerment hollywood ultimately black panther landmark thrilling visually stunning culturally significant blend superhero action truly matter cinematic moment remember year come</t>
+          <t>amazing black panther amazing entry cinematic offer typical superhero significance go entertainment resonate deeply audience seek representation cultural empowerment feature entirely black cast celebrate african culture give audience rare opportunity reflect global stage disney take major risk approach pay deliver thrill meaningful excel visually stylistically wakanda render stunning futuristic african nation seamlessly blend tradition cut edge technology costume design production value computer generate imagery contribute world feel immersive alive director ryan coogler balance spectacle substance create culturally rich action pack performance standout chadwick boseman embody tchalla quiet authority gravita make king heroic relatable michael b jordan killmonger deliver compelling villain performance mcu bring depth personal motivation elevate typical antagonist trope support cast include lupita nyongo danai gurira letitia wright add emotional weight complexity round feels ground despite fantastical element black panther succeed thematically explore identity responsibility legacy touch social political issue feel heavy hand impact go screen inspire conversation representation inclusion empowerment hollywood ultimately black panther landmark thrilling visually stunning culturally significant blend superhero action truly matter cinematic moment remember year come amazing black panther amazing entry cinematic offer typical superhero significance entertainment resonate deeply audience seek representation cultural empowerment feature entirely black cast celebrate african culture audience rare opportunity reflect global stage disney major risk approach pay deliver thrill meaningful excel visually stylistically wakanda render stunning futuristic african nation seamlessly blend tradition cut edge technology costume design production value computer generate imagery contribute world feel immersive alive director ryan coogler balance spectacle substance create culturally rich action pack performance standout chadwick boseman embody tchalla quiet authority gravita king heroic relatable michael b jordan killmonger deliver compelling villain performance mcu bring depth personal motivation elevate typical antagonist trope support cast include lupita nyongo danai gurira letitia wright add emotional weight complexity round feels ground despite fantastical element black panther succeed thematically explore identity responsibility legacy touch social political issue feel heavy hand impact screen inspire conversation representation inclusion empowerment hollywood ultimately black panther landmark thrilling visually stunning culturally significant blend superhero action truly matter cinematic moment remember year come [SEP] ENTLBL_PERSON ENTTXT_chadwick_boseman ENTLBL_PERSON ENTTXT_michael_b_jordan_killmonger ENTLBL_PERSON ENTTXT_gurira_letitia_wright ENTLBL_PERSON ENTTXT_gravita_king</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -12210,20 +9520,10 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -12247,12 +9547,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>worst cinematic illogical travel n forth loki think fail miserably worth theater continuation actually try forcefully mcu eternal sleep thano justify instant try convince external ask interven human ongoing issue total waste time</t>
+          <t>ENTLBL_ORG ENTTXT_loki</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>worst cinematic illogical keep travel n forth loki think well fail miserably worth theater continuation actually try forcefully mcu eternal sleep thano justify instant try convince external ask interven human ongoing issue total waste time worst cinematic illogical travel n forth loki think fail miserably worth theater continuation actually try forcefully mcu eternal sleep thano justify instant try convince external ask interven human ongoing issue total waste time worst cinematic illogical travel n forth loki think fail miserably worth theater continuation actually try forcefully mcu eternal sleep thano justify instant try convince external ask interven human ongoing issue total waste time</t>
+          <t>worst cinematic illogical keep travel n forth loki think well fail miserably worth theater continuation actually try forcefully mcu eternal sleep thano justify instant try convince external ask interven human ongoing issue total waste time worst cinematic illogical travel n forth loki think fail miserably worth theater continuation actually try forcefully mcu eternal sleep thano justify instant try convince external ask interven human ongoing issue total waste time [SEP] ENTLBL_ORG ENTTXT_loki</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -12267,20 +9567,10 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12302,14 +9592,10 @@
           <t>see way long boring action lack depth like train spider 2 well expect action time mess action climax not know go new creative not enjoy 30 minute way long boring action lack depth like train spider 2 expect action time mess action climax know new creative enjoy 30 minute</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>way long boring action lack depth like train spider 2 expect action time mess action climax know new creative enjoy 30 minute</t>
-        </is>
-      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>see way long boring action lack depth like train spider 2 well expect action time mess action climax not know go new creative not enjoy 30 minute way long boring action lack depth like train spider 2 expect action time mess action climax know new creative enjoy 30 minute way long boring action lack depth like train spider 2 expect action time mess action climax know new creative enjoy 30 minute</t>
+          <t>see way long boring action lack depth like train spider 2 well expect action time mess action climax not know go new creative not enjoy 30 minute way long boring action lack depth like train spider 2 expect action time mess action climax know new creative enjoy 30 minute [SEP]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -12324,20 +9610,10 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12361,12 +9637,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>good iron 2 mildly entertaining problem glare second talk talk talk content dialog tony stark arguing forth use good bad guy mickey rorke great bad guy use near fourth use obnoxious bad guy hammer nerve fifth use great actor like samuel l jackson suppose bit mess</t>
+          <t>ENTLBL_PERSON ENTTXT_samuel_l_jackson ENTLBL_PERSON ENTTXT_tony</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>good iron 2 mildly entertaining problem glare hero actually obnoxious learn iron 1 not transfer second talk talk talk content dialog not tony stark arguing forth use good bad guy mickey rorke make great bad guy not use near fourth use obnoxious bad guy hammer get nerve fifth use great actor like samuel l jackson suppose bit mess well good iron 2 mildly entertaining problem glare hero actually obnoxious learn iron 1 transfer second talk talk talk content dialog tony stark arguing forth use good bad guy mickey rorke great bad guy use near fourth use obnoxious bad guy hammer nerve fifth use great actor like samuel l jackson suppose bit mess good iron 2 mildly entertaining problem glare second talk talk talk content dialog tony stark arguing forth use good bad guy mickey rorke great bad guy use near fourth use obnoxious bad guy hammer nerve fifth use great actor like samuel l jackson suppose bit mess</t>
+          <t>good iron 2 mildly entertaining problem glare hero actually obnoxious learn iron 1 not transfer second talk talk talk content dialog not tony stark arguing forth use good bad guy mickey rorke make great bad guy not use near fourth use obnoxious bad guy hammer get nerve fifth use great actor like samuel l jackson suppose bit mess well good iron 2 mildly entertaining problem glare hero actually obnoxious learn iron 1 transfer second talk talk talk content dialog tony stark arguing forth use good bad guy mickey rorke great bad guy use near fourth use obnoxious bad guy hammer nerve fifth use great actor like samuel l jackson suppose bit mess [SEP] ENTLBL_PERSON ENTTXT_samuel_l_jackson ENTLBL_PERSON ENTTXT_tony</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -12381,20 +9657,10 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12418,12 +9684,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>shang chi legend ring 2021 bring martial art franchise breath fresh air showcase series excellent action sequence intelligent mind hide origin fantasy science fiction feature shang chi legend ring cinematic pro tip point life seek gem   solid uhd hdr blu ray 3d impressive albeit minor cross talk forgivable intricate set piece left right eye navigate post conversion 3d visual absolutely stunning comedic relief point fight sequence sleek powerful arch pace unfold gradually emotionally involve   acting superb talente ensemble   directing pacing spot shang chi legend ring easily origin franchise favorite entry ll leave theater satisfy</t>
+          <t>ENTLBL_PERSON ENTTXT_shang_chi_legend ENTLBL_PERSON ENTTXT_uhd_hdr ENTLBL_ORG ENTTXT_shang_chi_legend_ring</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>shang chi legend ring 2021 bring martial art franchise breath fresh air showcase series excellent action sequence intelligent mind hide origin fantasy science fiction feature shang chi legend ring well cinematic film pro tip point life seek gem   go solid uhd hdr blu ray 3d impressive albeit minor cross talk forgivable intricate set piece left right eye navigate post conversion 3d visual absolutely stunning comedic relief point fight sequence sleek powerful arch pace unfold gradually emotionally involve film   acting superb front film talente ensemble   directing pacing spot shang chi legend ten ring easily origin film franchise give favorite entry ll leave theater satisfy shang chi legend ring 2021 bring martial art franchise breath fresh air showcase series excellent action sequence intelligent mind hide origin fantasy science fiction feature shang chi legend ring cinematic pro tip point life seek gem   solid uhd hdr blu ray 3d impressive albeit minor cross talk forgivable intricate set piece left right eye navigate post conversion 3d visual absolutely stunning comedic relief point fight sequence sleek powerful arch pace unfold gradually emotionally involve   acting superb talente ensemble   directing pacing spot shang chi legend ring easily origin franchise favorite entry ll leave theater satisfy shang chi legend ring 2021 bring martial art franchise breath fresh air showcase series excellent action sequence intelligent mind hide origin fantasy science fiction feature shang chi legend ring cinematic pro tip point life seek gem   solid uhd hdr blu ray 3d impressive albeit minor cross talk forgivable intricate set piece left right eye navigate post conversion 3d visual absolutely stunning comedic relief point fight sequence sleek powerful arch pace unfold gradually emotionally involve   acting superb talente ensemble   directing pacing spot shang chi legend ring easily origin franchise favorite entry ll leave theater satisfy</t>
+          <t>shang chi legend ring 2021 bring martial art franchise breath fresh air showcase series excellent action sequence intelligent mind hide origin fantasy science fiction feature shang chi legend ring well cinematic film pro tip point life seek gem   go solid uhd hdr blu ray 3d impressive albeit minor cross talk forgivable intricate set piece left right eye navigate post conversion 3d visual absolutely stunning comedic relief point fight sequence sleek powerful arch pace unfold gradually emotionally involve film   acting superb front film talente ensemble   directing pacing spot shang chi legend ten ring easily origin film franchise give favorite entry ll leave theater satisfy shang chi legend ring 2021 bring martial art franchise breath fresh air showcase series excellent action sequence intelligent mind hide origin fantasy science fiction feature shang chi legend ring cinematic pro tip point life seek gem   solid uhd hdr blu ray 3d impressive albeit minor cross talk forgivable intricate set piece left right eye navigate post conversion 3d visual absolutely stunning comedic relief point fight sequence sleek powerful arch pace unfold gradually emotionally involve   acting superb talente ensemble   directing pacing spot shang chi legend ring easily origin franchise favorite entry ll leave theater satisfy [SEP] ENTLBL_PERSON ENTTXT_shang_chi_legend ENTLBL_PERSON ENTTXT_uhd_hdr ENTLBL_ORG ENTTXT_shang_chi_legend_ring</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -12438,20 +9704,10 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -12475,12 +9731,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>disappoint sitcom talk dad joke   release 1999 second bad reassemble future definitely catch 1989 explosion left wing ideology instantly t cd4 lymphocyte drop vomit rainbow end spoiler alert capitan america black computer generate imagery great enjoy good trailer hope modern world   m look forward</t>
+          <t>ENTLBL_ORG ENTTXT_capitan_america_black_computer</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>disappoint sitcom talk dad joke   catch friend release 1999 second bad reassemble future definitely catch 1989 explosion left wing ideology instantly t cd4 lymphocyte drop vomit rainbow end spoiler alert capitan america black computer generate imagery great enjoy good trailer hope modern world bad boy black brilliant 2009 m look forward watch disappoint sitcom talk dad joke   catch friend release 1999 second bad reassemble future definitely catch 1989 explosion left wing ideology instantly t cd4 lymphocyte drop vomit rainbow end spoiler alert capitan america black computer generate imagery great enjoy good trailer hope modern world bad boy black brilliant 2009 m look forward disappoint sitcom talk dad joke   release 1999 second bad reassemble future definitely catch 1989 explosion left wing ideology instantly t cd4 lymphocyte drop vomit rainbow end spoiler alert capitan america black computer generate imagery great enjoy good trailer hope modern world   m look forward</t>
+          <t>disappoint sitcom talk dad joke   catch friend release 1999 second bad reassemble future definitely catch 1989 explosion left wing ideology instantly t cd4 lymphocyte drop vomit rainbow end spoiler alert capitan america black computer generate imagery great enjoy good trailer hope modern world bad boy black brilliant 2009 m look forward watch disappoint sitcom talk dad joke   catch friend release 1999 second bad reassemble future definitely catch 1989 explosion left wing ideology instantly t cd4 lymphocyte drop vomit rainbow end spoiler alert capitan america black computer generate imagery great enjoy good trailer hope modern world bad boy black brilliant 2009 m look forward [SEP] ENTLBL_ORG ENTTXT_capitan_america_black_computer</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -12495,20 +9751,10 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12532,12 +9778,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>tear eye recommend colleague tear eye end tear eye mainly bad 3 hour start slowly tempo later black   valkyrie know lead asen future asen nordic dynasty god african seek vain valkyrie god lead god hollywood decisive battle focus seven woman remember woman fighter match reality sell strong offer new battle ridiculous like battle exciting grip let come new heroine evil white</t>
+          <t>ENTLBL_PERSON ENTTXT_god_african</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>tear eye recommend colleague say tear eye end tear eye mainly bad last 3 hour start slowly get tempo later especially woke element damage attract attention thor fat pitiful beer drinking joke figure god thunder symbol masculinity castrate black   valkyrie know lead asen future asen nordic dynasty god african seek vain valkyrie god lead god hollywood decisive battle focus seven woman remember woman well fighter not match reality sell rescue come course captain african superhero black panther strong not offer new battle ridiculous like battle exciting grip let come new heroine evil white man tear eye recommend colleague tear eye end tear eye mainly bad 3 hour start slowly tempo later especially woke element damage attract attention thor fat pitiful beer drinking joke figure god thunder symbol masculinity castrate black   valkyrie know lead asen future asen nordic dynasty god african seek vain valkyrie god lead god hollywood decisive battle focus seven woman remember woman fighter match reality sell rescue come course captain african superhero black panther strong offer new battle ridiculous like battle exciting grip let come new heroine evil white tear eye recommend colleague tear eye end tear eye mainly bad 3 hour start slowly tempo later black   valkyrie know lead asen future asen nordic dynasty god african seek vain valkyrie god lead god hollywood decisive battle focus seven woman remember woman fighter match reality sell strong offer new battle ridiculous like battle exciting grip let come new heroine evil white</t>
+          <t>tear eye recommend colleague say tear eye end tear eye mainly bad last 3 hour start slowly get tempo later especially woke element damage attract attention thor fat pitiful beer drinking joke figure god thunder symbol masculinity castrate black   valkyrie know lead asen future asen nordic dynasty god african seek vain valkyrie god lead god hollywood decisive battle focus seven woman remember woman well fighter not match reality sell rescue come course captain african superhero black panther strong not offer new battle ridiculous like battle exciting grip let come new heroine evil white man tear eye recommend colleague tear eye end tear eye mainly bad 3 hour start slowly tempo later especially woke element damage attract attention thor fat pitiful beer drinking joke figure god thunder symbol masculinity castrate black   valkyrie know lead asen future asen nordic dynasty god african seek vain valkyrie god lead god hollywood decisive battle focus seven woman remember woman fighter match reality sell rescue come course captain african superhero black panther strong offer new battle ridiculous like battle exciting grip let come new heroine evil white [SEP] ENTLBL_PERSON ENTTXT_god_african</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -12552,20 +9798,10 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12589,12 +9825,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>power money play legendary actor like christian bale 65 point social medium manipulation power imdb reverse evolution turn neo liberal callous mass gradually lose power art korg gay member kronan society rule military dictatorship girl kill shadow warrior jump butterfly toy hand oh boy friend million people world gay 5 year old maybe little careful think time time okay money power manipulation superhero read childhood like ache cinematic superficial choice wonder far ll job remember wrongly h e l d set huge base middle desert hammer time point villain look like weird shapeless animation time villain zeus god popular powerful god ancient greek mythology turn orgy guy pleated skirt friend inner world wealthy liberal businessman know step away comfort type descend real world observe real world stan lees design connect reality way term logic fiction 5 year old okay occasionally studied act scripted work pity money technological equipment studio</t>
+          <t>ENTLBL_ORG ENTTXT_axl_rise_cry ENTLBL_PERSON ENTTXT_zeus</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>axl rise cry gun rose enthusiasm script act important bunch kid not listen gun rose life fun power money play legendary actor like christian bale 65 point social medium manipulation power imdb reverse evolution turn neo liberal callous mass gradually lose power art korg gay member kronan society rule military dictatorship girl kill shadow warrior jump butterfly toy hand oh boy friend million people world movie gay 5 year old maybe little careful think time time okay money power manipulation see superhero read childhood like make ache cinematic superficial choice not turn bus rose petal eternal wonder far ll job past watch huge production excitement lift thor hammer thor weapon everyone hand like pebble remember wrongly h e l d set huge base middle desert hammer not time point make villain look like weird shapeless animation time not villain zeus god popular powerful god ancient greek mythology turn orgy guy pleated skirt friend inner world wealthy liberal businessman know step away comfort type descend real world observe real world stan lees design connect reality way term logic fiction movie 5 year old okay occasionally studied act scripted work not pity money technological equipment studio axl rise cry gun rose enthusiasm script act important bunch kid listen gun rose life fun power money play legendary actor like christian bale 65 point social medium manipulation power imdb reverse evolution turn neo liberal callous mass gradually lose power art korg gay member kronan society rule military dictatorship girl kill shadow warrior jump butterfly toy hand oh boy friend million people world gay 5 year old maybe little careful think time time okay money power manipulation superhero read childhood like ache cinematic superficial choice turn bus rose petal eternal wonder far ll job past huge production excitement lift thor hammer thor weapon hand like pebble remember wrongly h e l d set huge base middle desert hammer time point villain look like weird shapeless animation time villain zeus god popular powerful god ancient greek mythology turn orgy guy pleated skirt friend inner world wealthy liberal businessman know step away comfort type descend real world observe real world stan lees design connect reality way term logic fiction 5 year old okay occasionally studied act scripted work pity money technological equipment studio power money play legendary actor like christian bale 65 point social medium manipulation power imdb reverse evolution turn neo liberal callous mass gradually lose power art korg gay member kronan society rule military dictatorship girl kill shadow warrior jump butterfly toy hand oh boy friend million people world gay 5 year old maybe little careful think time time okay money power manipulation superhero read childhood like ache cinematic superficial choice wonder far ll job remember wrongly h e l d set huge base middle desert hammer time point villain look like weird shapeless animation time villain zeus god popular powerful god ancient greek mythology turn orgy guy pleated skirt friend inner world wealthy liberal businessman know step away comfort type descend real world observe real world stan lees design connect reality way term logic fiction 5 year old okay occasionally studied act scripted work pity money technological equipment studio</t>
+          <t>axl rise cry gun rose enthusiasm script act important bunch kid not listen gun rose life fun power money play legendary actor like christian bale 65 point social medium manipulation power imdb reverse evolution turn neo liberal callous mass gradually lose power art korg gay member kronan society rule military dictatorship girl kill shadow warrior jump butterfly toy hand oh boy friend million people world movie gay 5 year old maybe little careful think time time okay money power manipulation see superhero read childhood like make ache cinematic superficial choice not turn bus rose petal eternal wonder far ll job past watch huge production excitement lift thor hammer thor weapon everyone hand like pebble remember wrongly h e l d set huge base middle desert hammer not time point make villain look like weird shapeless animation time not villain zeus god popular powerful god ancient greek mythology turn orgy guy pleated skirt friend inner world wealthy liberal businessman know step away comfort type descend real world observe real world stan lees design connect reality way term logic fiction movie 5 year old okay occasionally studied act scripted work not pity money technological equipment studio axl rise cry gun rose enthusiasm script act important bunch kid listen gun rose life fun power money play legendary actor like christian bale 65 point social medium manipulation power imdb reverse evolution turn neo liberal callous mass gradually lose power art korg gay member kronan society rule military dictatorship girl kill shadow warrior jump butterfly toy hand oh boy friend million people world gay 5 year old maybe little careful think time time okay money power manipulation superhero read childhood like ache cinematic superficial choice turn bus rose petal eternal wonder far ll job past huge production excitement lift thor hammer thor weapon hand like pebble remember wrongly h e l d set huge base middle desert hammer time point villain look like weird shapeless animation time villain zeus god popular powerful god ancient greek mythology turn orgy guy pleated skirt friend inner world wealthy liberal businessman know step away comfort type descend real world observe real world stan lees design connect reality way term logic fiction 5 year old okay occasionally studied act scripted work pity money technological equipment studio [SEP] ENTLBL_ORG ENTTXT_axl_rise_cry ENTLBL_PERSON ENTTXT_zeus</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -12609,20 +9845,10 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12644,14 +9870,10 @@
           <t>bad plot horrible writer wanda enemy deserve well writing bad plus way portray professor xavier like live action cartoon stupid disappoint bad plot horrible writer wanda enemy deserve writing bad plus way portray professor xavier like live action cartoon stupid disappoint</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>bad plot horrible writer wanda enemy deserve writing bad plus way portray professor xavier like live action cartoon stupid disappoint</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>bad plot horrible writer wanda enemy deserve well writing bad plus way portray professor xavier like live action cartoon stupid disappoint bad plot horrible writer wanda enemy deserve writing bad plus way portray professor xavier like live action cartoon stupid disappoint bad plot horrible writer wanda enemy deserve writing bad plus way portray professor xavier like live action cartoon stupid disappoint</t>
+          <t>bad plot horrible writer wanda enemy deserve well writing bad plus way portray professor xavier like live action cartoon stupid disappoint bad plot horrible writer wanda enemy deserve writing bad plus way portray professor xavier like live action cartoon stupid disappoint [SEP]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -12666,20 +9888,10 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12701,14 +9913,10 @@
           <t>terrible way finish series film disappoint series film end spaceship suck music not great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference not land villain good act need drive home message feature animal cruelty subject design not great not kid terrible way finish series disappoint series end spaceship use suck music great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference land villain good act need drive home message feature animal cruelty subject design great kid</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>terrible way finish series disappoint series end spaceship use suck music great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference land villain good act need drive home message feature animal cruelty subject design great kid</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>terrible way finish series film disappoint series film end spaceship suck music not great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference not land villain good act need drive home message feature animal cruelty subject design not great not kid terrible way finish series disappoint series end spaceship use suck music great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference land villain good act need drive home message feature animal cruelty subject design great kid terrible way finish series disappoint series end spaceship use suck music great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference land villain good act need drive home message feature animal cruelty subject design great kid</t>
+          <t>terrible way finish series film disappoint series film end spaceship suck music not great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference not land villain good act need drive home message feature animal cruelty subject design not great not kid terrible way finish series disappoint series end spaceship use suck music great humor force nathan fillion shoe horn guard organic planet look terrible cruelty imply happen rocketno need far win formula 2 pop culture reference land villain good act need drive home message feature animal cruelty subject design great kid [SEP]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -12723,20 +9931,10 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12760,12 +9958,12 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>want love try hard enjoy dr strange great good visual effect sadly feel bored moment new goodit feel little spider 3 like kind patch ton idea flow effect feel completely polished truly excited announce wish original director</t>
+          <t>ENTLBL_PERSON ENTTXT_patch_ton</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>want love try hard enjoy dr strange great good visual effect sadly feel bored moment new not goodit feel little spider 3 like kind patch ton idea flow effect not feel completely polished truly excited announce wish original director want love try hard enjoy dr strange great good visual effect sadly feel bored moment new goodit feel little spider 3 like kind patch ton idea flow effect feel completely polished truly excited announce wish original director want love try hard enjoy dr strange great good visual effect sadly feel bored moment new goodit feel little spider 3 like kind patch ton idea flow effect feel completely polished truly excited announce wish original director</t>
+          <t>want love try hard enjoy dr strange great good visual effect sadly feel bored moment new not goodit feel little spider 3 like kind patch ton idea flow effect not feel completely polished truly excited announce wish original director want love try hard enjoy dr strange great good visual effect sadly feel bored moment new goodit feel little spider 3 like kind patch ton idea flow effect feel completely polished truly excited announce wish original director [SEP] ENTLBL_PERSON ENTTXT_patch_ton</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -12775,27 +9973,17 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
     </row>
@@ -12815,14 +10003,10 @@
           <t>honest review get home see mile well second great feel lot plot hole think worth state super hero movie plot hole like focus thing suit come 10 time focus power suit fade point feel need share not antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care not sense not explain entertaining think solid 6 generous honest review home mile second great feel lot plot hole think worth state super hero plot hole like focus thing suit come 10 time focus power suit fade point feel need share antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care sense explain entertaining think solid 6 generous</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>honest review home mile second great feel lot plot hole think worth state super hero plot hole like focus thing suit come 10 time focus power suit fade point feel need share antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care sense explain entertaining think solid 6 generous</t>
-        </is>
-      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>honest review get home see mile well second great feel lot plot hole think worth state super hero movie plot hole like focus thing suit come 10 time focus power suit fade point feel need share not antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care not sense not explain entertaining think solid 6 generous honest review home mile second great feel lot plot hole think worth state super hero plot hole like focus thing suit come 10 time focus power suit fade point feel need share antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care sense explain entertaining think solid 6 generous honest review home mile second great feel lot plot hole think worth state super hero plot hole like focus thing suit come 10 time focus power suit fade point feel need share antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care sense explain entertaining think solid 6 generous</t>
+          <t>honest review get home see mile well second great feel lot plot hole think worth state super hero movie plot hole like focus thing suit come 10 time focus power suit fade point feel need share not antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care not sense not explain entertaining think solid 6 generous honest review home mile second great feel lot plot hole think worth state super hero plot hole like focus thing suit come 10 time focus power suit fade point feel need share antidote sudden breath fire crazy think lot explaining need antidote sum plenty plot hole bad guy care sense explain entertaining think solid 6 generous [SEP]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -12837,20 +10021,10 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12874,12 +10048,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>huge dynamic easily forgettable   deserve credit dynamic execution bring cast structured firmly blockbuster exciting drive filmmaker joss whedon clash interaction hero development exuberant witty simply hilarious progress action tone explosive warfare new york city teamwork building chemistry anymore dynamic humorous whedon continuous comic relief combination contrast superhero popcorn fun simple vital flaw remain instead score fail connect lack pure epicness beauty ultimately lose connection important aspect sound score work simple expose lack depth telling ultimately feel small weak small important aspect frustratingly execute instead end high note end zero connection mark ruffalos brilliant interpretation hulk lack connection score lack depth storytelling ultimately wear appear screen lack connection lead forgettable connect stick possibly remember forget easily concept forget joss whedon incredible portrayal superhero forget anticipation potential brilliance huge motion picture 2012 dark knight rise hobbit think come early year huge movieoh yeah possibly forget good awesome intense blockbuster little thing leave slightly par simplify fun deserve high praise execution glorious look unfortunately sound nearly good want easily likable viewer like excitement</t>
+          <t>ENTLBL_PERSON ENTTXT_christopher</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>huge dynamic easily forgettable marvel deserve credit dynamic execution bring cast structured firmly blockbuster exciting drive filmmaker joss whedon clash interaction hero development exuberant witty simply hilarious progress action tone explosive warfare new york city teamwork building chemistry not anymore dynamic humorous whedon continuous comic relief combination contrast superhero popcorn fun simple vital flaw remain score massively anticipated feature ve magical intense sound similar lord ring christopher nolans batman film instead score fail connect lack pure epicness beauty ultimately lose connection important aspect sound score work simple expose lack depth telling ultimately feel small weak small important aspect frustratingly execute instead marvel end high note end have zero connection mark ruffalos brilliant interpretation hulk lack connection score lack depth storytelling ultimately wear appear screen lack connection lead forgettable not connect stick possibly remember marvel forget easily concept will not forget joss whedon incredible portrayal superhero forget anticipation potential brilliance huge motion picture 2012 dark knight rise hobbit think come early year huge movieoh yeah possibly forget not good awesome intense blockbuster little thing leave slightly par simplify marvel fun deserve high praise execution glorious look unfortunately sound nearly good want easily likable viewer like excitement huge dynamic easily forgettable deserve credit dynamic execution bring cast structured firmly blockbuster exciting drive filmmaker joss whedon clash interaction hero development exuberant witty simply hilarious progress action tone explosive warfare new york city teamwork building chemistry anymore dynamic humorous whedon continuous comic relief combination contrast superhero popcorn fun simple vital flaw remain score massively anticipated feature ve magical intense sound similar lord ring christopher nolans batman instead score fail connect lack pure epicness beauty ultimately lose connection important aspect sound score work simple expose lack depth telling ultimately feel small weak small important aspect frustratingly execute instead end high note end zero connection mark ruffalos brilliant interpretation hulk lack connection score lack depth storytelling ultimately wear appear screen lack connection lead forgettable connect stick possibly remember forget easily concept forget joss whedon incredible portrayal superhero forget anticipation potential brilliance huge motion picture 2012 dark knight rise hobbit think come early year huge movieoh yeah possibly forget good awesome intense blockbuster little thing leave slightly par simplify fun deserve high praise execution glorious look unfortunately sound nearly good want easily likable viewer like excitement huge dynamic easily forgettable   deserve credit dynamic execution bring cast structured firmly blockbuster exciting drive filmmaker joss whedon clash interaction hero development exuberant witty simply hilarious progress action tone explosive warfare new york city teamwork building chemistry anymore dynamic humorous whedon continuous comic relief combination contrast superhero popcorn fun simple vital flaw remain instead score fail connect lack pure epicness beauty ultimately lose connection important aspect sound score work simple expose lack depth telling ultimately feel small weak small important aspect frustratingly execute instead end high note end zero connection mark ruffalos brilliant interpretation hulk lack connection score lack depth storytelling ultimately wear appear screen lack connection lead forgettable connect stick possibly remember forget easily concept forget joss whedon incredible portrayal superhero forget anticipation potential brilliance huge motion picture 2012 dark knight rise hobbit think come early year huge movieoh yeah possibly forget good awesome intense blockbuster little thing leave slightly par simplify fun deserve high praise execution glorious look unfortunately sound nearly good want easily likable viewer like excitement</t>
+          <t>huge dynamic easily forgettable marvel deserve credit dynamic execution bring cast structured firmly blockbuster exciting drive filmmaker joss whedon clash interaction hero development exuberant witty simply hilarious progress action tone explosive warfare new york city teamwork building chemistry not anymore dynamic humorous whedon continuous comic relief combination contrast superhero popcorn fun simple vital flaw remain score massively anticipated feature ve magical intense sound similar lord ring christopher nolans batman film instead score fail connect lack pure epicness beauty ultimately lose connection important aspect sound score work simple expose lack depth telling ultimately feel small weak small important aspect frustratingly execute instead marvel end high note end have zero connection mark ruffalos brilliant interpretation hulk lack connection score lack depth storytelling ultimately wear appear screen lack connection lead forgettable not connect stick possibly remember marvel forget easily concept will not forget joss whedon incredible portrayal superhero forget anticipation potential brilliance huge motion picture 2012 dark knight rise hobbit think come early year huge movieoh yeah possibly forget not good awesome intense blockbuster little thing leave slightly par simplify marvel fun deserve high praise execution glorious look unfortunately sound nearly good want easily likable viewer like excitement huge dynamic easily forgettable deserve credit dynamic execution bring cast structured firmly blockbuster exciting drive filmmaker joss whedon clash interaction hero development exuberant witty simply hilarious progress action tone explosive warfare new york city teamwork building chemistry anymore dynamic humorous whedon continuous comic relief combination contrast superhero popcorn fun simple vital flaw remain score massively anticipated feature ve magical intense sound similar lord ring christopher nolans batman instead score fail connect lack pure epicness beauty ultimately lose connection important aspect sound score work simple expose lack depth telling ultimately feel small weak small important aspect frustratingly execute instead end high note end zero connection mark ruffalos brilliant interpretation hulk lack connection score lack depth storytelling ultimately wear appear screen lack connection lead forgettable connect stick possibly remember forget easily concept forget joss whedon incredible portrayal superhero forget anticipation potential brilliance huge motion picture 2012 dark knight rise hobbit think come early year huge movieoh yeah possibly forget good awesome intense blockbuster little thing leave slightly par simplify fun deserve high praise execution glorious look unfortunately sound nearly good want easily likable viewer like excitement [SEP] ENTLBL_PERSON ENTTXT_christopher</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -12894,20 +10068,10 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -12931,12 +10095,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>weak series bind time master misstep age ultron disappointing moment archon review like review clean possible age ultron lead force utilize term break rule joss whedon age ultron clusterfk massive proportion inevitable age ultron proof mind entertainment perfect joss whedon bite significantly handle age ultron feel light year ahead previous leave like horror eighth installment age ultron plot convolute entire lack structure intent propel propel forward time tony stark jump start peacekeeping programming use android state art computer programming course superhero fight save world age ultron force unnecessarily complicated multi layered newly manufacture nonchalantly introduce age ultron feel dull lifeless blockbuster cash fate completely unlike caliber material fan accustom typically resign michael bay concoction age ultron tired actor appear difficulty utter dialogue familiar face previous adequate job newcomer like elizabeth olsen aaron taylor johnson laughably inferior act diction cast director fire comedic moment unlike initial feel gimmicky painfully overused understand point franchise filmmaker huge task unfortunately fail produce lover disappointment come vapid whining superfan check website review recent release</t>
+          <t>ENTLBL_PERSON ENTTXT_joss_whedon ENTLBL_PERSON ENTTXT_michael_bay_concoction ENTLBL_PERSON ENTTXT_elizabeth ENTLBL_PERSON ENTTXT_aaron_taylor ENTLBL_PERSON ENTTXT_johnson</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>weak series bind time master misstep age ultron disappointing moment archon review like review clean possible age ultron lead force utilize term break rule joss whedon age ultron clusterfk massive proportion inevitable age ultron proof mind entertainment perfect joss whedon bite significantly handle age ultron feel light year ahead previous film leave like horror eighth installment age ultron plot convolute entire lack structure intent propel propel forward time tony stark jump start peacekeeping programming android state art computer programming jump forward group know realize entity form stark unintentionally create artificial intelligence seek malevolently target earth course superhero fight save world age ultron force unnecessarily complicated multi layered newly manufacture nonchalantly introduce age ultron feel dull lifeless blockbuster cash fate completely unlike caliber material fan accustom typically resign michael bay concoction well age ultron tired actor appear difficulty utter dialogue familiar face previous film adequate job newcomer like elizabeth olsen aaron taylor johnson laughably inferior act diction cast director fire comedic moment unlike initial feel gimmicky painfully overused understand point franchise filmmaker huge task unfortunately fail produce lover disappointment come vapid whining superfan check website review recent release weak series bind time master misstep age ultron disappointing moment archon review like review clean possible age ultron lead force utilize term break rule joss whedon age ultron clusterfk massive proportion inevitable age ultron proof mind entertainment perfect joss whedon bite significantly handle age ultron feel light year ahead previous leave like horror eighth installment age ultron plot convolute entire lack structure intent propel propel forward time tony stark jump start peacekeeping programming use android state art computer programming jump forward group know realize entity form stark unintentionally create artificial intelligence seek malevolently target earth course superhero fight save world age ultron force unnecessarily complicated multi layered newly manufacture nonchalantly introduce age ultron feel dull lifeless blockbuster cash fate completely unlike caliber material fan accustom typically resign michael bay concoction age ultron tired actor appear difficulty utter dialogue familiar face previous adequate job newcomer like elizabeth olsen aaron taylor johnson laughably inferior act diction cast director fire comedic moment unlike initial feel gimmicky painfully overused understand point franchise filmmaker huge task unfortunately fail produce lover disappointment come vapid whining superfan check website review recent release weak series bind time master misstep age ultron disappointing moment archon review like review clean possible age ultron lead force utilize term break rule joss whedon age ultron clusterfk massive proportion inevitable age ultron proof mind entertainment perfect joss whedon bite significantly handle age ultron feel light year ahead previous leave like horror eighth installment age ultron plot convolute entire lack structure intent propel propel forward time tony stark jump start peacekeeping programming use android state art computer programming course superhero fight save world age ultron force unnecessarily complicated multi layered newly manufacture nonchalantly introduce age ultron feel dull lifeless blockbuster cash fate completely unlike caliber material fan accustom typically resign michael bay concoction age ultron tired actor appear difficulty utter dialogue familiar face previous adequate job newcomer like elizabeth olsen aaron taylor johnson laughably inferior act diction cast director fire comedic moment unlike initial feel gimmicky painfully overused understand point franchise filmmaker huge task unfortunately fail produce lover disappointment come vapid whining superfan check website review recent release</t>
+          <t>weak series bind time master misstep age ultron disappointing moment archon review like review clean possible age ultron lead force utilize term break rule joss whedon age ultron clusterfk massive proportion inevitable age ultron proof mind entertainment perfect joss whedon bite significantly handle age ultron feel light year ahead previous film leave like horror eighth installment age ultron plot convolute entire lack structure intent propel propel forward time tony stark jump start peacekeeping programming android state art computer programming jump forward group know realize entity form stark unintentionally create artificial intelligence seek malevolently target earth course superhero fight save world age ultron force unnecessarily complicated multi layered newly manufacture nonchalantly introduce age ultron feel dull lifeless blockbuster cash fate completely unlike caliber material fan accustom typically resign michael bay concoction well age ultron tired actor appear difficulty utter dialogue familiar face previous film adequate job newcomer like elizabeth olsen aaron taylor johnson laughably inferior act diction cast director fire comedic moment unlike initial feel gimmicky painfully overused understand point franchise filmmaker huge task unfortunately fail produce lover disappointment come vapid whining superfan check website review recent release weak series bind time master misstep age ultron disappointing moment archon review like review clean possible age ultron lead force utilize term break rule joss whedon age ultron clusterfk massive proportion inevitable age ultron proof mind entertainment perfect joss whedon bite significantly handle age ultron feel light year ahead previous leave like horror eighth installment age ultron plot convolute entire lack structure intent propel propel forward time tony stark jump start peacekeeping programming use android state art computer programming jump forward group know realize entity form stark unintentionally create artificial intelligence seek malevolently target earth course superhero fight save world age ultron force unnecessarily complicated multi layered newly manufacture nonchalantly introduce age ultron feel dull lifeless blockbuster cash fate completely unlike caliber material fan accustom typically resign michael bay concoction age ultron tired actor appear difficulty utter dialogue familiar face previous adequate job newcomer like elizabeth olsen aaron taylor johnson laughably inferior act diction cast director fire comedic moment unlike initial feel gimmicky painfully overused understand point franchise filmmaker huge task unfortunately fail produce lover disappointment come vapid whining superfan check website review recent release [SEP] ENTLBL_PERSON ENTTXT_joss_whedon ENTLBL_PERSON ENTTXT_michael_bay_concoction ENTLBL_PERSON ENTTXT_elizabeth ENTLBL_PERSON ENTTXT_aaron_taylor ENTLBL_PERSON ENTTXT_johnson</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -12951,20 +10115,10 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -12988,12 +10142,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>mcus far bad eternal cinematic close general consensus review aggregate website painfully misrepresent good special effect exceptional zhaos decision location layer authenticity find lot acting good particularly kumail nanjiani gemma chan richard madden cast great chemistry diverse typical industry doubt factor surprisingly low rating depiction deaf handle screen queer relationship significant issue eternal additionally eternal deal lot comic book lore leave consider people read comic book eternal tend dump lot lore conversation feel forced way exposition handle far favourite eternal eternal worth feel lot like cinematic ve interesting look entertainment time feel like dc produce aware way eternal fall short piece cinema entertain visually stunning time moving set interesting concept future mcu order magnitude let mediocre rating dissuade eternal shot good ve solid entertainment</t>
+          <t>ENTLBL_PERSON ENTTXT_richard_madden</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>mcus well far bad eternal well cinematic close general consensus review aggregate website painfully misrepresent good special effect exceptional zhaos decision location give layer authenticity not find lot film acting good particularly kumail nanjiani gemma chan richard madden cast great chemistry diverse typical industry not doubt factor film surprisingly low rating depiction deaf handle marvel screen queer relationship not significant issue eternal long second long endgame pacing drag place additionally eternal deal lot comic book lore not leave consider people watch will not read comic book eternal tend dump lot lore conversation feel forced way exposition handle far favourite eternal eternal worth feel lot like cinematic ve see interesting look entertainment time feel like dc produce aware way eternal fall short piece cinema entertain visually stunning time moving set interesting concept future mcu frankly fact currently lower rat incredible hulk thor dark world ridiculous order magnitude well film not let mediocre rating dissuade give eternal shot good ve see solid entertainment mcus far bad eternal cinematic close general consensus review aggregate website painfully misrepresent good special effect exceptional zhaos decision location layer authenticity find lot acting good particularly kumail nanjiani gemma chan richard madden cast great chemistry diverse typical industry doubt factor surprisingly low rating depiction deaf handle screen queer relationship significant issue eternal long second long endgame pacing drag place additionally eternal deal lot comic book lore leave consider people read comic book eternal tend dump lot lore conversation feel forced way exposition handle far favourite eternal eternal worth feel lot like cinematic ve interesting look entertainment time feel like dc produce aware way eternal fall short piece cinema entertain visually stunning time moving set interesting concept future mcu frankly fact currently lower rat incredible hulk thor dark world ridiculous order magnitude let mediocre rating dissuade eternal shot good ve solid entertainment mcus far bad eternal cinematic close general consensus review aggregate website painfully misrepresent good special effect exceptional zhaos decision location layer authenticity find lot acting good particularly kumail nanjiani gemma chan richard madden cast great chemistry diverse typical industry doubt factor surprisingly low rating depiction deaf handle screen queer relationship significant issue eternal additionally eternal deal lot comic book lore leave consider people read comic book eternal tend dump lot lore conversation feel forced way exposition handle far favourite eternal eternal worth feel lot like cinematic ve interesting look entertainment time feel like dc produce aware way eternal fall short piece cinema entertain visually stunning time moving set interesting concept future mcu order magnitude let mediocre rating dissuade eternal shot good ve solid entertainment</t>
+          <t>mcus well far bad eternal well cinematic close general consensus review aggregate website painfully misrepresent good special effect exceptional zhaos decision location give layer authenticity not find lot film acting good particularly kumail nanjiani gemma chan richard madden cast great chemistry diverse typical industry not doubt factor film surprisingly low rating depiction deaf handle marvel screen queer relationship not significant issue eternal long second long endgame pacing drag place additionally eternal deal lot comic book lore not leave consider people watch will not read comic book eternal tend dump lot lore conversation feel forced way exposition handle far favourite eternal eternal worth feel lot like cinematic ve see interesting look entertainment time feel like dc produce aware way eternal fall short piece cinema entertain visually stunning time moving set interesting concept future mcu frankly fact currently lower rat incredible hulk thor dark world ridiculous order magnitude well film not let mediocre rating dissuade give eternal shot good ve see solid entertainment mcus far bad eternal cinematic close general consensus review aggregate website painfully misrepresent good special effect exceptional zhaos decision location layer authenticity find lot acting good particularly kumail nanjiani gemma chan richard madden cast great chemistry diverse typical industry doubt factor surprisingly low rating depiction deaf handle screen queer relationship significant issue eternal long second long endgame pacing drag place additionally eternal deal lot comic book lore leave consider people read comic book eternal tend dump lot lore conversation feel forced way exposition handle far favourite eternal eternal worth feel lot like cinematic ve interesting look entertainment time feel like dc produce aware way eternal fall short piece cinema entertain visually stunning time moving set interesting concept future mcu frankly fact currently lower rat incredible hulk thor dark world ridiculous order magnitude let mediocre rating dissuade eternal shot good ve solid entertainment [SEP] ENTLBL_PERSON ENTTXT_richard_madden</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -13008,20 +10162,10 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13043,14 +10187,10 @@
           <t>absolute perfection blow away absolute perfection blow away</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>absolute perfection blow away</t>
-        </is>
-      </c>
+      <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>absolute perfection blow away absolute perfection blow away absolute perfection blow away</t>
+          <t>absolute perfection blow away absolute perfection blow away [SEP]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -13065,20 +10205,10 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13102,12 +10232,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>doctor comic_strip great superhero finally turn screen immortality doctor strange manner similar television doctor house self satisfied smug individual genius sure know night involve automobile crash physical body fail heal entirely leave palsy surgeon question mean tree surgery learn lot metaphysical nature earth world co exist space choose like choose guard portal world world open real messy time plot bit vague guess comic_strip fanatic order lot subtlety claim doctor strange oscar nomination visual effect doubt sequel demand money right</t>
+          <t>ENTLBL_PERSON ENTTXT_john_strange ENTLBL_ORG ENTTXT_tilda_swinton</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>doctor comic_strip great superhero finally get turn screen immortality doctor strange manner similar television doctor name house self satisfied smug individual genius make sure know night involve automobile crash physical body fail heal entirely leave palsy make surgeon question mean tree surgery benedict cumberbatch play doctor john strange like tyrone power razor edge go mystic east find healing ancient gender bend guru play tilda swinton learn lot metaphysical nature earth world co exist space choose like choose guard portal world world open real messy time plot get bit vague guess comic_strip fanatic order lot subtlety claim doctor strange oscar nomination visual effect doubt sequel demand money right doctor comic_strip great superhero finally turn screen immortality doctor strange manner similar television doctor house self satisfied smug individual genius sure know night involve automobile crash physical body fail heal entirely leave palsy surgeon question mean tree surgery benedict cumberbatch play doctor john strange like tyrone power razor edge mystic east find healing ancient gender bend guru play tilda swinton learn lot metaphysical nature earth world co exist space choose like choose guard portal world world open real messy time plot bit vague guess comic_strip fanatic order lot subtlety claim doctor strange oscar nomination visual effect doubt sequel demand money right doctor comic_strip great superhero finally turn screen immortality doctor strange manner similar television doctor house self satisfied smug individual genius sure know night involve automobile crash physical body fail heal entirely leave palsy surgeon question mean tree surgery learn lot metaphysical nature earth world co exist space choose like choose guard portal world world open real messy time plot bit vague guess comic_strip fanatic order lot subtlety claim doctor strange oscar nomination visual effect doubt sequel demand money right</t>
+          <t>doctor comic_strip great superhero finally get turn screen immortality doctor strange manner similar television doctor name house self satisfied smug individual genius make sure know night involve automobile crash physical body fail heal entirely leave palsy make surgeon question mean tree surgery benedict cumberbatch play doctor john strange like tyrone power razor edge go mystic east find healing ancient gender bend guru play tilda swinton learn lot metaphysical nature earth world co exist space choose like choose guard portal world world open real messy time plot get bit vague guess comic_strip fanatic order lot subtlety claim doctor strange oscar nomination visual effect doubt sequel demand money right doctor comic_strip great superhero finally turn screen immortality doctor strange manner similar television doctor house self satisfied smug individual genius sure know night involve automobile crash physical body fail heal entirely leave palsy surgeon question mean tree surgery benedict cumberbatch play doctor john strange like tyrone power razor edge mystic east find healing ancient gender bend guru play tilda swinton learn lot metaphysical nature earth world co exist space choose like choose guard portal world world open real messy time plot bit vague guess comic_strip fanatic order lot subtlety claim doctor strange oscar nomination visual effect doubt sequel demand money right [SEP] ENTLBL_PERSON ENTTXT_john_strange ENTLBL_ORG ENTTXT_tilda_swinton</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -13117,25 +10247,15 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13159,12 +10279,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>contain spoiler slightly boring wrong potential like cap bucky end fury eye creepythe post credit good think hell super powered kid super fast hulk girl telepathic thing mind good amazing spider 2 level opinion solid falcon hilarious johanson good pretty star</t>
+          <t>ENTLBL_ORG ENTTXT_falcon</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>contain spoiler well partbut slightly boringdont wrong part show potential like cap bucky go endand fury show eyecreepythe post credit good think not hell super power kidsone super fast hulk girl telepathic thing mindall good filmnot amazing spider 2 level opinion solidand falcon hilariousjohanson good pretty star inand thing thing plan watch 2 concert contain spoiler partbut slightly boringdont wrong potential like cap bucky endand fury eyecreepythe post credit good think hell super power kidsone super fast hulk girl telepathic thing mindall good filmnot amazing spider 2 level opinion solidand falcon hilariousjohanson good pretty star inand thing thing plan 2 concert contain spoiler slightly boring wrong potential like cap bucky end fury eye creepythe post credit good think hell super powered kid super fast hulk girl telepathic thing mind good amazing spider 2 level opinion solid falcon hilarious johanson good pretty star</t>
+          <t>contain spoiler well partbut slightly boringdont wrong part show potential like cap bucky go endand fury show eyecreepythe post credit good think not hell super power kidsone super fast hulk girl telepathic thing mindall good filmnot amazing spider 2 level opinion solidand falcon hilariousjohanson good pretty star inand thing thing plan watch 2 concert contain spoiler partbut slightly boringdont wrong potential like cap bucky endand fury eyecreepythe post credit good think hell super power kidsone super fast hulk girl telepathic thing mindall good filmnot amazing spider 2 level opinion solidand falcon hilariousjohanson good pretty star inand thing thing plan 2 concert [SEP] ENTLBL_ORG ENTTXT_falcon</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -13179,20 +10299,10 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13216,12 +10326,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>small scale hero big follow ant edgar wright set direct massive fan work leave project worried ant lose different screenplay hear wright work incorporate plus know comic_strip need worry turn hop trump expectation paul rudd great job bring role scott lang thief come jail year pym tech darren cross corey stoll develop formula mirror hank pyms original ant create new breed soldier yellowjacket pym recruit scott lang new ant pull heist save life million pretty michael douglas play pym time screen blast listen fatherdaughter dynamic storyline hope evangeline lilly spoiler great pym train scott new ant fun tell paul rudd michael douglas great time work sort worried shrink grow repeatedly fight nerve adjust especially 3d   actually like lot love scott train ant small speaking ant brilliant way introduce pym ridiculous love scott interact fly cool previously strong villain know countless time villain like abomination whiplash ronan feel weak serve plot device love corey stoll darren crossyellowjacket mean sort introduce villain start reason unlike cinematic villain expand actually yellowjacket suit great feel fresh ant duke whilst grow shrink throw object time size climax feature thomas tank engine favourite fight entire series fact fight feature know probably know case reveal love michael pena standout performance feature comic relief lot time work fix time screen laugh think good job anywayto wrap enjoy ant love scott kick ant love michael douglas yellowjacket awesome think flaw plus post credit love excited ant future future mcu great rating age ultron m fanboy know good entertainment entertain ant deserve high rating</t>
+          <t>ENTLBL_PERSON ENTTXT_edgar_wright ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_scott_lang ENTLBL_ORG ENTTXT_pym_tech_darren ENTLBL_PERSON ENTTXT_corey_stoll ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_scott_train ENTLBL_PERSON ENTTXT_scott ENTLBL_PERSON ENTTXT_corey_stoll_darren ENTLBL_PERSON ENTTXT_michael_pena ENTLBL_PERSON ENTTXT_scott_kick</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>small scale hero film not big follow ant edgar wright set direct massive fan work leave project worried ant lose different screenplay hear wright work incorporate plus know comic_strip need worry turn well hop trump expectation paul rudd great job bring role scott lang thief come jail year pym tech darren cross corey stoll develop formula mirror hank pyms original ant create new breed soldier call yellowjacket pym recruit scott lang new ant pull heist save life million pretty michael douglas play pym time screen blast listen fatherdaughter dynamic storyline hope evangeline lilly give spoiler great pym train scott new ant fun tell paul rudd michael douglas great time work sort worried shrink grow repeatedly fight nerve take adjust especially 3d   actually like lot love see scott train ant small speaking ant brilliant way introduce pym ridiculous love watch see scott interact fly cool not previously see not strong villain know show countless time villain like abomination whiplash ronan feel weak serve plot device love corey stoll darren crossyellowjacket mean sort introduce villain start reason unlike cinematic villain expand actually yellowjacket suit great feel fresh ant duke whilst grow shrink throw object time size climax feature thomas tank engine favourite fight entire series fact fight feature know probably know case not will not reveal love michael pena give standout performance film feature comic relief lot time work not fix time screen laugh think good job anywayto wrap enjoy ant love scott kick ant love michael douglas yellowjacket awesome not think see flaw continue less know good film definitely board way guardian galaxy plus post credit love get excited ant man future future mcu great not give rating age ultron m fanboy know good entertainment entertain ant deserve high rating small scale hero big follow ant edgar wright set direct massive fan work leave project worried ant lose different screenplay hear wright work incorporate plus know comic_strip need worry turn hop trump expectation paul rudd great job bring role scott lang thief come jail year pym tech darren cross corey stoll develop formula mirror hank pyms original ant create new breed soldier yellowjacket pym recruit scott lang new ant pull heist save life million pretty michael douglas play pym time screen blast listen fatherdaughter dynamic storyline hope evangeline lilly spoiler great pym train scott new ant fun tell paul rudd michael douglas great time work sort worried shrink grow repeatedly fight nerve adjust especially 3d   actually like lot love scott train ant small speaking ant brilliant way introduce pym ridiculous love scott interact fly cool previously strong villain know countless time villain like abomination whiplash ronan feel weak serve plot device love corey stoll darren crossyellowjacket mean sort introduce villain start reason unlike cinematic villain expand actually yellowjacket suit great feel fresh ant duke whilst grow shrink throw object time size climax feature thomas tank engine favourite fight entire series fact fight feature know probably know case reveal love michael pena standout performance feature comic relief lot time work fix time screen laugh think good job anywayto wrap enjoy ant love scott kick ant love michael douglas yellowjacket awesome think flaw continue know good definitely board way guardian galaxy plus post credit love excited ant future future mcu great rating age ultron m fanboy know good entertainment entertain ant deserve high rating small scale hero big follow ant edgar wright set direct massive fan work leave project worried ant lose different screenplay hear wright work incorporate plus know comic_strip need worry turn hop trump expectation paul rudd great job bring role scott lang thief come jail year pym tech darren cross corey stoll develop formula mirror hank pyms original ant create new breed soldier yellowjacket pym recruit scott lang new ant pull heist save life million pretty michael douglas play pym time screen blast listen fatherdaughter dynamic storyline hope evangeline lilly spoiler great pym train scott new ant fun tell paul rudd michael douglas great time work sort worried shrink grow repeatedly fight nerve adjust especially 3d   actually like lot love scott train ant small speaking ant brilliant way introduce pym ridiculous love scott interact fly cool previously strong villain know countless time villain like abomination whiplash ronan feel weak serve plot device love corey stoll darren crossyellowjacket mean sort introduce villain start reason unlike cinematic villain expand actually yellowjacket suit great feel fresh ant duke whilst grow shrink throw object time size climax feature thomas tank engine favourite fight entire series fact fight feature know probably know case reveal love michael pena standout performance feature comic relief lot time work fix time screen laugh think good job anywayto wrap enjoy ant love scott kick ant love michael douglas yellowjacket awesome think flaw plus post credit love excited ant future future mcu great rating age ultron m fanboy know good entertainment entertain ant deserve high rating</t>
+          <t>small scale hero film not big follow ant edgar wright set direct massive fan work leave project worried ant lose different screenplay hear wright work incorporate plus know comic_strip need worry turn well hop trump expectation paul rudd great job bring role scott lang thief come jail year pym tech darren cross corey stoll develop formula mirror hank pyms original ant create new breed soldier call yellowjacket pym recruit scott lang new ant pull heist save life million pretty michael douglas play pym time screen blast listen fatherdaughter dynamic storyline hope evangeline lilly give spoiler great pym train scott new ant fun tell paul rudd michael douglas great time work sort worried shrink grow repeatedly fight nerve take adjust especially 3d   actually like lot love see scott train ant small speaking ant brilliant way introduce pym ridiculous love watch see scott interact fly cool not previously see not strong villain know show countless time villain like abomination whiplash ronan feel weak serve plot device love corey stoll darren crossyellowjacket mean sort introduce villain start reason unlike cinematic villain expand actually yellowjacket suit great feel fresh ant duke whilst grow shrink throw object time size climax feature thomas tank engine favourite fight entire series fact fight feature know probably know case not will not reveal love michael pena give standout performance film feature comic relief lot time work not fix time screen laugh think good job anywayto wrap enjoy ant love scott kick ant love michael douglas yellowjacket awesome not think see flaw continue less know good film definitely board way guardian galaxy plus post credit love get excited ant man future future mcu great not give rating age ultron m fanboy know good entertainment entertain ant deserve high rating small scale hero big follow ant edgar wright set direct massive fan work leave project worried ant lose different screenplay hear wright work incorporate plus know comic_strip need worry turn hop trump expectation paul rudd great job bring role scott lang thief come jail year pym tech darren cross corey stoll develop formula mirror hank pyms original ant create new breed soldier yellowjacket pym recruit scott lang new ant pull heist save life million pretty michael douglas play pym time screen blast listen fatherdaughter dynamic storyline hope evangeline lilly spoiler great pym train scott new ant fun tell paul rudd michael douglas great time work sort worried shrink grow repeatedly fight nerve adjust especially 3d   actually like lot love scott train ant small speaking ant brilliant way introduce pym ridiculous love scott interact fly cool previously strong villain know countless time villain like abomination whiplash ronan feel weak serve plot device love corey stoll darren crossyellowjacket mean sort introduce villain start reason unlike cinematic villain expand actually yellowjacket suit great feel fresh ant duke whilst grow shrink throw object time size climax feature thomas tank engine favourite fight entire series fact fight feature know probably know case reveal love michael pena standout performance feature comic relief lot time work fix time screen laugh think good job anywayto wrap enjoy ant love scott kick ant love michael douglas yellowjacket awesome think flaw continue know good definitely board way guardian galaxy plus post credit love excited ant future future mcu great rating age ultron m fanboy know good entertainment entertain ant deserve high rating [SEP] ENTLBL_PERSON ENTTXT_edgar_wright ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_scott_lang ENTLBL_ORG ENTTXT_pym_tech_darren ENTLBL_PERSON ENTTXT_corey_stoll ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_scott_train ENTLBL_PERSON ENTTXT_scott ENTLBL_PERSON ENTTXT_corey_stoll_darren ENTLBL_PERSON ENTTXT_michael_pena ENTLBL_PERSON ENTTXT_scott_kick</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -13236,20 +10346,10 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13273,12 +10373,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>1 tell marvelous ragtag team misfit entertain emotional heartwarming tell way superhero pull james gunn work vol 2 continue delivery heart pound action humor 1st good deliver deep moment love guardians strong want reiterate doubt funniest cinematic possibly funny 1st break new ground add richness ragtag team hero love root</t>
+          <t>ENTLBL_PERSON ENTTXT_mary_poppin ENTLBL_PERSON ENTTXT_james_gunn</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>m mary poppin you guardian galaxy vol 1 tell marvelous ragtag team misfit entertain emotional heartwarming tell way superhero movie pull james gunn work vol 2 continue delivery heart pound action humor 1st good deliver deep moment make love guardians strong want reiterate doubt funniest cinematic movie possibly funny 1st not break new ground add richness ragtag team hero make love root m mary poppin guardian galaxy vol 1 tell marvelous ragtag team misfit entertain emotional heartwarming tell way superhero pull james gunn work vol 2 continue delivery heart pound action humor 1st good deliver deep moment love guardians strong want reiterate doubt funniest cinematic possibly funny 1st break new ground add richness ragtag team hero love root 1 tell marvelous ragtag team misfit entertain emotional heartwarming tell way superhero pull james gunn work vol 2 continue delivery heart pound action humor 1st good deliver deep moment love guardians strong want reiterate doubt funniest cinematic possibly funny 1st break new ground add richness ragtag team hero love root</t>
+          <t>m mary poppin you guardian galaxy vol 1 tell marvelous ragtag team misfit entertain emotional heartwarming tell way superhero movie pull james gunn work vol 2 continue delivery heart pound action humor 1st good deliver deep moment make love guardians strong want reiterate doubt funniest cinematic movie possibly funny 1st not break new ground add richness ragtag team hero make love root m mary poppin guardian galaxy vol 1 tell marvelous ragtag team misfit entertain emotional heartwarming tell way superhero pull james gunn work vol 2 continue delivery heart pound action humor 1st good deliver deep moment love guardians strong want reiterate doubt funniest cinematic possibly funny 1st break new ground add richness ragtag team hero love root [SEP] ENTLBL_PERSON ENTTXT_mary_poppin ENTLBL_PERSON ENTTXT_james_gunn</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -13293,20 +10393,10 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13328,14 +10418,10 @@
           <t>hat second maybe dance racoon drunk hat second maybe dance racoon drunk</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>hat second maybe dance racoon drunk</t>
-        </is>
-      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>hat second maybe dance racoon drunk hat second maybe dance racoon drunk hat second maybe dance racoon drunk</t>
+          <t>hat second maybe dance racoon drunk hat second maybe dance racoon drunk [SEP]</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -13350,20 +10436,10 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13387,12 +10463,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>superhero like ant bit different way sorta remind honey shrink kid strong plot typical good guy bad guy work government project develop instance point michael douglas break lab big tank helicopter corey stoll henchman understand tank fire helicopter blow kill stoll paul rudd ant lead ant attack plot sense bad superhero apart deadpool   recommend paul rudd good portrayal ant michael douglas hank pym good evangeline lilly hope good bobby cannavale paxto michael pina luis annoying know suppose comic relief annoying rate 5 star</t>
+          <t>ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_stoll_paul_rudd ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_michael_douglas_hank_pym_good_evangeline ENTLBL_PERSON ENTTXT_bobby_cannavale ENTLBL_PERSON ENTTXT_michael_pina_luis ENTLBL_PERSON ENTTXT_corey_stoll</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>superhero like ant bit different see sure like deadpool interesting aspect superhero superpower bit like batman   robin iron spider depend gadget superpower way sorta remind honey shrink kid subvert superhero genre carefully stay inside tie command ant gadget kinda cool strong plot typical good guy bad guy work government project develop instance point michael douglas break lab big tank helicopter corey stoll henchman not understand tank not fire helicopter blow kill stoll paul rudd ant lead ant attack plot movie not sense not bad see superhero movie apart deadpool   recommend paul rudd good portrayal ant michael douglas hank pym good evangeline lilly hope good bobby cannavale paxto michael pina luis annoying know suppose comic relief annoying rate 5 star superhero like ant bit different sure like deadpool interesting aspect superhero superpower bit like batman   robin iron spider depend gadget superpower way sorta remind honey shrink kid subvert superhero genre carefully stay inside tie command ant gadget kinda cool strong plot typical good guy bad guy work government project develop instance point michael douglas break lab big tank helicopter corey stoll henchman understand tank fire helicopter blow kill stoll paul rudd ant lead ant attack plot sense bad superhero apart deadpool   recommend paul rudd good portrayal ant michael douglas hank pym good evangeline lilly hope good bobby cannavale paxto michael pina luis annoying know suppose comic relief annoying rate 5 star superhero like ant bit different way sorta remind honey shrink kid strong plot typical good guy bad guy work government project develop instance point michael douglas break lab big tank helicopter corey stoll henchman understand tank fire helicopter blow kill stoll paul rudd ant lead ant attack plot sense bad superhero apart deadpool   recommend paul rudd good portrayal ant michael douglas hank pym good evangeline lilly hope good bobby cannavale paxto michael pina luis annoying know suppose comic relief annoying rate 5 star</t>
+          <t>superhero like ant bit different see sure like deadpool interesting aspect superhero superpower bit like batman   robin iron spider depend gadget superpower way sorta remind honey shrink kid subvert superhero genre carefully stay inside tie command ant gadget kinda cool strong plot typical good guy bad guy work government project develop instance point michael douglas break lab big tank helicopter corey stoll henchman not understand tank not fire helicopter blow kill stoll paul rudd ant lead ant attack plot movie not sense not bad see superhero movie apart deadpool   recommend paul rudd good portrayal ant michael douglas hank pym good evangeline lilly hope good bobby cannavale paxto michael pina luis annoying know suppose comic relief annoying rate 5 star superhero like ant bit different sure like deadpool interesting aspect superhero superpower bit like batman   robin iron spider depend gadget superpower way sorta remind honey shrink kid subvert superhero genre carefully stay inside tie command ant gadget kinda cool strong plot typical good guy bad guy work government project develop instance point michael douglas break lab big tank helicopter corey stoll henchman understand tank fire helicopter blow kill stoll paul rudd ant lead ant attack plot sense bad superhero apart deadpool   recommend paul rudd good portrayal ant michael douglas hank pym good evangeline lilly hope good bobby cannavale paxto michael pina luis annoying know suppose comic relief annoying rate 5 star [SEP] ENTLBL_PERSON ENTTXT_michael_douglas ENTLBL_PERSON ENTTXT_stoll_paul_rudd ENTLBL_PERSON ENTTXT_paul_rudd ENTLBL_PERSON ENTTXT_michael_douglas_hank_pym_good_evangeline ENTLBL_PERSON ENTTXT_bobby_cannavale ENTLBL_PERSON ENTTXT_michael_pina_luis ENTLBL_PERSON ENTTXT_corey_stoll</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -13402,25 +10478,15 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13444,12 +10510,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>alternate thought far home ravingly collect praise outing course great vote good spidy time tom halland gradually quickly skin spiderman 5 appearance spiderman look like confused teenager superpower friendly neighborhood superhero peter parker spiderman sorry know future like tobey maguire spiderman far home soft future proof launchpad mcu monumental series massacre infinity warendgame start slowly action heavy duty stuff big earth risk challenge definitely colossal villain breathing space hero warm future time revive shock loss mentor tony stark focus mj usual monotonous gibberish nick fury feel pain prejudice far home comical non harmful brute mysterio jake gyllenhaal justice role mysterio fit arena cinematic spiderman probably mushy non damaging villain surely suitable hero soft kick wake far home try establish leader gang read powerful marketing material cinematic superhero league   happen cap contract chris evans chris hemsworth end plan plot half dozen</t>
+          <t>ENTLBL_PERSON ENTTXT_peter_parker ENTLBL_PERSON ENTTXT_tony_stark ENTLBL_PERSON ENTTXT_nick_fury ENTLBL_PERSON ENTTXT_mysterio_jake_gyllenhaal_justice ENTLBL_PERSON ENTTXT_chris_evans ENTLBL_PERSON ENTTXT_chris_hemsworth ENTLBL_ORG ENTTXT_mysterio_fit_arena_cinematic</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>alternate thought far home ravingly collect praise outing course great vote good spidy time tom halland gradually quickly get skin spiderman 5 appearance spiderman look like confused teenager superpower friendly neighborhood superhero peter parker spiderman sorry not know future movie like tobey maguire spiderman far home soft future proof launchpad mcu monumental series massacre infinity warendgame start slowly action heavy duty stuff big earth risk challenge definitely colossal villain breathing space hero warm future time revive shock loss mentor tony stark focus mj usual monotonous gibberish nick fury feel pain prejudice far home give comical non harmful brute mysterio jake gyllenhaal justice role mysterio not fit arena cinematic spiderman probably not see mushy non damaging villain movie surely suitable hero soft kick wake far home try establish leader gang read powerful marketing material cinematic superhero league   happen cap thor contract chris evans chris hemsworth end doctor strange race late movie reduce hulk mere comic material cinematic sure future captain well duty universe start caution endgame planning plot half dozen film alternate thought far home ravingly collect praise outing course great vote good spidy time tom halland gradually quickly skin spiderman 5 appearance spiderman look like confused teenager superpower friendly neighborhood superhero peter parker spiderman sorry know future like tobey maguire spiderman far home soft future proof launchpad mcu monumental series massacre infinity warendgame start slowly action heavy duty stuff big earth risk challenge definitely colossal villain breathing space hero warm future time revive shock loss mentor tony stark focus mj usual monotonous gibberish nick fury feel pain prejudice far home comical non harmful brute mysterio jake gyllenhaal justice role mysterio fit arena cinematic spiderman probably mushy non damaging villain surely suitable hero soft kick wake far home try establish leader gang read powerful marketing material cinematic superhero league   happen cap thor contract chris evans chris hemsworth end doctor strange race late reduce hulk mere comic material cinematic sure future captain duty start caution endgame planning plot half dozen alternate thought far home ravingly collect praise outing course great vote good spidy time tom halland gradually quickly skin spiderman 5 appearance spiderman look like confused teenager superpower friendly neighborhood superhero peter parker spiderman sorry know future like tobey maguire spiderman far home soft future proof launchpad mcu monumental series massacre infinity warendgame start slowly action heavy duty stuff big earth risk challenge definitely colossal villain breathing space hero warm future time revive shock loss mentor tony stark focus mj usual monotonous gibberish nick fury feel pain prejudice far home comical non harmful brute mysterio jake gyllenhaal justice role mysterio fit arena cinematic spiderman probably mushy non damaging villain surely suitable hero soft kick wake far home try establish leader gang read powerful marketing material cinematic superhero league   happen cap contract chris evans chris hemsworth end plan plot half dozen</t>
+          <t>alternate thought far home ravingly collect praise outing course great vote good spidy time tom halland gradually quickly get skin spiderman 5 appearance spiderman look like confused teenager superpower friendly neighborhood superhero peter parker spiderman sorry not know future movie like tobey maguire spiderman far home soft future proof launchpad mcu monumental series massacre infinity warendgame start slowly action heavy duty stuff big earth risk challenge definitely colossal villain breathing space hero warm future time revive shock loss mentor tony stark focus mj usual monotonous gibberish nick fury feel pain prejudice far home give comical non harmful brute mysterio jake gyllenhaal justice role mysterio not fit arena cinematic spiderman probably not see mushy non damaging villain movie surely suitable hero soft kick wake far home try establish leader gang read powerful marketing material cinematic superhero league   happen cap thor contract chris evans chris hemsworth end doctor strange race late movie reduce hulk mere comic material cinematic sure future captain well duty universe start caution endgame planning plot half dozen film alternate thought far home ravingly collect praise outing course great vote good spidy time tom halland gradually quickly skin spiderman 5 appearance spiderman look like confused teenager superpower friendly neighborhood superhero peter parker spiderman sorry know future like tobey maguire spiderman far home soft future proof launchpad mcu monumental series massacre infinity warendgame start slowly action heavy duty stuff big earth risk challenge definitely colossal villain breathing space hero warm future time revive shock loss mentor tony stark focus mj usual monotonous gibberish nick fury feel pain prejudice far home comical non harmful brute mysterio jake gyllenhaal justice role mysterio fit arena cinematic spiderman probably mushy non damaging villain surely suitable hero soft kick wake far home try establish leader gang read powerful marketing material cinematic superhero league   happen cap thor contract chris evans chris hemsworth end doctor strange race late reduce hulk mere comic material cinematic sure future captain duty start caution endgame planning plot half dozen [SEP] ENTLBL_PERSON ENTTXT_peter_parker ENTLBL_PERSON ENTTXT_tony_stark ENTLBL_PERSON ENTTXT_nick_fury ENTLBL_PERSON ENTTXT_mysterio_jake_gyllenhaal_justice ENTLBL_PERSON ENTTXT_chris_evans ENTLBL_PERSON ENTTXT_chris_hemsworth ENTLBL_ORG ENTTXT_mysterio_fit_arena_cinematic</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -13464,20 +10530,10 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13501,12 +10557,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ab solute ly good evangeline lilly killer wasp totally badass paul rudd amazing job comedic time chemistry comedic timing excellent absolutely love computer generate imagery bad</t>
+          <t>ENTLBL_PERSON ENTTXT_paul_rudd</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>ab solute ly good evangeline lilly killer wasp totally badass paul rudd amazing job comedic time chemistry comedic timing excellent absolutely love computer generate imagery bad ab solute ly good evangeline lilly killer wasp totally badass paul rudd amazing job comedic time chemistry comedic timing excellent absolutely love computer generate imagery bad ab solute ly good evangeline lilly killer wasp totally badass paul rudd amazing job comedic time chemistry comedic timing excellent absolutely love computer generate imagery bad</t>
+          <t>ab solute ly good evangeline lilly killer wasp totally badass paul rudd amazing job comedic time chemistry comedic timing excellent absolutely love computer generate imagery bad ab solute ly good evangeline lilly killer wasp totally badass paul rudd amazing job comedic time chemistry comedic timing excellent absolutely love computer generate imagery bad [SEP] ENTLBL_PERSON ENTTXT_paul_rudd</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -13521,20 +10577,10 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13556,14 +10602,10 @@
           <t>cheap lazy bad franchise far awful computer generate imagery script make jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve see awful ruin hulk cheap lazy bad franchise far awful computer generate imagery script jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve awful ruin hulk</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>cheap lazy bad franchise far awful computer generate imagery script jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve awful ruin hulk</t>
-        </is>
-      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>cheap lazy bad franchise far awful computer generate imagery script make jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve see awful ruin hulk cheap lazy bad franchise far awful computer generate imagery script jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve awful ruin hulk cheap lazy bad franchise far awful computer generate imagery script jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve awful ruin hulk</t>
+          <t>cheap lazy bad franchise far awful computer generate imagery script make jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve see awful ruin hulk cheap lazy bad franchise far awful computer generate imagery script jar jar bink level annoying remind awful star war prequel walk blue screen set wanting budget cut bad ve awful ruin hulk [SEP]</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -13578,20 +10620,10 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13615,12 +10647,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>fall minority like think mega overrate like general direction tone small problem love honestly love visual haunt epic score triumphant h performance perfect sequel lot shoulder tribute chadwick boseman celebration bring life sequel bring life level work phenomenally start gush minor problem perfect score think beat need time breathe especially end final battle politic feel like stuff shove cameo excuse bilbo riri williams fun add particularly major way function macguffin wakandans need safe add shuris arc riri lose family member editing hit miss good shot need little long impact want computer generate imagery shot little iffy consistently great cinematic cgi great stuff act damn good single actor role mbaku seat comedy relief good shuri angela basset phenomenal performance guttural emotional belief wonder emotion tenoch huerta wonderful antagonist word mouth dripping emotion standout letitia wright shuri cautiously optimistic regard role especially twitter controversy regard letitia view vaccine kill performance good recent history visually easily look point easy point formula come visual design cinematography bland grey shot little interesting camera movement break cinematography rule lighting dramatic distinct camerawork excellently frame direction phenomenal ryan coogler dp autumn durald arkapaw knock park want special shoutout sound design incredibly easy generic sound effect especially atlantan sound design underwater gorgeous artist sound effect deserve award notable aspect tone brand humor find humor far write insert overall joke ve overall love love clear sign improvement theater definitely worth</t>
+          <t>ENTLBL_PERSON ENTTXT_chadwick_boseman ENTLBL_PERSON ENTTXT_williams ENTLBL_PERSON ENTTXT_role_mbaku ENTLBL_PERSON ENTTXT_shuri_angela ENTLBL_ORG ENTTXT_letitia ENTLBL_ORG ENTTXT_wright_shuri_cautiously ENTLBL_PERSON ENTTXT_letitia ENTLBL_ORG ENTTXT_grey_shot_little ENTLBL_PERSON ENTTXT_durald ENTLBL_PERSON ENTTXT_tenoch_huerta ENTLBL_ORG ENTTXT_wright_shuri</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>well start think good context thought black panther fall minority like think mega overrate like general direction tone small problem love say honestly love visual haunt epic score triumphant h performance perfect sequel lot shoulder tribute chadwick boseman celebration bring life sequel bring life level work phenomenally start gush minor problem give perfect score think beat need time breathe especially end final battle politic feel like stuff shove cameo excuse bilbo riri williams fun not add particularly major way function macguffin wakandans need safe not add shuris arc riri lose family member editing hit miss good shot need little long impact want computer generate imagery shot little iffy consistently great cinematic cgi great stuff act damn good not single actor put role mbaku take seat comedy relief good shuri angela basset phenomenal performance guttural emotional belief wonder emotion go tenoch huerta wonderful antagonist word mouth dripping emotion standout letitia wright shuri cautiously optimistic role especially twitter controversy letitia view vaccine kill performance good recent history visually easily well look point easy point formula come visual design cinematography bland grey shot little interesting camera movement recent try break formula notably multiverse madness eternal ultimately double return safe gray color palette multiple break cinematography rule lighting dramatic distinct camerawork excellently frame direction phenomenal ryan coogler dp autumn durald arkapaw knock park want special shoutout sound design incredibly easy generic sound effect especially atlantan sound design go underwater gorgeous artist sound effect deserve award notable aspect tone brand humor find humor far well write insert movie few overall joke ve see eternal come close joke feel like feigi mandate insert genuine natural attempt humor overall love not love clear sign improvement theater definitely worth start think good context thought black panther fall minority like think mega overrate like general direction tone small problem love honestly love visual haunt epic score triumphant h performance perfect sequel lot shoulder tribute chadwick boseman celebration bring life sequel bring life level work phenomenally start gush minor problem perfect score think beat need time breathe especially end final battle politic feel like stuff shove cameo excuse bilbo riri williams fun add particularly major way function macguffin wakandans need safe add shuris arc riri lose family member editing hit miss good shot need little long impact want computer generate imagery shot little iffy consistently great cinematic cgi great stuff act damn good single actor role mbaku seat comedy relief good shuri angela basset phenomenal performance guttural emotional belief wonder emotion tenoch huerta wonderful antagonist word mouth dripping emotion standout letitia wright shuri cautiously optimistic regard role especially twitter controversy regard letitia view vaccine kill performance good recent history visually easily look point easy point formula come visual design cinematography bland grey shot little interesting camera movement recent try break formula notably multiverse madness eternal ultimately double return safe gray color palette multiple break cinematography rule lighting dramatic distinct camerawork excellently frame direction phenomenal ryan coogler dp autumn durald arkapaw knock park want special shoutout sound design incredibly easy generic sound effect especially atlantan sound design underwater gorgeous artist sound effect deserve award notable aspect tone brand humor find humor far write insert overall joke ve eternal come close joke feel like feigi mandate insert genuine natural attempt humor overall love love clear sign improvement theater definitely worth fall minority like think mega overrate like general direction tone small problem love honestly love visual haunt epic score triumphant h performance perfect sequel lot shoulder tribute chadwick boseman celebration bring life sequel bring life level work phenomenally start gush minor problem perfect score think beat need time breathe especially end final battle politic feel like stuff shove cameo excuse bilbo riri williams fun add particularly major way function macguffin wakandans need safe add shuris arc riri lose family member editing hit miss good shot need little long impact want computer generate imagery shot little iffy consistently great cinematic cgi great stuff act damn good single actor role mbaku seat comedy relief good shuri angela basset phenomenal performance guttural emotional belief wonder emotion tenoch huerta wonderful antagonist word mouth dripping emotion standout letitia wright shuri cautiously optimistic regard role especially twitter controversy regard letitia view vaccine kill performance good recent history visually easily look point easy point formula come visual design cinematography bland grey shot little interesting camera movement break cinematography rule lighting dramatic distinct camerawork excellently frame direction phenomenal ryan coogler dp autumn durald arkapaw knock park want special shoutout sound design incredibly easy generic sound effect especially atlantan sound design underwater gorgeous artist sound effect deserve award notable aspect tone brand humor find humor far write insert overall joke ve overall love love clear sign improvement theater definitely worth</t>
+          <t>well start think good context thought black panther fall minority like think mega overrate like general direction tone small problem love say honestly love visual haunt epic score triumphant h performance perfect sequel lot shoulder tribute chadwick boseman celebration bring life sequel bring life level work phenomenally start gush minor problem give perfect score think beat need time breathe especially end final battle politic feel like stuff shove cameo excuse bilbo riri williams fun not add particularly major way function macguffin wakandans need safe not add shuris arc riri lose family member editing hit miss good shot need little long impact want computer generate imagery shot little iffy consistently great cinematic cgi great stuff act damn good not single actor put role mbaku take seat comedy relief good shuri angela basset phenomenal performance guttural emotional belief wonder emotion go tenoch huerta wonderful antagonist word mouth dripping emotion standout letitia wright shuri cautiously optimistic role especially twitter controversy letitia view vaccine kill performance good recent history visually easily well look point easy point formula come visual design cinematography bland grey shot little interesting camera movement recent try break formula notably multiverse madness eternal ultimately double return safe gray color palette multiple break cinematography rule lighting dramatic distinct camerawork excellently frame direction phenomenal ryan coogler dp autumn durald arkapaw knock park want special shoutout sound design incredibly easy generic sound effect especially atlantan sound design go underwater gorgeous artist sound effect deserve award notable aspect tone brand humor find humor far well write insert movie few overall joke ve see eternal come close joke feel like feigi mandate insert genuine natural attempt humor overall love not love clear sign improvement theater definitely worth start think good context thought black panther fall minority like think mega overrate like general direction tone small problem love honestly love visual haunt epic score triumphant h performance perfect sequel lot shoulder tribute chadwick boseman celebration bring life sequel bring life level work phenomenally start gush minor problem perfect score think beat need time breathe especially end final battle politic feel like stuff shove cameo excuse bilbo riri williams fun add particularly major way function macguffin wakandans need safe add shuris arc riri lose family member editing hit miss good shot need little long impact want computer generate imagery shot little iffy consistently great cinematic cgi great stuff act damn good single actor role mbaku seat comedy relief good shuri angela basset phenomenal performance guttural emotional belief wonder emotion tenoch huerta wonderful antagonist word mouth dripping emotion standout letitia wright shuri cautiously optimistic regard role especially twitter controversy regard letitia view vaccine kill performance good recent history visually easily look point easy point formula come visual design cinematography bland grey shot little interesting camera movement recent try break formula notably multiverse madness eternal ultimately double return safe gray color palette multiple break cinematography rule lighting dramatic distinct camerawork excellently frame direction phenomenal ryan coogler dp autumn durald arkapaw knock park want special shoutout sound design incredibly easy generic sound effect especially atlantan sound design underwater gorgeous artist sound effect deserve award notable aspect tone brand humor find humor far write insert overall joke ve eternal come close joke feel like feigi mandate insert genuine natural attempt humor overall love love clear sign improvement theater definitely worth [SEP] ENTLBL_PERSON ENTTXT_chadwick_boseman ENTLBL_PERSON ENTTXT_williams ENTLBL_PERSON ENTTXT_role_mbaku ENTLBL_PERSON ENTTXT_shuri_angela ENTLBL_ORG ENTTXT_letitia ENTLBL_ORG ENTTXT_wright_shuri_cautiously ENTLBL_PERSON ENTTXT_letitia ENTLBL_ORG ENTTXT_grey_shot_little ENTLBL_PERSON ENTTXT_durald ENTLBL_PERSON ENTTXT_tenoch_huerta ENTLBL_ORG ENTTXT_wright_shuri</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -13635,20 +10667,10 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13672,12 +10694,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>predictablebut good opinion endgame start aftermath infinity war spidy thing leave emotional start time predictablebut comedy fill void hilarious enjoy   feel emotion dying favourite feel like franchise end way   russo brother hurry clumsy final battle vfx great like   finally end   feel emotional m time overall   endgame bad movienor great good good comedy drama</t>
+          <t>ENTLBL_PERSON ENTTXT_hurry ENTLBL_PERSON ENTTXT_hurry_clumsy</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>predictablebut good opinion endgame start aftermath infinity war spidy thing leave emotional start time predictablebut comedy fill void hilarious go to enjoy   entire 2hrs deal time heist thing 1hr await combat thanosthe mad titan clumsy effective infinity war not feel emotion watch dying favourite feel like franchise end way   russo brother hurry make clumsy final battle vfx great like   finally end   feel emotional m go time overall   endgame bad movienor great good good comedy drama infinity war stand predictablebut good opinion endgame start aftermath infinity war spidy thing leave emotional start time predictablebut comedy fill void hilarious enjoy   entire 2hrs deal time heist thing 1hr await combat thanosthe mad titan clumsy effective infinity war feel emotion dying favourite feel like franchise end way   russo brother hurry clumsy final battle vfx great like   finally end   feel emotional m time overall   endgame bad movienor great good good comedy drama infinity war stand predictablebut good opinion endgame start aftermath infinity war spidy thing leave emotional start time predictablebut comedy fill void hilarious enjoy   feel emotion dying favourite feel like franchise end way   russo brother hurry clumsy final battle vfx great like   finally end   feel emotional m time overall   endgame bad movienor great good good comedy drama</t>
+          <t>predictablebut good opinion endgame start aftermath infinity war spidy thing leave emotional start time predictablebut comedy fill void hilarious go to enjoy   entire 2hrs deal time heist thing 1hr await combat thanosthe mad titan clumsy effective infinity war not feel emotion watch dying favourite feel like franchise end way   russo brother hurry make clumsy final battle vfx great like   finally end   feel emotional m go time overall   endgame bad movienor great good good comedy drama infinity war stand predictablebut good opinion endgame start aftermath infinity war spidy thing leave emotional start time predictablebut comedy fill void hilarious enjoy   entire 2hrs deal time heist thing 1hr await combat thanosthe mad titan clumsy effective infinity war feel emotion dying favourite feel like franchise end way   russo brother hurry clumsy final battle vfx great like   finally end   feel emotional m time overall   endgame bad movienor great good good comedy drama infinity war stand [SEP] ENTLBL_PERSON ENTTXT_hurry ENTLBL_PERSON ENTTXT_hurry_clumsy</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -13692,20 +10714,10 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13729,12 +10741,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>nearly hour mindless computer generate imagery confess superhero jump excitement appear aim year old need non stop explosion destruction hold attention doctor strange new level doubt minute use blue screen sad industry deteriorate level garbage like draw huge box office encourage trash produce hollywood obsession pc plotting lower standard far intelligent produce audience prepare follow drive plot struggle profit appear stick superhero foreseeable future</t>
+          <t>ENTLBL_PERSON ENTTXT_nicholson</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>nearly hour mindless computer generate imagery confess superhero film jump excitement appear aim year old need non stop explosion destruction hold attention batman nicholson entertaining funny original superman film reasonable plot enterainment value dc take genre new direction time go successive superhero reduce human element increase special effect cgi doctor strange take new level doubt minute film blue screen sad industry deteriorate level garbage like draw huge box office encourage trash produce hollywood obsession pc plotting lower standard intelligent film produce audience prepare follow drive plot struggle profit appear stick superhero foreseeable future nearly hour mindless computer generate imagery confess superhero jump excitement appear aim year old need non stop explosion destruction hold attention batman nicholson entertaining funny original superman reasonable plot enterainment value dc genre new direction time successive superhero reduce human element increase special effect cgi doctor strange new level doubt minute use blue screen sad industry deteriorate level garbage like draw huge box office encourage trash produce hollywood obsession pc plotting lower standard far intelligent produce audience prepare follow drive plot struggle profit appear stick superhero foreseeable future nearly hour mindless computer generate imagery confess superhero jump excitement appear aim year old need non stop explosion destruction hold attention doctor strange new level doubt minute use blue screen sad industry deteriorate level garbage like draw huge box office encourage trash produce hollywood obsession pc plotting lower standard far intelligent produce audience prepare follow drive plot struggle profit appear stick superhero foreseeable future</t>
+          <t>nearly hour mindless computer generate imagery confess superhero film jump excitement appear aim year old need non stop explosion destruction hold attention batman nicholson entertaining funny original superman film reasonable plot enterainment value dc take genre new direction time go successive superhero reduce human element increase special effect cgi doctor strange take new level doubt minute film blue screen sad industry deteriorate level garbage like draw huge box office encourage trash produce hollywood obsession pc plotting lower standard intelligent film produce audience prepare follow drive plot struggle profit appear stick superhero foreseeable future nearly hour mindless computer generate imagery confess superhero jump excitement appear aim year old need non stop explosion destruction hold attention batman nicholson entertaining funny original superman reasonable plot enterainment value dc genre new direction time successive superhero reduce human element increase special effect cgi doctor strange new level doubt minute use blue screen sad industry deteriorate level garbage like draw huge box office encourage trash produce hollywood obsession pc plotting lower standard far intelligent produce audience prepare follow drive plot struggle profit appear stick superhero foreseeable future [SEP] ENTLBL_PERSON ENTTXT_nicholson</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -13749,20 +10761,10 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13786,12 +10788,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2 thrilling new entry cinematic perfect family especially teenager hour follow installment place month later base comic fantasy prove lose touch team peter quill chris pratt   drax dave bautista   rocket racoon bradly cooper   gamora zoe saldana   course baby groot vin diesel   return yondu michael rooker nebula karen gillan   direct james gunn begin creative unique way reintroduce team mission sovereign super elite race genetically engineer sparkle gold humanoid ship crash deserted planet peters long lose father ego kurt russel   innocent assistant mantis pom klementieff   pick ego bring planet place stay repair ship split team empire strike esque fashion overwhelming similarity empire strike effect spot believe actually happen include joke rocket racoon effect nail work fluidly actor acting generally pretty good misstep chris pratt convince audience depressed relatively solid dramatic change tone look past weight situation nebula fit compare light joke tone rest cast soundtrack extremely good fit live hype soundtrack music perfect recommend buy soundtrack joke land distract rest hilarious drax oblivious genuine dialogue tend follow charming baby groot gag spectacular good far outweigh band easily remember great comic book lot laugh plenty heartfelt</t>
+          <t>ENTLBL_PERSON ENTTXT_peter_quill ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_drax_dave_bautista ENTLBL_ORG ENTTXT_rocket_racoon ENTLBL_PERSON ENTTXT_gamora_zoe ENTLBL_PERSON ENTTXT_saldana ENTLBL_PERSON ENTTXT_michael_rooker ENTLBL_PERSON ENTTXT_nebula_karen_gillan___direct ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_peters_long ENTLBL_ORG ENTTXT_klementieff ENTLBL_PERSON ENTTXT_chris_pratt_convince</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>brilliant new entry cinematic guardian galaxy vol 2 thrilling new entry cinematic perfect family especially teenager hour follow installment take place month later base comic fantasy prove not lose touch team peter quill chris pratt   drax dave bautista   rocket racoon bradly cooper   gamora zoe saldana   course baby groot vin diesel   return yondu michael rooker nebula karen gillan   direct james gunn begin creative unique way reintroduce team mission sovereign super elite race genetically engineer sparkle gold humanoid ship crash deserted planet peters long lose father ego kurt russel   innocent assistant mantis pom klementieff   pick ego bring planet take place stay repair ship split team empire strike esque fashion overwhelming amount similarity empire strike effect spot make believe actually happen include joke well rocket racoon effect nail work fluidly actor acting generally pretty good misstep chris pratt not convince audience depressed relatively solid dramatic change tone look past give weight situation nebula fit compare light joke tone rest cast soundtrack extremely good fit not live hype movie soundtrack music perfect recommend buy soundtrack joke land not distract rest hilarious drax oblivious genuine dialogue tend well follow charming baby groot gag spectacular good far outweigh band easily remember great comic book lot laugh plenty heartfelt brilliant new entry cinematic guardian galaxy vol 2 thrilling new entry cinematic perfect family especially teenager hour follow installment place month later base comic fantasy prove lose touch team peter quill chris pratt   drax dave bautista   rocket racoon bradly cooper   gamora zoe saldana   course baby groot vin diesel   return yondu michael rooker nebula karen gillan   direct james gunn begin creative unique way reintroduce team mission sovereign super elite race genetically engineer sparkle gold humanoid ship crash deserted planet peters long lose father ego kurt russel   innocent assistant mantis pom klementieff   pick ego bring planet place stay repair ship split team empire strike esque fashion overwhelming similarity empire strike effect spot believe actually happen include joke rocket racoon effect nail work fluidly actor acting generally pretty good misstep chris pratt convince audience depressed relatively solid dramatic change tone look past weight situation nebula fit compare light joke tone rest cast soundtrack extremely good fit live hype soundtrack music perfect recommend buy soundtrack joke land distract rest hilarious drax oblivious genuine dialogue tend follow charming baby groot gag spectacular good far outweigh band easily remember great comic book lot laugh plenty heartfelt 2 thrilling new entry cinematic perfect family especially teenager hour follow installment place month later base comic fantasy prove lose touch team peter quill chris pratt   drax dave bautista   rocket racoon bradly cooper   gamora zoe saldana   course baby groot vin diesel   return yondu michael rooker nebula karen gillan   direct james gunn begin creative unique way reintroduce team mission sovereign super elite race genetically engineer sparkle gold humanoid ship crash deserted planet peters long lose father ego kurt russel   innocent assistant mantis pom klementieff   pick ego bring planet place stay repair ship split team empire strike esque fashion overwhelming similarity empire strike effect spot believe actually happen include joke rocket racoon effect nail work fluidly actor acting generally pretty good misstep chris pratt convince audience depressed relatively solid dramatic change tone look past weight situation nebula fit compare light joke tone rest cast soundtrack extremely good fit live hype soundtrack music perfect recommend buy soundtrack joke land distract rest hilarious drax oblivious genuine dialogue tend follow charming baby groot gag spectacular good far outweigh band easily remember great comic book lot laugh plenty heartfelt</t>
+          <t>brilliant new entry cinematic guardian galaxy vol 2 thrilling new entry cinematic perfect family especially teenager hour follow installment take place month later base comic fantasy prove not lose touch team peter quill chris pratt   drax dave bautista   rocket racoon bradly cooper   gamora zoe saldana   course baby groot vin diesel   return yondu michael rooker nebula karen gillan   direct james gunn begin creative unique way reintroduce team mission sovereign super elite race genetically engineer sparkle gold humanoid ship crash deserted planet peters long lose father ego kurt russel   innocent assistant mantis pom klementieff   pick ego bring planet take place stay repair ship split team empire strike esque fashion overwhelming amount similarity empire strike effect spot make believe actually happen include joke well rocket racoon effect nail work fluidly actor acting generally pretty good misstep chris pratt not convince audience depressed relatively solid dramatic change tone look past give weight situation nebula fit compare light joke tone rest cast soundtrack extremely good fit not live hype movie soundtrack music perfect recommend buy soundtrack joke land not distract rest hilarious drax oblivious genuine dialogue tend well follow charming baby groot gag spectacular good far outweigh band easily remember great comic book lot laugh plenty heartfelt brilliant new entry cinematic guardian galaxy vol 2 thrilling new entry cinematic perfect family especially teenager hour follow installment place month later base comic fantasy prove lose touch team peter quill chris pratt   drax dave bautista   rocket racoon bradly cooper   gamora zoe saldana   course baby groot vin diesel   return yondu michael rooker nebula karen gillan   direct james gunn begin creative unique way reintroduce team mission sovereign super elite race genetically engineer sparkle gold humanoid ship crash deserted planet peters long lose father ego kurt russel   innocent assistant mantis pom klementieff   pick ego bring planet place stay repair ship split team empire strike esque fashion overwhelming similarity empire strike effect spot believe actually happen include joke rocket racoon effect nail work fluidly actor acting generally pretty good misstep chris pratt convince audience depressed relatively solid dramatic change tone look past weight situation nebula fit compare light joke tone rest cast soundtrack extremely good fit live hype soundtrack music perfect recommend buy soundtrack joke land distract rest hilarious drax oblivious genuine dialogue tend follow charming baby groot gag spectacular good far outweigh band easily remember great comic book lot laugh plenty heartfelt [SEP] ENTLBL_PERSON ENTTXT_peter_quill ENTLBL_PERSON ENTTXT_chris_pratt ENTLBL_PERSON ENTTXT_drax_dave_bautista ENTLBL_ORG ENTTXT_rocket_racoon ENTLBL_PERSON ENTTXT_gamora_zoe ENTLBL_PERSON ENTTXT_saldana ENTLBL_PERSON ENTTXT_michael_rooker ENTLBL_PERSON ENTTXT_nebula_karen_gillan___direct ENTLBL_PERSON ENTTXT_james_gunn ENTLBL_PERSON ENTTXT_peters_long ENTLBL_ORG ENTTXT_klementieff ENTLBL_PERSON ENTTXT_chris_pratt_convince</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -13806,20 +10808,10 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
@@ -13843,12 +10835,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>great close hype seriously sell people rating know basic storyline lack twist expect pack lot important decent screen time downey nail role josh brolin amazing thano fight dr strange use time stone use think pain thano reason explain use use stone alternate defeat future hulk 95 big disappointment overall good superhero reside 9 250 kid seriously wrong rating close lotr</t>
+          <t>ENTLBL_PERSON ENTTXT_thano_reason</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>great close hype get seriously sell people give rating not know basic storyline lack twist expect pack lot important get decent screen time downey nail role josh brolin amazing thano fact movie thano good villain overpower fight dr strange not use time stone think pain thano reason explain not use stone alternate see defeat future hulk 95 big disappointment overall good superhero reside 9 250 get kid seriously wrong rating close lotr great close hype seriously sell people rating know basic storyline lack twist expect pack lot important decent screen time downey nail role josh brolin amazing thano fact thano good villain overpower fight dr strange use time stone use think pain thano reason explain use use stone alternate defeat future hulk 95 big disappointment overall good superhero reside 9 250 kid seriously wrong rating close lotr great close hype seriously sell people rating know basic storyline lack twist expect pack lot important decent screen time downey nail role josh brolin amazing thano fight dr strange use time stone use think pain thano reason explain use use stone alternate defeat future hulk 95 big disappointment overall good superhero reside 9 250 kid seriously wrong rating close lotr</t>
+          <t>great close hype get seriously sell people give rating not know basic storyline lack twist expect pack lot important get decent screen time downey nail role josh brolin amazing thano fact movie thano good villain overpower fight dr strange not use time stone think pain thano reason explain not use stone alternate see defeat future hulk 95 big disappointment overall good superhero reside 9 250 get kid seriously wrong rating close lotr great close hype seriously sell people rating know basic storyline lack twist expect pack lot important decent screen time downey nail role josh brolin amazing thano fact thano good villain overpower fight dr strange use time stone use think pain thano reason explain use use stone alternate defeat future hulk 95 big disappointment overall good superhero reside 9 250 kid seriously wrong rating close lotr [SEP] ENTLBL_PERSON ENTTXT_thano_reason</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -13863,20 +10855,10 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13900,12 +10882,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>chase point fully hop good americans 1 week waste 14 recall chase chase chase fight lame ass romance valid porn real lusty look lusty look awful feel like grow kid party barney smart suave person purple sing pathetic song seriously setup like indy 500 loud exciting repetitive boring 420 lap hear sound action care oh capin america hero actual reason title winter soldier</t>
+          <t>ENTLBL_ORG ENTTXT_chase_point</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>chase point fully hop good americans 1 week waste 14 well recall chase chase chase fight lame ass romance valid porn real lusty look lusty look awful feel like grow kid party say barney smart suave person purple sing pathetic song seriously not setup like watch indy 500 loud exciting repetitive boring 420 lap hear sound action care oh capin america hero actual reason title winter soldier chase point fully hop good americans 1 week waste 14 recall chase chase chase fight lame ass romance valid porn real lusty look lusty look awful feel like grow kid party barney smart suave person purple sing pathetic song seriously setup like indy 500 loud exciting repetitive boring 420 lap hear sound action care oh capin america hero actual reason title winter soldier chase point fully hop good americans 1 week waste 14 recall chase chase chase fight lame ass romance valid porn real lusty look lusty look awful feel like grow kid party barney smart suave person purple sing pathetic song seriously setup like indy 500 loud exciting repetitive boring 420 lap hear sound action care oh capin america hero actual reason title winter soldier</t>
+          <t>chase point fully hop good americans 1 week waste 14 well recall chase chase chase fight lame ass romance valid porn real lusty look lusty look awful feel like grow kid party say barney smart suave person purple sing pathetic song seriously not setup like watch indy 500 loud exciting repetitive boring 420 lap hear sound action care oh capin america hero actual reason title winter soldier chase point fully hop good americans 1 week waste 14 recall chase chase chase fight lame ass romance valid porn real lusty look lusty look awful feel like grow kid party barney smart suave person purple sing pathetic song seriously setup like indy 500 loud exciting repetitive boring 420 lap hear sound action care oh capin america hero actual reason title winter soldier [SEP] ENTLBL_ORG ENTTXT_chase_point</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -13920,20 +10902,10 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
-        <is>
-          <t>NEGATIVE</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
         <is>
           <t>NEGATIVE</t>
         </is>
@@ -13957,12 +10929,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>number beautiful dragon charming location shang chi legend ring inspire constantly inspire cinematic world decade follow usual stereotype manage stand stunning special effect location revolve shaun chinese immigrant living united states america work valet quirky friend soulmate katy day attack group assassin bus manage survive shaun immediately understand attack relate influential estranged father katy decide team tough estranged sister xiale find convince multiple level act performance quirky convince especially lady steal awkwafina deliver good curious dynamic funny woman like friend zhang menger represent dark shape dramatic event past difficult approach tough relentless independent personality expensive special effect certainly deliver good fantasy world ancient china contemporary san francisco equally stunning fantastic creature dragon look impressive big screen lack originality entertain start finish thank steady pace inspire execution truly care fate different occasional flaw lead actor simu liu simply charisma actress actor involve cast bold choice fully pay opinion desperately try connect appearance trevor slattery play ben kingsley completely random pretext offer misplace comic relief mid credit start amusing fashion suddenly involve bruce banner carol danver like weak attempt develop hype potential sequel credit evoke question conclude appropriately end day shang chi legend ring entertaining fantasy action appeal faithful occasional fan alike franchise focus quality quantity instead monstrous capitalistic machine scary gigantic dragon</t>
+          <t>ENTLBL_ORG ENTTXT_united_states_america ENTLBL_PERSON ENTTXT_katy_day_attack_group ENTLBL_PERSON ENTTXT_katy ENTLBL_PERSON ENTTXT_zhang_menger ENTLBL_PERSON ENTTXT_simu_liu ENTLBL_PERSON ENTTXT_ben_kingsley</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>number beautiful dragon charming location shang chi legend ring inspire constantly inspire cinematic world decade follow usual stereotype manage stand stunning special effect location revolve shaun chinese immigrant living united states america work valet quirky friend soulmate katy day attack group assassin bus manage survive shaun immediately understand attack relate influential estranged father katy decide team tough estranged sister xiale find go convince multiple level act performance quirky convince especially lady steal awkwafina deliver good curious dynamic funny woman like friend zhang menger represent dark shape dramatic event past difficult approach tough relentless independent personality expensive special effect certainly deliver good fantasy world ancient china contemporary san francisco equally stunning fantastic creature dragon look impressive big screen lack originality entertain start finish thank steady pace inspire execution truly care fate different watch not occasional flaw lead actor simu liu simply not charisma actress actor involve cast bold choice not fully pay opinion desperately try connect appearance trevor slattery play ben kingsley completely random pretext offer misplace comic relief mid credit start amusing fashion suddenly involve bruce banner carol danver like weak attempt develop hype potential sequel go credit evoke question conclude appropriately end day shang chi legend ring entertaining fantasy action appeal faithful occasional fan alike well film franchise focus quality quantity instead monstrous capitalistic machine scary gigantic dragon show number beautiful dragon charming location shang chi legend ring inspire constantly inspire cinematic world decade follow usual stereotype manage stand stunning special effect location revolve shaun chinese immigrant living united states america work valet quirky friend soulmate katy day attack group assassin bus manage survive shaun immediately understand attack relate influential estranged father katy decide team tough estranged sister xiale find convince multiple level act performance quirky convince especially lady steal awkwafina deliver good curious dynamic funny woman like friend zhang menger represent dark shape dramatic event past difficult approach tough relentless independent personality expensive special effect certainly deliver good fantasy world ancient china contemporary san francisco equally stunning fantastic creature dragon look impressive big screen lack originality entertain start finish thank steady pace inspire execution truly care fate different occasional flaw lead actor simu liu simply charisma actress actor involve cast bold choice fully pay opinion desperately try connect appearance trevor slattery play ben kingsley completely random pretext offer misplace comic relief mid credit start amusing fashion suddenly involve bruce banner carol danver like weak attempt develop hype potential sequel credit evoke question conclude appropriately end day shang chi legend ring entertaining fantasy action appeal faithful occasional fan alike franchise focus quality quantity instead monstrous capitalistic machine scary gigantic dragon number beautiful dragon charming location shang chi legend ring inspire constantly inspire cinematic world decade follow usual stereotype manage stand stunning special effect location revolve shaun chinese immigrant living united states america work valet quirky friend soulmate katy day attack group assassin bus manage survive shaun immediately understand attack relate influential estranged father katy decide team tough estranged sister xiale find convince multiple level act performance quirky convince especially lady steal awkwafina deliver good curious dynamic funny woman like friend zhang menger represent dark shape dramatic event past difficult approach tough relentless independent personality expensive special effect certainly deliver good fantasy world ancient china contemporary san francisco equally stunning fantastic creature dragon look impressive big screen lack originality entertain start finish thank steady pace inspire execution truly care fate different occasional flaw lead actor simu liu simply charisma actress actor involve cast bold choice fully pay opinion desperately try connect appearance trevor slattery play ben kingsley completely random pretext offer misplace comic relief mid credit start amusing fashion suddenly involve bruce banner carol danver like weak attempt develop hype potential sequel credit evoke question conclude appropriately end day shang chi legend ring entertaining fantasy action appeal faithful occasional fan alike franchise focus quality quantity instead monstrous capitalistic machine scary gigantic dragon</t>
+          <t>number beautiful dragon charming location shang chi legend ring inspire constantly inspire cinematic world decade follow usual stereotype manage stand stunning special effect location revolve shaun chinese immigrant living united states america work valet quirky friend soulmate katy day attack group assassin bus manage survive shaun immediately understand attack relate influential estranged father katy decide team tough estranged sister xiale find go convince multiple level act performance quirky convince especially lady steal awkwafina deliver good curious dynamic funny woman like friend zhang menger represent dark shape dramatic event past difficult approach tough relentless independent personality expensive special effect certainly deliver good fantasy world ancient china contemporary san francisco equally stunning fantastic creature dragon look impressive big screen lack originality entertain start finish thank steady pace inspire execution truly care fate different watch not occasional flaw lead actor simu liu simply not charisma actress actor involve cast bold choice not fully pay opinion desperately try connect appearance trevor slattery play ben kingsley completely random pretext offer misplace comic relief mid credit start amusing fashion suddenly involve bruce banner carol danver like weak attempt develop hype potential sequel go credit evoke question conclude appropriately end day shang chi legend ring entertaining fantasy action appeal faithful occasional fan alike well film franchise focus quality quantity instead monstrous capitalistic machine scary gigantic dragon show number beautiful dragon charming location shang chi legend ring inspire constantly inspire cinematic world decade follow usual stereotype manage stand stunning special effect location revolve shaun chinese immigrant living united states america work valet quirky friend soulmate katy day attack group assassin bus manage survive shaun immediately understand attack relate influential estranged father katy decide team tough estranged sister xiale find convince multiple level act performance quirky convince especially lady steal awkwafina deliver good curious dynamic funny woman like friend zhang menger represent dark shape dramatic event past difficult approach tough relentless independent personality expensive special effect certainly deliver good fantasy world ancient china contemporary san francisco equally stunning fantastic creature dragon look impressive big screen lack originality entertain start finish thank steady pace inspire execution truly care fate different occasional flaw lead actor simu liu simply charisma actress actor involve cast bold choice fully pay opinion desperately try connect appearance trevor slattery play ben kingsley completely random pretext offer misplace comic relief mid credit start amusing fashion suddenly involve bruce banner carol danver like weak attempt develop hype potential sequel credit evoke question conclude appropriately end day shang chi legend ring entertaining fantasy action appeal faithful occasional fan alike franchise focus quality quantity instead monstrous capitalistic machine scary gigantic dragon [SEP] ENTLBL_ORG ENTTXT_united_states_america ENTLBL_PERSON ENTTXT_katy_day_attack_group ENTLBL_PERSON ENTTXT_katy ENTLBL_PERSON ENTTXT_zhang_menger ENTLBL_PERSON ENTTXT_simu_liu ENTLBL_PERSON ENTTXT_ben_kingsley</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -13977,20 +10949,10 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Transformer (DistilBERT)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
-        <is>
-          <t>POSITIVE</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>Transformer (DistilBERT)</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
         <is>
           <t>POSITIVE</t>
         </is>
